--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -221,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="322">
   <si>
     <t>_id</t>
   </si>
@@ -295,9 +295,6 @@
     <t>朽木战刃</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>4,1004</t>
   </si>
   <si>
@@ -307,9 +304,6 @@
     <t>朽木战甲</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>2,1002</t>
   </si>
   <si>
@@ -319,15 +313,9 @@
     <t>朽木战链</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>朽木战盔</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>1,1001</t>
   </si>
   <si>
@@ -349,16 +337,10 @@
     <t>朽木战带</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>5,1</t>
   </si>
   <si>
     <t>朽木战靴</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
   <si>
     <t>朽木法刃</t>
@@ -2356,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>23</v>
@@ -2364,14 +2346,14 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -2403,22 +2385,22 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1" t="s">
+      <c r="J7" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -2450,22 +2432,22 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>32</v>
+      <c r="H8" s="1">
+        <v>3</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -2497,22 +2479,22 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>34</v>
+      <c r="H9" s="1">
+        <v>4</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -2544,22 +2526,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -2591,22 +2573,22 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -2638,22 +2620,22 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>42</v>
+      <c r="H12" s="1">
+        <v>9</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -2685,22 +2667,22 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>45</v>
+      <c r="H13" s="1">
+        <v>10</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -2732,22 +2714,22 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>24</v>
+      <c r="H14" s="1">
+        <v>1</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -2779,22 +2761,22 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -2826,22 +2808,22 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>32</v>
+      <c r="H16" s="1">
+        <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -2873,22 +2855,22 @@
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>34</v>
+      <c r="H17" s="1">
+        <v>4</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -2920,22 +2902,22 @@
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -2967,22 +2949,22 @@
         <v>1</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -3014,22 +2996,22 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>42</v>
+      <c r="H20" s="1">
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -3061,22 +3043,22 @@
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>45</v>
+      <c r="H21" s="1">
+        <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -3108,22 +3090,22 @@
         <v>1</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>24</v>
+      <c r="H22" s="1">
+        <v>1</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -3155,22 +3137,22 @@
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -3202,22 +3184,22 @@
         <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>32</v>
+      <c r="H24" s="1">
+        <v>3</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -3249,22 +3231,22 @@
         <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>34</v>
+      <c r="H25" s="1">
+        <v>4</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -3296,22 +3278,22 @@
         <v>1</v>
       </c>
       <c r="E26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -3343,22 +3325,22 @@
         <v>1</v>
       </c>
       <c r="E27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -3390,22 +3372,22 @@
         <v>1</v>
       </c>
       <c r="E28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>42</v>
+      <c r="H28" s="1">
+        <v>9</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -3437,22 +3419,22 @@
         <v>1</v>
       </c>
       <c r="E29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>45</v>
+      <c r="H29" s="1">
+        <v>10</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -3487,19 +3469,19 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="J31" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -3534,19 +3516,19 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="1">
+        <v>2</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -3581,19 +3563,19 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>32</v>
+      <c r="H33" s="1">
+        <v>3</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -3628,19 +3610,19 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>34</v>
+      <c r="H34" s="1">
+        <v>4</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -3675,19 +3657,19 @@
         <v>10</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -3722,19 +3704,19 @@
         <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -3769,19 +3751,19 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>42</v>
+      <c r="H37" s="1">
+        <v>9</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -3816,19 +3798,19 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>45</v>
+      <c r="H38" s="1">
+        <v>10</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -3863,19 +3845,19 @@
         <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>24</v>
+      <c r="H39" s="1">
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -3910,19 +3892,19 @@
         <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -3957,19 +3939,19 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>32</v>
+      <c r="H41" s="1">
+        <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -4004,19 +3986,19 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>34</v>
+      <c r="H42" s="1">
+        <v>4</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -4051,19 +4033,19 @@
         <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -4098,19 +4080,19 @@
         <v>10</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -4145,19 +4127,19 @@
         <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>42</v>
+      <c r="H45" s="1">
+        <v>9</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -4192,19 +4174,19 @@
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>45</v>
+      <c r="H46" s="1">
+        <v>10</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -4239,19 +4221,19 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>24</v>
+      <c r="H47" s="1">
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -4286,19 +4268,19 @@
         <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -4333,19 +4315,19 @@
         <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>32</v>
+      <c r="H49" s="1">
+        <v>3</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -4380,19 +4362,19 @@
         <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>34</v>
+      <c r="H50" s="1">
+        <v>4</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -4427,19 +4409,19 @@
         <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -4474,19 +4456,19 @@
         <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -4521,19 +4503,19 @@
         <v>10</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>42</v>
+      <c r="H53" s="1">
+        <v>9</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -4568,19 +4550,19 @@
         <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>45</v>
+      <c r="H54" s="1">
+        <v>10</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -4632,19 +4614,19 @@
         <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="J56" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -4679,19 +4661,19 @@
         <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -4726,19 +4708,19 @@
         <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>32</v>
+      <c r="H58" s="1">
+        <v>3</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -4773,19 +4755,19 @@
         <v>20</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>34</v>
+      <c r="H59" s="1">
+        <v>4</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -4820,19 +4802,19 @@
         <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -4867,19 +4849,19 @@
         <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -4914,19 +4896,19 @@
         <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>42</v>
+      <c r="H62" s="1">
+        <v>9</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -4961,19 +4943,19 @@
         <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>45</v>
+      <c r="H63" s="1">
+        <v>10</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -5008,19 +4990,19 @@
         <v>20</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>24</v>
+      <c r="H64" s="1">
+        <v>1</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -5055,19 +5037,19 @@
         <v>20</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -5102,19 +5084,19 @@
         <v>20</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>32</v>
+      <c r="H66" s="1">
+        <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -5149,19 +5131,19 @@
         <v>20</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>34</v>
+      <c r="H67" s="1">
+        <v>4</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -5196,19 +5178,19 @@
         <v>20</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -5243,19 +5225,19 @@
         <v>20</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -5290,19 +5272,19 @@
         <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>42</v>
+      <c r="H70" s="1">
+        <v>9</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -5337,19 +5319,19 @@
         <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>45</v>
+      <c r="H71" s="1">
+        <v>10</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -5384,19 +5366,19 @@
         <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>24</v>
+      <c r="H72" s="1">
+        <v>1</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -5431,19 +5413,19 @@
         <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="1">
+        <v>2</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -5478,19 +5460,19 @@
         <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>32</v>
+      <c r="H74" s="1">
+        <v>3</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -5525,19 +5507,19 @@
         <v>20</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
       </c>
-      <c r="H75" s="6" t="s">
-        <v>34</v>
+      <c r="H75" s="1">
+        <v>4</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -5572,19 +5554,19 @@
         <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -5619,19 +5601,19 @@
         <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -5666,19 +5648,19 @@
         <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>42</v>
+      <c r="H78" s="1">
+        <v>9</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -5713,19 +5695,19 @@
         <v>20</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>45</v>
+      <c r="H79" s="1">
+        <v>10</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -5777,19 +5759,19 @@
         <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="J81" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -5824,19 +5806,19 @@
         <v>30</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="1">
+        <v>2</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -5871,19 +5853,19 @@
         <v>30</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>32</v>
+      <c r="H83" s="1">
+        <v>3</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -5918,19 +5900,19 @@
         <v>30</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
       </c>
-      <c r="H84" s="6" t="s">
-        <v>34</v>
+      <c r="H84" s="1">
+        <v>4</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -5965,19 +5947,19 @@
         <v>30</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -6012,19 +5994,19 @@
         <v>30</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -6059,19 +6041,19 @@
         <v>30</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>42</v>
+      <c r="H87" s="1">
+        <v>9</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -6106,19 +6088,19 @@
         <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>45</v>
+      <c r="H88" s="1">
+        <v>10</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -6153,19 +6135,19 @@
         <v>30</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>24</v>
+      <c r="H89" s="1">
+        <v>1</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -6200,19 +6182,19 @@
         <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="1">
+        <v>2</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -6247,19 +6229,19 @@
         <v>30</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>32</v>
+      <c r="H91" s="1">
+        <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -6294,19 +6276,19 @@
         <v>30</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>34</v>
+      <c r="H92" s="1">
+        <v>4</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -6341,19 +6323,19 @@
         <v>30</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -6388,19 +6370,19 @@
         <v>30</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -6435,19 +6417,19 @@
         <v>30</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>42</v>
+      <c r="H95" s="1">
+        <v>9</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -6482,19 +6464,19 @@
         <v>30</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>45</v>
+      <c r="H96" s="1">
+        <v>10</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -6529,19 +6511,19 @@
         <v>30</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>24</v>
+      <c r="H97" s="1">
+        <v>1</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -6576,19 +6558,19 @@
         <v>30</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="1">
+        <v>2</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J98" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -6623,19 +6605,19 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>32</v>
+      <c r="H99" s="1">
+        <v>3</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -6670,19 +6652,19 @@
         <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
       </c>
-      <c r="H100" s="6" t="s">
-        <v>34</v>
+      <c r="H100" s="1">
+        <v>4</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -6717,19 +6699,19 @@
         <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -6764,19 +6746,19 @@
         <v>30</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -6811,19 +6793,19 @@
         <v>30</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>42</v>
+      <c r="H103" s="1">
+        <v>9</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -6858,19 +6840,19 @@
         <v>30</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>45</v>
+      <c r="H104" s="1">
+        <v>10</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -6915,7 +6897,7 @@
     <row r="107" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3 O4 O5 C3:H5 K3:N5 P3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -7100,19 +7082,19 @@
         <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -7147,19 +7129,19 @@
         <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -7194,19 +7176,19 @@
         <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>32</v>
+      <c r="H8" s="1">
+        <v>3</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -7241,19 +7223,19 @@
         <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>34</v>
+      <c r="H9" s="1">
+        <v>4</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -7288,19 +7270,19 @@
         <v>40</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -7335,19 +7317,19 @@
         <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -7382,19 +7364,19 @@
         <v>40</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>42</v>
+      <c r="H12" s="1">
+        <v>9</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -7429,19 +7411,19 @@
         <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>45</v>
+      <c r="H13" s="1">
+        <v>10</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -7476,19 +7458,19 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>24</v>
+      <c r="H14" s="1">
+        <v>1</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -7523,19 +7505,19 @@
         <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -7570,19 +7552,19 @@
         <v>40</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>32</v>
+      <c r="H16" s="1">
+        <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -7617,19 +7599,19 @@
         <v>40</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>34</v>
+      <c r="H17" s="1">
+        <v>4</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -7664,19 +7646,19 @@
         <v>40</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -7711,19 +7693,19 @@
         <v>40</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -7758,19 +7740,19 @@
         <v>40</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>42</v>
+      <c r="H20" s="1">
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -7805,19 +7787,19 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>45</v>
+      <c r="H21" s="1">
+        <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -7852,19 +7834,19 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>24</v>
+      <c r="H22" s="1">
+        <v>1</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -7899,19 +7881,19 @@
         <v>40</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -7946,19 +7928,19 @@
         <v>40</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>32</v>
+      <c r="H24" s="1">
+        <v>3</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -7993,19 +7975,19 @@
         <v>40</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>34</v>
+      <c r="H25" s="1">
+        <v>4</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -8040,19 +8022,19 @@
         <v>40</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -8087,19 +8069,19 @@
         <v>40</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -8134,19 +8116,19 @@
         <v>40</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>42</v>
+      <c r="H28" s="1">
+        <v>9</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -8181,19 +8163,19 @@
         <v>40</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>45</v>
+      <c r="H29" s="1">
+        <v>10</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -8228,19 +8210,19 @@
         <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="J31" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -8275,19 +8257,19 @@
         <v>50</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="1">
+        <v>2</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -8322,19 +8304,19 @@
         <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>32</v>
+      <c r="H33" s="1">
+        <v>3</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -8369,19 +8351,19 @@
         <v>50</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>34</v>
+      <c r="H34" s="1">
+        <v>4</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -8416,19 +8398,19 @@
         <v>50</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -8463,19 +8445,19 @@
         <v>50</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -8510,19 +8492,19 @@
         <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>42</v>
+      <c r="H37" s="1">
+        <v>9</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -8557,19 +8539,19 @@
         <v>50</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>45</v>
+      <c r="H38" s="1">
+        <v>10</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -8604,19 +8586,19 @@
         <v>50</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>24</v>
+      <c r="H39" s="1">
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -8651,19 +8633,19 @@
         <v>50</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -8698,19 +8680,19 @@
         <v>50</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>32</v>
+      <c r="H41" s="1">
+        <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -8745,19 +8727,19 @@
         <v>50</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>34</v>
+      <c r="H42" s="1">
+        <v>4</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -8792,19 +8774,19 @@
         <v>50</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -8839,19 +8821,19 @@
         <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -8886,19 +8868,19 @@
         <v>50</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>42</v>
+      <c r="H45" s="1">
+        <v>9</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -8933,19 +8915,19 @@
         <v>50</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>45</v>
+      <c r="H46" s="1">
+        <v>10</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -8980,19 +8962,19 @@
         <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>24</v>
+      <c r="H47" s="1">
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -9027,19 +9009,19 @@
         <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -9074,19 +9056,19 @@
         <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>32</v>
+      <c r="H49" s="1">
+        <v>3</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -9121,19 +9103,19 @@
         <v>50</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>34</v>
+      <c r="H50" s="1">
+        <v>4</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -9168,19 +9150,19 @@
         <v>50</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -9215,19 +9197,19 @@
         <v>50</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -9262,19 +9244,19 @@
         <v>50</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>42</v>
+      <c r="H53" s="1">
+        <v>9</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -9309,19 +9291,19 @@
         <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>45</v>
+      <c r="H54" s="1">
+        <v>10</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -9373,19 +9355,19 @@
         <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="J56" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -9421,19 +9403,19 @@
         <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -9469,19 +9451,19 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>32</v>
+      <c r="H58" s="1">
+        <v>3</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -9517,19 +9499,19 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>34</v>
+      <c r="H59" s="1">
+        <v>4</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -9565,19 +9547,19 @@
         <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -9613,19 +9595,19 @@
         <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -9661,19 +9643,19 @@
         <v>60</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>42</v>
+      <c r="H62" s="1">
+        <v>9</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -9709,19 +9691,19 @@
         <v>60</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>45</v>
+      <c r="H63" s="1">
+        <v>10</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -9757,19 +9739,19 @@
         <v>60</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>24</v>
+      <c r="H64" s="1">
+        <v>1</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -9805,19 +9787,19 @@
         <v>60</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -9853,19 +9835,19 @@
         <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>32</v>
+      <c r="H66" s="1">
+        <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -9901,19 +9883,19 @@
         <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>34</v>
+      <c r="H67" s="1">
+        <v>4</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -9949,19 +9931,19 @@
         <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -9997,19 +9979,19 @@
         <v>60</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -10045,19 +10027,19 @@
         <v>60</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>42</v>
+      <c r="H70" s="1">
+        <v>9</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -10093,19 +10075,19 @@
         <v>60</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>45</v>
+      <c r="H71" s="1">
+        <v>10</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -10141,19 +10123,19 @@
         <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>24</v>
+      <c r="H72" s="1">
+        <v>1</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -10189,19 +10171,19 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="1">
+        <v>2</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -10237,19 +10219,19 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>32</v>
+      <c r="H74" s="1">
+        <v>3</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -10285,19 +10267,19 @@
         <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
       </c>
-      <c r="H75" s="6" t="s">
-        <v>34</v>
+      <c r="H75" s="1">
+        <v>4</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -10333,19 +10315,19 @@
         <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -10381,19 +10363,19 @@
         <v>60</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -10429,19 +10411,19 @@
         <v>60</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>42</v>
+      <c r="H78" s="1">
+        <v>9</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -10477,19 +10459,19 @@
         <v>60</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>45</v>
+      <c r="H79" s="1">
+        <v>10</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -10542,19 +10524,19 @@
         <v>70</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="J81" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -10590,19 +10572,19 @@
         <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="1">
+        <v>2</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -10638,19 +10620,19 @@
         <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>32</v>
+      <c r="H83" s="1">
+        <v>3</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -10686,19 +10668,19 @@
         <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
       </c>
-      <c r="H84" s="6" t="s">
-        <v>34</v>
+      <c r="H84" s="1">
+        <v>4</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -10734,19 +10716,19 @@
         <v>70</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -10782,19 +10764,19 @@
         <v>70</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -10830,19 +10812,19 @@
         <v>70</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>42</v>
+      <c r="H87" s="1">
+        <v>9</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -10878,19 +10860,19 @@
         <v>70</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>45</v>
+      <c r="H88" s="1">
+        <v>10</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -10926,19 +10908,19 @@
         <v>70</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>24</v>
+      <c r="H89" s="1">
+        <v>1</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -10974,19 +10956,19 @@
         <v>70</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="1">
+        <v>2</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -11022,19 +11004,19 @@
         <v>70</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>32</v>
+      <c r="H91" s="1">
+        <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -11070,19 +11052,19 @@
         <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>34</v>
+      <c r="H92" s="1">
+        <v>4</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -11118,19 +11100,19 @@
         <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -11166,19 +11148,19 @@
         <v>70</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -11214,19 +11196,19 @@
         <v>70</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>42</v>
+      <c r="H95" s="1">
+        <v>9</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -11262,19 +11244,19 @@
         <v>70</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>45</v>
+      <c r="H96" s="1">
+        <v>10</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -11310,19 +11292,19 @@
         <v>70</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>24</v>
+      <c r="H97" s="1">
+        <v>1</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -11358,19 +11340,19 @@
         <v>70</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="1">
+        <v>2</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J98" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -11406,19 +11388,19 @@
         <v>70</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>32</v>
+      <c r="H99" s="1">
+        <v>3</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -11454,19 +11436,19 @@
         <v>70</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
       </c>
-      <c r="H100" s="6" t="s">
-        <v>34</v>
+      <c r="H100" s="1">
+        <v>4</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -11502,19 +11484,19 @@
         <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -11550,19 +11532,19 @@
         <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -11598,19 +11580,19 @@
         <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>42</v>
+      <c r="H103" s="1">
+        <v>9</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -11646,19 +11628,19 @@
         <v>70</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>45</v>
+      <c r="H104" s="1">
+        <v>10</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -11706,7 +11688,7 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
+      <c r="H106"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -11723,7 +11705,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
+      <c r="H107"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
@@ -11787,19 +11769,22 @@
     </row>
     <row r="114" customFormat="1" customHeight="1" spans="5:15">
       <c r="E114" s="1"/>
+      <c r="H114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="O114" s="1"/>
     </row>
     <row r="115" customFormat="1" customHeight="1" spans="5:15">
+      <c r="H115" s="1"/>
       <c r="O115" s="1"/>
     </row>
     <row r="116" customFormat="1" customHeight="1" spans="5:15">
+      <c r="H116" s="1"/>
       <c r="O116" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3 O4 O5 K3:N5 C3:H5 P3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:H5 K3:Q5 C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -11984,19 +11969,19 @@
         <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -12031,19 +12016,19 @@
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -12078,19 +12063,19 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>32</v>
+      <c r="H8" s="1">
+        <v>3</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -12125,19 +12110,19 @@
         <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>34</v>
+      <c r="H9" s="1">
+        <v>4</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -12172,19 +12157,19 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -12219,19 +12204,19 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -12266,19 +12251,19 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>42</v>
+      <c r="H12" s="1">
+        <v>9</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -12313,19 +12298,19 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>45</v>
+      <c r="H13" s="1">
+        <v>10</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -12360,19 +12345,19 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>24</v>
+      <c r="H14" s="1">
+        <v>1</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -12407,19 +12392,19 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -12454,19 +12439,19 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>32</v>
+      <c r="H16" s="1">
+        <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -12501,19 +12486,19 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>34</v>
+      <c r="H17" s="1">
+        <v>4</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -12548,19 +12533,19 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -12595,19 +12580,19 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -12642,19 +12627,19 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>42</v>
+      <c r="H20" s="1">
+        <v>9</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -12689,19 +12674,19 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>45</v>
+      <c r="H21" s="1">
+        <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -12736,19 +12721,19 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>24</v>
+      <c r="H22" s="1">
+        <v>1</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -12783,19 +12768,19 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -12830,19 +12815,19 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>32</v>
+      <c r="H24" s="1">
+        <v>3</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -12877,19 +12862,19 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>34</v>
+      <c r="H25" s="1">
+        <v>4</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -12924,19 +12909,19 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -12971,19 +12956,19 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -13018,19 +13003,19 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>42</v>
+      <c r="H28" s="1">
+        <v>9</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -13065,19 +13050,19 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>45</v>
+      <c r="H29" s="1">
+        <v>10</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -13112,19 +13097,19 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="J31" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -13159,19 +13144,19 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="1">
+        <v>2</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -13206,19 +13191,19 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>32</v>
+      <c r="H33" s="1">
+        <v>3</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -13253,19 +13238,19 @@
         <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>34</v>
+      <c r="H34" s="1">
+        <v>4</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -13300,19 +13285,19 @@
         <v>90</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -13347,19 +13332,19 @@
         <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -13394,19 +13379,19 @@
         <v>90</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>42</v>
+      <c r="H37" s="1">
+        <v>9</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -13441,19 +13426,19 @@
         <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>45</v>
+      <c r="H38" s="1">
+        <v>10</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -13488,19 +13473,19 @@
         <v>90</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>24</v>
+      <c r="H39" s="1">
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -13535,19 +13520,19 @@
         <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -13582,19 +13567,19 @@
         <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>32</v>
+      <c r="H41" s="1">
+        <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -13629,19 +13614,19 @@
         <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>34</v>
+      <c r="H42" s="1">
+        <v>4</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -13676,19 +13661,19 @@
         <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -13723,19 +13708,19 @@
         <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -13770,19 +13755,19 @@
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>42</v>
+      <c r="H45" s="1">
+        <v>9</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -13817,19 +13802,19 @@
         <v>90</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>45</v>
+      <c r="H46" s="1">
+        <v>10</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -13864,19 +13849,19 @@
         <v>90</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>24</v>
+      <c r="H47" s="1">
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -13911,19 +13896,19 @@
         <v>90</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -13958,19 +13943,19 @@
         <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>32</v>
+      <c r="H49" s="1">
+        <v>3</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -14005,19 +13990,19 @@
         <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>34</v>
+      <c r="H50" s="1">
+        <v>4</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -14052,19 +14037,19 @@
         <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -14099,19 +14084,19 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -14146,19 +14131,19 @@
         <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>42</v>
+      <c r="H53" s="1">
+        <v>9</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -14193,19 +14178,19 @@
         <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>45</v>
+      <c r="H54" s="1">
+        <v>10</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -14257,19 +14242,19 @@
         <v>100</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="J56" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -14305,19 +14290,19 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -14353,19 +14338,19 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>32</v>
+      <c r="H58" s="1">
+        <v>3</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -14401,19 +14386,19 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>34</v>
+      <c r="H59" s="1">
+        <v>4</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -14449,19 +14434,19 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -14497,19 +14482,19 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -14545,19 +14530,19 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>42</v>
+      <c r="H62" s="1">
+        <v>9</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -14593,19 +14578,19 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>45</v>
+      <c r="H63" s="1">
+        <v>10</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -14641,19 +14626,19 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>24</v>
+      <c r="H64" s="1">
+        <v>1</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -14689,19 +14674,19 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -14737,19 +14722,19 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>32</v>
+      <c r="H66" s="1">
+        <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -14785,19 +14770,19 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>34</v>
+      <c r="H67" s="1">
+        <v>4</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -14833,19 +14818,19 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -14881,19 +14866,19 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -14929,19 +14914,19 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>42</v>
+      <c r="H70" s="1">
+        <v>9</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -14977,19 +14962,19 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>45</v>
+      <c r="H71" s="1">
+        <v>10</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -15025,19 +15010,19 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>24</v>
+      <c r="H72" s="1">
+        <v>1</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -15073,19 +15058,19 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="1">
+        <v>2</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -15121,19 +15106,19 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>32</v>
+      <c r="H74" s="1">
+        <v>3</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -15169,19 +15154,19 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
       </c>
-      <c r="H75" s="6" t="s">
-        <v>34</v>
+      <c r="H75" s="1">
+        <v>4</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -15217,19 +15202,19 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -15265,19 +15250,19 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -15313,19 +15298,19 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>42</v>
+      <c r="H78" s="1">
+        <v>9</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -15361,19 +15346,19 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>45</v>
+      <c r="H79" s="1">
+        <v>10</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -15426,19 +15411,19 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="J81" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -15474,19 +15459,19 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="1">
+        <v>2</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -15522,19 +15507,19 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>32</v>
+      <c r="H83" s="1">
+        <v>3</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -15570,19 +15555,19 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
       </c>
-      <c r="H84" s="6" t="s">
-        <v>34</v>
+      <c r="H84" s="1">
+        <v>4</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -15618,19 +15603,19 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -15666,19 +15651,19 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -15714,19 +15699,19 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>42</v>
+      <c r="H87" s="1">
+        <v>9</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -15762,19 +15747,19 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>45</v>
+      <c r="H88" s="1">
+        <v>10</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -15810,19 +15795,19 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>24</v>
+      <c r="H89" s="1">
+        <v>1</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -15858,19 +15843,19 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="1">
+        <v>2</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -15906,19 +15891,19 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>32</v>
+      <c r="H91" s="1">
+        <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -15954,19 +15939,19 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>34</v>
+      <c r="H92" s="1">
+        <v>4</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -16002,19 +15987,19 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -16050,19 +16035,19 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -16098,19 +16083,19 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>42</v>
+      <c r="H95" s="1">
+        <v>9</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -16146,19 +16131,19 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>45</v>
+      <c r="H96" s="1">
+        <v>10</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -16194,19 +16179,19 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>24</v>
+      <c r="H97" s="1">
+        <v>1</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -16242,19 +16227,19 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="1">
+        <v>2</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J98" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -16290,19 +16275,19 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>32</v>
+      <c r="H99" s="1">
+        <v>3</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -16338,19 +16323,19 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
       </c>
-      <c r="H100" s="6" t="s">
-        <v>34</v>
+      <c r="H100" s="1">
+        <v>4</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -16386,19 +16371,19 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -16434,19 +16419,19 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -16482,19 +16467,19 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>42</v>
+      <c r="H103" s="1">
+        <v>9</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -16530,19 +16515,19 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>45</v>
+      <c r="H104" s="1">
+        <v>10</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -16590,7 +16575,7 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
+      <c r="H106"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -16607,7 +16592,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
+      <c r="H107"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
@@ -16671,19 +16656,22 @@
     </row>
     <row r="114" customFormat="1" customHeight="1" spans="5:15">
       <c r="E114" s="1"/>
+      <c r="H114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="O114" s="1"/>
     </row>
     <row r="115" customFormat="1" customHeight="1" spans="5:15">
+      <c r="H115" s="1"/>
       <c r="O115" s="1"/>
     </row>
     <row r="116" customFormat="1" customHeight="1" spans="5:15">
+      <c r="H116" s="1"/>
       <c r="O116" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3 O4 O5 C3:H5 K3:N5 P3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:H5 K3:Q5 C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
     <sheet name="50-80" sheetId="8" r:id="rId2"/>
     <sheet name="90-120" sheetId="9" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -220,8 +221,72 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 武器
+2 衣服
+3 头盔
+4 项链
+5 左手镯
+6 右手镯
+7 左戒指
+8 右戒指
+9 腰带
+10 鞋子
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+属性ID列表</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="325">
   <si>
     <t>_id</t>
   </si>
@@ -1187,6 +1252,15 @@
   </si>
   <si>
     <t>暗龙道靴</t>
+  </si>
+  <si>
+    <t>新手武器</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>30,30,30</t>
   </si>
 </sst>
 </file>
@@ -11784,7 +11858,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:H5 K3:Q5 C3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -16671,7 +16745,218 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:H5 K3:Q5 C3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="A3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="A4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="A5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C6" s="1">
+        <v>200001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
     <sheet name="50-80" sheetId="8" r:id="rId2"/>
     <sheet name="90-120" sheetId="9" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId4"/>
+    <sheet name="定制" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="328">
   <si>
     <t>_id</t>
   </si>
@@ -1261,6 +1261,15 @@
   </si>
   <si>
     <t>30,30,30</t>
+  </si>
+  <si>
+    <t>新手衣服</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1000,10</t>
   </si>
 </sst>
 </file>
@@ -16758,8 +16767,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="5"/>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6"/>
+  <cols>
+    <col min="5" max="5" width="14.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -16951,6 +16964,53 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="C7" s="1">
+        <v>200002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -11990,7 +11990,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 C3:H5 K3:M5 O3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="356">
   <si>
     <t>_id</t>
   </si>
@@ -378,15 +378,15 @@
     <t>2,1002</t>
   </si>
   <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>朽木战链</t>
+  </si>
+  <si>
     <t>10,2</t>
   </si>
   <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>朽木战链</t>
-  </si>
-  <si>
     <t>10,5</t>
   </si>
   <si>
@@ -396,213 +396,225 @@
     <t>1,1001</t>
   </si>
   <si>
+    <t>1000,10</t>
+  </si>
+  <si>
+    <t>4,1</t>
+  </si>
+  <si>
+    <t>10,200</t>
+  </si>
+  <si>
+    <t>朽木战镯</t>
+  </si>
+  <si>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>10,1</t>
+  </si>
+  <si>
+    <t>朽木战戒</t>
+  </si>
+  <si>
+    <t>7,8</t>
+  </si>
+  <si>
+    <t>朽木战带</t>
+  </si>
+  <si>
+    <t>朽木战靴</t>
+  </si>
+  <si>
+    <t>朽木法刃</t>
+  </si>
+  <si>
+    <t>5,1005</t>
+  </si>
+  <si>
+    <t>5,3</t>
+  </si>
+  <si>
+    <t>朽木法甲</t>
+  </si>
+  <si>
+    <t>5,2</t>
+  </si>
+  <si>
+    <t>朽木法链</t>
+  </si>
+  <si>
+    <t>朽木法盔</t>
+  </si>
+  <si>
+    <t>5,1</t>
+  </si>
+  <si>
+    <t>朽木法镯</t>
+  </si>
+  <si>
+    <t>朽木法戒</t>
+  </si>
+  <si>
+    <t>朽木法带</t>
+  </si>
+  <si>
+    <t>朽木法靴</t>
+  </si>
+  <si>
+    <t>朽木道刃</t>
+  </si>
+  <si>
+    <t>6,1006</t>
+  </si>
+  <si>
+    <t>6,3</t>
+  </si>
+  <si>
+    <t>朽木道甲</t>
+  </si>
+  <si>
+    <t>6,2</t>
+  </si>
+  <si>
+    <t>朽木道链</t>
+  </si>
+  <si>
+    <t>朽木道盔</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>朽木道镯</t>
+  </si>
+  <si>
+    <t>朽木道戒</t>
+  </si>
+  <si>
+    <t>朽木道带</t>
+  </si>
+  <si>
+    <t>朽木道靴</t>
+  </si>
+  <si>
+    <t>黑铁战刃</t>
+  </si>
+  <si>
+    <t>100,25</t>
+  </si>
+  <si>
+    <t>40,20</t>
+  </si>
+  <si>
+    <t>黑铁战甲</t>
+  </si>
+  <si>
+    <t>黑铁战链</t>
+  </si>
+  <si>
+    <t>50,10</t>
+  </si>
+  <si>
+    <t>20,20</t>
+  </si>
+  <si>
+    <t>黑铁战盔</t>
+  </si>
+  <si>
+    <t>5000,50</t>
+  </si>
+  <si>
+    <t>20,400</t>
+  </si>
+  <si>
+    <t>黑铁战镯</t>
+  </si>
+  <si>
+    <t>20,2</t>
+  </si>
+  <si>
+    <t>黑铁战戒</t>
+  </si>
+  <si>
+    <t>黑铁战带</t>
+  </si>
+  <si>
+    <t>黑铁战靴</t>
+  </si>
+  <si>
+    <t>黑铁法刃</t>
+  </si>
+  <si>
+    <t>黑铁法甲</t>
+  </si>
+  <si>
+    <t>黑铁法链</t>
+  </si>
+  <si>
+    <t>黑铁法盔</t>
+  </si>
+  <si>
+    <t>黑铁法镯</t>
+  </si>
+  <si>
+    <t>黑铁法戒</t>
+  </si>
+  <si>
+    <t>黑铁法带</t>
+  </si>
+  <si>
+    <t>黑铁法靴</t>
+  </si>
+  <si>
+    <t>黑铁道刃</t>
+  </si>
+  <si>
+    <t>黑铁道甲</t>
+  </si>
+  <si>
+    <t>黑铁道链</t>
+  </si>
+  <si>
+    <t>黑铁道盔</t>
+  </si>
+  <si>
+    <t>黑铁道镯</t>
+  </si>
+  <si>
+    <t>黑铁道戒</t>
+  </si>
+  <si>
+    <t>黑铁道带</t>
+  </si>
+  <si>
+    <t>黑铁道靴</t>
+  </si>
+  <si>
+    <t>白银战刃</t>
+  </si>
+  <si>
+    <t>60,30</t>
+  </si>
+  <si>
+    <t>白银战甲</t>
+  </si>
+  <si>
+    <t>60,35</t>
+  </si>
+  <si>
+    <t>白银战链</t>
+  </si>
+  <si>
+    <t>30,35</t>
+  </si>
+  <si>
+    <t>白银战盔</t>
+  </si>
+  <si>
     <t>100,10</t>
   </si>
   <si>
-    <t>4,1</t>
-  </si>
-  <si>
-    <t>10,200</t>
-  </si>
-  <si>
-    <t>朽木战镯</t>
-  </si>
-  <si>
-    <t>5,6</t>
-  </si>
-  <si>
-    <t>10,1</t>
-  </si>
-  <si>
-    <t>朽木战戒</t>
-  </si>
-  <si>
-    <t>7,8</t>
-  </si>
-  <si>
-    <t>朽木战带</t>
-  </si>
-  <si>
-    <t>5,1</t>
-  </si>
-  <si>
-    <t>朽木战靴</t>
-  </si>
-  <si>
-    <t>朽木法刃</t>
-  </si>
-  <si>
-    <t>5,1005</t>
-  </si>
-  <si>
-    <t>5,3</t>
-  </si>
-  <si>
-    <t>朽木法甲</t>
-  </si>
-  <si>
-    <t>5,2</t>
-  </si>
-  <si>
-    <t>朽木法链</t>
-  </si>
-  <si>
-    <t>朽木法盔</t>
-  </si>
-  <si>
-    <t>朽木法镯</t>
-  </si>
-  <si>
-    <t>朽木法戒</t>
-  </si>
-  <si>
-    <t>朽木法带</t>
-  </si>
-  <si>
-    <t>朽木法靴</t>
-  </si>
-  <si>
-    <t>朽木道刃</t>
-  </si>
-  <si>
-    <t>6,1006</t>
-  </si>
-  <si>
-    <t>6,3</t>
-  </si>
-  <si>
-    <t>朽木道甲</t>
-  </si>
-  <si>
-    <t>6,2</t>
-  </si>
-  <si>
-    <t>朽木道链</t>
-  </si>
-  <si>
-    <t>朽木道盔</t>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>朽木道镯</t>
-  </si>
-  <si>
-    <t>朽木道戒</t>
-  </si>
-  <si>
-    <t>朽木道带</t>
-  </si>
-  <si>
-    <t>朽木道靴</t>
-  </si>
-  <si>
-    <t>黑铁战刃</t>
-  </si>
-  <si>
-    <t>40,20</t>
-  </si>
-  <si>
-    <t>黑铁战甲</t>
-  </si>
-  <si>
-    <t>黑铁战链</t>
-  </si>
-  <si>
-    <t>20,20</t>
-  </si>
-  <si>
-    <t>黑铁战盔</t>
-  </si>
-  <si>
-    <t>20,400</t>
-  </si>
-  <si>
-    <t>黑铁战镯</t>
-  </si>
-  <si>
-    <t>20,2</t>
-  </si>
-  <si>
-    <t>黑铁战戒</t>
-  </si>
-  <si>
-    <t>黑铁战带</t>
-  </si>
-  <si>
-    <t>黑铁战靴</t>
-  </si>
-  <si>
-    <t>黑铁法刃</t>
-  </si>
-  <si>
-    <t>黑铁法甲</t>
-  </si>
-  <si>
-    <t>黑铁法链</t>
-  </si>
-  <si>
-    <t>黑铁法盔</t>
-  </si>
-  <si>
-    <t>黑铁法镯</t>
-  </si>
-  <si>
-    <t>黑铁法戒</t>
-  </si>
-  <si>
-    <t>黑铁法带</t>
-  </si>
-  <si>
-    <t>黑铁法靴</t>
-  </si>
-  <si>
-    <t>黑铁道刃</t>
-  </si>
-  <si>
-    <t>黑铁道甲</t>
-  </si>
-  <si>
-    <t>黑铁道链</t>
-  </si>
-  <si>
-    <t>黑铁道盔</t>
-  </si>
-  <si>
-    <t>黑铁道镯</t>
-  </si>
-  <si>
-    <t>黑铁道戒</t>
-  </si>
-  <si>
-    <t>黑铁道带</t>
-  </si>
-  <si>
-    <t>黑铁道靴</t>
-  </si>
-  <si>
-    <t>白银战刃</t>
-  </si>
-  <si>
-    <t>60,30</t>
-  </si>
-  <si>
-    <t>白银战甲</t>
-  </si>
-  <si>
-    <t>60,35</t>
-  </si>
-  <si>
-    <t>白银战链</t>
-  </si>
-  <si>
-    <t>30,35</t>
-  </si>
-  <si>
-    <t>白银战盔</t>
-  </si>
-  <si>
     <t>30,600</t>
   </si>
   <si>
@@ -1342,9 +1354,6 @@
   </si>
   <si>
     <t>1,2</t>
-  </si>
-  <si>
-    <t>1000,10</t>
   </si>
 </sst>
 </file>
@@ -1523,12 +1532,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2514,7 +2523,7 @@
         <v>25</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L6" s="1">
         <v>1</v>
@@ -2558,25 +2567,25 @@
         <v>29</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="1">
+        <v>300</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5</v>
+      </c>
+      <c r="P7" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
-        <v>5</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>25</v>
@@ -2593,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -2605,7 +2614,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -2717,7 +2726,7 @@
         <v>5</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>41</v>
@@ -2746,7 +2755,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -2793,7 +2802,7 @@
         <v>29</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -2828,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -2840,7 +2849,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -2875,22 +2884,22 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L14" s="1">
         <v>2</v>
@@ -2905,7 +2914,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>27</v>
@@ -2922,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -2934,10 +2943,10 @@
         <v>29</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
@@ -2952,7 +2961,7 @@
         <v>5</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>25</v>
@@ -2969,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -2978,28 +2987,28 @@
         <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>2</v>
+      </c>
+      <c r="O16" s="1">
+        <v>5</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-      <c r="L16" s="1">
-        <v>2</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>2</v>
-      </c>
-      <c r="O16" s="1">
-        <v>5</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>33</v>
@@ -3016,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -3046,7 +3055,7 @@
         <v>5</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>38</v>
@@ -3093,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>41</v>
@@ -3119,28 +3128,28 @@
         <v>43</v>
       </c>
       <c r="I19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2</v>
+      </c>
+      <c r="O19" s="1">
+        <v>5</v>
+      </c>
+      <c r="P19" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1">
-        <v>2</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>2</v>
-      </c>
-      <c r="O19" s="1">
-        <v>5</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>33</v>
@@ -3169,7 +3178,7 @@
         <v>29</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -3187,7 +3196,7 @@
         <v>5</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>38</v>
@@ -3213,10 +3222,10 @@
         <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -3234,7 +3243,7 @@
         <v>5</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>38</v>
@@ -3266,7 +3275,7 @@
         <v>25</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L22" s="1">
         <v>3</v>
@@ -3310,10 +3319,10 @@
         <v>29</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L23" s="1">
         <v>3</v>
@@ -3357,7 +3366,7 @@
         <v>59</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -3498,7 +3507,7 @@
         <v>59</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -3545,7 +3554,7 @@
         <v>29</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -3592,7 +3601,7 @@
         <v>59</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -3639,10 +3648,10 @@
         <v>24</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L31" s="1">
         <v>1</v>
@@ -3660,7 +3669,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3674,7 +3683,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -3686,10 +3695,10 @@
         <v>29</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L32" s="1">
         <v>1</v>
@@ -3704,10 +3713,10 @@
         <v>5</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3721,7 +3730,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -3733,10 +3742,10 @@
         <v>24</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L33" s="1">
         <v>1</v>
@@ -3754,7 +3763,7 @@
         <v>26</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3768,7 +3777,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -3780,10 +3789,10 @@
         <v>35</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L34" s="1">
         <v>1</v>
@@ -3801,7 +3810,7 @@
         <v>37</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3815,7 +3824,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -3827,10 +3836,10 @@
         <v>35</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L35" s="1">
         <v>1</v>
@@ -3845,10 +3854,10 @@
         <v>5</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3862,7 +3871,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -3874,10 +3883,10 @@
         <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L36" s="1">
         <v>1</v>
@@ -3895,7 +3904,7 @@
         <v>26</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:17">
@@ -3909,7 +3918,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -3921,10 +3930,10 @@
         <v>29</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L37" s="1">
         <v>1</v>
@@ -3942,7 +3951,7 @@
         <v>37</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -3956,7 +3965,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -3968,10 +3977,10 @@
         <v>24</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L38" s="1">
         <v>1</v>
@@ -3989,7 +3998,7 @@
         <v>37</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -4003,7 +4012,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -4012,31 +4021,31 @@
         <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K39" s="1">
+        <v>600</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>5</v>
+      </c>
+      <c r="O39" s="1">
+        <v>5</v>
+      </c>
+      <c r="P39" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="1">
-        <v>100</v>
-      </c>
-      <c r="L39" s="1">
-        <v>2</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>5</v>
-      </c>
-      <c r="O39" s="1">
-        <v>5</v>
-      </c>
-      <c r="P39" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="Q39" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -4050,7 +4059,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -4062,10 +4071,10 @@
         <v>29</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L40" s="1">
         <v>2</v>
@@ -4080,10 +4089,10 @@
         <v>5</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -4097,7 +4106,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -4106,31 +4115,31 @@
         <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K41" s="1">
+        <v>200</v>
+      </c>
+      <c r="L41" s="1">
+        <v>2</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>5</v>
+      </c>
+      <c r="O41" s="1">
+        <v>5</v>
+      </c>
+      <c r="P41" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J41" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>2</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1">
-        <v>5</v>
-      </c>
-      <c r="O41" s="1">
-        <v>5</v>
-      </c>
-      <c r="P41" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="Q41" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -4144,7 +4153,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -4156,10 +4165,10 @@
         <v>35</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L42" s="1">
         <v>2</v>
@@ -4174,10 +4183,10 @@
         <v>5</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -4191,7 +4200,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -4203,10 +4212,10 @@
         <v>35</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L43" s="1">
         <v>2</v>
@@ -4221,10 +4230,10 @@
         <v>5</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -4238,7 +4247,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -4247,31 +4256,31 @@
         <v>43</v>
       </c>
       <c r="I44" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" s="1">
+        <v>200</v>
+      </c>
+      <c r="L44" s="1">
+        <v>2</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>5</v>
+      </c>
+      <c r="O44" s="1">
+        <v>5</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <v>2</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>5</v>
-      </c>
-      <c r="O44" s="1">
-        <v>5</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="Q44" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -4285,7 +4294,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -4297,10 +4306,10 @@
         <v>29</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L45" s="1">
         <v>2</v>
@@ -4315,10 +4324,10 @@
         <v>5</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -4332,7 +4341,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -4341,13 +4350,13 @@
         <v>10</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L46" s="1">
         <v>2</v>
@@ -4362,10 +4371,10 @@
         <v>5</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -4379,7 +4388,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -4391,10 +4400,10 @@
         <v>59</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L47" s="1">
         <v>3</v>
@@ -4412,7 +4421,7 @@
         <v>60</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -4426,7 +4435,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -4438,10 +4447,10 @@
         <v>29</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L48" s="1">
         <v>3</v>
@@ -4459,7 +4468,7 @@
         <v>62</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -4473,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -4485,10 +4494,10 @@
         <v>59</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L49" s="1">
         <v>3</v>
@@ -4506,7 +4515,7 @@
         <v>60</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -4520,7 +4529,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -4532,10 +4541,10 @@
         <v>35</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L50" s="1">
         <v>3</v>
@@ -4553,7 +4562,7 @@
         <v>65</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -4567,7 +4576,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -4579,10 +4588,10 @@
         <v>35</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L51" s="1">
         <v>3</v>
@@ -4600,7 +4609,7 @@
         <v>62</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -4614,7 +4623,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -4626,10 +4635,10 @@
         <v>59</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L52" s="1">
         <v>3</v>
@@ -4647,7 +4656,7 @@
         <v>60</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -4661,7 +4670,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -4673,10 +4682,10 @@
         <v>29</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L53" s="1">
         <v>3</v>
@@ -4694,7 +4703,7 @@
         <v>65</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -4708,7 +4717,7 @@
         <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -4720,10 +4729,10 @@
         <v>59</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L54" s="1">
         <v>3</v>
@@ -4741,7 +4750,7 @@
         <v>65</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -4772,7 +4781,7 @@
         <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -4787,7 +4796,7 @@
         <v>25</v>
       </c>
       <c r="K56" s="1">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L56" s="1">
         <v>1</v>
@@ -4805,7 +4814,7 @@
         <v>26</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -4819,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -4831,10 +4840,10 @@
         <v>29</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
@@ -4849,10 +4858,10 @@
         <v>5</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -4866,7 +4875,7 @@
         <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -4878,10 +4887,10 @@
         <v>24</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L58" s="1">
         <v>1</v>
@@ -4899,7 +4908,7 @@
         <v>26</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -4913,7 +4922,7 @@
         <v>20</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -4925,10 +4934,10 @@
         <v>35</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L59" s="1">
         <v>1</v>
@@ -4946,7 +4955,7 @@
         <v>37</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -4960,7 +4969,7 @@
         <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -4972,10 +4981,10 @@
         <v>35</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L60" s="1">
         <v>1</v>
@@ -4990,10 +4999,10 @@
         <v>5</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -5007,7 +5016,7 @@
         <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -5019,10 +5028,10 @@
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L61" s="1">
         <v>1</v>
@@ -5040,7 +5049,7 @@
         <v>26</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -5054,7 +5063,7 @@
         <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -5066,10 +5075,10 @@
         <v>29</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L62" s="1">
         <v>1</v>
@@ -5087,7 +5096,7 @@
         <v>37</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -5101,7 +5110,7 @@
         <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -5113,10 +5122,10 @@
         <v>24</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L63" s="1">
         <v>1</v>
@@ -5134,7 +5143,7 @@
         <v>37</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -5148,7 +5157,7 @@
         <v>20</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -5157,13 +5166,13 @@
         <v>1</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K64" s="1">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L64" s="1">
         <v>2</v>
@@ -5178,10 +5187,10 @@
         <v>5</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -5195,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -5207,10 +5216,10 @@
         <v>29</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K65" s="1">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L65" s="1">
         <v>2</v>
@@ -5225,10 +5234,10 @@
         <v>5</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -5242,7 +5251,7 @@
         <v>20</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -5251,13 +5260,13 @@
         <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K66" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L66" s="1">
         <v>2</v>
@@ -5272,10 +5281,10 @@
         <v>5</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -5289,7 +5298,7 @@
         <v>20</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -5301,10 +5310,10 @@
         <v>35</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L67" s="1">
         <v>2</v>
@@ -5319,10 +5328,10 @@
         <v>5</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -5336,7 +5345,7 @@
         <v>20</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -5348,10 +5357,10 @@
         <v>35</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L68" s="1">
         <v>2</v>
@@ -5366,10 +5375,10 @@
         <v>5</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -5383,7 +5392,7 @@
         <v>20</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -5392,13 +5401,13 @@
         <v>43</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L69" s="1">
         <v>2</v>
@@ -5413,10 +5422,10 @@
         <v>5</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -5430,7 +5439,7 @@
         <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -5442,10 +5451,10 @@
         <v>29</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L70" s="1">
         <v>2</v>
@@ -5460,10 +5469,10 @@
         <v>5</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -5477,7 +5486,7 @@
         <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -5486,13 +5495,13 @@
         <v>10</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L71" s="1">
         <v>2</v>
@@ -5507,10 +5516,10 @@
         <v>5</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -5524,7 +5533,7 @@
         <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -5539,7 +5548,7 @@
         <v>25</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L72" s="1">
         <v>3</v>
@@ -5557,7 +5566,7 @@
         <v>60</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -5571,7 +5580,7 @@
         <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -5583,10 +5592,10 @@
         <v>29</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="L73" s="1">
         <v>3</v>
@@ -5604,7 +5613,7 @@
         <v>62</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -5618,7 +5627,7 @@
         <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -5630,10 +5639,10 @@
         <v>59</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L74" s="1">
         <v>3</v>
@@ -5651,7 +5660,7 @@
         <v>60</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -5665,7 +5674,7 @@
         <v>20</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -5677,10 +5686,10 @@
         <v>35</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L75" s="1">
         <v>3</v>
@@ -5698,7 +5707,7 @@
         <v>65</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -5712,7 +5721,7 @@
         <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -5724,10 +5733,10 @@
         <v>35</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L76" s="1">
         <v>3</v>
@@ -5745,7 +5754,7 @@
         <v>62</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -5759,7 +5768,7 @@
         <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -5771,10 +5780,10 @@
         <v>59</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L77" s="1">
         <v>3</v>
@@ -5792,7 +5801,7 @@
         <v>60</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -5806,7 +5815,7 @@
         <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -5818,10 +5827,10 @@
         <v>29</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L78" s="1">
         <v>3</v>
@@ -5839,7 +5848,7 @@
         <v>65</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -5853,7 +5862,7 @@
         <v>20</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -5865,10 +5874,10 @@
         <v>59</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L79" s="1">
         <v>3</v>
@@ -5886,7 +5895,7 @@
         <v>65</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -5917,7 +5926,7 @@
         <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -5950,7 +5959,7 @@
         <v>26</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -5964,7 +5973,7 @@
         <v>30</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -5976,7 +5985,7 @@
         <v>29</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -5994,10 +6003,10 @@
         <v>5</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -6011,7 +6020,7 @@
         <v>30</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -6023,7 +6032,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -6044,7 +6053,7 @@
         <v>26</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -6058,7 +6067,7 @@
         <v>30</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -6070,7 +6079,7 @@
         <v>35</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -6091,7 +6100,7 @@
         <v>37</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -6105,7 +6114,7 @@
         <v>30</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -6117,7 +6126,7 @@
         <v>35</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -6135,10 +6144,10 @@
         <v>5</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -6152,7 +6161,7 @@
         <v>30</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -6164,7 +6173,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -6185,7 +6194,7 @@
         <v>26</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -6199,7 +6208,7 @@
         <v>30</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -6211,7 +6220,7 @@
         <v>29</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -6232,7 +6241,7 @@
         <v>37</v>
       </c>
       <c r="Q87" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -6246,7 +6255,7 @@
         <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -6258,7 +6267,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -6279,7 +6288,7 @@
         <v>37</v>
       </c>
       <c r="Q88" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -6293,7 +6302,7 @@
         <v>30</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -6302,7 +6311,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>25</v>
@@ -6323,10 +6332,10 @@
         <v>5</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q89" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -6340,7 +6349,7 @@
         <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -6352,7 +6361,7 @@
         <v>29</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -6370,10 +6379,10 @@
         <v>5</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q90" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -6387,7 +6396,7 @@
         <v>30</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -6396,10 +6405,10 @@
         <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -6417,10 +6426,10 @@
         <v>5</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q91" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -6434,7 +6443,7 @@
         <v>30</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -6446,7 +6455,7 @@
         <v>35</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -6464,10 +6473,10 @@
         <v>5</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q92" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -6481,7 +6490,7 @@
         <v>30</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -6493,7 +6502,7 @@
         <v>35</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -6511,10 +6520,10 @@
         <v>5</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q93" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -6528,7 +6537,7 @@
         <v>30</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -6537,10 +6546,10 @@
         <v>43</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -6558,10 +6567,10 @@
         <v>5</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q94" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -6575,7 +6584,7 @@
         <v>30</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -6587,7 +6596,7 @@
         <v>29</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -6605,10 +6614,10 @@
         <v>5</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -6622,7 +6631,7 @@
         <v>30</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -6631,10 +6640,10 @@
         <v>10</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -6652,10 +6661,10 @@
         <v>5</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -6669,7 +6678,7 @@
         <v>30</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -6702,7 +6711,7 @@
         <v>60</v>
       </c>
       <c r="Q97" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -6716,7 +6725,7 @@
         <v>30</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -6728,7 +6737,7 @@
         <v>29</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -6749,7 +6758,7 @@
         <v>62</v>
       </c>
       <c r="Q98" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -6763,7 +6772,7 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -6775,7 +6784,7 @@
         <v>59</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -6796,7 +6805,7 @@
         <v>60</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -6810,7 +6819,7 @@
         <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -6822,7 +6831,7 @@
         <v>35</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -6843,7 +6852,7 @@
         <v>65</v>
       </c>
       <c r="Q100" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -6857,7 +6866,7 @@
         <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -6869,7 +6878,7 @@
         <v>35</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -6890,7 +6899,7 @@
         <v>62</v>
       </c>
       <c r="Q101" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -6904,7 +6913,7 @@
         <v>30</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -6916,7 +6925,7 @@
         <v>59</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -6937,7 +6946,7 @@
         <v>60</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -6951,7 +6960,7 @@
         <v>30</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -6963,7 +6972,7 @@
         <v>29</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -6984,7 +6993,7 @@
         <v>65</v>
       </c>
       <c r="Q103" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -6998,7 +7007,7 @@
         <v>30</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -7010,7 +7019,7 @@
         <v>59</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -7031,7 +7040,7 @@
         <v>65</v>
       </c>
       <c r="Q104" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -7240,7 +7249,7 @@
         <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -7288,7 +7297,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -7300,7 +7309,7 @@
         <v>29</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -7319,7 +7328,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>25</v>
@@ -7336,7 +7345,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -7348,7 +7357,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -7384,7 +7393,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -7396,7 +7405,7 @@
         <v>35</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -7432,7 +7441,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -7444,7 +7453,7 @@
         <v>35</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -7463,7 +7472,7 @@
         <v>5</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>41</v>
@@ -7480,7 +7489,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -7492,7 +7501,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -7528,7 +7537,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -7540,7 +7549,7 @@
         <v>29</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -7576,7 +7585,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -7588,7 +7597,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -7624,7 +7633,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -7633,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
@@ -7655,7 +7664,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>27</v>
@@ -7672,7 +7681,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -7684,7 +7693,7 @@
         <v>29</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -7703,7 +7712,7 @@
         <v>5</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>25</v>
@@ -7720,7 +7729,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -7729,10 +7738,10 @@
         <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -7751,7 +7760,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>33</v>
@@ -7768,7 +7777,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -7780,7 +7789,7 @@
         <v>35</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -7799,7 +7808,7 @@
         <v>5</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>38</v>
@@ -7816,7 +7825,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -7828,7 +7837,7 @@
         <v>35</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -7847,7 +7856,7 @@
         <v>5</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>41</v>
@@ -7864,7 +7873,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -7873,10 +7882,10 @@
         <v>43</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -7895,7 +7904,7 @@
         <v>5</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>33</v>
@@ -7912,7 +7921,7 @@
         <v>40</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -7924,7 +7933,7 @@
         <v>29</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -7943,7 +7952,7 @@
         <v>5</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>38</v>
@@ -7960,7 +7969,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -7969,10 +7978,10 @@
         <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -7991,7 +8000,7 @@
         <v>5</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>38</v>
@@ -8008,7 +8017,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -8056,7 +8065,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -8068,7 +8077,7 @@
         <v>29</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -8104,7 +8113,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -8116,7 +8125,7 @@
         <v>59</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -8152,7 +8161,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -8164,7 +8173,7 @@
         <v>35</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -8200,7 +8209,7 @@
         <v>40</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -8212,7 +8221,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -8248,7 +8257,7 @@
         <v>40</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -8260,7 +8269,7 @@
         <v>59</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -8296,7 +8305,7 @@
         <v>40</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -8308,7 +8317,7 @@
         <v>29</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -8344,7 +8353,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -8356,7 +8365,7 @@
         <v>59</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -8392,7 +8401,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -8426,7 +8435,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8440,7 +8449,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -8452,7 +8461,7 @@
         <v>29</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -8471,10 +8480,10 @@
         <v>5</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8488,7 +8497,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -8500,7 +8509,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -8522,7 +8531,7 @@
         <v>26</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8536,7 +8545,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -8548,7 +8557,7 @@
         <v>35</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -8570,7 +8579,7 @@
         <v>37</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8584,7 +8593,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -8596,7 +8605,7 @@
         <v>35</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -8615,10 +8624,10 @@
         <v>5</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8632,7 +8641,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -8644,7 +8653,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -8666,7 +8675,7 @@
         <v>26</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8680,7 +8689,7 @@
         <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -8692,7 +8701,7 @@
         <v>29</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -8714,7 +8723,7 @@
         <v>37</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -8728,7 +8737,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -8740,7 +8749,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -8762,7 +8771,7 @@
         <v>37</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -8776,7 +8785,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -8785,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>25</v>
@@ -8807,10 +8816,10 @@
         <v>5</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -8824,7 +8833,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -8836,7 +8845,7 @@
         <v>29</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -8855,10 +8864,10 @@
         <v>5</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -8872,7 +8881,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -8881,10 +8890,10 @@
         <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -8903,10 +8912,10 @@
         <v>5</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -8920,7 +8929,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -8932,7 +8941,7 @@
         <v>35</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -8951,10 +8960,10 @@
         <v>5</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -8968,7 +8977,7 @@
         <v>50</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -8980,7 +8989,7 @@
         <v>35</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -8999,10 +9008,10 @@
         <v>5</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -9016,7 +9025,7 @@
         <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -9025,10 +9034,10 @@
         <v>43</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -9047,10 +9056,10 @@
         <v>5</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -9064,7 +9073,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -9076,7 +9085,7 @@
         <v>29</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -9095,10 +9104,10 @@
         <v>5</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -9112,7 +9121,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -9121,10 +9130,10 @@
         <v>10</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -9143,10 +9152,10 @@
         <v>5</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -9160,7 +9169,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -9194,7 +9203,7 @@
         <v>60</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -9208,7 +9217,7 @@
         <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -9220,7 +9229,7 @@
         <v>29</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -9242,7 +9251,7 @@
         <v>62</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -9256,7 +9265,7 @@
         <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -9268,7 +9277,7 @@
         <v>59</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -9290,7 +9299,7 @@
         <v>60</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -9304,7 +9313,7 @@
         <v>50</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -9316,7 +9325,7 @@
         <v>35</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -9338,7 +9347,7 @@
         <v>65</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -9352,7 +9361,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -9364,7 +9373,7 @@
         <v>35</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -9386,7 +9395,7 @@
         <v>62</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -9400,7 +9409,7 @@
         <v>50</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -9412,7 +9421,7 @@
         <v>59</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -9434,7 +9443,7 @@
         <v>60</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -9448,7 +9457,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -9460,7 +9469,7 @@
         <v>29</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -9482,7 +9491,7 @@
         <v>65</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -9496,7 +9505,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -9508,7 +9517,7 @@
         <v>59</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -9530,7 +9539,7 @@
         <v>65</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -9561,7 +9570,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -9595,7 +9604,7 @@
         <v>26</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -9609,7 +9618,7 @@
         <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -9621,7 +9630,7 @@
         <v>29</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -9640,10 +9649,10 @@
         <v>5</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -9657,7 +9666,7 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -9669,7 +9678,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -9691,7 +9700,7 @@
         <v>26</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -9705,7 +9714,7 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -9717,7 +9726,7 @@
         <v>35</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -9739,7 +9748,7 @@
         <v>37</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -9753,7 +9762,7 @@
         <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -9765,7 +9774,7 @@
         <v>35</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -9784,10 +9793,10 @@
         <v>5</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -9801,7 +9810,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -9813,7 +9822,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -9835,7 +9844,7 @@
         <v>26</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -9849,7 +9858,7 @@
         <v>60</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -9861,7 +9870,7 @@
         <v>29</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -9883,7 +9892,7 @@
         <v>37</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -9897,7 +9906,7 @@
         <v>60</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -9909,7 +9918,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -9931,7 +9940,7 @@
         <v>37</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -9945,7 +9954,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -9954,7 +9963,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>25</v>
@@ -9976,10 +9985,10 @@
         <v>5</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -9993,7 +10002,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -10005,7 +10014,7 @@
         <v>29</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -10024,10 +10033,10 @@
         <v>5</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -10041,7 +10050,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -10050,10 +10059,10 @@
         <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -10072,10 +10081,10 @@
         <v>5</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -10089,7 +10098,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -10101,7 +10110,7 @@
         <v>35</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -10120,10 +10129,10 @@
         <v>5</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -10137,7 +10146,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -10149,7 +10158,7 @@
         <v>35</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -10168,10 +10177,10 @@
         <v>5</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -10185,7 +10194,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -10194,10 +10203,10 @@
         <v>43</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -10216,10 +10225,10 @@
         <v>5</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -10233,7 +10242,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -10245,7 +10254,7 @@
         <v>29</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -10264,10 +10273,10 @@
         <v>5</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -10281,7 +10290,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -10290,10 +10299,10 @@
         <v>10</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -10312,10 +10321,10 @@
         <v>5</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -10329,7 +10338,7 @@
         <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -10363,7 +10372,7 @@
         <v>60</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -10377,7 +10386,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -10389,7 +10398,7 @@
         <v>29</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -10411,7 +10420,7 @@
         <v>62</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -10425,7 +10434,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -10437,7 +10446,7 @@
         <v>59</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -10459,7 +10468,7 @@
         <v>60</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -10473,7 +10482,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -10485,7 +10494,7 @@
         <v>35</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -10507,7 +10516,7 @@
         <v>65</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -10521,7 +10530,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -10533,7 +10542,7 @@
         <v>35</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -10555,7 +10564,7 @@
         <v>62</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -10569,7 +10578,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -10581,7 +10590,7 @@
         <v>59</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -10603,7 +10612,7 @@
         <v>60</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -10617,7 +10626,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -10629,7 +10638,7 @@
         <v>29</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -10651,7 +10660,7 @@
         <v>65</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -10665,7 +10674,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -10677,7 +10686,7 @@
         <v>59</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -10699,7 +10708,7 @@
         <v>65</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -10730,7 +10739,7 @@
         <v>70</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -10764,7 +10773,7 @@
         <v>26</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -10778,7 +10787,7 @@
         <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -10790,7 +10799,7 @@
         <v>29</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -10809,10 +10818,10 @@
         <v>5</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -10826,7 +10835,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -10838,7 +10847,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -10860,7 +10869,7 @@
         <v>26</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -10874,7 +10883,7 @@
         <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -10886,7 +10895,7 @@
         <v>35</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -10908,7 +10917,7 @@
         <v>37</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -10922,7 +10931,7 @@
         <v>70</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -10934,7 +10943,7 @@
         <v>35</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -10953,10 +10962,10 @@
         <v>5</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -10970,7 +10979,7 @@
         <v>70</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -10982,7 +10991,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -11004,7 +11013,7 @@
         <v>26</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -11018,7 +11027,7 @@
         <v>70</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -11030,7 +11039,7 @@
         <v>29</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -11052,7 +11061,7 @@
         <v>37</v>
       </c>
       <c r="Q87" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -11066,7 +11075,7 @@
         <v>70</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -11078,7 +11087,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -11100,7 +11109,7 @@
         <v>37</v>
       </c>
       <c r="Q88" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -11114,7 +11123,7 @@
         <v>70</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -11123,7 +11132,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>25</v>
@@ -11145,10 +11154,10 @@
         <v>5</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q89" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -11162,7 +11171,7 @@
         <v>70</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -11174,7 +11183,7 @@
         <v>29</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -11193,10 +11202,10 @@
         <v>5</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q90" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -11210,7 +11219,7 @@
         <v>70</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -11219,10 +11228,10 @@
         <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -11241,10 +11250,10 @@
         <v>5</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q91" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -11258,7 +11267,7 @@
         <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -11270,7 +11279,7 @@
         <v>35</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -11289,10 +11298,10 @@
         <v>5</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q92" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -11306,7 +11315,7 @@
         <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -11318,7 +11327,7 @@
         <v>35</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -11337,10 +11346,10 @@
         <v>5</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q93" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -11354,7 +11363,7 @@
         <v>70</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -11363,10 +11372,10 @@
         <v>43</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -11385,10 +11394,10 @@
         <v>5</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q94" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -11402,7 +11411,7 @@
         <v>70</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -11414,7 +11423,7 @@
         <v>29</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -11433,10 +11442,10 @@
         <v>5</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -11450,7 +11459,7 @@
         <v>70</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -11459,10 +11468,10 @@
         <v>10</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -11481,10 +11490,10 @@
         <v>5</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -11498,7 +11507,7 @@
         <v>70</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -11532,7 +11541,7 @@
         <v>60</v>
       </c>
       <c r="Q97" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -11546,7 +11555,7 @@
         <v>70</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -11558,7 +11567,7 @@
         <v>29</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -11580,7 +11589,7 @@
         <v>62</v>
       </c>
       <c r="Q98" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -11594,7 +11603,7 @@
         <v>70</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -11606,7 +11615,7 @@
         <v>59</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -11628,7 +11637,7 @@
         <v>60</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -11642,7 +11651,7 @@
         <v>70</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -11654,7 +11663,7 @@
         <v>35</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -11676,7 +11685,7 @@
         <v>65</v>
       </c>
       <c r="Q100" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -11690,7 +11699,7 @@
         <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -11702,7 +11711,7 @@
         <v>35</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -11724,7 +11733,7 @@
         <v>62</v>
       </c>
       <c r="Q101" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -11738,7 +11747,7 @@
         <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -11750,7 +11759,7 @@
         <v>59</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -11772,7 +11781,7 @@
         <v>60</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -11786,7 +11795,7 @@
         <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -11798,7 +11807,7 @@
         <v>29</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -11820,7 +11829,7 @@
         <v>65</v>
       </c>
       <c r="Q103" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -11834,7 +11843,7 @@
         <v>70</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -11846,7 +11855,7 @@
         <v>59</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -11868,7 +11877,7 @@
         <v>65</v>
       </c>
       <c r="Q104" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -12175,7 +12184,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -12223,7 +12232,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -12235,7 +12244,7 @@
         <v>29</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -12254,7 +12263,7 @@
         <v>5</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>25</v>
@@ -12271,7 +12280,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -12283,7 +12292,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -12319,7 +12328,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -12331,7 +12340,7 @@
         <v>35</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -12367,7 +12376,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -12379,7 +12388,7 @@
         <v>35</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -12398,7 +12407,7 @@
         <v>5</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>41</v>
@@ -12415,7 +12424,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -12427,7 +12436,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -12463,7 +12472,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -12475,7 +12484,7 @@
         <v>29</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -12511,7 +12520,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -12523,7 +12532,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -12559,7 +12568,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -12568,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
@@ -12590,7 +12599,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>27</v>
@@ -12607,7 +12616,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -12619,7 +12628,7 @@
         <v>29</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -12638,7 +12647,7 @@
         <v>5</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>25</v>
@@ -12655,7 +12664,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -12664,10 +12673,10 @@
         <v>3</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -12686,7 +12695,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>33</v>
@@ -12703,7 +12712,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -12715,7 +12724,7 @@
         <v>35</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -12734,7 +12743,7 @@
         <v>5</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>38</v>
@@ -12751,7 +12760,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -12763,7 +12772,7 @@
         <v>35</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -12782,7 +12791,7 @@
         <v>5</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>41</v>
@@ -12799,7 +12808,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -12808,10 +12817,10 @@
         <v>43</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -12830,7 +12839,7 @@
         <v>5</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>33</v>
@@ -12847,7 +12856,7 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -12859,7 +12868,7 @@
         <v>29</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -12878,7 +12887,7 @@
         <v>5</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>38</v>
@@ -12895,7 +12904,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -12904,10 +12913,10 @@
         <v>10</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -12926,7 +12935,7 @@
         <v>5</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>38</v>
@@ -12943,7 +12952,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -12991,7 +13000,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -13003,7 +13012,7 @@
         <v>29</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -13039,7 +13048,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -13051,7 +13060,7 @@
         <v>59</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -13087,7 +13096,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -13099,7 +13108,7 @@
         <v>35</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -13135,7 +13144,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -13147,7 +13156,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -13183,7 +13192,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -13195,7 +13204,7 @@
         <v>59</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -13231,7 +13240,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -13243,7 +13252,7 @@
         <v>29</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -13279,7 +13288,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -13291,7 +13300,7 @@
         <v>59</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -13327,7 +13336,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -13361,7 +13370,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13375,7 +13384,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -13387,7 +13396,7 @@
         <v>29</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -13406,10 +13415,10 @@
         <v>5</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13423,7 +13432,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -13435,7 +13444,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -13457,7 +13466,7 @@
         <v>26</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13471,7 +13480,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -13483,7 +13492,7 @@
         <v>35</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -13505,7 +13514,7 @@
         <v>37</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13519,7 +13528,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -13531,7 +13540,7 @@
         <v>35</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -13550,10 +13559,10 @@
         <v>5</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13567,7 +13576,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -13579,7 +13588,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -13601,7 +13610,7 @@
         <v>26</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13615,7 +13624,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -13627,7 +13636,7 @@
         <v>29</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -13649,7 +13658,7 @@
         <v>37</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -13663,7 +13672,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -13675,7 +13684,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -13697,7 +13706,7 @@
         <v>37</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -13711,7 +13720,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -13720,7 +13729,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>25</v>
@@ -13742,10 +13751,10 @@
         <v>5</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -13759,7 +13768,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -13771,7 +13780,7 @@
         <v>29</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -13790,10 +13799,10 @@
         <v>5</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -13807,7 +13816,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -13816,10 +13825,10 @@
         <v>3</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -13838,10 +13847,10 @@
         <v>5</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -13855,7 +13864,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -13867,7 +13876,7 @@
         <v>35</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -13886,10 +13895,10 @@
         <v>5</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -13903,7 +13912,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -13915,7 +13924,7 @@
         <v>35</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -13934,10 +13943,10 @@
         <v>5</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -13951,7 +13960,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -13960,10 +13969,10 @@
         <v>43</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -13982,10 +13991,10 @@
         <v>5</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -13999,7 +14008,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -14011,7 +14020,7 @@
         <v>29</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -14030,10 +14039,10 @@
         <v>5</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -14047,7 +14056,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -14056,10 +14065,10 @@
         <v>10</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -14078,10 +14087,10 @@
         <v>5</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -14095,7 +14104,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -14129,7 +14138,7 @@
         <v>60</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -14143,7 +14152,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -14155,7 +14164,7 @@
         <v>29</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -14177,7 +14186,7 @@
         <v>62</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -14191,7 +14200,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -14203,7 +14212,7 @@
         <v>59</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -14225,7 +14234,7 @@
         <v>60</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -14239,7 +14248,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -14251,7 +14260,7 @@
         <v>35</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -14273,7 +14282,7 @@
         <v>65</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -14287,7 +14296,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -14299,7 +14308,7 @@
         <v>35</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -14321,7 +14330,7 @@
         <v>62</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -14335,7 +14344,7 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -14347,7 +14356,7 @@
         <v>59</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -14369,7 +14378,7 @@
         <v>60</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -14383,7 +14392,7 @@
         <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -14395,7 +14404,7 @@
         <v>29</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -14417,7 +14426,7 @@
         <v>65</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -14431,7 +14440,7 @@
         <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -14443,7 +14452,7 @@
         <v>59</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -14465,7 +14474,7 @@
         <v>65</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -14496,7 +14505,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -14530,7 +14539,7 @@
         <v>26</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -14544,7 +14553,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -14556,7 +14565,7 @@
         <v>29</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -14575,10 +14584,10 @@
         <v>5</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -14592,7 +14601,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -14604,7 +14613,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -14626,7 +14635,7 @@
         <v>26</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -14640,7 +14649,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -14652,7 +14661,7 @@
         <v>35</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -14674,7 +14683,7 @@
         <v>37</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -14688,7 +14697,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -14700,7 +14709,7 @@
         <v>35</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -14719,10 +14728,10 @@
         <v>5</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -14736,7 +14745,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -14748,7 +14757,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -14770,7 +14779,7 @@
         <v>26</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -14784,7 +14793,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -14796,7 +14805,7 @@
         <v>29</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -14818,7 +14827,7 @@
         <v>37</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -14832,7 +14841,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -14844,7 +14853,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -14866,7 +14875,7 @@
         <v>37</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -14880,7 +14889,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -14889,7 +14898,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>25</v>
@@ -14911,10 +14920,10 @@
         <v>5</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -14928,7 +14937,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -14940,7 +14949,7 @@
         <v>29</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -14959,10 +14968,10 @@
         <v>5</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -14976,7 +14985,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -14985,10 +14994,10 @@
         <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -15007,10 +15016,10 @@
         <v>5</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -15024,7 +15033,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15036,7 +15045,7 @@
         <v>35</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -15055,10 +15064,10 @@
         <v>5</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -15072,7 +15081,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15084,7 +15093,7 @@
         <v>35</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -15103,10 +15112,10 @@
         <v>5</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -15120,7 +15129,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15129,10 +15138,10 @@
         <v>43</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -15151,10 +15160,10 @@
         <v>5</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -15168,7 +15177,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15180,7 +15189,7 @@
         <v>29</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -15199,10 +15208,10 @@
         <v>5</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -15216,7 +15225,7 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15225,10 +15234,10 @@
         <v>10</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -15247,10 +15256,10 @@
         <v>5</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -15264,7 +15273,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -15298,7 +15307,7 @@
         <v>60</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -15312,7 +15321,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -15324,7 +15333,7 @@
         <v>29</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -15346,7 +15355,7 @@
         <v>62</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -15360,7 +15369,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -15372,7 +15381,7 @@
         <v>59</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -15394,7 +15403,7 @@
         <v>60</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -15408,7 +15417,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -15420,7 +15429,7 @@
         <v>35</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -15442,7 +15451,7 @@
         <v>65</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -15456,7 +15465,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -15468,7 +15477,7 @@
         <v>35</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -15490,7 +15499,7 @@
         <v>62</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -15504,7 +15513,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -15516,7 +15525,7 @@
         <v>59</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -15538,7 +15547,7 @@
         <v>60</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -15552,7 +15561,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -15564,7 +15573,7 @@
         <v>29</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -15586,7 +15595,7 @@
         <v>65</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -15600,7 +15609,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -15612,7 +15621,7 @@
         <v>59</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -15634,7 +15643,7 @@
         <v>65</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -15665,7 +15674,7 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -15699,7 +15708,7 @@
         <v>26</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -15713,7 +15722,7 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -15725,7 +15734,7 @@
         <v>29</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -15744,10 +15753,10 @@
         <v>5</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -15761,7 +15770,7 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -15773,7 +15782,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -15795,7 +15804,7 @@
         <v>26</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -15809,7 +15818,7 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -15821,7 +15830,7 @@
         <v>35</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -15843,7 +15852,7 @@
         <v>37</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -15857,7 +15866,7 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -15869,7 +15878,7 @@
         <v>35</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -15888,10 +15897,10 @@
         <v>5</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -15905,7 +15914,7 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -15917,7 +15926,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -15939,7 +15948,7 @@
         <v>26</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -15953,7 +15962,7 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -15965,7 +15974,7 @@
         <v>29</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -15987,7 +15996,7 @@
         <v>37</v>
       </c>
       <c r="Q87" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -16001,7 +16010,7 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16013,7 +16022,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -16035,7 +16044,7 @@
         <v>37</v>
       </c>
       <c r="Q88" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -16049,7 +16058,7 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16058,7 +16067,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>25</v>
@@ -16080,10 +16089,10 @@
         <v>5</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q89" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -16097,7 +16106,7 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16109,7 +16118,7 @@
         <v>29</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -16128,10 +16137,10 @@
         <v>5</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q90" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -16145,7 +16154,7 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16154,10 +16163,10 @@
         <v>3</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -16176,10 +16185,10 @@
         <v>5</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q91" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -16193,7 +16202,7 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -16205,7 +16214,7 @@
         <v>35</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -16224,10 +16233,10 @@
         <v>5</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q92" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -16241,7 +16250,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -16253,7 +16262,7 @@
         <v>35</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -16272,10 +16281,10 @@
         <v>5</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q93" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -16289,7 +16298,7 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -16298,10 +16307,10 @@
         <v>43</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -16320,10 +16329,10 @@
         <v>5</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q94" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -16337,7 +16346,7 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -16349,7 +16358,7 @@
         <v>29</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -16368,10 +16377,10 @@
         <v>5</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -16385,7 +16394,7 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -16394,10 +16403,10 @@
         <v>10</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -16416,10 +16425,10 @@
         <v>5</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -16433,7 +16442,7 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -16467,7 +16476,7 @@
         <v>60</v>
       </c>
       <c r="Q97" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -16481,7 +16490,7 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -16493,7 +16502,7 @@
         <v>29</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -16515,7 +16524,7 @@
         <v>62</v>
       </c>
       <c r="Q98" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -16529,7 +16538,7 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -16541,7 +16550,7 @@
         <v>59</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -16563,7 +16572,7 @@
         <v>60</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -16577,7 +16586,7 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -16589,7 +16598,7 @@
         <v>35</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -16611,7 +16620,7 @@
         <v>65</v>
       </c>
       <c r="Q100" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -16625,7 +16634,7 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -16637,7 +16646,7 @@
         <v>35</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -16659,7 +16668,7 @@
         <v>62</v>
       </c>
       <c r="Q101" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -16673,7 +16682,7 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -16685,7 +16694,7 @@
         <v>59</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -16707,7 +16716,7 @@
         <v>60</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -16721,7 +16730,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -16733,7 +16742,7 @@
         <v>29</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -16755,7 +16764,7 @@
         <v>65</v>
       </c>
       <c r="Q103" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -16769,7 +16778,7 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -16781,7 +16790,7 @@
         <v>59</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -16803,7 +16812,7 @@
         <v>65</v>
       </c>
       <c r="Q104" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -17104,7 +17113,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17113,10 +17122,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17145,7 +17154,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17154,10 +17163,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -1371,7 +1371,7 @@
     <t>4,5,6</t>
   </si>
   <si>
-    <t>30,30,30</t>
+    <t>50,50,50</t>
   </si>
   <si>
     <t>新手衣服</t>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -366,40 +366,40 @@
     <t>50,5</t>
   </si>
   <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>20,10</t>
+  </si>
+  <si>
+    <t>朽木战甲</t>
+  </si>
+  <si>
+    <t>2,1002</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>朽木战链</t>
+  </si>
+  <si>
+    <t>25,2</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>朽木战盔</t>
+  </si>
+  <si>
+    <t>1,1001</t>
+  </si>
+  <si>
+    <t>1000,5</t>
+  </si>
+  <si>
     <t>4,1</t>
-  </si>
-  <si>
-    <t>20,10</t>
-  </si>
-  <si>
-    <t>朽木战甲</t>
-  </si>
-  <si>
-    <t>2,1002</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>朽木战链</t>
-  </si>
-  <si>
-    <t>25,2</t>
-  </si>
-  <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>朽木战盔</t>
-  </si>
-  <si>
-    <t>1,1001</t>
-  </si>
-  <si>
-    <t>1000,5</t>
-  </si>
-  <si>
-    <t>4,3</t>
   </si>
   <si>
     <t>10,100</t>
@@ -2824,10 +2824,10 @@
         <v>5</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -2871,10 +2871,10 @@
         <v>5</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -3203,7 +3203,7 @@
         <v>47</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3250,7 +3250,7 @@
         <v>52</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3294,7 +3294,7 @@
         <v>5</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>33</v>
@@ -3579,7 +3579,7 @@
         <v>59</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3626,7 +3626,7 @@
         <v>64</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -3670,7 +3670,7 @@
         <v>5</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q29" s="6" t="s">
         <v>33</v>
@@ -3717,7 +3717,7 @@
         <v>5</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>71</v>
@@ -3811,7 +3811,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>75</v>
@@ -3858,7 +3858,7 @@
         <v>5</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>78</v>
@@ -3955,7 +3955,7 @@
         <v>37</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:17">
@@ -4002,7 +4002,7 @@
         <v>26</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -4328,10 +4328,10 @@
         <v>5</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -4375,10 +4375,10 @@
         <v>5</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -4422,7 +4422,7 @@
         <v>5</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q46" s="6" t="s">
         <v>75</v>
@@ -4704,10 +4704,10 @@
         <v>5</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -4751,10 +4751,10 @@
         <v>5</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -4798,7 +4798,7 @@
         <v>5</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>75</v>
@@ -4862,7 +4862,7 @@
         <v>5</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>101</v>
@@ -4956,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>105</v>
@@ -5003,7 +5003,7 @@
         <v>5</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>108</v>
@@ -5100,7 +5100,7 @@
         <v>37</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -5147,7 +5147,7 @@
         <v>26</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -5473,10 +5473,10 @@
         <v>5</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -5520,10 +5520,10 @@
         <v>5</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -5567,7 +5567,7 @@
         <v>5</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q71" s="6" t="s">
         <v>105</v>
@@ -5849,10 +5849,10 @@
         <v>5</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -5896,10 +5896,10 @@
         <v>5</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -5943,7 +5943,7 @@
         <v>5</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q79" s="6" t="s">
         <v>105</v>
@@ -6007,7 +6007,7 @@
         <v>5</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>131</v>
@@ -6101,7 +6101,7 @@
         <v>5</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>135</v>
@@ -6148,7 +6148,7 @@
         <v>5</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q84" s="6" t="s">
         <v>138</v>
@@ -6245,7 +6245,7 @@
         <v>37</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -6292,7 +6292,7 @@
         <v>26</v>
       </c>
       <c r="Q87" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -6618,10 +6618,10 @@
         <v>5</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q94" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -6665,10 +6665,10 @@
         <v>5</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -6712,7 +6712,7 @@
         <v>5</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="Q96" s="6" t="s">
         <v>135</v>
@@ -6994,10 +6994,10 @@
         <v>5</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -7041,10 +7041,10 @@
         <v>5</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q103" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -7088,7 +7088,7 @@
         <v>5</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q104" s="6" t="s">
         <v>135</v>
@@ -7331,7 +7331,7 @@
         <v>5</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="6" t="s">
         <v>27</v>
@@ -7427,7 +7427,7 @@
         <v>5</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>33</v>
@@ -7475,7 +7475,7 @@
         <v>5</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>166</v>
@@ -7571,7 +7571,7 @@
         <v>5</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>33</v>
@@ -7619,7 +7619,7 @@
         <v>5</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>166</v>
@@ -7667,7 +7667,7 @@
         <v>5</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>166</v>
@@ -8483,7 +8483,7 @@
         <v>5</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>75</v>
@@ -8579,7 +8579,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>191</v>
@@ -8627,7 +8627,7 @@
         <v>5</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>193</v>
@@ -8723,7 +8723,7 @@
         <v>5</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>191</v>
@@ -8771,7 +8771,7 @@
         <v>5</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>193</v>
@@ -8819,7 +8819,7 @@
         <v>5</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>193</v>
@@ -9652,7 +9652,7 @@
         <v>5</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>216</v>
@@ -9748,7 +9748,7 @@
         <v>5</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>220</v>
@@ -9796,7 +9796,7 @@
         <v>5</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>222</v>
@@ -9892,7 +9892,7 @@
         <v>5</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>220</v>
@@ -9940,7 +9940,7 @@
         <v>5</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>222</v>
@@ -9988,7 +9988,7 @@
         <v>5</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>222</v>
@@ -10821,7 +10821,7 @@
         <v>5</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>71</v>
@@ -10917,7 +10917,7 @@
         <v>5</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>75</v>
@@ -10965,7 +10965,7 @@
         <v>5</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q84" s="6" t="s">
         <v>249</v>
@@ -11061,7 +11061,7 @@
         <v>5</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q86" s="6" t="s">
         <v>75</v>
@@ -11109,7 +11109,7 @@
         <v>5</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q87" s="6" t="s">
         <v>249</v>
@@ -11157,7 +11157,7 @@
         <v>5</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q88" s="6" t="s">
         <v>249</v>
@@ -12266,7 +12266,7 @@
         <v>5</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="6" t="s">
         <v>27</v>
@@ -12362,7 +12362,7 @@
         <v>5</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>33</v>
@@ -12410,7 +12410,7 @@
         <v>5</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>166</v>
@@ -12506,7 +12506,7 @@
         <v>5</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>33</v>
@@ -12554,7 +12554,7 @@
         <v>5</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>166</v>
@@ -12602,7 +12602,7 @@
         <v>5</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>166</v>
@@ -13418,7 +13418,7 @@
         <v>5</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>75</v>
@@ -13514,7 +13514,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>191</v>
@@ -13562,7 +13562,7 @@
         <v>5</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>193</v>
@@ -13658,7 +13658,7 @@
         <v>5</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>191</v>
@@ -13706,7 +13706,7 @@
         <v>5</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>193</v>
@@ -13754,7 +13754,7 @@
         <v>5</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>193</v>
@@ -14587,7 +14587,7 @@
         <v>5</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>216</v>
@@ -14683,7 +14683,7 @@
         <v>5</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>220</v>
@@ -14731,7 +14731,7 @@
         <v>5</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>222</v>
@@ -14827,7 +14827,7 @@
         <v>5</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>220</v>
@@ -14875,7 +14875,7 @@
         <v>5</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>222</v>
@@ -14923,7 +14923,7 @@
         <v>5</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>222</v>
@@ -15756,7 +15756,7 @@
         <v>5</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>71</v>
@@ -15852,7 +15852,7 @@
         <v>5</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>75</v>
@@ -15900,7 +15900,7 @@
         <v>5</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q84" s="6" t="s">
         <v>249</v>
@@ -15996,7 +15996,7 @@
         <v>5</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q86" s="6" t="s">
         <v>75</v>
@@ -16044,7 +16044,7 @@
         <v>5</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q87" s="6" t="s">
         <v>249</v>
@@ -16092,7 +16092,7 @@
         <v>5</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q88" s="6" t="s">
         <v>249</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
     <sheet name="50-80" sheetId="8" r:id="rId2"/>
     <sheet name="90-120" sheetId="9" r:id="rId3"/>
     <sheet name="定制" sheetId="10" r:id="rId4"/>
+    <sheet name="神话" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -285,8 +286,72 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 武器
+2 衣服
+3 头盔
+4 项链
+5 左手镯
+6 右手镯
+7 左戒指
+8 右戒指
+9 腰带
+10 鞋子
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+属性ID列表</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="433">
   <si>
     <t>_id</t>
   </si>
@@ -1405,6 +1470,186 @@
   </si>
   <si>
     <t>1000,10</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>SpeAtrIdList</t>
+  </si>
+  <si>
+    <t>SpeAtrVueList</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>治愈之戒</t>
+  </si>
+  <si>
+    <t>治愈之镯</t>
+  </si>
+  <si>
+    <t>治愈之甲</t>
+  </si>
+  <si>
+    <t>回复效果提高100%</t>
+  </si>
+  <si>
+    <t>天命之剑</t>
+  </si>
+  <si>
+    <t>攻击概率降低50%，概率2倍，5倍，10倍，100倍</t>
+  </si>
+  <si>
+    <t>天命之链</t>
+  </si>
+  <si>
+    <t>天命之戒</t>
+  </si>
+  <si>
+    <t>贪婪之链</t>
+  </si>
+  <si>
+    <t>怪物掉落概率翻倍</t>
+  </si>
+  <si>
+    <t>贪婪之镯</t>
+  </si>
+  <si>
+    <t>贪婪之戒</t>
+  </si>
+  <si>
+    <t>重击之刃</t>
+  </si>
+  <si>
+    <t>此次攻击概率翻倍</t>
+  </si>
+  <si>
+    <t>重击之链</t>
+  </si>
+  <si>
+    <t>重击之戒</t>
+  </si>
+  <si>
+    <t>神速之链</t>
+  </si>
+  <si>
+    <t>攻速增加10%</t>
+  </si>
+  <si>
+    <t>神速之带</t>
+  </si>
+  <si>
+    <t>神速之靴</t>
+  </si>
+  <si>
+    <t>坚韧之甲</t>
+  </si>
+  <si>
+    <t>最高承伤10%</t>
+  </si>
+  <si>
+    <t>坚韧之盔</t>
+  </si>
+  <si>
+    <t>坚韧之带</t>
+  </si>
+  <si>
+    <t>暴击之剑</t>
+  </si>
+  <si>
+    <t>如果此次攻击暴击了，伤害额外翻倍</t>
+  </si>
+  <si>
+    <t>暴击之链</t>
+  </si>
+  <si>
+    <t>暴击之戒</t>
+  </si>
+  <si>
+    <t>致命之剑</t>
+  </si>
+  <si>
+    <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
+  </si>
+  <si>
+    <t>致命之链</t>
+  </si>
+  <si>
+    <t>致命之戒</t>
+  </si>
+  <si>
+    <t>背刺之匕</t>
+  </si>
+  <si>
+    <t>首次攻击敌人，降低敌人10%最大生命</t>
+  </si>
+  <si>
+    <t>背刺之带</t>
+  </si>
+  <si>
+    <t>背刺之削</t>
+  </si>
+  <si>
+    <t>毒蛇之刺</t>
+  </si>
+  <si>
+    <t>每次攻击，有1%概率降低敌人最大生命的1%</t>
+  </si>
+  <si>
+    <t>毒蛇之链</t>
+  </si>
+  <si>
+    <t>毒蛇之戒</t>
+  </si>
+  <si>
+    <t>财富之袍</t>
+  </si>
+  <si>
+    <t>杀敌金币增加100，金币加成增加20%</t>
+  </si>
+  <si>
+    <t>财富之链</t>
+  </si>
+  <si>
+    <t>财富之带</t>
+  </si>
+  <si>
+    <t>修炼之袍</t>
+  </si>
+  <si>
+    <t>杀敌经验增加100，经验加成增加20%</t>
+  </si>
+  <si>
+    <t>修炼之盔</t>
+  </si>
+  <si>
+    <t>修炼之靴</t>
+  </si>
+  <si>
+    <t>幸运项链</t>
+  </si>
+  <si>
+    <t>幸运+3</t>
+  </si>
+  <si>
+    <t>幸运戒指</t>
+  </si>
+  <si>
+    <t>幸运腰带</t>
+  </si>
+  <si>
+    <t>诅咒魔甲</t>
+  </si>
+  <si>
+    <t>诅咒+3</t>
+  </si>
+  <si>
+    <t>诅咒魔盔</t>
+  </si>
+  <si>
+    <t>诅咒魔靴</t>
   </si>
 </sst>
 </file>
@@ -17247,4 +17492,1212 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:T47"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.8333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="1" customWidth="1"/>
+    <col min="13" max="18" width="13" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="13" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A6" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="1">
+        <v>211001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M6" s="1">
+        <v>100</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
+        <v>6</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>101</v>
+      </c>
+      <c r="R6" s="1">
+        <v>6</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A7" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="1">
+        <v>211002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A8" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C8" s="1">
+        <v>211003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:20">
+      <c r="A9" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" s="1">
+        <v>211004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:20">
+      <c r="A10" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="1">
+        <v>211005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:20">
+      <c r="A11" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="1">
+        <v>211006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:20">
+      <c r="A12" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" s="1">
+        <v>211007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:20">
+      <c r="A13" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="1">
+        <v>211008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:20">
+      <c r="A14" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C14" s="1">
+        <v>211009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:20">
+      <c r="A15" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C15" s="1">
+        <v>211010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:20">
+      <c r="A16" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C16" s="1">
+        <v>211011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:20">
+      <c r="A17" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" s="1">
+        <v>211012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:20">
+      <c r="A18" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C18" s="1">
+        <v>211013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:20">
+      <c r="A19" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C19" s="1">
+        <v>211014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:20">
+      <c r="A20" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C20" s="1">
+        <v>211015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:20">
+      <c r="A21" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C21" s="1">
+        <v>211016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:20">
+      <c r="A22" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C22" s="1">
+        <v>211017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>10</v>
+      </c>
+      <c r="E22" s="1">
+        <v>10</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:20">
+      <c r="A23" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C23" s="1">
+        <v>211018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>10</v>
+      </c>
+      <c r="E23" s="1">
+        <v>10</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:20">
+      <c r="A24" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C24" s="1">
+        <v>211019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>10</v>
+      </c>
+      <c r="E24" s="1">
+        <v>10</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:20">
+      <c r="A25" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="1">
+        <v>211020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1">
+        <v>10</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:20">
+      <c r="A26" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C26" s="1">
+        <v>211021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1">
+        <v>10</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:20">
+      <c r="A27" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" s="1">
+        <v>211022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1">
+        <v>10</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:20">
+      <c r="A28" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" s="1">
+        <v>211023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1">
+        <v>10</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:20">
+      <c r="A29" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C29" s="1">
+        <v>211024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:20">
+      <c r="A30" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="1">
+        <v>211025</v>
+      </c>
+      <c r="D30" s="1">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1">
+        <v>10</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A31" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="1">
+        <v>211026</v>
+      </c>
+      <c r="D31" s="1">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1">
+        <v>10</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A32" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C32" s="1">
+        <v>211027</v>
+      </c>
+      <c r="D32" s="1">
+        <v>10</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A33" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C33" s="1">
+        <v>211028</v>
+      </c>
+      <c r="D33" s="1">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1">
+        <v>10</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A34" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C34" s="1">
+        <v>211029</v>
+      </c>
+      <c r="D34" s="1">
+        <v>10</v>
+      </c>
+      <c r="E34" s="1">
+        <v>10</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A35" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C35" s="1">
+        <v>211030</v>
+      </c>
+      <c r="D35" s="1">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1">
+        <v>10</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A36" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C36" s="1">
+        <v>211031</v>
+      </c>
+      <c r="D36" s="1">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1">
+        <v>10</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:20">
+      <c r="A37" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C37" s="1">
+        <v>211032</v>
+      </c>
+      <c r="D37" s="1">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:20">
+      <c r="A38" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C38" s="1">
+        <v>211033</v>
+      </c>
+      <c r="D38" s="1">
+        <v>10</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:20">
+      <c r="A39" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C39" s="1">
+        <v>211034</v>
+      </c>
+      <c r="D39" s="1">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1">
+        <v>10</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A40" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C40" s="1">
+        <v>211035</v>
+      </c>
+      <c r="D40" s="1">
+        <v>10</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A41" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C41" s="1">
+        <v>211036</v>
+      </c>
+      <c r="D41" s="1">
+        <v>10</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A42" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C42" s="1">
+        <v>211037</v>
+      </c>
+      <c r="D42" s="1">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1">
+        <v>10</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G42" t="s">
+        <v>426</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:20">
+      <c r="A43" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C43" s="1">
+        <v>211038</v>
+      </c>
+      <c r="D43" s="1">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1">
+        <v>10</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:20">
+      <c r="A44" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C44" s="1">
+        <v>211039</v>
+      </c>
+      <c r="D44" s="1">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1">
+        <v>10</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:20">
+      <c r="A45" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C45" s="1">
+        <v>211040</v>
+      </c>
+      <c r="D45" s="1">
+        <v>10</v>
+      </c>
+      <c r="E45" s="1">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:20">
+      <c r="A46" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C46" s="1">
+        <v>211041</v>
+      </c>
+      <c r="D46" s="1">
+        <v>10</v>
+      </c>
+      <c r="E46" s="1">
+        <v>10</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:20">
+      <c r="A47" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C47" s="1">
+        <v>211042</v>
+      </c>
+      <c r="D47" s="1">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1">
+        <v>10</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 M3:T5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -461,7 +461,7 @@
     <t>1,1001</t>
   </si>
   <si>
-    <t>1000,5</t>
+    <t>500,4</t>
   </si>
   <si>
     <t>4,1</t>
@@ -584,7 +584,7 @@
     <t>黑铁战盔</t>
   </si>
   <si>
-    <t>4000,10</t>
+    <t>2000,8</t>
   </si>
   <si>
     <t>40,400</t>
@@ -674,7 +674,7 @@
     <t>白银战盔</t>
   </si>
   <si>
-    <t>20000,15</t>
+    <t>10000,12</t>
   </si>
   <si>
     <t>200,2000</t>
@@ -764,7 +764,7 @@
     <t>黄金战盔</t>
   </si>
   <si>
-    <t>100000,20</t>
+    <t>50000,15</t>
   </si>
   <si>
     <t>1000,10000</t>
@@ -1828,12 +1828,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5465,7 +5465,7 @@
         <v>46</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K64" s="1">
         <v>900</v>
@@ -5512,7 +5512,7 @@
         <v>29</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K65" s="1">
         <v>900</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
     <sheet name="50-80" sheetId="8" r:id="rId2"/>
     <sheet name="90-120" sheetId="9" r:id="rId3"/>
     <sheet name="定制" sheetId="10" r:id="rId4"/>
-    <sheet name="神话" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -286,72 +285,8 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 武器
-2 衣服
-3 头盔
-4 项链
-5 左手镯
-6 右手镯
-7 左戒指
-8 右戒指
-9 腰带
-10 鞋子
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-属性ID列表</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="373">
   <si>
     <t>_id</t>
   </si>
@@ -1470,186 +1405,6 @@
   </si>
   <si>
     <t>1000,10</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>SpeAtrIdList</t>
-  </si>
-  <si>
-    <t>SpeAtrVueList</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>治愈之戒</t>
-  </si>
-  <si>
-    <t>治愈之镯</t>
-  </si>
-  <si>
-    <t>治愈之甲</t>
-  </si>
-  <si>
-    <t>回复效果提高100%</t>
-  </si>
-  <si>
-    <t>天命之剑</t>
-  </si>
-  <si>
-    <t>攻击概率降低50%，概率2倍，5倍，10倍，100倍</t>
-  </si>
-  <si>
-    <t>天命之链</t>
-  </si>
-  <si>
-    <t>天命之戒</t>
-  </si>
-  <si>
-    <t>贪婪之链</t>
-  </si>
-  <si>
-    <t>怪物掉落概率翻倍</t>
-  </si>
-  <si>
-    <t>贪婪之镯</t>
-  </si>
-  <si>
-    <t>贪婪之戒</t>
-  </si>
-  <si>
-    <t>重击之刃</t>
-  </si>
-  <si>
-    <t>此次攻击概率翻倍</t>
-  </si>
-  <si>
-    <t>重击之链</t>
-  </si>
-  <si>
-    <t>重击之戒</t>
-  </si>
-  <si>
-    <t>神速之链</t>
-  </si>
-  <si>
-    <t>攻速增加10%</t>
-  </si>
-  <si>
-    <t>神速之带</t>
-  </si>
-  <si>
-    <t>神速之靴</t>
-  </si>
-  <si>
-    <t>坚韧之甲</t>
-  </si>
-  <si>
-    <t>最高承伤10%</t>
-  </si>
-  <si>
-    <t>坚韧之盔</t>
-  </si>
-  <si>
-    <t>坚韧之带</t>
-  </si>
-  <si>
-    <t>暴击之剑</t>
-  </si>
-  <si>
-    <t>如果此次攻击暴击了，伤害额外翻倍</t>
-  </si>
-  <si>
-    <t>暴击之链</t>
-  </si>
-  <si>
-    <t>暴击之戒</t>
-  </si>
-  <si>
-    <t>致命之剑</t>
-  </si>
-  <si>
-    <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
-  </si>
-  <si>
-    <t>致命之链</t>
-  </si>
-  <si>
-    <t>致命之戒</t>
-  </si>
-  <si>
-    <t>背刺之匕</t>
-  </si>
-  <si>
-    <t>首次攻击敌人，降低敌人10%最大生命</t>
-  </si>
-  <si>
-    <t>背刺之带</t>
-  </si>
-  <si>
-    <t>背刺之削</t>
-  </si>
-  <si>
-    <t>毒蛇之刺</t>
-  </si>
-  <si>
-    <t>每次攻击，有1%概率降低敌人最大生命的1%</t>
-  </si>
-  <si>
-    <t>毒蛇之链</t>
-  </si>
-  <si>
-    <t>毒蛇之戒</t>
-  </si>
-  <si>
-    <t>财富之袍</t>
-  </si>
-  <si>
-    <t>杀敌金币增加100，金币加成增加20%</t>
-  </si>
-  <si>
-    <t>财富之链</t>
-  </si>
-  <si>
-    <t>财富之带</t>
-  </si>
-  <si>
-    <t>修炼之袍</t>
-  </si>
-  <si>
-    <t>杀敌经验增加100，经验加成增加20%</t>
-  </si>
-  <si>
-    <t>修炼之盔</t>
-  </si>
-  <si>
-    <t>修炼之靴</t>
-  </si>
-  <si>
-    <t>幸运项链</t>
-  </si>
-  <si>
-    <t>幸运+3</t>
-  </si>
-  <si>
-    <t>幸运戒指</t>
-  </si>
-  <si>
-    <t>幸运腰带</t>
-  </si>
-  <si>
-    <t>诅咒魔甲</t>
-  </si>
-  <si>
-    <t>诅咒+3</t>
-  </si>
-  <si>
-    <t>诅咒魔盔</t>
-  </si>
-  <si>
-    <t>诅咒魔靴</t>
   </si>
 </sst>
 </file>
@@ -1828,12 +1583,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -17492,1212 +17247,4 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A3:T47"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.8333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="1" customWidth="1"/>
-    <col min="13" max="18" width="13" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="13" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A6" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C6" s="1">
-        <v>211001</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="M6" s="1">
-        <v>100</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="1">
-        <v>6</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>101</v>
-      </c>
-      <c r="R6" s="1">
-        <v>6</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A7" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C7" s="1">
-        <v>211002</v>
-      </c>
-      <c r="D7" s="1">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A8" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C8" s="1">
-        <v>211003</v>
-      </c>
-      <c r="D8" s="1">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:20">
-      <c r="A9" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C9" s="1">
-        <v>211004</v>
-      </c>
-      <c r="D9" s="1">
-        <v>10</v>
-      </c>
-      <c r="E9" s="1">
-        <v>10</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:20">
-      <c r="A10" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C10" s="1">
-        <v>211005</v>
-      </c>
-      <c r="D10" s="1">
-        <v>10</v>
-      </c>
-      <c r="E10" s="1">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:20">
-      <c r="A11" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C11" s="1">
-        <v>211006</v>
-      </c>
-      <c r="D11" s="1">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:20">
-      <c r="A12" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" s="1">
-        <v>211007</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10</v>
-      </c>
-      <c r="E12" s="1">
-        <v>10</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:20">
-      <c r="A13" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C13" s="1">
-        <v>211008</v>
-      </c>
-      <c r="D13" s="1">
-        <v>10</v>
-      </c>
-      <c r="E13" s="1">
-        <v>10</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:20">
-      <c r="A14" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C14" s="1">
-        <v>211009</v>
-      </c>
-      <c r="D14" s="1">
-        <v>10</v>
-      </c>
-      <c r="E14" s="1">
-        <v>10</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:20">
-      <c r="A15" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C15" s="1">
-        <v>211010</v>
-      </c>
-      <c r="D15" s="1">
-        <v>10</v>
-      </c>
-      <c r="E15" s="1">
-        <v>10</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:20">
-      <c r="A16" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C16" s="1">
-        <v>211011</v>
-      </c>
-      <c r="D16" s="1">
-        <v>10</v>
-      </c>
-      <c r="E16" s="1">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C17" s="1">
-        <v>211012</v>
-      </c>
-      <c r="D17" s="1">
-        <v>10</v>
-      </c>
-      <c r="E17" s="1">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C18" s="1">
-        <v>211013</v>
-      </c>
-      <c r="D18" s="1">
-        <v>10</v>
-      </c>
-      <c r="E18" s="1">
-        <v>10</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C19" s="1">
-        <v>211014</v>
-      </c>
-      <c r="D19" s="1">
-        <v>10</v>
-      </c>
-      <c r="E19" s="1">
-        <v>10</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C20" s="1">
-        <v>211015</v>
-      </c>
-      <c r="D20" s="1">
-        <v>10</v>
-      </c>
-      <c r="E20" s="1">
-        <v>10</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C21" s="1">
-        <v>211016</v>
-      </c>
-      <c r="D21" s="1">
-        <v>10</v>
-      </c>
-      <c r="E21" s="1">
-        <v>10</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C22" s="1">
-        <v>211017</v>
-      </c>
-      <c r="D22" s="1">
-        <v>10</v>
-      </c>
-      <c r="E22" s="1">
-        <v>10</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C23" s="1">
-        <v>211018</v>
-      </c>
-      <c r="D23" s="1">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1">
-        <v>10</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C24" s="1">
-        <v>211019</v>
-      </c>
-      <c r="D24" s="1">
-        <v>10</v>
-      </c>
-      <c r="E24" s="1">
-        <v>10</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="1">
-        <v>211020</v>
-      </c>
-      <c r="D25" s="1">
-        <v>10</v>
-      </c>
-      <c r="E25" s="1">
-        <v>10</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C26" s="1">
-        <v>211021</v>
-      </c>
-      <c r="D26" s="1">
-        <v>10</v>
-      </c>
-      <c r="E26" s="1">
-        <v>10</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C27" s="1">
-        <v>211022</v>
-      </c>
-      <c r="D27" s="1">
-        <v>10</v>
-      </c>
-      <c r="E27" s="1">
-        <v>10</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C28" s="1">
-        <v>211023</v>
-      </c>
-      <c r="D28" s="1">
-        <v>10</v>
-      </c>
-      <c r="E28" s="1">
-        <v>10</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C29" s="1">
-        <v>211024</v>
-      </c>
-      <c r="D29" s="1">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C30" s="1">
-        <v>211025</v>
-      </c>
-      <c r="D30" s="1">
-        <v>10</v>
-      </c>
-      <c r="E30" s="1">
-        <v>10</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C31" s="1">
-        <v>211026</v>
-      </c>
-      <c r="D31" s="1">
-        <v>10</v>
-      </c>
-      <c r="E31" s="1">
-        <v>10</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C32" s="1">
-        <v>211027</v>
-      </c>
-      <c r="D32" s="1">
-        <v>10</v>
-      </c>
-      <c r="E32" s="1">
-        <v>10</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C33" s="1">
-        <v>211028</v>
-      </c>
-      <c r="D33" s="1">
-        <v>10</v>
-      </c>
-      <c r="E33" s="1">
-        <v>10</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C34" s="1">
-        <v>211029</v>
-      </c>
-      <c r="D34" s="1">
-        <v>10</v>
-      </c>
-      <c r="E34" s="1">
-        <v>10</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C35" s="1">
-        <v>211030</v>
-      </c>
-      <c r="D35" s="1">
-        <v>10</v>
-      </c>
-      <c r="E35" s="1">
-        <v>10</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-    </row>
-    <row r="36" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C36" s="1">
-        <v>211031</v>
-      </c>
-      <c r="D36" s="1">
-        <v>10</v>
-      </c>
-      <c r="E36" s="1">
-        <v>10</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C37" s="1">
-        <v>211032</v>
-      </c>
-      <c r="D37" s="1">
-        <v>10</v>
-      </c>
-      <c r="E37" s="1">
-        <v>10</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:20">
-      <c r="A38" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C38" s="1">
-        <v>211033</v>
-      </c>
-      <c r="D38" s="1">
-        <v>10</v>
-      </c>
-      <c r="E38" s="1">
-        <v>10</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:20">
-      <c r="A39" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C39" s="1">
-        <v>211034</v>
-      </c>
-      <c r="D39" s="1">
-        <v>10</v>
-      </c>
-      <c r="E39" s="1">
-        <v>10</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A40" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C40" s="1">
-        <v>211035</v>
-      </c>
-      <c r="D40" s="1">
-        <v>10</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A41" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C41" s="1">
-        <v>211036</v>
-      </c>
-      <c r="D41" s="1">
-        <v>10</v>
-      </c>
-      <c r="E41" s="1">
-        <v>10</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A42" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C42" s="1">
-        <v>211037</v>
-      </c>
-      <c r="D42" s="1">
-        <v>10</v>
-      </c>
-      <c r="E42" s="1">
-        <v>10</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="G42" t="s">
-        <v>426</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:20">
-      <c r="A43" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C43" s="1">
-        <v>211038</v>
-      </c>
-      <c r="D43" s="1">
-        <v>10</v>
-      </c>
-      <c r="E43" s="1">
-        <v>10</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:20">
-      <c r="A44" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C44" s="1">
-        <v>211039</v>
-      </c>
-      <c r="D44" s="1">
-        <v>10</v>
-      </c>
-      <c r="E44" s="1">
-        <v>10</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:20">
-      <c r="A45" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C45" s="1">
-        <v>211040</v>
-      </c>
-      <c r="D45" s="1">
-        <v>10</v>
-      </c>
-      <c r="E45" s="1">
-        <v>10</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:20">
-      <c r="A46" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C46" s="1">
-        <v>211041</v>
-      </c>
-      <c r="D46" s="1">
-        <v>10</v>
-      </c>
-      <c r="E46" s="1">
-        <v>10</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:20">
-      <c r="A47" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C47" s="1">
-        <v>211042</v>
-      </c>
-      <c r="D47" s="1">
-        <v>10</v>
-      </c>
-      <c r="E47" s="1">
-        <v>10</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 M3:T5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -18085,8 +18085,8 @@
       <c r="B16" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C16" s="2">
-        <v>211010</v>
+      <c r="C16" s="1">
+        <v>201010</v>
       </c>
       <c r="D16" s="2">
         <v>10</v>
@@ -18121,8 +18121,8 @@
       <c r="B17" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C17" s="2">
-        <v>211011</v>
+      <c r="C17" s="1">
+        <v>201011</v>
       </c>
       <c r="D17" s="2">
         <v>10</v>
@@ -18155,8 +18155,8 @@
       <c r="B18" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C18" s="2">
-        <v>211012</v>
+      <c r="C18" s="1">
+        <v>201012</v>
       </c>
       <c r="D18" s="2">
         <v>10</v>
@@ -18189,8 +18189,8 @@
       <c r="B19" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C19" s="2">
-        <v>211013</v>
+      <c r="C19" s="1">
+        <v>201013</v>
       </c>
       <c r="D19" s="2">
         <v>10</v>
@@ -18225,8 +18225,8 @@
       <c r="B20" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C20" s="2">
-        <v>211014</v>
+      <c r="C20" s="1">
+        <v>201014</v>
       </c>
       <c r="D20" s="2">
         <v>10</v>
@@ -18259,8 +18259,8 @@
       <c r="B21" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C21" s="2">
-        <v>211015</v>
+      <c r="C21" s="1">
+        <v>201015</v>
       </c>
       <c r="D21" s="2">
         <v>10</v>
@@ -18293,8 +18293,8 @@
       <c r="B22" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C22" s="2">
-        <v>211016</v>
+      <c r="C22" s="1">
+        <v>201016</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -18329,8 +18329,8 @@
       <c r="B23" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C23" s="2">
-        <v>211017</v>
+      <c r="C23" s="1">
+        <v>201017</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -18363,8 +18363,8 @@
       <c r="B24" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="2">
-        <v>211018</v>
+      <c r="C24" s="1">
+        <v>201018</v>
       </c>
       <c r="D24" s="2">
         <v>10</v>
@@ -18411,8 +18411,8 @@
       <c r="B26" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C26" s="2">
-        <v>211004</v>
+      <c r="C26" s="1">
+        <v>201019</v>
       </c>
       <c r="D26" s="2">
         <v>10</v>
@@ -18447,8 +18447,8 @@
       <c r="B27" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C27" s="2">
-        <v>211005</v>
+      <c r="C27" s="1">
+        <v>201020</v>
       </c>
       <c r="D27" s="2">
         <v>10</v>
@@ -18481,8 +18481,8 @@
       <c r="B28" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C28" s="2">
-        <v>211006</v>
+      <c r="C28" s="1">
+        <v>201021</v>
       </c>
       <c r="D28" s="2">
         <v>10</v>
@@ -19238,7 +19238,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 N3:N5 C3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 L3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -18079,12 +18079,8 @@
       <c r="N15" s="7"/>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A16" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="1">
         <v>201010</v>
       </c>
@@ -18103,24 +18099,28 @@
       <c r="H16" s="1">
         <v>3</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="I16" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>380</v>
+      </c>
       <c r="K16" s="2">
         <v>5</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="L16" s="2">
+        <v>7</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
       <c r="N16" s="2" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A17" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="1">
         <v>201011</v>
       </c>
@@ -18139,22 +18139,26 @@
       <c r="H17" s="1">
         <v>9</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="I17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>383</v>
+      </c>
       <c r="K17" s="2">
         <v>5</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="L17" s="2">
+        <v>7</v>
+      </c>
+      <c r="M17" s="2">
+        <v>1</v>
+      </c>
       <c r="N17" s="2"/>
     </row>
     <row r="18" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A18" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="1">
         <v>201012</v>
       </c>
@@ -18173,22 +18177,26 @@
       <c r="H18" s="1">
         <v>10</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="I18" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>380</v>
+      </c>
       <c r="K18" s="2">
         <v>5</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="L18" s="2">
+        <v>7</v>
+      </c>
+      <c r="M18" s="2">
+        <v>1</v>
+      </c>
       <c r="N18" s="2"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A19" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="1">
         <v>201013</v>
       </c>
@@ -18207,24 +18215,28 @@
       <c r="H19" s="1">
         <v>1</v>
       </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="I19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>387</v>
+      </c>
       <c r="K19" s="2">
         <v>4</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="L19" s="2">
+        <v>7</v>
+      </c>
+      <c r="M19" s="2">
+        <v>1</v>
+      </c>
       <c r="N19" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A20" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="1">
         <v>201014</v>
       </c>
@@ -18243,22 +18255,26 @@
       <c r="H20" s="1">
         <v>3</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="I20" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>390</v>
+      </c>
       <c r="K20" s="2">
         <v>4</v>
       </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+      <c r="L20" s="2">
+        <v>7</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1</v>
+      </c>
       <c r="N20" s="2"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A21" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
       <c r="C21" s="1">
         <v>201015</v>
       </c>
@@ -18277,22 +18293,26 @@
       <c r="H21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="I21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>390</v>
+      </c>
       <c r="K21" s="2">
         <v>4</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="L21" s="2">
+        <v>7</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1</v>
+      </c>
       <c r="N21" s="2"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A22" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="1">
         <v>201016</v>
       </c>
@@ -18311,24 +18331,28 @@
       <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="I22" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>394</v>
+      </c>
       <c r="K22" s="2">
         <v>7</v>
       </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
+      <c r="L22" s="2">
+        <v>7</v>
+      </c>
+      <c r="M22" s="2">
+        <v>1</v>
+      </c>
       <c r="N22" s="2" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A23" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
       <c r="C23" s="1">
         <v>201017</v>
       </c>
@@ -18347,22 +18371,26 @@
       <c r="H23" s="1">
         <v>3</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="I23" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>397</v>
+      </c>
       <c r="K23" s="2">
         <v>7</v>
       </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="L23" s="2">
+        <v>7</v>
+      </c>
+      <c r="M23" s="2">
+        <v>1</v>
+      </c>
       <c r="N23" s="2"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A24" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>373</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="1">
         <v>201018</v>
       </c>
@@ -18381,13 +18409,21 @@
       <c r="H24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="I24" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>394</v>
+      </c>
       <c r="K24" s="2">
         <v>7</v>
       </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
+      <c r="L24" s="2">
+        <v>7</v>
+      </c>
+      <c r="M24" s="2">
+        <v>1</v>
+      </c>
       <c r="N24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="445">
   <si>
     <t>_id</t>
   </si>
@@ -1517,7 +1517,7 @@
     <t>治愈之甲</t>
   </si>
   <si>
-    <t>财富之袍</t>
+    <t>财富扳指</t>
   </si>
   <si>
     <t>20000,60</t>
@@ -1526,7 +1526,7 @@
     <t>金币加成增加20%</t>
   </si>
   <si>
-    <t>财富之链</t>
+    <t>财富项链</t>
   </si>
   <si>
     <t>2000,30</t>
@@ -1535,10 +1535,10 @@
     <t>杀敌金币，杀敌金币，杀敌金币，</t>
   </si>
   <si>
-    <t>财富之带</t>
-  </si>
-  <si>
-    <t>修炼之袍</t>
+    <t>财富玉带</t>
+  </si>
+  <si>
+    <t>杀戮血剑</t>
   </si>
   <si>
     <t>10000,40</t>
@@ -1547,13 +1547,13 @@
     <t>经验加成增加20%</t>
   </si>
   <si>
-    <t>修炼之面</t>
+    <t>杀戮面罩</t>
   </si>
   <si>
     <t>100000,80</t>
   </si>
   <si>
-    <t>修炼之靴</t>
+    <t>杀戮战靴</t>
   </si>
   <si>
     <t>神速之链</t>
@@ -1864,12 +1864,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8007,7 +8007,7 @@
     <row r="107" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3 S3 R4 S4 R5 S5 C3:H5 K3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -13552,7 +13552,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3 S3 R4 S4 R5 S5 C3:H5 K3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -18771,7 +18771,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3 S3 R4 S4 R5 S5 C3:H5 K3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -19123,11 +19123,11 @@
       <c r="F9" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="G9" s="2">
-        <v>2</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2</v>
+      <c r="G9" s="1">
+        <v>7</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>37</v>
@@ -19260,13 +19260,13 @@
         <v>395</v>
       </c>
       <c r="G12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>31</v>
+        <v>381</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>396</v>
@@ -19356,7 +19356,7 @@
         <v>10</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>381</v>
+        <v>31</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>396</v>
@@ -20800,7 +20800,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3 P3 O4 P4 O5 P5 C3:H5 L3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 L3:P5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="448">
   <si>
     <t>_id</t>
   </si>
@@ -1556,16 +1556,25 @@
     <t>杀戮战靴</t>
   </si>
   <si>
-    <t>神速之链</t>
+    <t>狂风影刃</t>
+  </si>
+  <si>
+    <t>20000,80</t>
   </si>
   <si>
     <t>攻速增加10%，冷却增加10%</t>
   </si>
   <si>
-    <t>神速之带</t>
-  </si>
-  <si>
-    <t>神速之靴</t>
+    <t>狂风项链</t>
+  </si>
+  <si>
+    <t>10000,80</t>
+  </si>
+  <si>
+    <t>狂风戒指</t>
+  </si>
+  <si>
+    <t>200000,120</t>
   </si>
   <si>
     <t>重击之刃</t>
@@ -1864,12 +1873,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -19412,16 +19421,16 @@
         <v>401</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>381</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="K16" s="2">
         <v>5</v>
@@ -19433,7 +19442,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -19455,19 +19464,19 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G17" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H17" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="K17" s="2">
         <v>5</v>
@@ -19499,19 +19508,19 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G18" s="1">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="K18" s="2">
         <v>5</v>
@@ -19543,7 +19552,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -19567,7 +19576,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -19589,7 +19598,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
@@ -19633,7 +19642,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G21" s="1">
         <v>7</v>
@@ -19677,7 +19686,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -19701,7 +19710,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -19723,7 +19732,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G23" s="1">
         <v>3</v>
@@ -19767,7 +19776,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G24" s="1">
         <v>7</v>
@@ -19831,7 +19840,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -19847,7 +19856,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -19873,7 +19882,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -19913,7 +19922,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -19953,7 +19962,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -19969,7 +19978,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -19995,7 +20004,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -20035,7 +20044,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -20075,7 +20084,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -20091,7 +20100,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -20117,7 +20126,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -20157,7 +20166,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -20197,7 +20206,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -20213,7 +20222,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -20239,7 +20248,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -20279,7 +20288,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -20319,7 +20328,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -20335,7 +20344,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -20361,7 +20370,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -20401,7 +20410,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -20441,7 +20450,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -20457,7 +20466,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -20483,7 +20492,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -20523,7 +20532,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -20563,7 +20572,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -20579,7 +20588,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -20605,7 +20614,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -20645,7 +20654,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -20685,7 +20694,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -20701,7 +20710,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -20727,7 +20736,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -20767,7 +20776,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -5879,7 +5879,7 @@
         <v>48</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K64" s="1">
         <v>900</v>
@@ -5932,7 +5932,7 @@
         <v>31</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K65" s="1">
         <v>900</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="454">
   <si>
     <t>_id</t>
   </si>
@@ -839,354 +839,372 @@
     <t>钻石战刃</t>
   </si>
   <si>
+    <t>20000,25</t>
+  </si>
+  <si>
+    <t>6000,3000</t>
+  </si>
+  <si>
+    <t>钻石战甲</t>
+  </si>
+  <si>
+    <t>钻石战链</t>
+  </si>
+  <si>
+    <t>10000,15</t>
+  </si>
+  <si>
+    <t>3000,1500</t>
+  </si>
+  <si>
+    <t>钻石战盔</t>
+  </si>
+  <si>
+    <t>200000,20</t>
+  </si>
+  <si>
+    <t>3000,30000</t>
+  </si>
+  <si>
+    <t>钻石战镯</t>
+  </si>
+  <si>
+    <t>钻石战戒</t>
+  </si>
+  <si>
+    <t>钻石战带</t>
+  </si>
+  <si>
+    <t>钻石战靴</t>
+  </si>
+  <si>
+    <t>钻石法刃</t>
+  </si>
+  <si>
+    <t>钻石法甲</t>
+  </si>
+  <si>
+    <t>钻石法链</t>
+  </si>
+  <si>
+    <t>钻石法盔</t>
+  </si>
+  <si>
+    <t>钻石法镯</t>
+  </si>
+  <si>
+    <t>钻石法戒</t>
+  </si>
+  <si>
+    <t>钻石法带</t>
+  </si>
+  <si>
+    <t>钻石法靴</t>
+  </si>
+  <si>
+    <t>钻石道刃</t>
+  </si>
+  <si>
+    <t>钻石道甲</t>
+  </si>
+  <si>
+    <t>钻石道链</t>
+  </si>
+  <si>
+    <t>钻石道盔</t>
+  </si>
+  <si>
+    <t>钻石道镯</t>
+  </si>
+  <si>
+    <t>钻石道戒</t>
+  </si>
+  <si>
+    <t>钻石道带</t>
+  </si>
+  <si>
+    <t>钻石道靴</t>
+  </si>
+  <si>
+    <t>金龙战刃</t>
+  </si>
+  <si>
     <t>20,5</t>
   </si>
   <si>
-    <t>钻石战甲</t>
+    <t>金龙战甲</t>
   </si>
   <si>
     <t>10,2</t>
   </si>
   <si>
-    <t>钻石战链</t>
-  </si>
-  <si>
-    <t>钻石战盔</t>
+    <t>金龙战链</t>
+  </si>
+  <si>
+    <t>20,20</t>
+  </si>
+  <si>
+    <t>金龙战盔</t>
   </si>
   <si>
     <t>100,10</t>
   </si>
   <si>
+    <t>20,400</t>
+  </si>
+  <si>
+    <t>金龙战镯</t>
+  </si>
+  <si>
+    <t>20,2</t>
+  </si>
+  <si>
+    <t>金龙战戒</t>
+  </si>
+  <si>
+    <t>金龙战带</t>
+  </si>
+  <si>
+    <t>金龙战靴</t>
+  </si>
+  <si>
+    <t>金龙法刃</t>
+  </si>
+  <si>
+    <t>金龙法甲</t>
+  </si>
+  <si>
+    <t>金龙法链</t>
+  </si>
+  <si>
+    <t>金龙法盔</t>
+  </si>
+  <si>
+    <t>金龙法镯</t>
+  </si>
+  <si>
+    <t>金龙法戒</t>
+  </si>
+  <si>
+    <t>金龙法带</t>
+  </si>
+  <si>
+    <t>金龙法靴</t>
+  </si>
+  <si>
+    <t>金龙道刃</t>
+  </si>
+  <si>
+    <t>金龙道甲</t>
+  </si>
+  <si>
+    <t>金龙道链</t>
+  </si>
+  <si>
+    <t>金龙道盔</t>
+  </si>
+  <si>
+    <t>金龙道镯</t>
+  </si>
+  <si>
+    <t>金龙道戒</t>
+  </si>
+  <si>
+    <t>金龙道带</t>
+  </si>
+  <si>
+    <t>金龙道靴</t>
+  </si>
+  <si>
+    <t>木龙战刃</t>
+  </si>
+  <si>
+    <t>60,30</t>
+  </si>
+  <si>
+    <t>木龙战甲</t>
+  </si>
+  <si>
+    <t>60,35</t>
+  </si>
+  <si>
+    <t>木龙战链</t>
+  </si>
+  <si>
+    <t>30,35</t>
+  </si>
+  <si>
+    <t>木龙战盔</t>
+  </si>
+  <si>
+    <t>30,600</t>
+  </si>
+  <si>
+    <t>木龙战镯</t>
+  </si>
+  <si>
+    <t>30,3</t>
+  </si>
+  <si>
+    <t>木龙战戒</t>
+  </si>
+  <si>
+    <t>木龙战带</t>
+  </si>
+  <si>
+    <t>木龙战靴</t>
+  </si>
+  <si>
+    <t>木龙法刃</t>
+  </si>
+  <si>
+    <t>木龙法甲</t>
+  </si>
+  <si>
+    <t>木龙法链</t>
+  </si>
+  <si>
+    <t>木龙法盔</t>
+  </si>
+  <si>
+    <t>木龙法镯</t>
+  </si>
+  <si>
+    <t>木龙法戒</t>
+  </si>
+  <si>
+    <t>木龙法带</t>
+  </si>
+  <si>
+    <t>木龙法靴</t>
+  </si>
+  <si>
+    <t>木龙道刃</t>
+  </si>
+  <si>
+    <t>木龙道甲</t>
+  </si>
+  <si>
+    <t>木龙道链</t>
+  </si>
+  <si>
+    <t>木龙道盔</t>
+  </si>
+  <si>
+    <t>木龙道镯</t>
+  </si>
+  <si>
+    <t>木龙道戒</t>
+  </si>
+  <si>
+    <t>木龙道带</t>
+  </si>
+  <si>
+    <t>木龙道靴</t>
+  </si>
+  <si>
+    <t>土龙战刃</t>
+  </si>
+  <si>
+    <t>土龙战甲</t>
+  </si>
+  <si>
+    <t>80,20</t>
+  </si>
+  <si>
+    <t>土龙战链</t>
+  </si>
+  <si>
+    <t>土龙战盔</t>
+  </si>
+  <si>
+    <t>40,800</t>
+  </si>
+  <si>
+    <t>土龙战镯</t>
+  </si>
+  <si>
+    <t>40,4</t>
+  </si>
+  <si>
+    <t>土龙战戒</t>
+  </si>
+  <si>
+    <t>土龙战带</t>
+  </si>
+  <si>
+    <t>土龙战靴</t>
+  </si>
+  <si>
+    <t>土龙法刃</t>
+  </si>
+  <si>
+    <t>土龙法甲</t>
+  </si>
+  <si>
+    <t>土龙法链</t>
+  </si>
+  <si>
+    <t>土龙法盔</t>
+  </si>
+  <si>
+    <t>土龙法镯</t>
+  </si>
+  <si>
+    <t>土龙法戒</t>
+  </si>
+  <si>
+    <t>土龙法带</t>
+  </si>
+  <si>
+    <t>土龙法靴</t>
+  </si>
+  <si>
+    <t>土龙道刃</t>
+  </si>
+  <si>
+    <t>土龙道甲</t>
+  </si>
+  <si>
+    <t>土龙道链</t>
+  </si>
+  <si>
+    <t>土龙道盔</t>
+  </si>
+  <si>
+    <t>土龙道镯</t>
+  </si>
+  <si>
+    <t>土龙道戒</t>
+  </si>
+  <si>
+    <t>土龙道带</t>
+  </si>
+  <si>
+    <t>土龙道靴</t>
+  </si>
+  <si>
+    <t>冰龙战刃</t>
+  </si>
+  <si>
+    <t>冰龙战甲</t>
+  </si>
+  <si>
+    <t>冰龙战链</t>
+  </si>
+  <si>
+    <t>冰龙战盔</t>
+  </si>
+  <si>
     <t>10,200</t>
   </si>
   <si>
-    <t>钻石战镯</t>
+    <t>冰龙战镯</t>
   </si>
   <si>
     <t>10,1</t>
   </si>
   <si>
-    <t>钻石战戒</t>
-  </si>
-  <si>
-    <t>钻石战带</t>
-  </si>
-  <si>
-    <t>钻石战靴</t>
-  </si>
-  <si>
-    <t>钻石法刃</t>
-  </si>
-  <si>
-    <t>钻石法甲</t>
-  </si>
-  <si>
-    <t>钻石法链</t>
-  </si>
-  <si>
-    <t>钻石法盔</t>
-  </si>
-  <si>
-    <t>钻石法镯</t>
-  </si>
-  <si>
-    <t>钻石法戒</t>
-  </si>
-  <si>
-    <t>钻石法带</t>
-  </si>
-  <si>
-    <t>钻石法靴</t>
-  </si>
-  <si>
-    <t>钻石道刃</t>
-  </si>
-  <si>
-    <t>钻石道甲</t>
-  </si>
-  <si>
-    <t>钻石道链</t>
-  </si>
-  <si>
-    <t>钻石道盔</t>
-  </si>
-  <si>
-    <t>钻石道镯</t>
-  </si>
-  <si>
-    <t>钻石道戒</t>
-  </si>
-  <si>
-    <t>钻石道带</t>
-  </si>
-  <si>
-    <t>钻石道靴</t>
-  </si>
-  <si>
-    <t>金龙战刃</t>
-  </si>
-  <si>
-    <t>金龙战甲</t>
-  </si>
-  <si>
-    <t>金龙战链</t>
-  </si>
-  <si>
-    <t>20,20</t>
-  </si>
-  <si>
-    <t>金龙战盔</t>
-  </si>
-  <si>
-    <t>20,400</t>
-  </si>
-  <si>
-    <t>金龙战镯</t>
-  </si>
-  <si>
-    <t>20,2</t>
-  </si>
-  <si>
-    <t>金龙战戒</t>
-  </si>
-  <si>
-    <t>金龙战带</t>
-  </si>
-  <si>
-    <t>金龙战靴</t>
-  </si>
-  <si>
-    <t>金龙法刃</t>
-  </si>
-  <si>
-    <t>金龙法甲</t>
-  </si>
-  <si>
-    <t>金龙法链</t>
-  </si>
-  <si>
-    <t>金龙法盔</t>
-  </si>
-  <si>
-    <t>金龙法镯</t>
-  </si>
-  <si>
-    <t>金龙法戒</t>
-  </si>
-  <si>
-    <t>金龙法带</t>
-  </si>
-  <si>
-    <t>金龙法靴</t>
-  </si>
-  <si>
-    <t>金龙道刃</t>
-  </si>
-  <si>
-    <t>金龙道甲</t>
-  </si>
-  <si>
-    <t>金龙道链</t>
-  </si>
-  <si>
-    <t>金龙道盔</t>
-  </si>
-  <si>
-    <t>金龙道镯</t>
-  </si>
-  <si>
-    <t>金龙道戒</t>
-  </si>
-  <si>
-    <t>金龙道带</t>
-  </si>
-  <si>
-    <t>金龙道靴</t>
-  </si>
-  <si>
-    <t>木龙战刃</t>
-  </si>
-  <si>
-    <t>60,30</t>
-  </si>
-  <si>
-    <t>木龙战甲</t>
-  </si>
-  <si>
-    <t>60,35</t>
-  </si>
-  <si>
-    <t>木龙战链</t>
-  </si>
-  <si>
-    <t>30,35</t>
-  </si>
-  <si>
-    <t>木龙战盔</t>
-  </si>
-  <si>
-    <t>30,600</t>
-  </si>
-  <si>
-    <t>木龙战镯</t>
-  </si>
-  <si>
-    <t>30,3</t>
-  </si>
-  <si>
-    <t>木龙战戒</t>
-  </si>
-  <si>
-    <t>木龙战带</t>
-  </si>
-  <si>
-    <t>木龙战靴</t>
-  </si>
-  <si>
-    <t>木龙法刃</t>
-  </si>
-  <si>
-    <t>木龙法甲</t>
-  </si>
-  <si>
-    <t>木龙法链</t>
-  </si>
-  <si>
-    <t>木龙法盔</t>
-  </si>
-  <si>
-    <t>木龙法镯</t>
-  </si>
-  <si>
-    <t>木龙法戒</t>
-  </si>
-  <si>
-    <t>木龙法带</t>
-  </si>
-  <si>
-    <t>木龙法靴</t>
-  </si>
-  <si>
-    <t>木龙道刃</t>
-  </si>
-  <si>
-    <t>木龙道甲</t>
-  </si>
-  <si>
-    <t>木龙道链</t>
-  </si>
-  <si>
-    <t>木龙道盔</t>
-  </si>
-  <si>
-    <t>木龙道镯</t>
-  </si>
-  <si>
-    <t>木龙道戒</t>
-  </si>
-  <si>
-    <t>木龙道带</t>
-  </si>
-  <si>
-    <t>木龙道靴</t>
-  </si>
-  <si>
-    <t>土龙战刃</t>
-  </si>
-  <si>
-    <t>土龙战甲</t>
-  </si>
-  <si>
-    <t>80,20</t>
-  </si>
-  <si>
-    <t>土龙战链</t>
-  </si>
-  <si>
-    <t>土龙战盔</t>
-  </si>
-  <si>
-    <t>40,800</t>
-  </si>
-  <si>
-    <t>土龙战镯</t>
-  </si>
-  <si>
-    <t>40,4</t>
-  </si>
-  <si>
-    <t>土龙战戒</t>
-  </si>
-  <si>
-    <t>土龙战带</t>
-  </si>
-  <si>
-    <t>土龙战靴</t>
-  </si>
-  <si>
-    <t>土龙法刃</t>
-  </si>
-  <si>
-    <t>土龙法甲</t>
-  </si>
-  <si>
-    <t>土龙法链</t>
-  </si>
-  <si>
-    <t>土龙法盔</t>
-  </si>
-  <si>
-    <t>土龙法镯</t>
-  </si>
-  <si>
-    <t>土龙法戒</t>
-  </si>
-  <si>
-    <t>土龙法带</t>
-  </si>
-  <si>
-    <t>土龙法靴</t>
-  </si>
-  <si>
-    <t>土龙道刃</t>
-  </si>
-  <si>
-    <t>土龙道甲</t>
-  </si>
-  <si>
-    <t>土龙道链</t>
-  </si>
-  <si>
-    <t>土龙道盔</t>
-  </si>
-  <si>
-    <t>土龙道镯</t>
-  </si>
-  <si>
-    <t>土龙道戒</t>
-  </si>
-  <si>
-    <t>土龙道带</t>
-  </si>
-  <si>
-    <t>土龙道靴</t>
-  </si>
-  <si>
-    <t>冰龙战刃</t>
-  </si>
-  <si>
-    <t>冰龙战甲</t>
-  </si>
-  <si>
-    <t>冰龙战链</t>
-  </si>
-  <si>
-    <t>冰龙战盔</t>
-  </si>
-  <si>
-    <t>冰龙战镯</t>
-  </si>
-  <si>
     <t>冰龙战戒</t>
   </si>
   <si>
@@ -1556,7 +1574,7 @@
     <t>杀戮战靴</t>
   </si>
   <si>
-    <t>狂风影刃</t>
+    <t>狂风面具</t>
   </si>
   <si>
     <t>20000,80</t>
@@ -1577,28 +1595,28 @@
     <t>200000,120</t>
   </si>
   <si>
-    <t>重击之刃</t>
+    <t>重击巨剑</t>
   </si>
   <si>
     <t>此次攻击概率翻倍</t>
   </si>
   <si>
-    <t>重击之链</t>
-  </si>
-  <si>
-    <t>重击之戒</t>
-  </si>
-  <si>
-    <t>暴击之剑</t>
+    <t>重击护腕</t>
+  </si>
+  <si>
+    <t>重击腰带</t>
+  </si>
+  <si>
+    <t>暴击扳指</t>
   </si>
   <si>
     <t>如果此次攻击暴击了，伤害额外翻倍</t>
   </si>
   <si>
-    <t>暴击之链</t>
-  </si>
-  <si>
-    <t>暴击之戒</t>
+    <t>暴击板甲</t>
+  </si>
+  <si>
+    <t>暴击铁履</t>
   </si>
   <si>
     <t>天命之剑</t>
@@ -8253,7 +8271,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="R6" s="1">
         <v>10</v>
@@ -8273,7 +8291,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -8285,7 +8303,7 @@
         <v>31</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -8307,7 +8325,7 @@
         <v>32</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R7" s="1">
         <v>10</v>
@@ -8339,7 +8357,7 @@
         <v>26</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -8361,7 +8379,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="R8" s="1">
         <v>5</v>
@@ -8381,7 +8399,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -8393,7 +8411,7 @@
         <v>37</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -8415,7 +8433,7 @@
         <v>39</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R9" s="1">
         <v>5</v>
@@ -8435,7 +8453,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -8447,7 +8465,7 @@
         <v>37</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -8489,7 +8507,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -8501,7 +8519,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -8523,7 +8541,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="R11" s="1">
         <v>5</v>
@@ -8543,7 +8561,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -8555,7 +8573,7 @@
         <v>31</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -8577,7 +8595,7 @@
         <v>39</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R12" s="1">
         <v>5</v>
@@ -8597,7 +8615,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -8609,7 +8627,7 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -8628,10 +8646,10 @@
         <v>5</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R13" s="1">
         <v>5</v>
@@ -8651,7 +8669,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -8685,7 +8703,7 @@
         <v>49</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="R14" s="1">
         <v>10</v>
@@ -8705,7 +8723,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -8717,7 +8735,7 @@
         <v>31</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -8739,7 +8757,7 @@
         <v>51</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R15" s="1">
         <v>10</v>
@@ -8759,7 +8777,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -8771,7 +8789,7 @@
         <v>48</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -8793,7 +8811,7 @@
         <v>49</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="R16" s="1">
         <v>5</v>
@@ -8813,7 +8831,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -8825,7 +8843,7 @@
         <v>37</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -8847,7 +8865,7 @@
         <v>54</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R17" s="1">
         <v>5</v>
@@ -8867,7 +8885,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -8879,7 +8897,7 @@
         <v>37</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -8921,7 +8939,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -8933,7 +8951,7 @@
         <v>48</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -8955,7 +8973,7 @@
         <v>49</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="R19" s="1">
         <v>5</v>
@@ -8975,7 +8993,7 @@
         <v>40</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -8987,7 +9005,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -9009,7 +9027,7 @@
         <v>54</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R20" s="1">
         <v>5</v>
@@ -9029,7 +9047,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -9041,7 +9059,7 @@
         <v>48</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -9060,10 +9078,10 @@
         <v>5</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R21" s="1">
         <v>5</v>
@@ -9083,7 +9101,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -9117,7 +9135,7 @@
         <v>61</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="R22" s="1">
         <v>10</v>
@@ -9137,7 +9155,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -9149,7 +9167,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -9171,7 +9189,7 @@
         <v>63</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R23" s="1">
         <v>10</v>
@@ -9191,7 +9209,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -9203,7 +9221,7 @@
         <v>60</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -9225,7 +9243,7 @@
         <v>61</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="R24" s="1">
         <v>5</v>
@@ -9245,7 +9263,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -9257,7 +9275,7 @@
         <v>37</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -9279,7 +9297,7 @@
         <v>66</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R25" s="1">
         <v>5</v>
@@ -9299,7 +9317,7 @@
         <v>40</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -9311,7 +9329,7 @@
         <v>37</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -9353,7 +9371,7 @@
         <v>40</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -9365,7 +9383,7 @@
         <v>60</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -9387,7 +9405,7 @@
         <v>61</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="R27" s="1">
         <v>5</v>
@@ -9407,7 +9425,7 @@
         <v>40</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -9419,7 +9437,7 @@
         <v>31</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -9441,7 +9459,7 @@
         <v>66</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R28" s="1">
         <v>5</v>
@@ -9461,7 +9479,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -9473,7 +9491,7 @@
         <v>60</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -9492,10 +9510,10 @@
         <v>5</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R29" s="1">
         <v>5</v>
@@ -9515,7 +9533,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -9527,7 +9545,7 @@
         <v>26</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -9569,7 +9587,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -9581,7 +9599,7 @@
         <v>31</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -9623,7 +9641,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -9635,7 +9653,7 @@
         <v>26</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -9657,7 +9675,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R33" s="1">
         <v>7</v>
@@ -9677,7 +9695,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -9689,7 +9707,7 @@
         <v>37</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -9711,7 +9729,7 @@
         <v>39</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R34" s="1">
         <v>7</v>
@@ -9731,7 +9749,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -9743,7 +9761,7 @@
         <v>37</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -9765,7 +9783,7 @@
         <v>32</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R35" s="1">
         <v>7</v>
@@ -9785,7 +9803,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -9797,7 +9815,7 @@
         <v>26</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -9819,7 +9837,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R36" s="1">
         <v>7</v>
@@ -9839,7 +9857,7 @@
         <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -9873,7 +9891,7 @@
         <v>39</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R37" s="1">
         <v>7</v>
@@ -9893,7 +9911,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -9905,7 +9923,7 @@
         <v>26</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -9927,7 +9945,7 @@
         <v>39</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R38" s="1">
         <v>7</v>
@@ -9947,7 +9965,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -9959,7 +9977,7 @@
         <v>48</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -10001,7 +10019,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -10013,7 +10031,7 @@
         <v>31</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -10055,7 +10073,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -10067,7 +10085,7 @@
         <v>48</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -10089,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R41" s="1">
         <v>7</v>
@@ -10109,7 +10127,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -10121,7 +10139,7 @@
         <v>37</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -10143,7 +10161,7 @@
         <v>54</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R42" s="1">
         <v>7</v>
@@ -10163,7 +10181,7 @@
         <v>50</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -10175,7 +10193,7 @@
         <v>37</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -10197,7 +10215,7 @@
         <v>51</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R43" s="1">
         <v>7</v>
@@ -10217,7 +10235,7 @@
         <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -10229,7 +10247,7 @@
         <v>48</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -10251,7 +10269,7 @@
         <v>49</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R44" s="1">
         <v>7</v>
@@ -10271,7 +10289,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -10305,7 +10323,7 @@
         <v>54</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R45" s="1">
         <v>7</v>
@@ -10325,7 +10343,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -10337,7 +10355,7 @@
         <v>48</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -10359,7 +10377,7 @@
         <v>54</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R46" s="1">
         <v>7</v>
@@ -10379,7 +10397,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -10391,7 +10409,7 @@
         <v>60</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -10433,7 +10451,7 @@
         <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -10445,7 +10463,7 @@
         <v>31</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -10487,7 +10505,7 @@
         <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -10499,7 +10517,7 @@
         <v>60</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -10521,7 +10539,7 @@
         <v>61</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R49" s="1">
         <v>7</v>
@@ -10541,7 +10559,7 @@
         <v>50</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -10553,7 +10571,7 @@
         <v>37</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -10575,7 +10593,7 @@
         <v>66</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R50" s="1">
         <v>7</v>
@@ -10595,7 +10613,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -10607,7 +10625,7 @@
         <v>37</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -10629,7 +10647,7 @@
         <v>63</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R51" s="1">
         <v>7</v>
@@ -10649,7 +10667,7 @@
         <v>50</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -10661,7 +10679,7 @@
         <v>60</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -10683,7 +10701,7 @@
         <v>61</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="R52" s="1">
         <v>7</v>
@@ -10703,7 +10721,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -10737,7 +10755,7 @@
         <v>66</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R53" s="1">
         <v>7</v>
@@ -10757,7 +10775,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -10769,7 +10787,7 @@
         <v>60</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -10791,7 +10809,7 @@
         <v>66</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R54" s="1">
         <v>7</v>
@@ -10830,7 +10848,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -10842,7 +10860,7 @@
         <v>26</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -10864,7 +10882,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R56" s="1">
         <v>20</v>
@@ -10884,7 +10902,7 @@
         <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -10896,7 +10914,7 @@
         <v>31</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -10918,7 +10936,7 @@
         <v>32</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="R57" s="1">
         <v>20</v>
@@ -10938,7 +10956,7 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -10950,7 +10968,7 @@
         <v>26</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -10972,7 +10990,7 @@
         <v>28</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R58" s="1">
         <v>10</v>
@@ -10992,7 +11010,7 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -11004,7 +11022,7 @@
         <v>37</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -11026,7 +11044,7 @@
         <v>39</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R59" s="1">
         <v>10</v>
@@ -11046,7 +11064,7 @@
         <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -11058,7 +11076,7 @@
         <v>37</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -11080,7 +11098,7 @@
         <v>32</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="R60" s="1">
         <v>10</v>
@@ -11100,7 +11118,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -11112,7 +11130,7 @@
         <v>26</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -11134,7 +11152,7 @@
         <v>28</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R61" s="1">
         <v>10</v>
@@ -11154,7 +11172,7 @@
         <v>60</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -11188,7 +11206,7 @@
         <v>39</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R62" s="1">
         <v>10</v>
@@ -11208,7 +11226,7 @@
         <v>60</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -11220,7 +11238,7 @@
         <v>26</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -11242,7 +11260,7 @@
         <v>39</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R63" s="1">
         <v>10</v>
@@ -11262,7 +11280,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -11274,7 +11292,7 @@
         <v>48</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -11296,7 +11314,7 @@
         <v>49</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R64" s="1">
         <v>20</v>
@@ -11316,7 +11334,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -11328,7 +11346,7 @@
         <v>31</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -11350,7 +11368,7 @@
         <v>51</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="R65" s="1">
         <v>20</v>
@@ -11370,7 +11388,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -11382,7 +11400,7 @@
         <v>48</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -11404,7 +11422,7 @@
         <v>49</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R66" s="1">
         <v>10</v>
@@ -11424,7 +11442,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -11436,7 +11454,7 @@
         <v>37</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -11458,7 +11476,7 @@
         <v>54</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R67" s="1">
         <v>10</v>
@@ -11478,7 +11496,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -11490,7 +11508,7 @@
         <v>37</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -11512,7 +11530,7 @@
         <v>51</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="R68" s="1">
         <v>10</v>
@@ -11532,7 +11550,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -11544,7 +11562,7 @@
         <v>48</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -11566,7 +11584,7 @@
         <v>49</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R69" s="1">
         <v>10</v>
@@ -11586,7 +11604,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -11620,7 +11638,7 @@
         <v>54</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R70" s="1">
         <v>10</v>
@@ -11640,7 +11658,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -11652,7 +11670,7 @@
         <v>48</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -11674,7 +11692,7 @@
         <v>54</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R71" s="1">
         <v>10</v>
@@ -11694,7 +11712,7 @@
         <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -11706,7 +11724,7 @@
         <v>60</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -11728,7 +11746,7 @@
         <v>61</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R72" s="1">
         <v>20</v>
@@ -11748,7 +11766,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -11760,7 +11778,7 @@
         <v>31</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -11782,7 +11800,7 @@
         <v>63</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="R73" s="1">
         <v>20</v>
@@ -11802,7 +11820,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -11814,7 +11832,7 @@
         <v>60</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -11836,7 +11854,7 @@
         <v>61</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R74" s="1">
         <v>10</v>
@@ -11856,7 +11874,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -11868,7 +11886,7 @@
         <v>37</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -11890,7 +11908,7 @@
         <v>66</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R75" s="1">
         <v>10</v>
@@ -11910,7 +11928,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -11922,7 +11940,7 @@
         <v>37</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -11944,7 +11962,7 @@
         <v>63</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="R76" s="1">
         <v>10</v>
@@ -11964,7 +11982,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -11976,7 +11994,7 @@
         <v>60</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -11998,7 +12016,7 @@
         <v>61</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="R77" s="1">
         <v>10</v>
@@ -12018,7 +12036,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -12052,7 +12070,7 @@
         <v>66</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R78" s="1">
         <v>10</v>
@@ -12072,7 +12090,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -12084,7 +12102,7 @@
         <v>60</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -12106,7 +12124,7 @@
         <v>66</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="R79" s="1">
         <v>10</v>
@@ -12143,7 +12161,7 @@
         <v>70</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -12155,7 +12173,7 @@
         <v>26</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -12197,7 +12215,7 @@
         <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -12209,7 +12227,7 @@
         <v>31</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -12231,7 +12249,7 @@
         <v>32</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="R82" s="1">
         <v>30</v>
@@ -12251,7 +12269,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -12263,7 +12281,7 @@
         <v>26</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -12305,7 +12323,7 @@
         <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -12317,7 +12335,7 @@
         <v>37</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -12339,7 +12357,7 @@
         <v>39</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R84" s="1">
         <v>15</v>
@@ -12359,7 +12377,7 @@
         <v>70</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -12371,7 +12389,7 @@
         <v>37</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -12393,7 +12411,7 @@
         <v>32</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="R85" s="1">
         <v>15</v>
@@ -12413,7 +12431,7 @@
         <v>70</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -12425,7 +12443,7 @@
         <v>26</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -12467,7 +12485,7 @@
         <v>70</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -12501,7 +12519,7 @@
         <v>39</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R87" s="1">
         <v>15</v>
@@ -12521,7 +12539,7 @@
         <v>70</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -12533,7 +12551,7 @@
         <v>26</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -12555,7 +12573,7 @@
         <v>39</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R88" s="1">
         <v>15</v>
@@ -12575,7 +12593,7 @@
         <v>70</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -12587,7 +12605,7 @@
         <v>48</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -12629,7 +12647,7 @@
         <v>70</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -12641,7 +12659,7 @@
         <v>31</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -12663,7 +12681,7 @@
         <v>51</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="R90" s="1">
         <v>30</v>
@@ -12683,7 +12701,7 @@
         <v>70</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -12695,7 +12713,7 @@
         <v>48</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -12737,7 +12755,7 @@
         <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -12749,7 +12767,7 @@
         <v>37</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -12771,7 +12789,7 @@
         <v>54</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R92" s="1">
         <v>15</v>
@@ -12791,7 +12809,7 @@
         <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -12803,7 +12821,7 @@
         <v>37</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -12825,7 +12843,7 @@
         <v>51</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="R93" s="1">
         <v>15</v>
@@ -12845,7 +12863,7 @@
         <v>70</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -12857,7 +12875,7 @@
         <v>48</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -12899,7 +12917,7 @@
         <v>70</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -12933,7 +12951,7 @@
         <v>54</v>
       </c>
       <c r="Q95" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R95" s="1">
         <v>15</v>
@@ -12953,7 +12971,7 @@
         <v>70</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -12965,7 +12983,7 @@
         <v>48</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -12987,7 +13005,7 @@
         <v>54</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R96" s="1">
         <v>15</v>
@@ -13007,7 +13025,7 @@
         <v>70</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -13019,7 +13037,7 @@
         <v>60</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -13061,7 +13079,7 @@
         <v>70</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -13073,7 +13091,7 @@
         <v>31</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -13095,7 +13113,7 @@
         <v>63</v>
       </c>
       <c r="Q98" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="R98" s="1">
         <v>30</v>
@@ -13115,7 +13133,7 @@
         <v>70</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -13127,7 +13145,7 @@
         <v>60</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -13169,7 +13187,7 @@
         <v>70</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -13181,7 +13199,7 @@
         <v>37</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -13203,7 +13221,7 @@
         <v>66</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R100" s="1">
         <v>15</v>
@@ -13223,7 +13241,7 @@
         <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -13235,7 +13253,7 @@
         <v>37</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -13257,7 +13275,7 @@
         <v>63</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="R101" s="1">
         <v>15</v>
@@ -13277,7 +13295,7 @@
         <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -13289,7 +13307,7 @@
         <v>60</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -13331,7 +13349,7 @@
         <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -13365,7 +13383,7 @@
         <v>66</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R103" s="1">
         <v>15</v>
@@ -13385,7 +13403,7 @@
         <v>70</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -13397,7 +13415,7 @@
         <v>60</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -13419,7 +13437,7 @@
         <v>66</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R104" s="1">
         <v>15</v>
@@ -13746,7 +13764,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -13758,7 +13776,7 @@
         <v>26</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -13794,7 +13812,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -13806,7 +13824,7 @@
         <v>31</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -13828,7 +13846,7 @@
         <v>32</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -13842,7 +13860,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -13854,7 +13872,7 @@
         <v>26</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -13890,7 +13908,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -13902,7 +13920,7 @@
         <v>37</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -13924,7 +13942,7 @@
         <v>39</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -13938,7 +13956,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -13950,7 +13968,7 @@
         <v>37</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -13972,7 +13990,7 @@
         <v>32</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -13986,7 +14004,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -13998,7 +14016,7 @@
         <v>26</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -14034,7 +14052,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -14068,7 +14086,7 @@
         <v>39</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -14082,7 +14100,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -14094,7 +14112,7 @@
         <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -14116,7 +14134,7 @@
         <v>39</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -14130,7 +14148,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -14142,7 +14160,7 @@
         <v>48</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -14178,7 +14196,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -14190,7 +14208,7 @@
         <v>31</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -14212,7 +14230,7 @@
         <v>51</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -14226,7 +14244,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -14238,7 +14256,7 @@
         <v>48</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -14274,7 +14292,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -14286,7 +14304,7 @@
         <v>37</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -14308,7 +14326,7 @@
         <v>54</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14322,7 +14340,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -14334,7 +14352,7 @@
         <v>37</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -14356,7 +14374,7 @@
         <v>51</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14370,7 +14388,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -14382,7 +14400,7 @@
         <v>48</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -14418,7 +14436,7 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -14452,7 +14470,7 @@
         <v>54</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14466,7 +14484,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -14478,7 +14496,7 @@
         <v>48</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -14500,7 +14518,7 @@
         <v>54</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14514,7 +14532,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -14526,7 +14544,7 @@
         <v>60</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -14562,7 +14580,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -14574,7 +14592,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -14596,7 +14614,7 @@
         <v>63</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14610,7 +14628,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -14622,7 +14640,7 @@
         <v>60</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -14658,7 +14676,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -14670,7 +14688,7 @@
         <v>37</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -14692,7 +14710,7 @@
         <v>66</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14706,7 +14724,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -14718,7 +14736,7 @@
         <v>37</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -14740,7 +14758,7 @@
         <v>63</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14754,7 +14772,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -14766,7 +14784,7 @@
         <v>60</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -14802,7 +14820,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -14836,7 +14854,7 @@
         <v>66</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14850,7 +14868,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -14862,7 +14880,7 @@
         <v>60</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -14884,7 +14902,7 @@
         <v>66</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14898,7 +14916,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -14910,7 +14928,7 @@
         <v>26</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -14946,7 +14964,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -14958,7 +14976,7 @@
         <v>31</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -14994,7 +15012,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -15006,7 +15024,7 @@
         <v>26</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -15028,7 +15046,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -15042,7 +15060,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -15054,7 +15072,7 @@
         <v>37</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -15076,7 +15094,7 @@
         <v>39</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -15090,7 +15108,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -15102,7 +15120,7 @@
         <v>37</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -15124,7 +15142,7 @@
         <v>32</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -15138,7 +15156,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -15150,7 +15168,7 @@
         <v>26</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -15172,7 +15190,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -15186,7 +15204,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -15220,7 +15238,7 @@
         <v>39</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -15234,7 +15252,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -15246,7 +15264,7 @@
         <v>26</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -15268,7 +15286,7 @@
         <v>39</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -15282,7 +15300,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -15294,7 +15312,7 @@
         <v>48</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -15330,7 +15348,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -15342,7 +15360,7 @@
         <v>31</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -15378,7 +15396,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -15390,7 +15408,7 @@
         <v>48</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -15412,7 +15430,7 @@
         <v>49</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -15426,7 +15444,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -15438,7 +15456,7 @@
         <v>37</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -15460,7 +15478,7 @@
         <v>54</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -15474,7 +15492,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -15486,7 +15504,7 @@
         <v>37</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -15508,7 +15526,7 @@
         <v>51</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -15522,7 +15540,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -15534,7 +15552,7 @@
         <v>48</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -15556,7 +15574,7 @@
         <v>49</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -15570,7 +15588,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -15604,7 +15622,7 @@
         <v>54</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -15618,7 +15636,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -15630,7 +15648,7 @@
         <v>48</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -15652,7 +15670,7 @@
         <v>54</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -15666,7 +15684,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -15678,7 +15696,7 @@
         <v>60</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -15714,7 +15732,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -15726,7 +15744,7 @@
         <v>31</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -15762,7 +15780,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -15774,7 +15792,7 @@
         <v>60</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -15796,7 +15814,7 @@
         <v>61</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -15810,7 +15828,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -15822,7 +15840,7 @@
         <v>37</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -15844,7 +15862,7 @@
         <v>66</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -15858,7 +15876,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -15870,7 +15888,7 @@
         <v>37</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -15892,7 +15910,7 @@
         <v>63</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -15906,7 +15924,7 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -15918,7 +15936,7 @@
         <v>60</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -15940,7 +15958,7 @@
         <v>61</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -15954,7 +15972,7 @@
         <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -15988,7 +16006,7 @@
         <v>66</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -16002,7 +16020,7 @@
         <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -16014,7 +16032,7 @@
         <v>60</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -16036,7 +16054,7 @@
         <v>66</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -16067,7 +16085,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -16079,7 +16097,7 @@
         <v>26</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -16101,7 +16119,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -16115,7 +16133,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -16127,7 +16145,7 @@
         <v>31</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -16149,7 +16167,7 @@
         <v>32</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -16163,7 +16181,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -16175,7 +16193,7 @@
         <v>26</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -16197,7 +16215,7 @@
         <v>28</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -16211,7 +16229,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -16223,7 +16241,7 @@
         <v>37</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -16245,7 +16263,7 @@
         <v>39</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -16259,7 +16277,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -16271,7 +16289,7 @@
         <v>37</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -16293,7 +16311,7 @@
         <v>32</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -16307,7 +16325,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -16319,7 +16337,7 @@
         <v>26</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -16341,7 +16359,7 @@
         <v>28</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -16355,7 +16373,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -16389,7 +16407,7 @@
         <v>39</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -16403,7 +16421,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -16415,7 +16433,7 @@
         <v>26</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -16437,7 +16455,7 @@
         <v>39</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -16451,7 +16469,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -16463,7 +16481,7 @@
         <v>48</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -16485,7 +16503,7 @@
         <v>49</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -16499,7 +16517,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -16511,7 +16529,7 @@
         <v>31</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -16533,7 +16551,7 @@
         <v>51</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -16547,7 +16565,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -16559,7 +16577,7 @@
         <v>48</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -16581,7 +16599,7 @@
         <v>49</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -16595,7 +16613,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -16607,7 +16625,7 @@
         <v>37</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -16629,7 +16647,7 @@
         <v>54</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -16643,7 +16661,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -16655,7 +16673,7 @@
         <v>37</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -16677,7 +16695,7 @@
         <v>51</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -16691,7 +16709,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -16703,7 +16721,7 @@
         <v>48</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -16725,7 +16743,7 @@
         <v>49</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -16739,7 +16757,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -16773,7 +16791,7 @@
         <v>54</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -16787,7 +16805,7 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -16799,7 +16817,7 @@
         <v>48</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -16821,7 +16839,7 @@
         <v>54</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -16835,7 +16853,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -16847,7 +16865,7 @@
         <v>60</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -16869,7 +16887,7 @@
         <v>61</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -16883,7 +16901,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -16895,7 +16913,7 @@
         <v>31</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -16917,7 +16935,7 @@
         <v>63</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -16931,7 +16949,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -16943,7 +16961,7 @@
         <v>60</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -16965,7 +16983,7 @@
         <v>61</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -16979,7 +16997,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -16991,7 +17009,7 @@
         <v>37</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -17013,7 +17031,7 @@
         <v>66</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -17027,7 +17045,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -17039,7 +17057,7 @@
         <v>37</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -17061,7 +17079,7 @@
         <v>63</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -17075,7 +17093,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -17087,7 +17105,7 @@
         <v>60</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -17109,7 +17127,7 @@
         <v>61</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -17123,7 +17141,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -17157,7 +17175,7 @@
         <v>66</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -17171,7 +17189,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -17183,7 +17201,7 @@
         <v>60</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -17205,7 +17223,7 @@
         <v>66</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -17236,7 +17254,7 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -17248,7 +17266,7 @@
         <v>26</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -17284,7 +17302,7 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -17296,7 +17314,7 @@
         <v>31</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -17318,7 +17336,7 @@
         <v>32</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -17332,7 +17350,7 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -17344,7 +17362,7 @@
         <v>26</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -17380,7 +17398,7 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -17392,7 +17410,7 @@
         <v>37</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -17414,7 +17432,7 @@
         <v>39</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -17428,7 +17446,7 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -17440,7 +17458,7 @@
         <v>37</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -17462,7 +17480,7 @@
         <v>32</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -17476,7 +17494,7 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -17488,7 +17506,7 @@
         <v>26</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -17524,7 +17542,7 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -17558,7 +17576,7 @@
         <v>39</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -17572,7 +17590,7 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -17584,7 +17602,7 @@
         <v>26</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -17606,7 +17624,7 @@
         <v>39</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -17620,7 +17638,7 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -17632,7 +17650,7 @@
         <v>48</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -17668,7 +17686,7 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -17680,7 +17698,7 @@
         <v>31</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -17702,7 +17720,7 @@
         <v>51</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -17716,7 +17734,7 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -17728,7 +17746,7 @@
         <v>48</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -17764,7 +17782,7 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -17776,7 +17794,7 @@
         <v>37</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -17798,7 +17816,7 @@
         <v>54</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -17812,7 +17830,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -17824,7 +17842,7 @@
         <v>37</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -17846,7 +17864,7 @@
         <v>51</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -17860,7 +17878,7 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -17872,7 +17890,7 @@
         <v>48</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -17908,7 +17926,7 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -17942,7 +17960,7 @@
         <v>54</v>
       </c>
       <c r="Q95" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -17956,7 +17974,7 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -17968,7 +17986,7 @@
         <v>48</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -17990,7 +18008,7 @@
         <v>54</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -18004,7 +18022,7 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -18016,7 +18034,7 @@
         <v>60</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -18052,7 +18070,7 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -18064,7 +18082,7 @@
         <v>31</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -18086,7 +18104,7 @@
         <v>63</v>
       </c>
       <c r="Q98" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -18100,7 +18118,7 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -18112,7 +18130,7 @@
         <v>60</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -18148,7 +18166,7 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -18160,7 +18178,7 @@
         <v>37</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -18182,7 +18200,7 @@
         <v>66</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -18196,7 +18214,7 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -18208,7 +18226,7 @@
         <v>37</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -18230,7 +18248,7 @@
         <v>63</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -18244,7 +18262,7 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -18256,7 +18274,7 @@
         <v>60</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -18292,7 +18310,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -18326,7 +18344,7 @@
         <v>66</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -18340,7 +18358,7 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -18352,7 +18370,7 @@
         <v>60</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -18374,7 +18392,7 @@
         <v>66</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -18693,7 +18711,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -18702,10 +18720,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -18740,7 +18758,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -18749,10 +18767,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -18826,7 +18844,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18844,7 +18862,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18875,16 +18893,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>15</v>
@@ -18921,10 +18939,10 @@
         <v>19</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -18994,7 +19012,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -19003,10 +19021,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -19018,7 +19036,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -19040,7 +19058,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -19052,7 +19070,7 @@
         <v>37</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -19064,7 +19082,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -19086,7 +19104,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -19098,7 +19116,7 @@
         <v>31</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -19130,7 +19148,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -19142,7 +19160,7 @@
         <v>37</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -19154,7 +19172,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -19176,7 +19194,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -19185,10 +19203,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -19200,7 +19218,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -19222,7 +19240,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -19234,7 +19252,7 @@
         <v>31</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -19266,7 +19284,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -19275,10 +19293,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -19290,7 +19308,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -19312,7 +19330,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -19324,7 +19342,7 @@
         <v>37</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -19356,7 +19374,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -19368,7 +19386,7 @@
         <v>31</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -19418,22 +19436,22 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="K16" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L16" s="2">
         <v>7</v>
@@ -19442,7 +19460,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -19464,7 +19482,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -19476,10 +19494,10 @@
         <v>31</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K17" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L17" s="2">
         <v>7</v>
@@ -19508,7 +19526,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -19520,10 +19538,10 @@
         <v>37</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="K18" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" s="2">
         <v>7</v>
@@ -19552,22 +19570,22 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1">
+        <v>414</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>37</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K19" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L19" s="2">
         <v>7</v>
@@ -19576,7 +19594,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -19598,22 +19616,22 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G20" s="1">
-        <v>3</v>
-      </c>
-      <c r="H20" s="1">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K20" s="2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2">
         <v>7</v>
@@ -19642,22 +19660,22 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="G21" s="1">
-        <v>7</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>44</v>
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="s">
         <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K21" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L21" s="2">
         <v>7</v>
@@ -19686,22 +19704,22 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K22" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L22" s="2">
         <v>7</v>
@@ -19710,7 +19728,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -19732,22 +19750,22 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="G23" s="1">
-        <v>3</v>
-      </c>
-      <c r="H23" s="1">
-        <v>3</v>
+        <v>420</v>
+      </c>
+      <c r="G23" s="2">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2">
+        <v>2</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>37</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="K23" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L23" s="2">
         <v>7</v>
@@ -19776,22 +19794,22 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G24" s="1">
-        <v>7</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>44</v>
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>381</v>
+        <v>31</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K24" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L24" s="2">
         <v>7</v>
@@ -19825,10 +19843,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -19840,7 +19858,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -19856,7 +19874,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -19867,10 +19885,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -19882,7 +19900,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -19907,10 +19925,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -19922,7 +19940,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -19947,10 +19965,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -19962,7 +19980,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -19978,7 +19996,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -19989,10 +20007,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -20004,7 +20022,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -20029,10 +20047,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -20044,7 +20062,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -20069,10 +20087,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -20084,7 +20102,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -20100,7 +20118,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -20111,10 +20129,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -20126,7 +20144,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -20151,10 +20169,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -20166,7 +20184,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -20191,10 +20209,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -20206,7 +20224,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -20222,7 +20240,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -20233,10 +20251,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -20248,7 +20266,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -20273,10 +20291,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -20288,7 +20306,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -20313,10 +20331,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -20328,7 +20346,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -20344,7 +20362,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -20355,10 +20373,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -20370,7 +20388,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -20395,10 +20413,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -20410,7 +20428,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -20435,10 +20453,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -20450,7 +20468,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -20466,7 +20484,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -20477,10 +20495,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -20492,7 +20510,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -20517,10 +20535,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -20532,7 +20550,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -20557,10 +20575,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -20572,7 +20590,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -20588,7 +20606,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -20599,10 +20617,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -20614,7 +20632,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -20639,10 +20657,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -20654,7 +20672,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -20679,10 +20697,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -20694,7 +20712,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -20710,7 +20728,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -20721,10 +20739,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -20736,7 +20754,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -20761,10 +20779,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -20776,7 +20794,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="460">
   <si>
     <t>_id</t>
   </si>
@@ -1598,25 +1598,43 @@
     <t>重击巨剑</t>
   </si>
   <si>
+    <t>40000,100</t>
+  </si>
+  <si>
     <t>此次攻击概率翻倍</t>
   </si>
   <si>
     <t>重击护腕</t>
   </si>
   <si>
+    <t>400000,150</t>
+  </si>
+  <si>
     <t>重击腰带</t>
   </si>
   <si>
+    <t>20000,100</t>
+  </si>
+  <si>
     <t>暴击扳指</t>
   </si>
   <si>
+    <t>80000,120</t>
+  </si>
+  <si>
     <t>如果此次攻击暴击了，伤害额外翻倍</t>
   </si>
   <si>
     <t>暴击板甲</t>
   </si>
   <si>
+    <t>800000,180</t>
+  </si>
+  <si>
     <t>暴击铁履</t>
+  </si>
+  <si>
+    <t>80000,100</t>
   </si>
   <si>
     <t>天命之剑</t>
@@ -19579,10 +19597,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>37</v>
+        <v>387</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -19594,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -19616,7 +19634,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -19625,10 +19643,10 @@
         <v>42</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>387</v>
+        <v>37</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -19660,7 +19678,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -19672,7 +19690,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -19704,7 +19722,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -19716,7 +19734,7 @@
         <v>387</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -19728,7 +19746,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -19750,7 +19768,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -19762,7 +19780,7 @@
         <v>37</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -19794,7 +19812,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -19806,7 +19824,7 @@
         <v>31</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -19858,7 +19876,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -19874,7 +19892,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -19900,7 +19918,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -19940,7 +19958,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -19980,7 +19998,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -19996,7 +20014,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -20022,7 +20040,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -20062,7 +20080,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -20102,7 +20120,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -20118,7 +20136,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -20144,7 +20162,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -20184,7 +20202,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -20224,7 +20242,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -20240,7 +20258,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -20266,7 +20284,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -20306,7 +20324,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -20346,7 +20364,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -20362,7 +20380,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -20388,7 +20406,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -20428,7 +20446,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -20468,7 +20486,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -20484,7 +20502,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -20510,7 +20528,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -20550,7 +20568,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -20590,7 +20608,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -20606,7 +20624,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -20632,7 +20650,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -20672,7 +20690,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -20712,7 +20730,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -20728,7 +20746,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -20754,7 +20772,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -20794,7 +20812,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -428,7 +428,7 @@
     <t>4,1004</t>
   </si>
   <si>
-    <t>50,5</t>
+    <t>100,2</t>
   </si>
   <si>
     <t>朽木战甲</t>
@@ -440,7 +440,7 @@
     <t>朽木战链</t>
   </si>
   <si>
-    <t>25,2</t>
+    <t>50,1</t>
   </si>
   <si>
     <t>朽木战盔</t>
@@ -449,7 +449,7 @@
     <t>1,1001</t>
   </si>
   <si>
-    <t>500,4</t>
+    <t>1000,2</t>
   </si>
   <si>
     <t>朽木战镯</t>
@@ -527,7 +527,7 @@
     <t>黑铁战刃</t>
   </si>
   <si>
-    <t>200,10</t>
+    <t>300,4</t>
   </si>
   <si>
     <t>黑铁战甲</t>
@@ -536,175 +536,175 @@
     <t>黑铁战链</t>
   </si>
   <si>
-    <t>100,5</t>
+    <t>150,2</t>
   </si>
   <si>
     <t>黑铁战盔</t>
   </si>
   <si>
+    <t>3000,4</t>
+  </si>
+  <si>
+    <t>黑铁战镯</t>
+  </si>
+  <si>
+    <t>黑铁战戒</t>
+  </si>
+  <si>
+    <t>黑铁战带</t>
+  </si>
+  <si>
+    <t>黑铁战靴</t>
+  </si>
+  <si>
+    <t>黑铁法刃</t>
+  </si>
+  <si>
+    <t>黑铁法甲</t>
+  </si>
+  <si>
+    <t>黑铁法链</t>
+  </si>
+  <si>
+    <t>黑铁法盔</t>
+  </si>
+  <si>
+    <t>黑铁法镯</t>
+  </si>
+  <si>
+    <t>黑铁法戒</t>
+  </si>
+  <si>
+    <t>黑铁法带</t>
+  </si>
+  <si>
+    <t>黑铁法靴</t>
+  </si>
+  <si>
+    <t>黑铁道刃</t>
+  </si>
+  <si>
+    <t>黑铁道甲</t>
+  </si>
+  <si>
+    <t>黑铁道链</t>
+  </si>
+  <si>
+    <t>黑铁道盔</t>
+  </si>
+  <si>
+    <t>黑铁道镯</t>
+  </si>
+  <si>
+    <t>黑铁道戒</t>
+  </si>
+  <si>
+    <t>黑铁道带</t>
+  </si>
+  <si>
+    <t>黑铁道靴</t>
+  </si>
+  <si>
+    <t>白银战刃</t>
+  </si>
+  <si>
+    <t>1000,6</t>
+  </si>
+  <si>
+    <t>白银战甲</t>
+  </si>
+  <si>
+    <t>白银战链</t>
+  </si>
+  <si>
+    <t>500,3</t>
+  </si>
+  <si>
+    <t>白银战盔</t>
+  </si>
+  <si>
+    <t>10000,6</t>
+  </si>
+  <si>
+    <t>白银战镯</t>
+  </si>
+  <si>
+    <t>白银战戒</t>
+  </si>
+  <si>
+    <t>白银战带</t>
+  </si>
+  <si>
+    <t>白银战靴</t>
+  </si>
+  <si>
+    <t>白银法刃</t>
+  </si>
+  <si>
+    <t>白银法甲</t>
+  </si>
+  <si>
+    <t>白银法链</t>
+  </si>
+  <si>
+    <t>白银法盔</t>
+  </si>
+  <si>
+    <t>白银法镯</t>
+  </si>
+  <si>
+    <t>白银法戒</t>
+  </si>
+  <si>
+    <t>白银法带</t>
+  </si>
+  <si>
+    <t>白银法靴</t>
+  </si>
+  <si>
+    <t>白银道刃</t>
+  </si>
+  <si>
+    <t>白银道甲</t>
+  </si>
+  <si>
+    <t>白银道链</t>
+  </si>
+  <si>
+    <t>白银道盔</t>
+  </si>
+  <si>
+    <t>白银道镯</t>
+  </si>
+  <si>
+    <t>白银道戒</t>
+  </si>
+  <si>
+    <t>白银道带</t>
+  </si>
+  <si>
+    <t>白银道靴</t>
+  </si>
+  <si>
+    <t>黄金战刃</t>
+  </si>
+  <si>
     <t>2000,8</t>
   </si>
   <si>
-    <t>黑铁战镯</t>
-  </si>
-  <si>
-    <t>黑铁战戒</t>
-  </si>
-  <si>
-    <t>黑铁战带</t>
-  </si>
-  <si>
-    <t>黑铁战靴</t>
-  </si>
-  <si>
-    <t>黑铁法刃</t>
-  </si>
-  <si>
-    <t>黑铁法甲</t>
-  </si>
-  <si>
-    <t>黑铁法链</t>
-  </si>
-  <si>
-    <t>黑铁法盔</t>
-  </si>
-  <si>
-    <t>黑铁法镯</t>
-  </si>
-  <si>
-    <t>黑铁法戒</t>
-  </si>
-  <si>
-    <t>黑铁法带</t>
-  </si>
-  <si>
-    <t>黑铁法靴</t>
-  </si>
-  <si>
-    <t>黑铁道刃</t>
-  </si>
-  <si>
-    <t>黑铁道甲</t>
-  </si>
-  <si>
-    <t>黑铁道链</t>
-  </si>
-  <si>
-    <t>黑铁道盔</t>
-  </si>
-  <si>
-    <t>黑铁道镯</t>
-  </si>
-  <si>
-    <t>黑铁道戒</t>
-  </si>
-  <si>
-    <t>黑铁道带</t>
-  </si>
-  <si>
-    <t>黑铁道靴</t>
-  </si>
-  <si>
-    <t>白银战刃</t>
-  </si>
-  <si>
-    <t>1000,15</t>
-  </si>
-  <si>
-    <t>白银战甲</t>
-  </si>
-  <si>
-    <t>白银战链</t>
-  </si>
-  <si>
-    <t>500,8</t>
-  </si>
-  <si>
-    <t>白银战盔</t>
-  </si>
-  <si>
-    <t>10000,12</t>
-  </si>
-  <si>
-    <t>白银战镯</t>
-  </si>
-  <si>
-    <t>白银战戒</t>
-  </si>
-  <si>
-    <t>白银战带</t>
-  </si>
-  <si>
-    <t>白银战靴</t>
-  </si>
-  <si>
-    <t>白银法刃</t>
-  </si>
-  <si>
-    <t>白银法甲</t>
-  </si>
-  <si>
-    <t>白银法链</t>
-  </si>
-  <si>
-    <t>白银法盔</t>
-  </si>
-  <si>
-    <t>白银法镯</t>
-  </si>
-  <si>
-    <t>白银法戒</t>
-  </si>
-  <si>
-    <t>白银法带</t>
-  </si>
-  <si>
-    <t>白银法靴</t>
-  </si>
-  <si>
-    <t>白银道刃</t>
-  </si>
-  <si>
-    <t>白银道甲</t>
-  </si>
-  <si>
-    <t>白银道链</t>
-  </si>
-  <si>
-    <t>白银道盔</t>
-  </si>
-  <si>
-    <t>白银道镯</t>
-  </si>
-  <si>
-    <t>白银道戒</t>
-  </si>
-  <si>
-    <t>白银道带</t>
-  </si>
-  <si>
-    <t>白银道靴</t>
-  </si>
-  <si>
-    <t>黄金战刃</t>
-  </si>
-  <si>
-    <t>5000,20</t>
-  </si>
-  <si>
     <t>黄金战甲</t>
   </si>
   <si>
     <t>黄金战链</t>
   </si>
   <si>
-    <t>2500,10</t>
+    <t>1000,4</t>
   </si>
   <si>
     <t>黄金战盔</t>
   </si>
   <si>
-    <t>50000,15</t>
+    <t>20000,8</t>
   </si>
   <si>
     <t>黄金战镯</t>
@@ -1804,12 +1804,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7345,7 +7345,7 @@
     <row r="107" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:O3 K4:M4 N4 O4 K5:O5 C3:H5 P3:Q5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -12276,7 +12276,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:O3 N4 O4 K5:O5 P5:Q5 C3:H5 K3:M4 P3:Q4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -17207,7 +17207,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:O3 N4 O4 K5:O5 P5:Q5 K3:M4 C3:H5 P3:Q4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="422">
   <si>
     <t>_id</t>
   </si>
@@ -1362,15 +1362,6 @@
   </si>
   <si>
     <t>暗龙道靴</t>
-  </si>
-  <si>
-    <t>CardGroupId</t>
-  </si>
-  <si>
-    <t>CardAtrList</t>
-  </si>
-  <si>
-    <t>CardVueList</t>
   </si>
   <si>
     <t>新手武器</t>
@@ -1804,12 +1795,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2862,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="1">
         <v>5</v>
@@ -2909,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" s="1">
         <v>5</v>
@@ -2956,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" s="1">
         <v>5</v>
@@ -3003,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O10" s="1">
         <v>5</v>
@@ -3050,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
@@ -3097,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" s="1">
         <v>5</v>
@@ -3144,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" s="1">
         <v>5</v>
@@ -3191,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
         <v>5</v>
@@ -3285,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" s="1">
         <v>5</v>
@@ -3332,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="1">
         <v>5</v>
@@ -3379,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O18" s="1">
         <v>5</v>
@@ -3426,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="1">
         <v>5</v>
@@ -3473,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="1">
         <v>5</v>
@@ -3520,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21" s="1">
         <v>5</v>
@@ -3567,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O22" s="1">
         <v>5</v>
@@ -3614,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O23" s="1">
         <v>5</v>
@@ -3990,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32" s="1">
         <v>5</v>
@@ -4037,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O33" s="1">
         <v>5</v>
@@ -4084,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O34" s="1">
         <v>5</v>
@@ -4131,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O35" s="1">
         <v>5</v>
@@ -4178,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O36" s="1">
         <v>5</v>
@@ -4225,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O37" s="1">
         <v>5</v>
@@ -4272,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O38" s="1">
         <v>5</v>
@@ -4319,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O39" s="1">
         <v>5</v>
@@ -4413,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O41" s="1">
         <v>5</v>
@@ -4460,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42" s="1">
         <v>5</v>
@@ -4507,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="1">
         <v>5</v>
@@ -4554,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O44" s="1">
         <v>5</v>
@@ -4601,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O45" s="1">
         <v>5</v>
@@ -4648,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O46" s="1">
         <v>5</v>
@@ -4695,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O47" s="1">
         <v>5</v>
@@ -4742,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48" s="1">
         <v>5</v>
@@ -5135,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O57" s="1">
         <v>5</v>
@@ -5182,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O58" s="1">
         <v>5</v>
@@ -5276,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O60" s="1">
         <v>5</v>
@@ -5323,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O61" s="1">
         <v>5</v>
@@ -5417,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O63" s="1">
         <v>5</v>
@@ -5464,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O64" s="1">
         <v>5</v>
@@ -5511,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O65" s="1">
         <v>5</v>
@@ -5605,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O67" s="1">
         <v>5</v>
@@ -5652,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O68" s="1">
         <v>5</v>
@@ -5746,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O70" s="1">
         <v>5</v>
@@ -5793,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O71" s="1">
         <v>5</v>
@@ -5840,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O72" s="1">
         <v>5</v>
@@ -5934,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O74" s="1">
         <v>5</v>
@@ -5981,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O75" s="1">
         <v>5</v>
@@ -6075,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O77" s="1">
         <v>5</v>
@@ -6122,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O78" s="1">
         <v>5</v>
@@ -6278,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O82" s="1">
         <v>5</v>
@@ -6325,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O83" s="1">
         <v>5</v>
@@ -6372,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O84" s="1">
         <v>5</v>
@@ -6419,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O85" s="1">
         <v>5</v>
@@ -6466,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O86" s="1">
         <v>5</v>
@@ -6513,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O87" s="1">
         <v>5</v>
@@ -6560,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O88" s="1">
         <v>5</v>
@@ -6607,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O89" s="1">
         <v>5</v>
@@ -6701,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O91" s="1">
         <v>5</v>
@@ -6748,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O92" s="1">
         <v>5</v>
@@ -6795,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O93" s="1">
         <v>5</v>
@@ -6842,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O94" s="1">
         <v>5</v>
@@ -6889,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O95" s="1">
         <v>5</v>
@@ -6936,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O96" s="1">
         <v>5</v>
@@ -6983,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O97" s="1">
         <v>5</v>
@@ -7030,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O98" s="1">
         <v>5</v>
@@ -7552,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" ref="N6:N13" si="0">E6/10*3+1</f>
+        <f>E6/10*3+1</f>
         <v>13</v>
       </c>
       <c r="O6" s="1">
@@ -7600,8 +7591,8 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>E7/10*3+2</f>
+        <v>14</v>
       </c>
       <c r="O7" s="1">
         <v>5</v>
@@ -7648,8 +7639,8 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" ref="N8:N13" si="0">E8/10*3+3</f>
+        <v>15</v>
       </c>
       <c r="O8" s="1">
         <v>5</v>
@@ -7697,7 +7688,7 @@
       </c>
       <c r="N9" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O9" s="1">
         <v>5</v>
@@ -7745,7 +7736,7 @@
       </c>
       <c r="N10" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O10" s="1">
         <v>5</v>
@@ -7793,7 +7784,7 @@
       </c>
       <c r="N11" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
@@ -7841,7 +7832,7 @@
       </c>
       <c r="N12" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O12" s="1">
         <v>5</v>
@@ -7889,7 +7880,7 @@
       </c>
       <c r="N13" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1">
         <v>5</v>
@@ -7936,8 +7927,8 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" ref="N14:N21" si="1">E14/10*3+2</f>
-        <v>14</v>
+        <f>E14/10*3+1</f>
+        <v>13</v>
       </c>
       <c r="O14" s="1">
         <v>5</v>
@@ -7984,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="1"/>
+        <f>E15/10*3+2</f>
         <v>14</v>
       </c>
       <c r="O15" s="1">
@@ -8032,8 +8023,8 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f t="shared" ref="N16:N21" si="1">E16/10*3+3</f>
+        <v>15</v>
       </c>
       <c r="O16" s="1">
         <v>5</v>
@@ -8081,7 +8072,7 @@
       </c>
       <c r="N17" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1">
         <v>5</v>
@@ -8129,7 +8120,7 @@
       </c>
       <c r="N18" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1">
         <v>5</v>
@@ -8177,7 +8168,7 @@
       </c>
       <c r="N19" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1">
         <v>5</v>
@@ -8225,7 +8216,7 @@
       </c>
       <c r="N20" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O20" s="1">
         <v>5</v>
@@ -8273,7 +8264,7 @@
       </c>
       <c r="N21" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O21" s="1">
         <v>5</v>
@@ -8320,8 +8311,8 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <f t="shared" ref="N22:N29" si="2">E22/10*3+3</f>
-        <v>15</v>
+        <f>E22/10*3+1</f>
+        <v>13</v>
       </c>
       <c r="O22" s="1">
         <v>5</v>
@@ -8368,8 +8359,8 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>E23/10*3+2</f>
+        <v>14</v>
       </c>
       <c r="O23" s="1">
         <v>5</v>
@@ -8416,7 +8407,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N24:N29" si="2">E24/10*3+3</f>
         <v>15</v>
       </c>
       <c r="O24" s="1">
@@ -8704,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <f t="shared" ref="N31:N38" si="3">E31/10*3+1</f>
+        <f>E31/10*3+1</f>
         <v>16</v>
       </c>
       <c r="O31" s="1">
@@ -8752,8 +8743,8 @@
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <f t="shared" si="3"/>
-        <v>16</v>
+        <f>E32/10*3+2</f>
+        <v>17</v>
       </c>
       <c r="O32" s="1">
         <v>5</v>
@@ -8800,8 +8791,8 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <f t="shared" si="3"/>
-        <v>16</v>
+        <f t="shared" ref="N33:N38" si="3">E33/10*3+3</f>
+        <v>18</v>
       </c>
       <c r="O33" s="1">
         <v>5</v>
@@ -8849,7 +8840,7 @@
       </c>
       <c r="N34" s="1">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O34" s="1">
         <v>5</v>
@@ -8897,7 +8888,7 @@
       </c>
       <c r="N35" s="1">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O35" s="1">
         <v>5</v>
@@ -8945,7 +8936,7 @@
       </c>
       <c r="N36" s="1">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O36" s="1">
         <v>5</v>
@@ -8993,7 +8984,7 @@
       </c>
       <c r="N37" s="1">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O37" s="1">
         <v>5</v>
@@ -9041,7 +9032,7 @@
       </c>
       <c r="N38" s="1">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O38" s="1">
         <v>5</v>
@@ -9088,8 +9079,8 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <f t="shared" ref="N39:N46" si="4">E39/10*3+2</f>
-        <v>17</v>
+        <f>E39/10*3+1</f>
+        <v>16</v>
       </c>
       <c r="O39" s="1">
         <v>5</v>
@@ -9136,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <f t="shared" si="4"/>
+        <f>E40/10*3+2</f>
         <v>17</v>
       </c>
       <c r="O40" s="1">
@@ -9184,8 +9175,8 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" si="4"/>
-        <v>17</v>
+        <f t="shared" ref="N41:N46" si="4">E41/10*3+3</f>
+        <v>18</v>
       </c>
       <c r="O41" s="1">
         <v>5</v>
@@ -9233,7 +9224,7 @@
       </c>
       <c r="N42" s="1">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O42" s="1">
         <v>5</v>
@@ -9281,7 +9272,7 @@
       </c>
       <c r="N43" s="1">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O43" s="1">
         <v>5</v>
@@ -9329,7 +9320,7 @@
       </c>
       <c r="N44" s="1">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O44" s="1">
         <v>5</v>
@@ -9377,7 +9368,7 @@
       </c>
       <c r="N45" s="1">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O45" s="1">
         <v>5</v>
@@ -9425,7 +9416,7 @@
       </c>
       <c r="N46" s="1">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O46" s="1">
         <v>5</v>
@@ -9472,8 +9463,8 @@
         <v>0</v>
       </c>
       <c r="N47" s="1">
-        <f t="shared" ref="N47:N54" si="5">E47/10*3+3</f>
-        <v>18</v>
+        <f>E47/10*3+1</f>
+        <v>16</v>
       </c>
       <c r="O47" s="1">
         <v>5</v>
@@ -9520,8 +9511,8 @@
         <v>0</v>
       </c>
       <c r="N48" s="1">
-        <f t="shared" si="5"/>
-        <v>18</v>
+        <f>E48/10*3+2</f>
+        <v>17</v>
       </c>
       <c r="O48" s="1">
         <v>5</v>
@@ -9568,7 +9559,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="N49:N54" si="5">E49/10*3+3</f>
         <v>18</v>
       </c>
       <c r="O49" s="1">
@@ -9873,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
-        <f t="shared" ref="N56:N63" si="6">E56/10*3+1</f>
+        <f>E56/10*3+1</f>
         <v>19</v>
       </c>
       <c r="O56" s="1">
@@ -9921,8 +9912,8 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <f t="shared" si="6"/>
-        <v>19</v>
+        <f>E57/10*3+2</f>
+        <v>20</v>
       </c>
       <c r="O57" s="1">
         <v>5</v>
@@ -9969,8 +9960,8 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" si="6"/>
-        <v>19</v>
+        <f t="shared" ref="N58:N63" si="6">E58/10*3+3</f>
+        <v>21</v>
       </c>
       <c r="O58" s="1">
         <v>5</v>
@@ -10018,7 +10009,7 @@
       </c>
       <c r="N59" s="1">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O59" s="1">
         <v>5</v>
@@ -10066,7 +10057,7 @@
       </c>
       <c r="N60" s="1">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O60" s="1">
         <v>5</v>
@@ -10114,7 +10105,7 @@
       </c>
       <c r="N61" s="1">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O61" s="1">
         <v>5</v>
@@ -10162,7 +10153,7 @@
       </c>
       <c r="N62" s="1">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O62" s="1">
         <v>5</v>
@@ -10210,7 +10201,7 @@
       </c>
       <c r="N63" s="1">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O63" s="1">
         <v>5</v>
@@ -10257,8 +10248,8 @@
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <f t="shared" ref="N64:N71" si="7">E64/10*3+2</f>
-        <v>20</v>
+        <f>E64/10*3+1</f>
+        <v>19</v>
       </c>
       <c r="O64" s="1">
         <v>5</v>
@@ -10305,7 +10296,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <f t="shared" si="7"/>
+        <f>E65/10*3+2</f>
         <v>20</v>
       </c>
       <c r="O65" s="1">
@@ -10353,8 +10344,8 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" si="7"/>
-        <v>20</v>
+        <f t="shared" ref="N66:N71" si="7">E66/10*3+3</f>
+        <v>21</v>
       </c>
       <c r="O66" s="1">
         <v>5</v>
@@ -10402,7 +10393,7 @@
       </c>
       <c r="N67" s="1">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O67" s="1">
         <v>5</v>
@@ -10450,7 +10441,7 @@
       </c>
       <c r="N68" s="1">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O68" s="1">
         <v>5</v>
@@ -10498,7 +10489,7 @@
       </c>
       <c r="N69" s="1">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O69" s="1">
         <v>5</v>
@@ -10546,7 +10537,7 @@
       </c>
       <c r="N70" s="1">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O70" s="1">
         <v>5</v>
@@ -10594,7 +10585,7 @@
       </c>
       <c r="N71" s="1">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O71" s="1">
         <v>5</v>
@@ -10641,8 +10632,8 @@
         <v>0</v>
       </c>
       <c r="N72" s="1">
-        <f t="shared" ref="N72:N79" si="8">E72/10*3+3</f>
-        <v>21</v>
+        <f>E72/10*3+1</f>
+        <v>19</v>
       </c>
       <c r="O72" s="1">
         <v>5</v>
@@ -10689,8 +10680,8 @@
         <v>0</v>
       </c>
       <c r="N73" s="1">
-        <f t="shared" si="8"/>
-        <v>21</v>
+        <f>E73/10*3+2</f>
+        <v>20</v>
       </c>
       <c r="O73" s="1">
         <v>5</v>
@@ -10737,7 +10728,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="N74:N79" si="8">E74/10*3+3</f>
         <v>21</v>
       </c>
       <c r="O74" s="1">
@@ -11040,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="1">
-        <f t="shared" ref="N81:N88" si="9">E81/10*3+1</f>
+        <f>E81/10*3+1</f>
         <v>22</v>
       </c>
       <c r="O81" s="1">
@@ -11088,8 +11079,8 @@
         <v>0</v>
       </c>
       <c r="N82" s="1">
-        <f t="shared" si="9"/>
-        <v>22</v>
+        <f>E82/10*3+2</f>
+        <v>23</v>
       </c>
       <c r="O82" s="1">
         <v>5</v>
@@ -11136,8 +11127,8 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" si="9"/>
-        <v>22</v>
+        <f t="shared" ref="N83:N88" si="9">E83/10*3+3</f>
+        <v>24</v>
       </c>
       <c r="O83" s="1">
         <v>5</v>
@@ -11185,7 +11176,7 @@
       </c>
       <c r="N84" s="1">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O84" s="1">
         <v>5</v>
@@ -11233,7 +11224,7 @@
       </c>
       <c r="N85" s="1">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O85" s="1">
         <v>5</v>
@@ -11281,7 +11272,7 @@
       </c>
       <c r="N86" s="1">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O86" s="1">
         <v>5</v>
@@ -11329,7 +11320,7 @@
       </c>
       <c r="N87" s="1">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O87" s="1">
         <v>5</v>
@@ -11377,7 +11368,7 @@
       </c>
       <c r="N88" s="1">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O88" s="1">
         <v>5</v>
@@ -11424,8 +11415,8 @@
         <v>0</v>
       </c>
       <c r="N89" s="1">
-        <f t="shared" ref="N89:N96" si="10">E89/10*3+2</f>
-        <v>23</v>
+        <f>E89/10*3+1</f>
+        <v>22</v>
       </c>
       <c r="O89" s="1">
         <v>5</v>
@@ -11472,7 +11463,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="1">
-        <f t="shared" si="10"/>
+        <f>E90/10*3+2</f>
         <v>23</v>
       </c>
       <c r="O90" s="1">
@@ -11520,8 +11511,8 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" si="10"/>
-        <v>23</v>
+        <f t="shared" ref="N91:N96" si="10">E91/10*3+3</f>
+        <v>24</v>
       </c>
       <c r="O91" s="1">
         <v>5</v>
@@ -11569,7 +11560,7 @@
       </c>
       <c r="N92" s="1">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O92" s="1">
         <v>5</v>
@@ -11617,7 +11608,7 @@
       </c>
       <c r="N93" s="1">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O93" s="1">
         <v>5</v>
@@ -11665,7 +11656,7 @@
       </c>
       <c r="N94" s="1">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O94" s="1">
         <v>5</v>
@@ -11713,7 +11704,7 @@
       </c>
       <c r="N95" s="1">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O95" s="1">
         <v>5</v>
@@ -11761,7 +11752,7 @@
       </c>
       <c r="N96" s="1">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O96" s="1">
         <v>5</v>
@@ -11808,8 +11799,8 @@
         <v>0</v>
       </c>
       <c r="N97" s="1">
-        <f t="shared" ref="N97:N104" si="11">E97/10*3+3</f>
-        <v>24</v>
+        <f>E97/10*3+1</f>
+        <v>22</v>
       </c>
       <c r="O97" s="1">
         <v>5</v>
@@ -11856,8 +11847,8 @@
         <v>0</v>
       </c>
       <c r="N98" s="1">
-        <f t="shared" si="11"/>
-        <v>24</v>
+        <f>E98/10*3+2</f>
+        <v>23</v>
       </c>
       <c r="O98" s="1">
         <v>5</v>
@@ -11904,7 +11895,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="N99:N104" si="11">E99/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O99" s="1">
@@ -17220,7 +17211,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="5" max="5" width="14.1666666666667" customWidth="1"/>
@@ -17231,7 +17222,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="18" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A3" s="9"/>
       <c r="C3" s="7" t="s">
         <v>0</v>
@@ -17267,25 +17258,19 @@
         <v>10</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A4" s="9"/>
       <c r="C4" s="7" t="s">
         <v>15</v>
@@ -17321,25 +17306,19 @@
         <v>10</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="A5" s="9"/>
       <c r="C5" s="7" t="s">
         <v>18</v>
@@ -17381,19 +17360,13 @@
         <v>18</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
+    </row>
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
       <c r="C6" s="1">
         <v>200001</v>
       </c>
@@ -17404,7 +17377,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17413,10 +17386,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17433,14 +17406,14 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="R6" s="1">
-        <v>2</v>
-      </c>
-      <c r="S6" s="1">
+      <c r="P6" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:17">
       <c r="C7" s="1">
         <v>200002</v>
       </c>
@@ -17451,7 +17424,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17460,10 +17433,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -17480,18 +17453,16 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7">
-        <v>2</v>
-      </c>
-      <c r="S7" s="1">
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="1">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:S5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -17537,7 +17508,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17555,7 +17526,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17586,16 +17557,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -17632,10 +17603,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -17705,7 +17676,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -17714,10 +17685,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -17729,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -17751,7 +17722,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -17763,7 +17734,7 @@
         <v>31</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -17775,7 +17746,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -17797,7 +17768,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -17809,7 +17780,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -17841,7 +17812,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -17853,7 +17824,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -17865,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -17887,7 +17858,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -17896,10 +17867,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -17911,7 +17882,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -17933,7 +17904,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -17945,7 +17916,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -17977,7 +17948,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -17986,10 +17957,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18001,7 +17972,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18023,7 +17994,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18035,7 +18006,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18067,7 +18038,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18079,7 +18050,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18129,7 +18100,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18138,10 +18109,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -18153,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18175,7 +18146,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18187,7 +18158,7 @@
         <v>27</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K17" s="2">
         <v>11</v>
@@ -18219,7 +18190,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18231,7 +18202,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K18" s="2">
         <v>12</v>
@@ -18263,7 +18234,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18272,10 +18243,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18287,7 +18258,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18309,7 +18280,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18321,7 +18292,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18353,7 +18324,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18365,7 +18336,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18397,7 +18368,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18406,10 +18377,10 @@
         <v>36</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18421,7 +18392,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18443,7 +18414,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18455,7 +18426,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18487,7 +18458,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -18499,7 +18470,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -18536,10 +18507,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -18551,7 +18522,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -18567,7 +18538,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -18578,10 +18549,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -18593,7 +18564,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -18618,10 +18589,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -18633,7 +18604,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -18658,10 +18629,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -18673,7 +18644,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -18689,7 +18660,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -18700,10 +18671,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -18715,7 +18686,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -18740,10 +18711,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -18755,7 +18726,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -18780,10 +18751,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -18795,7 +18766,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -18811,7 +18782,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -18822,10 +18793,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -18837,7 +18808,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -18862,10 +18833,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -18877,7 +18848,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -18902,10 +18873,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -18917,7 +18888,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -18933,7 +18904,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -18944,10 +18915,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -18959,7 +18930,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -18984,10 +18955,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -18999,7 +18970,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -19024,10 +18995,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -19039,7 +19010,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19055,7 +19026,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19066,10 +19037,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -19081,7 +19052,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19106,10 +19077,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -19121,7 +19092,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19146,10 +19117,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -19161,7 +19132,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19177,7 +19148,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19188,10 +19159,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -19203,7 +19174,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19228,10 +19199,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -19243,7 +19214,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19268,10 +19239,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -19283,7 +19254,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19299,7 +19270,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19310,10 +19281,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -19325,7 +19296,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19350,10 +19321,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -19365,7 +19336,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19390,10 +19361,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -19405,7 +19376,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19421,7 +19392,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19432,10 +19403,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -19447,7 +19418,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19472,10 +19443,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -19487,7 +19458,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
     <sheet name="50-80" sheetId="8" r:id="rId2"/>
     <sheet name="90-120" sheetId="9" r:id="rId3"/>
     <sheet name="定制" sheetId="10" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId5"/>
+    <sheet name="传奇装备" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="416">
   <si>
     <t>_id</t>
   </si>
@@ -770,7 +770,7 @@
     <t>钻石战刃</t>
   </si>
   <si>
-    <t>20000,25</t>
+    <t>4000,10</t>
   </si>
   <si>
     <t>钻石战甲</t>
@@ -779,13 +779,13 @@
     <t>钻石战链</t>
   </si>
   <si>
-    <t>10000,15</t>
+    <t>2000,5</t>
   </si>
   <si>
     <t>钻石战盔</t>
   </si>
   <si>
-    <t>200000,20</t>
+    <t>40000,10</t>
   </si>
   <si>
     <t>钻石战镯</t>
@@ -851,60 +851,69 @@
     <t>金龙战刃</t>
   </si>
   <si>
+    <t>8000,12</t>
+  </si>
+  <si>
+    <t>金龙战甲</t>
+  </si>
+  <si>
+    <t>金龙战链</t>
+  </si>
+  <si>
+    <t>4000,6</t>
+  </si>
+  <si>
+    <t>金龙战盔</t>
+  </si>
+  <si>
+    <t>80000,12</t>
+  </si>
+  <si>
+    <t>金龙战镯</t>
+  </si>
+  <si>
+    <t>金龙战戒</t>
+  </si>
+  <si>
+    <t>金龙战带</t>
+  </si>
+  <si>
+    <t>金龙战靴</t>
+  </si>
+  <si>
+    <t>金龙法刃</t>
+  </si>
+  <si>
     <t>20,5</t>
   </si>
   <si>
-    <t>金龙战甲</t>
+    <t>金龙法甲</t>
   </si>
   <si>
     <t>10,2</t>
   </si>
   <si>
-    <t>金龙战链</t>
-  </si>
-  <si>
-    <t>金龙战盔</t>
+    <t>金龙法链</t>
+  </si>
+  <si>
+    <t>金龙法盔</t>
   </si>
   <si>
     <t>100,10</t>
   </si>
   <si>
-    <t>金龙战镯</t>
-  </si>
-  <si>
-    <t>金龙战戒</t>
-  </si>
-  <si>
-    <t>金龙战带</t>
+    <t>金龙法镯</t>
+  </si>
+  <si>
+    <t>金龙法戒</t>
+  </si>
+  <si>
+    <t>金龙法带</t>
   </si>
   <si>
     <t>5,1</t>
   </si>
   <si>
-    <t>金龙战靴</t>
-  </si>
-  <si>
-    <t>金龙法刃</t>
-  </si>
-  <si>
-    <t>金龙法甲</t>
-  </si>
-  <si>
-    <t>金龙法链</t>
-  </si>
-  <si>
-    <t>金龙法盔</t>
-  </si>
-  <si>
-    <t>金龙法镯</t>
-  </si>
-  <si>
-    <t>金龙法戒</t>
-  </si>
-  <si>
-    <t>金龙法带</t>
-  </si>
-  <si>
     <t>金龙法靴</t>
   </si>
   <si>
@@ -1403,7 +1412,7 @@
     <t>3,1003</t>
   </si>
   <si>
-    <t>500,20</t>
+    <t>500,5</t>
   </si>
   <si>
     <t>回复效果提高100%</t>
@@ -1412,7 +1421,7 @@
     <t>治愈之镯</t>
   </si>
   <si>
-    <t>5000,40</t>
+    <t>5000,5</t>
   </si>
   <si>
     <t>减伤，诅咒，闪避</t>
@@ -1424,18 +1433,12 @@
     <t>财富扳指</t>
   </si>
   <si>
-    <t>20000,60</t>
-  </si>
-  <si>
     <t>金币加成增加20%</t>
   </si>
   <si>
     <t>财富项链</t>
   </si>
   <si>
-    <t>2000,30</t>
-  </si>
-  <si>
     <t>杀敌金币，杀敌金币，杀敌金币，</t>
   </si>
   <si>
@@ -1445,46 +1448,31 @@
     <t>杀戮血剑</t>
   </si>
   <si>
-    <t>10000,40</t>
-  </si>
-  <si>
     <t>经验加成增加20%</t>
   </si>
   <si>
     <t>杀戮面罩</t>
   </si>
   <si>
-    <t>100000,80</t>
-  </si>
-  <si>
     <t>杀戮战靴</t>
   </si>
   <si>
     <t>狂风面具</t>
   </si>
   <si>
-    <t>20000,80</t>
-  </si>
-  <si>
     <t>攻速增加10%，冷却增加10%</t>
   </si>
   <si>
     <t>狂风项链</t>
   </si>
   <si>
-    <t>10000,80</t>
-  </si>
-  <si>
     <t>狂风戒指</t>
   </si>
   <si>
-    <t>200000,120</t>
-  </si>
-  <si>
     <t>重击巨剑</t>
   </si>
   <si>
-    <t>40000,100</t>
+    <t>15000,14</t>
   </si>
   <si>
     <t>此次攻击概率翻倍</t>
@@ -1493,19 +1481,16 @@
     <t>重击护腕</t>
   </si>
   <si>
-    <t>400000,150</t>
+    <t>150000,14</t>
   </si>
   <si>
     <t>重击腰带</t>
   </si>
   <si>
-    <t>20000,100</t>
-  </si>
-  <si>
     <t>暴击扳指</t>
   </si>
   <si>
-    <t>80000,120</t>
+    <t>30000,16</t>
   </si>
   <si>
     <t>如果此次攻击暴击了，伤害额外翻倍</t>
@@ -1514,13 +1499,10 @@
     <t>暴击板甲</t>
   </si>
   <si>
-    <t>800000,180</t>
+    <t>300000,16</t>
   </si>
   <si>
     <t>暴击铁履</t>
-  </si>
-  <si>
-    <t>80000,100</t>
   </si>
   <si>
     <t>天命之剑</t>
@@ -8731,7 +8713,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -8767,7 +8749,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -8779,7 +8761,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -8923,7 +8905,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -8971,7 +8953,7 @@
         <v>27</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -9007,7 +8989,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -9019,7 +9001,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -9055,7 +9037,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -9067,7 +9049,7 @@
         <v>40</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -9115,7 +9097,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -9151,7 +9133,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -9163,7 +9145,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -9199,7 +9181,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -9211,7 +9193,7 @@
         <v>31</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -9247,7 +9229,7 @@
         <v>50</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -9259,7 +9241,7 @@
         <v>31</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -9295,7 +9277,7 @@
         <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -9307,7 +9289,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -9343,7 +9325,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -9355,7 +9337,7 @@
         <v>27</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -9391,7 +9373,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -9403,7 +9385,7 @@
         <v>40</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -9439,7 +9421,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -9451,7 +9433,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -9487,7 +9469,7 @@
         <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -9499,7 +9481,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -9535,7 +9517,7 @@
         <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -9547,7 +9529,7 @@
         <v>49</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -9583,7 +9565,7 @@
         <v>50</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -9595,7 +9577,7 @@
         <v>31</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -9631,7 +9613,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -9643,7 +9625,7 @@
         <v>31</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -9679,7 +9661,7 @@
         <v>50</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -9691,7 +9673,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -9727,7 +9709,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -9739,7 +9721,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -9775,7 +9757,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -9787,7 +9769,7 @@
         <v>49</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -9840,7 +9822,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -9852,7 +9834,7 @@
         <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -9888,7 +9870,7 @@
         <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -9900,7 +9882,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -9936,7 +9918,7 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -9948,7 +9930,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -9984,7 +9966,7 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -9996,7 +9978,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -10032,7 +10014,7 @@
         <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -10044,7 +10026,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -10080,7 +10062,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -10092,7 +10074,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -10128,7 +10110,7 @@
         <v>60</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -10140,7 +10122,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -10176,7 +10158,7 @@
         <v>60</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -10188,7 +10170,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -10224,7 +10206,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -10236,7 +10218,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -10272,7 +10254,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -10284,7 +10266,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -10320,7 +10302,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -10332,7 +10314,7 @@
         <v>40</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -10368,7 +10350,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -10380,7 +10362,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -10416,7 +10398,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -10428,7 +10410,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -10464,7 +10446,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -10476,7 +10458,7 @@
         <v>40</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -10512,7 +10494,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -10524,7 +10506,7 @@
         <v>27</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -10560,7 +10542,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -10572,7 +10554,7 @@
         <v>40</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -10608,7 +10590,7 @@
         <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -10620,7 +10602,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -10656,7 +10638,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -10668,7 +10650,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -10704,7 +10686,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -10716,7 +10698,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -10752,7 +10734,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -10764,7 +10746,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -10800,7 +10782,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -10812,7 +10794,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -10848,7 +10830,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -10860,7 +10842,7 @@
         <v>49</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -10896,7 +10878,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -10908,7 +10890,7 @@
         <v>27</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -10944,7 +10926,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -10956,7 +10938,7 @@
         <v>49</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -11007,7 +10989,7 @@
         <v>70</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -11019,7 +11001,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -11055,7 +11037,7 @@
         <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -11067,7 +11049,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -11103,7 +11085,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -11115,7 +11097,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -11151,7 +11133,7 @@
         <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -11163,7 +11145,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -11199,7 +11181,7 @@
         <v>70</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -11211,7 +11193,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -11247,7 +11229,7 @@
         <v>70</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -11259,7 +11241,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -11295,7 +11277,7 @@
         <v>70</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -11307,7 +11289,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -11343,7 +11325,7 @@
         <v>70</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -11355,7 +11337,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -11391,7 +11373,7 @@
         <v>70</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -11403,7 +11385,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -11439,7 +11421,7 @@
         <v>70</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -11451,7 +11433,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -11487,7 +11469,7 @@
         <v>70</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -11499,7 +11481,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -11535,7 +11517,7 @@
         <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -11547,7 +11529,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -11583,7 +11565,7 @@
         <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -11595,7 +11577,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -11631,7 +11613,7 @@
         <v>70</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -11643,7 +11625,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -11679,7 +11661,7 @@
         <v>70</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -11691,7 +11673,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -11727,7 +11709,7 @@
         <v>70</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -11739,7 +11721,7 @@
         <v>40</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -11775,7 +11757,7 @@
         <v>70</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -11787,7 +11769,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -11823,7 +11805,7 @@
         <v>70</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -11835,7 +11817,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -11871,7 +11853,7 @@
         <v>70</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -11883,7 +11865,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -11919,7 +11901,7 @@
         <v>70</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -11931,7 +11913,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -11967,7 +11949,7 @@
         <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -11979,7 +11961,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -12015,7 +11997,7 @@
         <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -12027,7 +12009,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -12063,7 +12045,7 @@
         <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -12075,7 +12057,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -12111,7 +12093,7 @@
         <v>70</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -12123,7 +12105,7 @@
         <v>49</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -12450,7 +12432,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -12462,7 +12444,7 @@
         <v>24</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -12498,7 +12480,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -12510,7 +12492,7 @@
         <v>27</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -12546,7 +12528,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -12558,7 +12540,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -12594,7 +12576,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -12606,7 +12588,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -12642,7 +12624,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -12654,7 +12636,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -12690,7 +12672,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -12702,7 +12684,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -12738,7 +12720,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -12750,7 +12732,7 @@
         <v>27</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -12786,7 +12768,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -12798,7 +12780,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -12834,7 +12816,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -12846,7 +12828,7 @@
         <v>40</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -12882,7 +12864,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -12894,7 +12876,7 @@
         <v>27</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -12930,7 +12912,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -12942,7 +12924,7 @@
         <v>40</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -12978,7 +12960,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -12990,7 +12972,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -13026,7 +13008,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -13038,7 +13020,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -13074,7 +13056,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -13086,7 +13068,7 @@
         <v>40</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -13122,7 +13104,7 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -13134,7 +13116,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -13170,7 +13152,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -13182,7 +13164,7 @@
         <v>40</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -13218,7 +13200,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -13230,7 +13212,7 @@
         <v>49</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -13266,7 +13248,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -13278,7 +13260,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -13314,7 +13296,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -13326,7 +13308,7 @@
         <v>49</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -13362,7 +13344,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -13374,7 +13356,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -13410,7 +13392,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -13422,7 +13404,7 @@
         <v>31</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -13458,7 +13440,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -13470,7 +13452,7 @@
         <v>49</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -13506,7 +13488,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -13518,7 +13500,7 @@
         <v>27</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -13554,7 +13536,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -13566,7 +13548,7 @@
         <v>49</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -13602,7 +13584,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -13614,7 +13596,7 @@
         <v>24</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -13650,7 +13632,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -13662,7 +13644,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -13698,7 +13680,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -13710,7 +13692,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -13746,7 +13728,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -13758,7 +13740,7 @@
         <v>31</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -13794,7 +13776,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -13806,7 +13788,7 @@
         <v>31</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -13842,7 +13824,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -13854,7 +13836,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -13890,7 +13872,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -13902,7 +13884,7 @@
         <v>27</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -13938,7 +13920,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -13950,7 +13932,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -13986,7 +13968,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -13998,7 +13980,7 @@
         <v>40</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -14034,7 +14016,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -14046,7 +14028,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -14082,7 +14064,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -14094,7 +14076,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -14130,7 +14112,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -14142,7 +14124,7 @@
         <v>31</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -14178,7 +14160,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -14190,7 +14172,7 @@
         <v>31</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -14226,7 +14208,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -14238,7 +14220,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -14274,7 +14256,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -14286,7 +14268,7 @@
         <v>27</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -14322,7 +14304,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -14334,7 +14316,7 @@
         <v>40</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -14370,7 +14352,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -14382,7 +14364,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -14418,7 +14400,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -14430,7 +14412,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -14466,7 +14448,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -14478,7 +14460,7 @@
         <v>49</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -14514,7 +14496,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -14526,7 +14508,7 @@
         <v>31</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -14562,7 +14544,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -14574,7 +14556,7 @@
         <v>31</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -14610,7 +14592,7 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -14622,7 +14604,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -14658,7 +14640,7 @@
         <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -14670,7 +14652,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -14706,7 +14688,7 @@
         <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -14718,7 +14700,7 @@
         <v>49</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -14771,7 +14753,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -14783,7 +14765,7 @@
         <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -14819,7 +14801,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -14831,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -14867,7 +14849,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -14879,7 +14861,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -14915,7 +14897,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -14927,7 +14909,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -14963,7 +14945,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -14975,7 +14957,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -15011,7 +14993,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -15023,7 +15005,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -15059,7 +15041,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -15071,7 +15053,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -15107,7 +15089,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -15119,7 +15101,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -15155,7 +15137,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -15167,7 +15149,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -15203,7 +15185,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -15215,7 +15197,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -15251,7 +15233,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -15263,7 +15245,7 @@
         <v>40</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -15299,7 +15281,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15311,7 +15293,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -15347,7 +15329,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15359,7 +15341,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -15395,7 +15377,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15407,7 +15389,7 @@
         <v>40</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -15443,7 +15425,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15455,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -15491,7 +15473,7 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15503,7 +15485,7 @@
         <v>40</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -15539,7 +15521,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -15551,7 +15533,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -15587,7 +15569,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -15599,7 +15581,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -15635,7 +15617,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -15647,7 +15629,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -15683,7 +15665,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -15695,7 +15677,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -15731,7 +15713,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -15743,7 +15725,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -15779,7 +15761,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -15791,7 +15773,7 @@
         <v>49</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -15827,7 +15809,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -15839,7 +15821,7 @@
         <v>27</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -15875,7 +15857,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -15887,7 +15869,7 @@
         <v>49</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -15938,7 +15920,7 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -15950,7 +15932,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -15986,7 +15968,7 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -15998,7 +15980,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -16034,7 +16016,7 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -16046,7 +16028,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -16082,7 +16064,7 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -16094,7 +16076,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -16130,7 +16112,7 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -16142,7 +16124,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -16178,7 +16160,7 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -16190,7 +16172,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -16226,7 +16208,7 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -16238,7 +16220,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -16274,7 +16256,7 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16286,7 +16268,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -16322,7 +16304,7 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16334,7 +16316,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -16370,7 +16352,7 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16382,7 +16364,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -16418,7 +16400,7 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16430,7 +16412,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -16466,7 +16448,7 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -16478,7 +16460,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -16514,7 +16496,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -16526,7 +16508,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -16562,7 +16544,7 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -16574,7 +16556,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -16610,7 +16592,7 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -16622,7 +16604,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -16658,7 +16640,7 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -16670,7 +16652,7 @@
         <v>40</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -16706,7 +16688,7 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -16718,7 +16700,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -16754,7 +16736,7 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -16766,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -16802,7 +16784,7 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -16814,7 +16796,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -16850,7 +16832,7 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -16862,7 +16844,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -16898,7 +16880,7 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -16910,7 +16892,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -16946,7 +16928,7 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -16958,7 +16940,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -16994,7 +16976,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -17006,7 +16988,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -17042,7 +17024,7 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -17054,7 +17036,7 @@
         <v>49</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -17377,7 +17359,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17386,10 +17368,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17424,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17433,10 +17415,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -17508,7 +17490,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17526,7 +17508,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17557,16 +17539,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -17603,10 +17585,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -17676,7 +17658,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -17685,10 +17667,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -17700,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -17722,7 +17704,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -17734,7 +17716,7 @@
         <v>31</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -17746,7 +17728,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -17768,7 +17750,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -17780,7 +17762,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -17812,7 +17794,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -17824,7 +17806,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>357</v>
+        <v>117</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -17836,7 +17818,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -17858,7 +17840,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -17867,10 +17849,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>360</v>
+        <v>112</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -17882,7 +17864,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -17904,7 +17886,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -17916,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>360</v>
+        <v>112</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -17948,7 +17930,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -17957,10 +17939,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>364</v>
+        <v>139</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18006,7 +17988,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>367</v>
+        <v>144</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18038,7 +18020,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18050,7 +18032,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>364</v>
+        <v>139</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18100,7 +18082,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18109,10 +18091,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>370</v>
+        <v>166</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -18124,7 +18106,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18146,7 +18128,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18157,8 +18139,8 @@
       <c r="I17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="12" t="s">
-        <v>373</v>
+      <c r="J17" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="K17" s="2">
         <v>11</v>
@@ -18190,7 +18172,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18202,7 +18184,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>375</v>
+        <v>171</v>
       </c>
       <c r="K18" s="2">
         <v>12</v>
@@ -18234,7 +18216,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18243,10 +18225,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18258,7 +18240,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18280,7 +18262,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18292,7 +18274,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18324,7 +18306,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18336,7 +18318,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18368,7 +18350,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18377,10 +18359,10 @@
         <v>36</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18392,7 +18374,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18414,7 +18396,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18426,7 +18408,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18458,7 +18440,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -18470,7 +18452,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -18507,10 +18489,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -18522,7 +18504,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -18538,7 +18520,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -18549,10 +18531,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -18564,7 +18546,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -18589,10 +18571,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -18604,7 +18586,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -18629,10 +18611,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -18644,7 +18626,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -18660,7 +18642,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -18671,10 +18653,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -18686,7 +18668,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -18711,10 +18693,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -18726,7 +18708,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -18751,10 +18733,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -18766,7 +18748,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -18782,7 +18764,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -18793,10 +18775,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -18808,7 +18790,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -18833,10 +18815,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -18848,7 +18830,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -18873,10 +18855,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -18888,7 +18870,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -18904,7 +18886,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -18915,10 +18897,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -18930,7 +18912,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -18955,10 +18937,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -18970,7 +18952,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -18995,10 +18977,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -19010,7 +18992,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19026,7 +19008,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19037,10 +19019,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -19052,7 +19034,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19077,10 +19059,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -19092,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19117,10 +19099,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -19132,7 +19114,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19148,7 +19130,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19159,10 +19141,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -19174,7 +19156,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19199,10 +19181,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -19214,7 +19196,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19239,10 +19221,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -19254,7 +19236,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19270,7 +19252,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19281,10 +19263,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -19296,7 +19278,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19321,10 +19303,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -19336,7 +19318,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19361,10 +19343,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -19376,7 +19358,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19392,7 +19374,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19403,10 +19385,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -19418,7 +19400,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19443,10 +19425,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -19458,7 +19440,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -1406,7 +1406,16 @@
     <t>LegendId</t>
   </si>
   <si>
-    <t>治愈之面</t>
+    <t>治愈护面</t>
+  </si>
+  <si>
+    <t>5000,5</t>
+  </si>
+  <si>
+    <t>回复效果提高100%</t>
+  </si>
+  <si>
+    <t>治愈护手</t>
   </si>
   <si>
     <t>3,1003</t>
@@ -1415,19 +1424,10 @@
     <t>500,5</t>
   </si>
   <si>
-    <t>回复效果提高100%</t>
-  </si>
-  <si>
-    <t>治愈之镯</t>
-  </si>
-  <si>
-    <t>5000,5</t>
-  </si>
-  <si>
     <t>减伤，诅咒，闪避</t>
   </si>
   <si>
-    <t>治愈之甲</t>
+    <t>治愈护袍</t>
   </si>
   <si>
     <t>财富扳指</t>
@@ -17667,10 +17667,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>352</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>353</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -17682,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -17704,7 +17704,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -17713,7 +17713,7 @@
         <v>34</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>31</v>
+        <v>355</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>356</v>
@@ -17762,7 +17762,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -17849,7 +17849,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>112</v>
@@ -17939,7 +17939,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>139</v>
@@ -18091,7 +18091,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J16" s="13" t="s">
         <v>166</v>
@@ -18225,7 +18225,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>373</v>
@@ -18359,7 +18359,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>379</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -3916,6 +3916,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="1">
+        <f>E31/10*3+1</f>
         <v>4</v>
       </c>
       <c r="O31" s="1">
@@ -3963,6 +3964,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="1">
+        <f>E32/10*3+2</f>
         <v>5</v>
       </c>
       <c r="O32" s="1">
@@ -4010,6 +4012,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
+        <f t="shared" ref="N33:N38" si="0">E33/10*3+3</f>
         <v>6</v>
       </c>
       <c r="O33" s="1">
@@ -4057,6 +4060,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O34" s="1">
@@ -4104,6 +4108,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O35" s="1">
@@ -4151,6 +4156,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O36" s="1">
@@ -4198,6 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O37" s="1">
@@ -4245,6 +4252,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="O38" s="1">
@@ -4292,6 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
+        <f>E39/10*3+1</f>
         <v>4</v>
       </c>
       <c r="O39" s="1">
@@ -4339,6 +4348,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
+        <f>E40/10*3+2</f>
         <v>5</v>
       </c>
       <c r="O40" s="1">
@@ -4386,6 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
+        <f t="shared" ref="N41:N46" si="1">E41/10*3+3</f>
         <v>6</v>
       </c>
       <c r="O41" s="1">
@@ -4433,6 +4444,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="O42" s="1">
@@ -4480,6 +4492,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="O43" s="1">
@@ -4527,6 +4540,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="O44" s="1">
@@ -4574,6 +4588,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="O45" s="1">
@@ -4621,6 +4636,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="1">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="O46" s="1">
@@ -4668,6 +4684,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="1">
+        <f>E47/10*3+1</f>
         <v>4</v>
       </c>
       <c r="O47" s="1">
@@ -4715,6 +4732,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="1">
+        <f>E48/10*3+2</f>
         <v>5</v>
       </c>
       <c r="O48" s="1">
@@ -4762,6 +4780,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
+        <f t="shared" ref="N49:N54" si="2">E49/10*3+3</f>
         <v>6</v>
       </c>
       <c r="O49" s="1">
@@ -4809,6 +4828,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O50" s="1">
@@ -4856,6 +4876,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O51" s="1">
@@ -4903,6 +4924,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="1">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O52" s="1">
@@ -4950,6 +4972,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="1">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O53" s="1">
@@ -4997,6 +5020,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O54" s="1">
@@ -5061,6 +5085,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
+        <f>E56/10*3+1</f>
         <v>7</v>
       </c>
       <c r="O56" s="1">
@@ -5108,6 +5133,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
+        <f>E57/10*3+2</f>
         <v>8</v>
       </c>
       <c r="O57" s="1">
@@ -5155,6 +5181,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
+        <f t="shared" ref="N58:N63" si="3">E58/10*3+3</f>
         <v>9</v>
       </c>
       <c r="O58" s="1">
@@ -5202,7 +5229,8 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="O59" s="1">
         <v>5</v>
@@ -5249,7 +5277,8 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="O60" s="1">
         <v>5</v>
@@ -5296,6 +5325,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="O61" s="1">
@@ -5343,7 +5373,8 @@
         <v>0</v>
       </c>
       <c r="N62" s="1">
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="O62" s="1">
         <v>5</v>
@@ -5390,7 +5421,8 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="O63" s="1">
         <v>5</v>
@@ -5437,7 +5469,8 @@
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <v>9</v>
+        <f>E64/10*3+1</f>
+        <v>7</v>
       </c>
       <c r="O64" s="1">
         <v>5</v>
@@ -5484,7 +5517,8 @@
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <v>7</v>
+        <f>E65/10*3+2</f>
+        <v>8</v>
       </c>
       <c r="O65" s="1">
         <v>5</v>
@@ -5531,7 +5565,8 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <v>8</v>
+        <f t="shared" ref="N66:N71" si="4">E66/10*3+3</f>
+        <v>9</v>
       </c>
       <c r="O66" s="1">
         <v>5</v>
@@ -5578,6 +5613,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="O67" s="1">
@@ -5625,7 +5661,8 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="O68" s="1">
         <v>5</v>
@@ -5672,7 +5709,8 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="O69" s="1">
         <v>5</v>
@@ -5719,6 +5757,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="O70" s="1">
@@ -5766,7 +5805,8 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="O71" s="1">
         <v>5</v>
@@ -5813,7 +5853,8 @@
         <v>0</v>
       </c>
       <c r="N72" s="1">
-        <v>8</v>
+        <f>E72/10*3+1</f>
+        <v>7</v>
       </c>
       <c r="O72" s="1">
         <v>5</v>
@@ -5860,7 +5901,8 @@
         <v>0</v>
       </c>
       <c r="N73" s="1">
-        <v>9</v>
+        <f>E73/10*3+2</f>
+        <v>8</v>
       </c>
       <c r="O73" s="1">
         <v>5</v>
@@ -5907,7 +5949,8 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <v>7</v>
+        <f t="shared" ref="N74:N79" si="5">E74/10*3+3</f>
+        <v>9</v>
       </c>
       <c r="O74" s="1">
         <v>5</v>
@@ -5954,7 +5997,8 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="O75" s="1">
         <v>5</v>
@@ -6001,6 +6045,7 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O76" s="1">
@@ -6048,7 +6093,8 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="O77" s="1">
         <v>5</v>
@@ -6095,7 +6141,8 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="O78" s="1">
         <v>5</v>
@@ -6142,6 +6189,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O79" s="1">
@@ -6204,6 +6252,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="1">
+        <f>E81/10*3+1</f>
         <v>10</v>
       </c>
       <c r="O81" s="1">
@@ -6251,6 +6300,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="1">
+        <f>E82/10*3+2</f>
         <v>11</v>
       </c>
       <c r="O82" s="1">
@@ -6298,6 +6348,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
+        <f t="shared" ref="N83:N88" si="6">E83/10*3+3</f>
         <v>12</v>
       </c>
       <c r="O83" s="1">
@@ -6345,6 +6396,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="O84" s="1">
@@ -6392,6 +6444,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="O85" s="1">
@@ -6439,6 +6492,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="O86" s="1">
@@ -6486,6 +6540,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="O87" s="1">
@@ -6533,6 +6588,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="O88" s="1">
@@ -6580,6 +6636,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="1">
+        <f>E89/10*3+1</f>
         <v>10</v>
       </c>
       <c r="O89" s="1">
@@ -6627,6 +6684,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="1">
+        <f>E90/10*3+2</f>
         <v>11</v>
       </c>
       <c r="O90" s="1">
@@ -6674,6 +6732,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
+        <f t="shared" ref="N91:N96" si="7">E91/10*3+3</f>
         <v>12</v>
       </c>
       <c r="O91" s="1">
@@ -6721,6 +6780,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="O92" s="1">
@@ -6768,6 +6828,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="O93" s="1">
@@ -6815,6 +6876,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="O94" s="1">
@@ -6862,6 +6924,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="O95" s="1">
@@ -6909,6 +6972,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="O96" s="1">
@@ -6956,6 +7020,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="1">
+        <f>E97/10*3+1</f>
         <v>10</v>
       </c>
       <c r="O97" s="1">
@@ -7003,6 +7068,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="1">
+        <f>E98/10*3+2</f>
         <v>11</v>
       </c>
       <c r="O98" s="1">
@@ -7050,6 +7116,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
+        <f t="shared" ref="N99:N104" si="8">E99/10*3+3</f>
         <v>12</v>
       </c>
       <c r="O99" s="1">
@@ -7097,6 +7164,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="1">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="O100" s="1">
@@ -7144,6 +7212,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="O101" s="1">
@@ -7191,6 +7260,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="O102" s="1">
@@ -7238,6 +7308,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="1">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="O103" s="1">
@@ -7285,6 +7356,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="1">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="O104" s="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="420">
   <si>
     <t>_id</t>
   </si>
@@ -884,226 +884,238 @@
     <t>金龙法刃</t>
   </si>
   <si>
+    <t>金龙法甲</t>
+  </si>
+  <si>
+    <t>金龙法链</t>
+  </si>
+  <si>
+    <t>金龙法盔</t>
+  </si>
+  <si>
+    <t>金龙法镯</t>
+  </si>
+  <si>
+    <t>金龙法戒</t>
+  </si>
+  <si>
+    <t>金龙法带</t>
+  </si>
+  <si>
+    <t>金龙法靴</t>
+  </si>
+  <si>
+    <t>金龙道刃</t>
+  </si>
+  <si>
+    <t>金龙道甲</t>
+  </si>
+  <si>
+    <t>金龙道链</t>
+  </si>
+  <si>
+    <t>金龙道盔</t>
+  </si>
+  <si>
+    <t>金龙道镯</t>
+  </si>
+  <si>
+    <t>金龙道戒</t>
+  </si>
+  <si>
+    <t>金龙道带</t>
+  </si>
+  <si>
+    <t>金龙道靴</t>
+  </si>
+  <si>
+    <t>木龙战刃</t>
+  </si>
+  <si>
+    <t>16000,15</t>
+  </si>
+  <si>
+    <t>木龙战甲</t>
+  </si>
+  <si>
+    <t>木龙战链</t>
+  </si>
+  <si>
+    <t>8000,8</t>
+  </si>
+  <si>
+    <t>木龙战盔</t>
+  </si>
+  <si>
+    <t>木龙战镯</t>
+  </si>
+  <si>
+    <t>木龙战戒</t>
+  </si>
+  <si>
+    <t>木龙战带</t>
+  </si>
+  <si>
+    <t>木龙战靴</t>
+  </si>
+  <si>
+    <t>木龙法刃</t>
+  </si>
+  <si>
+    <t>木龙法甲</t>
+  </si>
+  <si>
+    <t>木龙法链</t>
+  </si>
+  <si>
+    <t>木龙法盔</t>
+  </si>
+  <si>
+    <t>木龙法镯</t>
+  </si>
+  <si>
+    <t>木龙法戒</t>
+  </si>
+  <si>
+    <t>木龙法带</t>
+  </si>
+  <si>
+    <t>木龙法靴</t>
+  </si>
+  <si>
+    <t>木龙道刃</t>
+  </si>
+  <si>
+    <t>木龙道甲</t>
+  </si>
+  <si>
+    <t>木龙道链</t>
+  </si>
+  <si>
+    <t>木龙道盔</t>
+  </si>
+  <si>
+    <t>木龙道镯</t>
+  </si>
+  <si>
+    <t>木龙道戒</t>
+  </si>
+  <si>
+    <t>木龙道带</t>
+  </si>
+  <si>
+    <t>木龙道靴</t>
+  </si>
+  <si>
+    <t>土龙战刃</t>
+  </si>
+  <si>
+    <t>30000,20</t>
+  </si>
+  <si>
+    <t>土龙战甲</t>
+  </si>
+  <si>
+    <t>土龙战链</t>
+  </si>
+  <si>
+    <t>15000,10</t>
+  </si>
+  <si>
+    <t>土龙战盔</t>
+  </si>
+  <si>
+    <t>土龙战镯</t>
+  </si>
+  <si>
+    <t>土龙战戒</t>
+  </si>
+  <si>
+    <t>土龙战带</t>
+  </si>
+  <si>
+    <t>土龙战靴</t>
+  </si>
+  <si>
+    <t>土龙法刃</t>
+  </si>
+  <si>
+    <t>土龙法甲</t>
+  </si>
+  <si>
+    <t>土龙法链</t>
+  </si>
+  <si>
+    <t>土龙法盔</t>
+  </si>
+  <si>
+    <t>土龙法镯</t>
+  </si>
+  <si>
+    <t>土龙法戒</t>
+  </si>
+  <si>
+    <t>土龙法带</t>
+  </si>
+  <si>
+    <t>土龙法靴</t>
+  </si>
+  <si>
+    <t>土龙道刃</t>
+  </si>
+  <si>
+    <t>土龙道甲</t>
+  </si>
+  <si>
+    <t>土龙道链</t>
+  </si>
+  <si>
+    <t>土龙道盔</t>
+  </si>
+  <si>
+    <t>土龙道镯</t>
+  </si>
+  <si>
+    <t>土龙道戒</t>
+  </si>
+  <si>
+    <t>土龙道带</t>
+  </si>
+  <si>
+    <t>土龙道靴</t>
+  </si>
+  <si>
+    <t>冰龙战刃</t>
+  </si>
+  <si>
     <t>20,5</t>
   </si>
   <si>
-    <t>金龙法甲</t>
+    <t>冰龙战甲</t>
   </si>
   <si>
     <t>10,2</t>
   </si>
   <si>
-    <t>金龙法链</t>
-  </si>
-  <si>
-    <t>金龙法盔</t>
+    <t>冰龙战链</t>
+  </si>
+  <si>
+    <t>冰龙战盔</t>
   </si>
   <si>
     <t>100,10</t>
   </si>
   <si>
-    <t>金龙法镯</t>
-  </si>
-  <si>
-    <t>金龙法戒</t>
-  </si>
-  <si>
-    <t>金龙法带</t>
+    <t>冰龙战镯</t>
+  </si>
+  <si>
+    <t>冰龙战戒</t>
+  </si>
+  <si>
+    <t>冰龙战带</t>
   </si>
   <si>
     <t>5,1</t>
-  </si>
-  <si>
-    <t>金龙法靴</t>
-  </si>
-  <si>
-    <t>金龙道刃</t>
-  </si>
-  <si>
-    <t>金龙道甲</t>
-  </si>
-  <si>
-    <t>金龙道链</t>
-  </si>
-  <si>
-    <t>金龙道盔</t>
-  </si>
-  <si>
-    <t>金龙道镯</t>
-  </si>
-  <si>
-    <t>金龙道戒</t>
-  </si>
-  <si>
-    <t>金龙道带</t>
-  </si>
-  <si>
-    <t>金龙道靴</t>
-  </si>
-  <si>
-    <t>木龙战刃</t>
-  </si>
-  <si>
-    <t>木龙战甲</t>
-  </si>
-  <si>
-    <t>木龙战链</t>
-  </si>
-  <si>
-    <t>木龙战盔</t>
-  </si>
-  <si>
-    <t>木龙战镯</t>
-  </si>
-  <si>
-    <t>木龙战戒</t>
-  </si>
-  <si>
-    <t>木龙战带</t>
-  </si>
-  <si>
-    <t>木龙战靴</t>
-  </si>
-  <si>
-    <t>木龙法刃</t>
-  </si>
-  <si>
-    <t>木龙法甲</t>
-  </si>
-  <si>
-    <t>木龙法链</t>
-  </si>
-  <si>
-    <t>木龙法盔</t>
-  </si>
-  <si>
-    <t>木龙法镯</t>
-  </si>
-  <si>
-    <t>木龙法戒</t>
-  </si>
-  <si>
-    <t>木龙法带</t>
-  </si>
-  <si>
-    <t>木龙法靴</t>
-  </si>
-  <si>
-    <t>木龙道刃</t>
-  </si>
-  <si>
-    <t>木龙道甲</t>
-  </si>
-  <si>
-    <t>木龙道链</t>
-  </si>
-  <si>
-    <t>木龙道盔</t>
-  </si>
-  <si>
-    <t>木龙道镯</t>
-  </si>
-  <si>
-    <t>木龙道戒</t>
-  </si>
-  <si>
-    <t>木龙道带</t>
-  </si>
-  <si>
-    <t>木龙道靴</t>
-  </si>
-  <si>
-    <t>土龙战刃</t>
-  </si>
-  <si>
-    <t>土龙战甲</t>
-  </si>
-  <si>
-    <t>土龙战链</t>
-  </si>
-  <si>
-    <t>土龙战盔</t>
-  </si>
-  <si>
-    <t>土龙战镯</t>
-  </si>
-  <si>
-    <t>土龙战戒</t>
-  </si>
-  <si>
-    <t>土龙战带</t>
-  </si>
-  <si>
-    <t>土龙战靴</t>
-  </si>
-  <si>
-    <t>土龙法刃</t>
-  </si>
-  <si>
-    <t>土龙法甲</t>
-  </si>
-  <si>
-    <t>土龙法链</t>
-  </si>
-  <si>
-    <t>土龙法盔</t>
-  </si>
-  <si>
-    <t>土龙法镯</t>
-  </si>
-  <si>
-    <t>土龙法戒</t>
-  </si>
-  <si>
-    <t>土龙法带</t>
-  </si>
-  <si>
-    <t>土龙法靴</t>
-  </si>
-  <si>
-    <t>土龙道刃</t>
-  </si>
-  <si>
-    <t>土龙道甲</t>
-  </si>
-  <si>
-    <t>土龙道链</t>
-  </si>
-  <si>
-    <t>土龙道盔</t>
-  </si>
-  <si>
-    <t>土龙道镯</t>
-  </si>
-  <si>
-    <t>土龙道戒</t>
-  </si>
-  <si>
-    <t>土龙道带</t>
-  </si>
-  <si>
-    <t>土龙道靴</t>
-  </si>
-  <si>
-    <t>冰龙战刃</t>
-  </si>
-  <si>
-    <t>冰龙战甲</t>
-  </si>
-  <si>
-    <t>冰龙战链</t>
-  </si>
-  <si>
-    <t>冰龙战盔</t>
-  </si>
-  <si>
-    <t>冰龙战镯</t>
-  </si>
-  <si>
-    <t>冰龙战戒</t>
-  </si>
-  <si>
-    <t>冰龙战带</t>
   </si>
   <si>
     <t>冰龙战靴</t>
@@ -6262,7 +6274,7 @@
         <v>8</v>
       </c>
       <c r="Q81" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -6310,7 +6322,7 @@
         <v>8</v>
       </c>
       <c r="Q82" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -6358,7 +6370,7 @@
         <v>4</v>
       </c>
       <c r="Q83" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -6406,7 +6418,7 @@
         <v>4</v>
       </c>
       <c r="Q84" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -6454,7 +6466,7 @@
         <v>4</v>
       </c>
       <c r="Q85" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -6502,7 +6514,7 @@
         <v>4</v>
       </c>
       <c r="Q86" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -6550,7 +6562,7 @@
         <v>4</v>
       </c>
       <c r="Q87" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -6598,7 +6610,7 @@
         <v>4</v>
       </c>
       <c r="Q88" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -6646,7 +6658,7 @@
         <v>8</v>
       </c>
       <c r="Q89" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -6694,7 +6706,7 @@
         <v>8</v>
       </c>
       <c r="Q90" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -6742,7 +6754,7 @@
         <v>4</v>
       </c>
       <c r="Q91" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -6790,7 +6802,7 @@
         <v>4</v>
       </c>
       <c r="Q92" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -6838,7 +6850,7 @@
         <v>4</v>
       </c>
       <c r="Q93" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -6886,7 +6898,7 @@
         <v>4</v>
       </c>
       <c r="Q94" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -6934,7 +6946,7 @@
         <v>4</v>
       </c>
       <c r="Q95" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -6982,7 +6994,7 @@
         <v>4</v>
       </c>
       <c r="Q96" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -7030,7 +7042,7 @@
         <v>8</v>
       </c>
       <c r="Q97" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -7078,7 +7090,7 @@
         <v>8</v>
       </c>
       <c r="Q98" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -7126,7 +7138,7 @@
         <v>4</v>
       </c>
       <c r="Q99" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -7174,7 +7186,7 @@
         <v>4</v>
       </c>
       <c r="Q100" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -7222,7 +7234,7 @@
         <v>4</v>
       </c>
       <c r="Q101" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -7270,7 +7282,7 @@
         <v>4</v>
       </c>
       <c r="Q102" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -7318,7 +7330,7 @@
         <v>4</v>
       </c>
       <c r="Q103" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -7366,7 +7378,7 @@
         <v>4</v>
       </c>
       <c r="Q104" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -7607,7 +7619,7 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7655,7 +7667,7 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7703,7 +7715,7 @@
         <v>5</v>
       </c>
       <c r="Q8" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7751,7 +7763,7 @@
         <v>5</v>
       </c>
       <c r="Q9" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7799,7 +7811,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7847,7 +7859,7 @@
         <v>5</v>
       </c>
       <c r="Q11" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7895,7 +7907,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7943,7 +7955,7 @@
         <v>5</v>
       </c>
       <c r="Q13" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7991,7 +8003,7 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8039,7 +8051,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8087,7 +8099,7 @@
         <v>5</v>
       </c>
       <c r="Q16" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8135,7 +8147,7 @@
         <v>5</v>
       </c>
       <c r="Q17" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8183,7 +8195,7 @@
         <v>5</v>
       </c>
       <c r="Q18" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8231,7 +8243,7 @@
         <v>5</v>
       </c>
       <c r="Q19" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8279,7 +8291,7 @@
         <v>5</v>
       </c>
       <c r="Q20" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8327,7 +8339,7 @@
         <v>5</v>
       </c>
       <c r="Q21" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8375,7 +8387,7 @@
         <v>10</v>
       </c>
       <c r="Q22" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8423,7 +8435,7 @@
         <v>10</v>
       </c>
       <c r="Q23" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8471,7 +8483,7 @@
         <v>5</v>
       </c>
       <c r="Q24" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8519,7 +8531,7 @@
         <v>5</v>
       </c>
       <c r="Q25" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8567,7 +8579,7 @@
         <v>5</v>
       </c>
       <c r="Q26" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8615,7 +8627,7 @@
         <v>5</v>
       </c>
       <c r="Q27" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8663,7 +8675,7 @@
         <v>5</v>
       </c>
       <c r="Q28" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8711,7 +8723,7 @@
         <v>5</v>
       </c>
       <c r="Q29" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8759,7 +8771,7 @@
         <v>15</v>
       </c>
       <c r="Q31" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8807,7 +8819,7 @@
         <v>15</v>
       </c>
       <c r="Q32" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8855,7 +8867,7 @@
         <v>7</v>
       </c>
       <c r="Q33" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8903,7 +8915,7 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8951,7 +8963,7 @@
         <v>7</v>
       </c>
       <c r="Q35" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8999,7 +9011,7 @@
         <v>7</v>
       </c>
       <c r="Q36" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -9047,7 +9059,7 @@
         <v>7</v>
       </c>
       <c r="Q37" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -9095,7 +9107,7 @@
         <v>7</v>
       </c>
       <c r="Q38" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -9121,7 +9133,7 @@
         <v>40</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -9143,7 +9155,7 @@
         <v>15</v>
       </c>
       <c r="Q39" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -9157,7 +9169,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -9169,7 +9181,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -9191,7 +9203,7 @@
         <v>15</v>
       </c>
       <c r="Q40" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -9205,7 +9217,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -9217,7 +9229,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -9239,7 +9251,7 @@
         <v>7</v>
       </c>
       <c r="Q41" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -9253,7 +9265,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -9265,7 +9277,7 @@
         <v>31</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -9287,7 +9299,7 @@
         <v>7</v>
       </c>
       <c r="Q42" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -9301,7 +9313,7 @@
         <v>50</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -9313,7 +9325,7 @@
         <v>31</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -9335,7 +9347,7 @@
         <v>7</v>
       </c>
       <c r="Q43" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -9349,7 +9361,7 @@
         <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -9361,7 +9373,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -9383,7 +9395,7 @@
         <v>7</v>
       </c>
       <c r="Q44" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -9397,7 +9409,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -9409,7 +9421,7 @@
         <v>27</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -9431,7 +9443,7 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -9445,7 +9457,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -9457,7 +9469,7 @@
         <v>40</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -9479,7 +9491,7 @@
         <v>7</v>
       </c>
       <c r="Q46" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -9493,7 +9505,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -9505,7 +9517,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -9527,7 +9539,7 @@
         <v>15</v>
       </c>
       <c r="Q47" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -9541,7 +9553,7 @@
         <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -9553,7 +9565,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -9575,7 +9587,7 @@
         <v>15</v>
       </c>
       <c r="Q48" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -9589,7 +9601,7 @@
         <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -9601,7 +9613,7 @@
         <v>49</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -9623,7 +9635,7 @@
         <v>7</v>
       </c>
       <c r="Q49" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -9637,7 +9649,7 @@
         <v>50</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -9649,7 +9661,7 @@
         <v>31</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -9671,7 +9683,7 @@
         <v>7</v>
       </c>
       <c r="Q50" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -9685,7 +9697,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -9697,7 +9709,7 @@
         <v>31</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -9719,7 +9731,7 @@
         <v>7</v>
       </c>
       <c r="Q51" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -9733,7 +9745,7 @@
         <v>50</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -9745,7 +9757,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -9767,7 +9779,7 @@
         <v>7</v>
       </c>
       <c r="Q52" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -9781,7 +9793,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -9793,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -9815,7 +9827,7 @@
         <v>7</v>
       </c>
       <c r="Q53" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -9829,7 +9841,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -9841,7 +9853,7 @@
         <v>49</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -9863,7 +9875,7 @@
         <v>7</v>
       </c>
       <c r="Q54" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -9894,7 +9906,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -9906,7 +9918,7 @@
         <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -9928,7 +9940,7 @@
         <v>20</v>
       </c>
       <c r="Q56" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -9942,7 +9954,7 @@
         <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -9954,7 +9966,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -9976,7 +9988,7 @@
         <v>20</v>
       </c>
       <c r="Q57" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -9990,7 +10002,7 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -10002,7 +10014,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -10024,7 +10036,7 @@
         <v>10</v>
       </c>
       <c r="Q58" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -10038,7 +10050,7 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -10050,7 +10062,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -10072,7 +10084,7 @@
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -10086,7 +10098,7 @@
         <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -10098,7 +10110,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -10120,7 +10132,7 @@
         <v>10</v>
       </c>
       <c r="Q60" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -10134,7 +10146,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -10146,7 +10158,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -10168,7 +10180,7 @@
         <v>10</v>
       </c>
       <c r="Q61" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -10182,7 +10194,7 @@
         <v>60</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -10194,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -10216,7 +10228,7 @@
         <v>10</v>
       </c>
       <c r="Q62" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -10230,7 +10242,7 @@
         <v>60</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -10242,7 +10254,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -10264,7 +10276,7 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -10278,7 +10290,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -10290,7 +10302,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -10312,7 +10324,7 @@
         <v>20</v>
       </c>
       <c r="Q64" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -10326,7 +10338,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -10338,7 +10350,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -10360,7 +10372,7 @@
         <v>20</v>
       </c>
       <c r="Q65" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -10374,7 +10386,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -10386,7 +10398,7 @@
         <v>40</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -10408,7 +10420,7 @@
         <v>10</v>
       </c>
       <c r="Q66" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -10422,7 +10434,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -10434,7 +10446,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -10456,7 +10468,7 @@
         <v>10</v>
       </c>
       <c r="Q67" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -10470,7 +10482,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -10482,7 +10494,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -10504,7 +10516,7 @@
         <v>10</v>
       </c>
       <c r="Q68" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -10518,7 +10530,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -10530,7 +10542,7 @@
         <v>40</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -10552,7 +10564,7 @@
         <v>10</v>
       </c>
       <c r="Q69" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -10566,7 +10578,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -10578,7 +10590,7 @@
         <v>27</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -10600,7 +10612,7 @@
         <v>10</v>
       </c>
       <c r="Q70" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -10614,7 +10626,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -10626,7 +10638,7 @@
         <v>40</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -10648,7 +10660,7 @@
         <v>10</v>
       </c>
       <c r="Q71" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -10662,7 +10674,7 @@
         <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -10674,7 +10686,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -10696,7 +10708,7 @@
         <v>20</v>
       </c>
       <c r="Q72" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -10710,7 +10722,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -10722,7 +10734,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -10744,7 +10756,7 @@
         <v>20</v>
       </c>
       <c r="Q73" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -10758,7 +10770,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -10770,7 +10782,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -10792,7 +10804,7 @@
         <v>10</v>
       </c>
       <c r="Q74" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -10806,7 +10818,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -10818,7 +10830,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -10840,7 +10852,7 @@
         <v>10</v>
       </c>
       <c r="Q75" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -10854,7 +10866,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -10866,7 +10878,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -10888,7 +10900,7 @@
         <v>10</v>
       </c>
       <c r="Q76" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -10902,7 +10914,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -10914,7 +10926,7 @@
         <v>49</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -10936,7 +10948,7 @@
         <v>10</v>
       </c>
       <c r="Q77" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -10950,7 +10962,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -10962,7 +10974,7 @@
         <v>27</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -10984,7 +10996,7 @@
         <v>10</v>
       </c>
       <c r="Q78" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -10998,7 +11010,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -11010,7 +11022,7 @@
         <v>49</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -11032,7 +11044,7 @@
         <v>10</v>
       </c>
       <c r="Q79" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -11061,7 +11073,7 @@
         <v>70</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -11073,7 +11085,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -11095,7 +11107,7 @@
         <v>30</v>
       </c>
       <c r="Q81" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -11109,7 +11121,7 @@
         <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -11121,7 +11133,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -11143,7 +11155,7 @@
         <v>30</v>
       </c>
       <c r="Q82" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -11157,7 +11169,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -11169,7 +11181,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -11191,7 +11203,7 @@
         <v>15</v>
       </c>
       <c r="Q83" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -11217,7 +11229,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -11239,7 +11251,7 @@
         <v>15</v>
       </c>
       <c r="Q84" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -11265,7 +11277,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -11287,7 +11299,7 @@
         <v>15</v>
       </c>
       <c r="Q85" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -11313,7 +11325,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -11335,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="Q86" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -11361,7 +11373,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -11383,7 +11395,7 @@
         <v>15</v>
       </c>
       <c r="Q87" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -11409,7 +11421,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -11431,7 +11443,7 @@
         <v>15</v>
       </c>
       <c r="Q88" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -11457,7 +11469,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -11479,7 +11491,7 @@
         <v>30</v>
       </c>
       <c r="Q89" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -11505,7 +11517,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -11527,7 +11539,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -11553,7 +11565,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -11575,7 +11587,7 @@
         <v>15</v>
       </c>
       <c r="Q91" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -11601,7 +11613,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -11623,7 +11635,7 @@
         <v>15</v>
       </c>
       <c r="Q92" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -11649,7 +11661,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -11671,7 +11683,7 @@
         <v>15</v>
       </c>
       <c r="Q93" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -11697,7 +11709,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -11719,7 +11731,7 @@
         <v>15</v>
       </c>
       <c r="Q94" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -11745,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -11767,7 +11779,7 @@
         <v>15</v>
       </c>
       <c r="Q95" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -11793,7 +11805,7 @@
         <v>40</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -11815,7 +11827,7 @@
         <v>15</v>
       </c>
       <c r="Q96" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -11841,7 +11853,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -11863,7 +11875,7 @@
         <v>30</v>
       </c>
       <c r="Q97" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -11889,7 +11901,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -11911,7 +11923,7 @@
         <v>30</v>
       </c>
       <c r="Q98" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -11937,7 +11949,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -11959,7 +11971,7 @@
         <v>15</v>
       </c>
       <c r="Q99" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -11985,7 +11997,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -12007,7 +12019,7 @@
         <v>15</v>
       </c>
       <c r="Q100" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -12033,7 +12045,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -12055,7 +12067,7 @@
         <v>15</v>
       </c>
       <c r="Q101" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -12081,7 +12093,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -12103,7 +12115,7 @@
         <v>15</v>
       </c>
       <c r="Q102" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -12129,7 +12141,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -12151,7 +12163,7 @@
         <v>15</v>
       </c>
       <c r="Q103" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -12177,7 +12189,7 @@
         <v>49</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -12199,7 +12211,7 @@
         <v>15</v>
       </c>
       <c r="Q104" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -12516,7 +12528,7 @@
         <v>24</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -12538,7 +12550,7 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12552,7 +12564,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -12564,7 +12576,7 @@
         <v>27</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -12586,7 +12598,7 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12600,7 +12612,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -12612,7 +12624,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -12634,7 +12646,7 @@
         <v>5</v>
       </c>
       <c r="Q8" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12648,7 +12660,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -12660,7 +12672,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -12682,7 +12694,7 @@
         <v>5</v>
       </c>
       <c r="Q9" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12696,7 +12708,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -12708,7 +12720,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -12730,7 +12742,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12744,7 +12756,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -12756,7 +12768,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -12778,7 +12790,7 @@
         <v>5</v>
       </c>
       <c r="Q11" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12792,7 +12804,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -12804,7 +12816,7 @@
         <v>27</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -12826,7 +12838,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12840,7 +12852,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -12852,7 +12864,7 @@
         <v>24</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -12874,7 +12886,7 @@
         <v>5</v>
       </c>
       <c r="Q13" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12888,7 +12900,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -12900,7 +12912,7 @@
         <v>40</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -12922,7 +12934,7 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12936,7 +12948,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -12948,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -12970,7 +12982,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12984,7 +12996,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -12996,7 +13008,7 @@
         <v>40</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -13018,7 +13030,7 @@
         <v>5</v>
       </c>
       <c r="Q16" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13032,7 +13044,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -13044,7 +13056,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -13066,7 +13078,7 @@
         <v>5</v>
       </c>
       <c r="Q17" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13080,7 +13092,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -13092,7 +13104,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -13114,7 +13126,7 @@
         <v>5</v>
       </c>
       <c r="Q18" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13128,7 +13140,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -13140,7 +13152,7 @@
         <v>40</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -13162,7 +13174,7 @@
         <v>5</v>
       </c>
       <c r="Q19" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13176,7 +13188,7 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -13188,7 +13200,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -13210,7 +13222,7 @@
         <v>5</v>
       </c>
       <c r="Q20" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13224,7 +13236,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -13236,7 +13248,7 @@
         <v>40</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -13258,7 +13270,7 @@
         <v>5</v>
       </c>
       <c r="Q21" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13272,7 +13284,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -13284,7 +13296,7 @@
         <v>49</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -13306,7 +13318,7 @@
         <v>10</v>
       </c>
       <c r="Q22" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13320,7 +13332,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -13332,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -13354,7 +13366,7 @@
         <v>10</v>
       </c>
       <c r="Q23" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13368,7 +13380,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -13380,7 +13392,7 @@
         <v>49</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -13402,7 +13414,7 @@
         <v>5</v>
       </c>
       <c r="Q24" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13416,7 +13428,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -13428,7 +13440,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -13450,7 +13462,7 @@
         <v>5</v>
       </c>
       <c r="Q25" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13464,7 +13476,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -13476,7 +13488,7 @@
         <v>31</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -13498,7 +13510,7 @@
         <v>5</v>
       </c>
       <c r="Q26" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13512,7 +13524,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -13524,7 +13536,7 @@
         <v>49</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -13546,7 +13558,7 @@
         <v>5</v>
       </c>
       <c r="Q27" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13560,7 +13572,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -13572,7 +13584,7 @@
         <v>27</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -13594,7 +13606,7 @@
         <v>5</v>
       </c>
       <c r="Q28" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13608,7 +13620,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -13620,7 +13632,7 @@
         <v>49</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -13642,7 +13654,7 @@
         <v>5</v>
       </c>
       <c r="Q29" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13656,7 +13668,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -13668,7 +13680,7 @@
         <v>24</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -13690,7 +13702,7 @@
         <v>15</v>
       </c>
       <c r="Q31" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13704,7 +13716,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -13716,7 +13728,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -13738,7 +13750,7 @@
         <v>15</v>
       </c>
       <c r="Q32" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13752,7 +13764,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -13764,7 +13776,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -13786,7 +13798,7 @@
         <v>7</v>
       </c>
       <c r="Q33" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13800,7 +13812,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -13812,7 +13824,7 @@
         <v>31</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -13834,7 +13846,7 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13848,7 +13860,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -13860,7 +13872,7 @@
         <v>31</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -13882,7 +13894,7 @@
         <v>7</v>
       </c>
       <c r="Q35" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13896,7 +13908,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -13908,7 +13920,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -13930,7 +13942,7 @@
         <v>7</v>
       </c>
       <c r="Q36" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13944,7 +13956,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -13956,7 +13968,7 @@
         <v>27</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -13978,7 +13990,7 @@
         <v>7</v>
       </c>
       <c r="Q37" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -13992,7 +14004,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -14004,7 +14016,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -14026,7 +14038,7 @@
         <v>7</v>
       </c>
       <c r="Q38" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -14040,7 +14052,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -14052,7 +14064,7 @@
         <v>40</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -14074,7 +14086,7 @@
         <v>15</v>
       </c>
       <c r="Q39" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -14088,7 +14100,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -14100,7 +14112,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -14122,7 +14134,7 @@
         <v>15</v>
       </c>
       <c r="Q40" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -14136,7 +14148,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -14148,7 +14160,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -14170,7 +14182,7 @@
         <v>7</v>
       </c>
       <c r="Q41" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -14184,7 +14196,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -14196,7 +14208,7 @@
         <v>31</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -14218,7 +14230,7 @@
         <v>7</v>
       </c>
       <c r="Q42" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -14232,7 +14244,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -14244,7 +14256,7 @@
         <v>31</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -14266,7 +14278,7 @@
         <v>7</v>
       </c>
       <c r="Q43" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -14280,7 +14292,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -14292,7 +14304,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -14314,7 +14326,7 @@
         <v>7</v>
       </c>
       <c r="Q44" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -14328,7 +14340,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -14340,7 +14352,7 @@
         <v>27</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -14362,7 +14374,7 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -14376,7 +14388,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -14388,7 +14400,7 @@
         <v>40</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -14410,7 +14422,7 @@
         <v>7</v>
       </c>
       <c r="Q46" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -14424,7 +14436,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -14436,7 +14448,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -14458,7 +14470,7 @@
         <v>15</v>
       </c>
       <c r="Q47" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -14472,7 +14484,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -14484,7 +14496,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -14506,7 +14518,7 @@
         <v>15</v>
       </c>
       <c r="Q48" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -14520,7 +14532,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -14532,7 +14544,7 @@
         <v>49</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -14554,7 +14566,7 @@
         <v>7</v>
       </c>
       <c r="Q49" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -14568,7 +14580,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -14580,7 +14592,7 @@
         <v>31</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -14602,7 +14614,7 @@
         <v>7</v>
       </c>
       <c r="Q50" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -14616,7 +14628,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -14628,7 +14640,7 @@
         <v>31</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -14650,7 +14662,7 @@
         <v>7</v>
       </c>
       <c r="Q51" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -14664,7 +14676,7 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -14676,7 +14688,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -14698,7 +14710,7 @@
         <v>7</v>
       </c>
       <c r="Q52" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -14712,7 +14724,7 @@
         <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -14724,7 +14736,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -14746,7 +14758,7 @@
         <v>7</v>
       </c>
       <c r="Q53" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -14760,7 +14772,7 @@
         <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -14772,7 +14784,7 @@
         <v>49</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -14794,7 +14806,7 @@
         <v>7</v>
       </c>
       <c r="Q54" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -14825,7 +14837,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -14837,7 +14849,7 @@
         <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -14859,7 +14871,7 @@
         <v>20</v>
       </c>
       <c r="Q56" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -14873,7 +14885,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -14885,7 +14897,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -14907,7 +14919,7 @@
         <v>20</v>
       </c>
       <c r="Q57" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -14921,7 +14933,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -14933,7 +14945,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -14955,7 +14967,7 @@
         <v>10</v>
       </c>
       <c r="Q58" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -14969,7 +14981,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -14981,7 +14993,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -15003,7 +15015,7 @@
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -15017,7 +15029,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -15029,7 +15041,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -15051,7 +15063,7 @@
         <v>10</v>
       </c>
       <c r="Q60" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -15065,7 +15077,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -15077,7 +15089,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -15099,7 +15111,7 @@
         <v>10</v>
       </c>
       <c r="Q61" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -15113,7 +15125,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -15125,7 +15137,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -15147,7 +15159,7 @@
         <v>10</v>
       </c>
       <c r="Q62" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -15161,7 +15173,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -15173,7 +15185,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -15195,7 +15207,7 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -15209,7 +15221,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -15221,7 +15233,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -15243,7 +15255,7 @@
         <v>20</v>
       </c>
       <c r="Q64" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -15257,7 +15269,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -15269,7 +15281,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -15291,7 +15303,7 @@
         <v>20</v>
       </c>
       <c r="Q65" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -15305,7 +15317,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -15317,7 +15329,7 @@
         <v>40</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -15339,7 +15351,7 @@
         <v>10</v>
       </c>
       <c r="Q66" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -15353,7 +15365,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15365,7 +15377,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -15387,7 +15399,7 @@
         <v>10</v>
       </c>
       <c r="Q67" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -15401,7 +15413,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15413,7 +15425,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -15435,7 +15447,7 @@
         <v>10</v>
       </c>
       <c r="Q68" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -15449,7 +15461,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15461,7 +15473,7 @@
         <v>40</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -15483,7 +15495,7 @@
         <v>10</v>
       </c>
       <c r="Q69" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -15497,7 +15509,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15509,7 +15521,7 @@
         <v>27</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -15531,7 +15543,7 @@
         <v>10</v>
       </c>
       <c r="Q70" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -15545,7 +15557,7 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15557,7 +15569,7 @@
         <v>40</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -15579,7 +15591,7 @@
         <v>10</v>
       </c>
       <c r="Q71" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -15593,7 +15605,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -15605,7 +15617,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -15627,7 +15639,7 @@
         <v>20</v>
       </c>
       <c r="Q72" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -15641,7 +15653,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -15653,7 +15665,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -15675,7 +15687,7 @@
         <v>20</v>
       </c>
       <c r="Q73" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -15689,7 +15701,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -15701,7 +15713,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -15723,7 +15735,7 @@
         <v>10</v>
       </c>
       <c r="Q74" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -15737,7 +15749,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -15749,7 +15761,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -15771,7 +15783,7 @@
         <v>10</v>
       </c>
       <c r="Q75" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -15785,7 +15797,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -15797,7 +15809,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -15819,7 +15831,7 @@
         <v>10</v>
       </c>
       <c r="Q76" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -15833,7 +15845,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -15845,7 +15857,7 @@
         <v>49</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -15867,7 +15879,7 @@
         <v>10</v>
       </c>
       <c r="Q77" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -15881,7 +15893,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -15893,7 +15905,7 @@
         <v>27</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -15915,7 +15927,7 @@
         <v>10</v>
       </c>
       <c r="Q78" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -15929,7 +15941,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -15941,7 +15953,7 @@
         <v>49</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -15963,7 +15975,7 @@
         <v>10</v>
       </c>
       <c r="Q79" s="1">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -15992,7 +16004,7 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -16004,7 +16016,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -16026,7 +16038,7 @@
         <v>30</v>
       </c>
       <c r="Q81" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -16040,7 +16052,7 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -16052,7 +16064,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -16074,7 +16086,7 @@
         <v>30</v>
       </c>
       <c r="Q82" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -16088,7 +16100,7 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -16100,7 +16112,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -16122,7 +16134,7 @@
         <v>15</v>
       </c>
       <c r="Q83" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -16136,7 +16148,7 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -16148,7 +16160,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -16170,7 +16182,7 @@
         <v>15</v>
       </c>
       <c r="Q84" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -16184,7 +16196,7 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -16196,7 +16208,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -16218,7 +16230,7 @@
         <v>15</v>
       </c>
       <c r="Q85" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -16232,7 +16244,7 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -16244,7 +16256,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -16266,7 +16278,7 @@
         <v>15</v>
       </c>
       <c r="Q86" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -16280,7 +16292,7 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -16292,7 +16304,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -16314,7 +16326,7 @@
         <v>15</v>
       </c>
       <c r="Q87" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -16328,7 +16340,7 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16340,7 +16352,7 @@
         <v>24</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -16362,7 +16374,7 @@
         <v>15</v>
       </c>
       <c r="Q88" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -16376,7 +16388,7 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16388,7 +16400,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -16410,7 +16422,7 @@
         <v>30</v>
       </c>
       <c r="Q89" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -16424,7 +16436,7 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16436,7 +16448,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -16458,7 +16470,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -16472,7 +16484,7 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16484,7 +16496,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -16506,7 +16518,7 @@
         <v>15</v>
       </c>
       <c r="Q91" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -16520,7 +16532,7 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -16532,7 +16544,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -16554,7 +16566,7 @@
         <v>15</v>
       </c>
       <c r="Q92" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -16568,7 +16580,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -16580,7 +16592,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -16602,7 +16614,7 @@
         <v>15</v>
       </c>
       <c r="Q93" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -16616,7 +16628,7 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -16628,7 +16640,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -16650,7 +16662,7 @@
         <v>15</v>
       </c>
       <c r="Q94" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -16664,7 +16676,7 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -16676,7 +16688,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -16698,7 +16710,7 @@
         <v>15</v>
       </c>
       <c r="Q95" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -16712,7 +16724,7 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -16724,7 +16736,7 @@
         <v>40</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -16746,7 +16758,7 @@
         <v>15</v>
       </c>
       <c r="Q96" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -16760,7 +16772,7 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -16772,7 +16784,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -16794,7 +16806,7 @@
         <v>30</v>
       </c>
       <c r="Q97" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -16808,7 +16820,7 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -16820,7 +16832,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -16842,7 +16854,7 @@
         <v>30</v>
       </c>
       <c r="Q98" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -16856,7 +16868,7 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -16868,7 +16880,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -16890,7 +16902,7 @@
         <v>15</v>
       </c>
       <c r="Q99" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -16904,7 +16916,7 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -16916,7 +16928,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -16938,7 +16950,7 @@
         <v>15</v>
       </c>
       <c r="Q100" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -16952,7 +16964,7 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -16964,7 +16976,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -16986,7 +16998,7 @@
         <v>15</v>
       </c>
       <c r="Q101" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -17000,7 +17012,7 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -17012,7 +17024,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -17034,7 +17046,7 @@
         <v>15</v>
       </c>
       <c r="Q102" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -17048,7 +17060,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -17060,7 +17072,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -17082,7 +17094,7 @@
         <v>15</v>
       </c>
       <c r="Q103" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -17096,7 +17108,7 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -17108,7 +17120,7 @@
         <v>49</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -17130,7 +17142,7 @@
         <v>15</v>
       </c>
       <c r="Q104" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -17431,7 +17443,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17440,10 +17452,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17478,7 +17490,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17487,10 +17499,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -17562,7 +17574,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17580,7 +17592,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17611,16 +17623,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -17657,10 +17669,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -17730,7 +17742,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -17742,7 +17754,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -17754,7 +17766,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -17776,7 +17788,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -17785,10 +17797,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -17800,7 +17812,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -17822,7 +17834,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -17834,7 +17846,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -17866,7 +17878,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -17890,7 +17902,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -17912,7 +17924,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -17921,7 +17933,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>112</v>
@@ -17936,7 +17948,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -17958,7 +17970,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -18002,7 +18014,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18011,7 +18023,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>139</v>
@@ -18026,7 +18038,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18048,7 +18060,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18092,7 +18104,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18154,7 +18166,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18163,7 +18175,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J16" s="13" t="s">
         <v>166</v>
@@ -18178,7 +18190,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18200,7 +18212,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18244,7 +18256,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18288,7 +18300,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18297,10 +18309,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18312,7 +18324,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18334,7 +18346,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18346,7 +18358,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18378,7 +18390,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18390,7 +18402,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18422,7 +18434,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18431,10 +18443,10 @@
         <v>36</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18446,7 +18458,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18468,7 +18480,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18480,7 +18492,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18512,7 +18524,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -18524,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -18561,10 +18573,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -18576,7 +18588,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -18592,7 +18604,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -18603,10 +18615,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -18618,7 +18630,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -18643,10 +18655,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -18658,7 +18670,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -18683,10 +18695,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -18698,7 +18710,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -18714,7 +18726,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -18725,10 +18737,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -18740,7 +18752,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -18765,10 +18777,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -18780,7 +18792,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -18805,10 +18817,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -18820,7 +18832,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -18836,7 +18848,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -18847,10 +18859,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -18862,7 +18874,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -18887,10 +18899,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -18902,7 +18914,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -18927,10 +18939,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -18942,7 +18954,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -18958,7 +18970,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -18969,10 +18981,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -18984,7 +18996,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -19009,10 +19021,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -19024,7 +19036,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -19049,10 +19061,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -19064,7 +19076,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19080,7 +19092,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19091,10 +19103,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -19106,7 +19118,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19131,10 +19143,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -19146,7 +19158,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19171,10 +19183,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -19186,7 +19198,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19202,7 +19214,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19213,10 +19225,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -19228,7 +19240,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19253,10 +19265,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -19268,7 +19280,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19293,10 +19305,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -19308,7 +19320,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19324,7 +19336,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19335,10 +19347,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -19350,7 +19362,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19375,10 +19387,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -19390,7 +19402,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19415,10 +19427,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -19430,7 +19442,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19446,7 +19458,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19457,10 +19469,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -19472,7 +19484,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19497,10 +19509,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -19512,7 +19524,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="426">
   <si>
     <t>_id</t>
   </si>
@@ -1445,12 +1445,18 @@
     <t>财富扳指</t>
   </si>
   <si>
+    <t>15000,8</t>
+  </si>
+  <si>
     <t>金币加成增加20%</t>
   </si>
   <si>
     <t>财富项链</t>
   </si>
   <si>
+    <t>1500,8</t>
+  </si>
+  <si>
     <t>杀敌金币，杀敌金币，杀敌金币，</t>
   </si>
   <si>
@@ -1460,18 +1466,27 @@
     <t>杀戮血剑</t>
   </si>
   <si>
+    <t>3000,10</t>
+  </si>
+  <si>
     <t>经验加成增加20%</t>
   </si>
   <si>
     <t>杀戮面罩</t>
   </si>
   <si>
+    <t>30000,10</t>
+  </si>
+  <si>
     <t>杀戮战靴</t>
   </si>
   <si>
     <t>狂风面具</t>
   </si>
   <si>
+    <t>6000,12</t>
+  </si>
+  <si>
     <t>攻速增加10%，冷却增加10%</t>
   </si>
   <si>
@@ -1481,10 +1496,13 @@
     <t>狂风戒指</t>
   </si>
   <si>
+    <t>60000,12</t>
+  </si>
+  <si>
     <t>重击巨剑</t>
   </si>
   <si>
-    <t>15000,14</t>
+    <t>12000,14</t>
   </si>
   <si>
     <t>此次攻击概率翻倍</t>
@@ -1493,7 +1511,7 @@
     <t>重击护腕</t>
   </si>
   <si>
-    <t>150000,14</t>
+    <t>120000,14</t>
   </si>
   <si>
     <t>重击腰带</t>
@@ -1502,7 +1520,7 @@
     <t>暴击扳指</t>
   </si>
   <si>
-    <t>30000,16</t>
+    <t>24000,16</t>
   </si>
   <si>
     <t>如果此次攻击暴击了，伤害额外翻倍</t>
@@ -1511,7 +1529,7 @@
     <t>暴击板甲</t>
   </si>
   <si>
-    <t>300000,16</t>
+    <t>240000,16</t>
   </si>
   <si>
     <t>暴击铁履</t>
@@ -17890,7 +17908,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>117</v>
+        <v>364</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -17902,7 +17920,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -17924,7 +17942,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -17936,7 +17954,7 @@
         <v>359</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>112</v>
+        <v>367</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -17948,7 +17966,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -17970,7 +17988,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -17982,7 +18000,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>112</v>
+        <v>367</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -18014,7 +18032,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18026,7 +18044,7 @@
         <v>359</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>139</v>
+        <v>371</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18038,7 +18056,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18060,7 +18078,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18072,7 +18090,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>144</v>
+        <v>374</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18104,7 +18122,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18116,7 +18134,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>139</v>
+        <v>371</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18166,7 +18184,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18178,7 +18196,7 @@
         <v>359</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>166</v>
+        <v>377</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -18190,7 +18208,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18212,7 +18230,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18224,7 +18242,7 @@
         <v>27</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>166</v>
+        <v>377</v>
       </c>
       <c r="K17" s="2">
         <v>11</v>
@@ -18256,7 +18274,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18268,7 +18286,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>171</v>
+        <v>381</v>
       </c>
       <c r="K18" s="2">
         <v>12</v>
@@ -18300,7 +18318,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18312,7 +18330,7 @@
         <v>359</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18324,7 +18342,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18346,7 +18364,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18358,7 +18376,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18390,7 +18408,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18402,7 +18420,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18434,7 +18452,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18446,7 +18464,7 @@
         <v>359</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18458,7 +18476,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18480,7 +18498,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18492,7 +18510,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18524,7 +18542,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -18536,7 +18554,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -18588,7 +18606,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -18604,7 +18622,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -18630,7 +18648,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -18670,7 +18688,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -18710,7 +18728,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -18726,7 +18744,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -18752,7 +18770,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -18792,7 +18810,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -18832,7 +18850,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -18848,7 +18866,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -18874,7 +18892,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -18914,7 +18932,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -18954,7 +18972,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -18970,7 +18988,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -18996,7 +19014,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -19036,7 +19054,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -19076,7 +19094,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19092,7 +19110,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19118,7 +19136,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19158,7 +19176,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19198,7 +19216,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19214,7 +19232,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19240,7 +19258,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19280,7 +19298,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19320,7 +19338,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19336,7 +19354,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19362,7 +19380,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19402,7 +19420,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19442,7 +19460,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19458,7 +19476,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19484,7 +19502,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19524,7 +19542,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -1807,12 +1807,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3132,10 +3132,10 @@
         <v>10</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -3508,10 +3508,10 @@
         <v>10</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -3884,10 +3884,10 @@
         <v>10</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -4267,10 +4267,10 @@
         <v>10</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K38" s="1">
         <v>200</v>
@@ -4651,10 +4651,10 @@
         <v>10</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K46" s="1">
         <v>200</v>
@@ -5035,10 +5035,10 @@
         <v>10</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K54" s="1">
         <v>200</v>
@@ -5436,10 +5436,10 @@
         <v>10</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K63" s="1">
         <v>300</v>
@@ -5820,10 +5820,10 @@
         <v>10</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K71" s="1">
         <v>300</v>
@@ -6204,10 +6204,10 @@
         <v>10</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K79" s="1">
         <v>300</v>
@@ -6603,10 +6603,10 @@
         <v>10</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -6987,10 +6987,10 @@
         <v>10</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -7371,10 +7371,10 @@
         <v>10</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -7948,10 +7948,10 @@
         <v>10</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -8332,10 +8332,10 @@
         <v>10</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -8716,10 +8716,10 @@
         <v>10</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -9100,10 +9100,10 @@
         <v>10</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -9484,10 +9484,10 @@
         <v>10</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -9868,10 +9868,10 @@
         <v>10</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -10269,10 +10269,10 @@
         <v>10</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -10653,10 +10653,10 @@
         <v>10</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -11037,10 +11037,10 @@
         <v>10</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -11436,10 +11436,10 @@
         <v>10</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -11820,10 +11820,10 @@
         <v>10</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -12204,10 +12204,10 @@
         <v>10</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -12879,7 +12879,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>247</v>
@@ -13263,7 +13263,7 @@
         <v>10</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>247</v>
@@ -13647,7 +13647,7 @@
         <v>10</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J29" s="12" t="s">
         <v>247</v>
@@ -14031,7 +14031,7 @@
         <v>10</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>247</v>
@@ -14415,7 +14415,7 @@
         <v>10</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>247</v>
@@ -14799,7 +14799,7 @@
         <v>10</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>247</v>
@@ -15200,7 +15200,7 @@
         <v>10</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
         <v>247</v>
@@ -15584,7 +15584,7 @@
         <v>10</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J71" s="12" t="s">
         <v>247</v>
@@ -15968,7 +15968,7 @@
         <v>10</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>247</v>
@@ -16367,7 +16367,7 @@
         <v>10</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J88" s="12" t="s">
         <v>247</v>
@@ -16751,7 +16751,7 @@
         <v>10</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J96" s="12" t="s">
         <v>247</v>
@@ -17135,7 +17135,7 @@
         <v>10</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
         <v>247</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -1807,12 +1807,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3956,7 +3956,7 @@
         <v>4</v>
       </c>
       <c r="Q31" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4004,7 +4004,7 @@
         <v>4</v>
       </c>
       <c r="Q32" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4052,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="Q33" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4100,7 +4100,7 @@
         <v>2</v>
       </c>
       <c r="Q34" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4148,7 +4148,7 @@
         <v>2</v>
       </c>
       <c r="Q35" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4196,7 +4196,7 @@
         <v>2</v>
       </c>
       <c r="Q36" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:17">
@@ -4244,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="Q37" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -4292,7 +4292,7 @@
         <v>2</v>
       </c>
       <c r="Q38" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -4340,7 +4340,7 @@
         <v>4</v>
       </c>
       <c r="Q39" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -4388,7 +4388,7 @@
         <v>4</v>
       </c>
       <c r="Q40" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -4436,7 +4436,7 @@
         <v>2</v>
       </c>
       <c r="Q41" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -4484,7 +4484,7 @@
         <v>2</v>
       </c>
       <c r="Q42" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -4532,7 +4532,7 @@
         <v>2</v>
       </c>
       <c r="Q43" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -4580,7 +4580,7 @@
         <v>2</v>
       </c>
       <c r="Q44" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -4628,7 +4628,7 @@
         <v>2</v>
       </c>
       <c r="Q45" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -4676,7 +4676,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -4724,7 +4724,7 @@
         <v>4</v>
       </c>
       <c r="Q47" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -4772,7 +4772,7 @@
         <v>4</v>
       </c>
       <c r="Q48" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -4820,7 +4820,7 @@
         <v>2</v>
       </c>
       <c r="Q49" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -4868,7 +4868,7 @@
         <v>2</v>
       </c>
       <c r="Q50" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -4916,7 +4916,7 @@
         <v>2</v>
       </c>
       <c r="Q51" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -4964,7 +4964,7 @@
         <v>2</v>
       </c>
       <c r="Q52" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -5012,7 +5012,7 @@
         <v>2</v>
       </c>
       <c r="Q53" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -5060,7 +5060,7 @@
         <v>2</v>
       </c>
       <c r="Q54" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -5125,7 +5125,7 @@
         <v>6</v>
       </c>
       <c r="Q56" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -5173,7 +5173,7 @@
         <v>6</v>
       </c>
       <c r="Q57" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -5221,7 +5221,7 @@
         <v>3</v>
       </c>
       <c r="Q58" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -5269,7 +5269,7 @@
         <v>3</v>
       </c>
       <c r="Q59" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -5317,7 +5317,7 @@
         <v>3</v>
       </c>
       <c r="Q60" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -5365,7 +5365,7 @@
         <v>3</v>
       </c>
       <c r="Q61" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -5413,7 +5413,7 @@
         <v>3</v>
       </c>
       <c r="Q62" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -5461,7 +5461,7 @@
         <v>3</v>
       </c>
       <c r="Q63" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -5509,7 +5509,7 @@
         <v>6</v>
       </c>
       <c r="Q64" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -5557,7 +5557,7 @@
         <v>6</v>
       </c>
       <c r="Q65" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -5605,7 +5605,7 @@
         <v>3</v>
       </c>
       <c r="Q66" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -5653,7 +5653,7 @@
         <v>3</v>
       </c>
       <c r="Q67" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -5701,7 +5701,7 @@
         <v>3</v>
       </c>
       <c r="Q68" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -5749,7 +5749,7 @@
         <v>3</v>
       </c>
       <c r="Q69" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -5797,7 +5797,7 @@
         <v>3</v>
       </c>
       <c r="Q70" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -5845,7 +5845,7 @@
         <v>3</v>
       </c>
       <c r="Q71" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -5893,7 +5893,7 @@
         <v>6</v>
       </c>
       <c r="Q72" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -5941,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="Q73" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -5989,7 +5989,7 @@
         <v>3</v>
       </c>
       <c r="Q74" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -6037,7 +6037,7 @@
         <v>3</v>
       </c>
       <c r="Q75" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -6085,7 +6085,7 @@
         <v>3</v>
       </c>
       <c r="Q76" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -6133,7 +6133,7 @@
         <v>3</v>
       </c>
       <c r="Q77" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -6181,7 +6181,7 @@
         <v>3</v>
       </c>
       <c r="Q78" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -6229,7 +6229,7 @@
         <v>3</v>
       </c>
       <c r="Q79" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -6292,7 +6292,7 @@
         <v>8</v>
       </c>
       <c r="Q81" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -6340,7 +6340,7 @@
         <v>8</v>
       </c>
       <c r="Q82" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -6388,7 +6388,7 @@
         <v>4</v>
       </c>
       <c r="Q83" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -6436,7 +6436,7 @@
         <v>4</v>
       </c>
       <c r="Q84" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -6484,7 +6484,7 @@
         <v>4</v>
       </c>
       <c r="Q85" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -6532,7 +6532,7 @@
         <v>4</v>
       </c>
       <c r="Q86" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -6580,7 +6580,7 @@
         <v>4</v>
       </c>
       <c r="Q87" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -6628,7 +6628,7 @@
         <v>4</v>
       </c>
       <c r="Q88" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -6676,7 +6676,7 @@
         <v>8</v>
       </c>
       <c r="Q89" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -6724,7 +6724,7 @@
         <v>8</v>
       </c>
       <c r="Q90" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -6772,7 +6772,7 @@
         <v>4</v>
       </c>
       <c r="Q91" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -6820,7 +6820,7 @@
         <v>4</v>
       </c>
       <c r="Q92" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -6868,7 +6868,7 @@
         <v>4</v>
       </c>
       <c r="Q93" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -6916,7 +6916,7 @@
         <v>4</v>
       </c>
       <c r="Q94" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -6964,7 +6964,7 @@
         <v>4</v>
       </c>
       <c r="Q95" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -7012,7 +7012,7 @@
         <v>4</v>
       </c>
       <c r="Q96" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -7060,7 +7060,7 @@
         <v>8</v>
       </c>
       <c r="Q97" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -7108,7 +7108,7 @@
         <v>8</v>
       </c>
       <c r="Q98" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -7156,7 +7156,7 @@
         <v>4</v>
       </c>
       <c r="Q99" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -7204,7 +7204,7 @@
         <v>4</v>
       </c>
       <c r="Q100" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -7252,7 +7252,7 @@
         <v>4</v>
       </c>
       <c r="Q101" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -7300,7 +7300,7 @@
         <v>4</v>
       </c>
       <c r="Q102" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -7348,7 +7348,7 @@
         <v>4</v>
       </c>
       <c r="Q103" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -7396,7 +7396,7 @@
         <v>4</v>
       </c>
       <c r="Q104" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -7637,7 +7637,7 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7685,7 +7685,7 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7733,7 +7733,7 @@
         <v>5</v>
       </c>
       <c r="Q8" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7781,7 +7781,7 @@
         <v>5</v>
       </c>
       <c r="Q9" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7829,7 +7829,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7877,7 +7877,7 @@
         <v>5</v>
       </c>
       <c r="Q11" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7925,7 +7925,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7973,7 +7973,7 @@
         <v>5</v>
       </c>
       <c r="Q13" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8021,7 +8021,7 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8069,7 +8069,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8117,7 +8117,7 @@
         <v>5</v>
       </c>
       <c r="Q16" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8165,7 +8165,7 @@
         <v>5</v>
       </c>
       <c r="Q17" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8213,7 +8213,7 @@
         <v>5</v>
       </c>
       <c r="Q18" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8261,7 +8261,7 @@
         <v>5</v>
       </c>
       <c r="Q19" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8309,7 +8309,7 @@
         <v>5</v>
       </c>
       <c r="Q20" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8357,7 +8357,7 @@
         <v>5</v>
       </c>
       <c r="Q21" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8405,7 +8405,7 @@
         <v>10</v>
       </c>
       <c r="Q22" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8453,7 +8453,7 @@
         <v>10</v>
       </c>
       <c r="Q23" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8501,7 +8501,7 @@
         <v>5</v>
       </c>
       <c r="Q24" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8549,7 +8549,7 @@
         <v>5</v>
       </c>
       <c r="Q25" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8597,7 +8597,7 @@
         <v>5</v>
       </c>
       <c r="Q26" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8645,7 +8645,7 @@
         <v>5</v>
       </c>
       <c r="Q27" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8693,7 +8693,7 @@
         <v>5</v>
       </c>
       <c r="Q28" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8741,7 +8741,7 @@
         <v>5</v>
       </c>
       <c r="Q29" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8789,7 +8789,7 @@
         <v>15</v>
       </c>
       <c r="Q31" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8837,7 +8837,7 @@
         <v>15</v>
       </c>
       <c r="Q32" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8885,7 +8885,7 @@
         <v>7</v>
       </c>
       <c r="Q33" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8933,7 +8933,7 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8981,7 +8981,7 @@
         <v>7</v>
       </c>
       <c r="Q35" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -9029,7 +9029,7 @@
         <v>7</v>
       </c>
       <c r="Q36" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -9077,7 +9077,7 @@
         <v>7</v>
       </c>
       <c r="Q37" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -9125,7 +9125,7 @@
         <v>7</v>
       </c>
       <c r="Q38" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -9173,7 +9173,7 @@
         <v>15</v>
       </c>
       <c r="Q39" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -9221,7 +9221,7 @@
         <v>15</v>
       </c>
       <c r="Q40" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -9269,7 +9269,7 @@
         <v>7</v>
       </c>
       <c r="Q41" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -9317,7 +9317,7 @@
         <v>7</v>
       </c>
       <c r="Q42" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -9365,7 +9365,7 @@
         <v>7</v>
       </c>
       <c r="Q43" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -9413,7 +9413,7 @@
         <v>7</v>
       </c>
       <c r="Q44" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -9461,7 +9461,7 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -9509,7 +9509,7 @@
         <v>7</v>
       </c>
       <c r="Q46" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -9557,7 +9557,7 @@
         <v>15</v>
       </c>
       <c r="Q47" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -9605,7 +9605,7 @@
         <v>15</v>
       </c>
       <c r="Q48" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -9653,7 +9653,7 @@
         <v>7</v>
       </c>
       <c r="Q49" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -9701,7 +9701,7 @@
         <v>7</v>
       </c>
       <c r="Q50" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -9749,7 +9749,7 @@
         <v>7</v>
       </c>
       <c r="Q51" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -9797,7 +9797,7 @@
         <v>7</v>
       </c>
       <c r="Q52" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -9845,7 +9845,7 @@
         <v>7</v>
       </c>
       <c r="Q53" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -9893,7 +9893,7 @@
         <v>7</v>
       </c>
       <c r="Q54" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -9958,7 +9958,7 @@
         <v>20</v>
       </c>
       <c r="Q56" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -10006,7 +10006,7 @@
         <v>20</v>
       </c>
       <c r="Q57" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -10054,7 +10054,7 @@
         <v>10</v>
       </c>
       <c r="Q58" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -10102,7 +10102,7 @@
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -10150,7 +10150,7 @@
         <v>10</v>
       </c>
       <c r="Q60" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -10198,7 +10198,7 @@
         <v>10</v>
       </c>
       <c r="Q61" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -10246,7 +10246,7 @@
         <v>10</v>
       </c>
       <c r="Q62" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -10294,7 +10294,7 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -10342,7 +10342,7 @@
         <v>20</v>
       </c>
       <c r="Q64" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -10390,7 +10390,7 @@
         <v>20</v>
       </c>
       <c r="Q65" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -10438,7 +10438,7 @@
         <v>10</v>
       </c>
       <c r="Q66" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -10486,7 +10486,7 @@
         <v>10</v>
       </c>
       <c r="Q67" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -10534,7 +10534,7 @@
         <v>10</v>
       </c>
       <c r="Q68" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -10582,7 +10582,7 @@
         <v>10</v>
       </c>
       <c r="Q69" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -10630,7 +10630,7 @@
         <v>10</v>
       </c>
       <c r="Q70" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -10678,7 +10678,7 @@
         <v>10</v>
       </c>
       <c r="Q71" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -10726,7 +10726,7 @@
         <v>20</v>
       </c>
       <c r="Q72" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -10774,7 +10774,7 @@
         <v>20</v>
       </c>
       <c r="Q73" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -10822,7 +10822,7 @@
         <v>10</v>
       </c>
       <c r="Q74" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -10870,7 +10870,7 @@
         <v>10</v>
       </c>
       <c r="Q75" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -10918,7 +10918,7 @@
         <v>10</v>
       </c>
       <c r="Q76" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -10966,7 +10966,7 @@
         <v>10</v>
       </c>
       <c r="Q77" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -11014,7 +11014,7 @@
         <v>10</v>
       </c>
       <c r="Q78" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -11062,7 +11062,7 @@
         <v>10</v>
       </c>
       <c r="Q79" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -11125,7 +11125,7 @@
         <v>30</v>
       </c>
       <c r="Q81" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -11173,7 +11173,7 @@
         <v>30</v>
       </c>
       <c r="Q82" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -11221,7 +11221,7 @@
         <v>15</v>
       </c>
       <c r="Q83" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -11269,7 +11269,7 @@
         <v>15</v>
       </c>
       <c r="Q84" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -11317,7 +11317,7 @@
         <v>15</v>
       </c>
       <c r="Q85" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -11365,7 +11365,7 @@
         <v>15</v>
       </c>
       <c r="Q86" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -11413,7 +11413,7 @@
         <v>15</v>
       </c>
       <c r="Q87" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -11461,7 +11461,7 @@
         <v>15</v>
       </c>
       <c r="Q88" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -11509,7 +11509,7 @@
         <v>30</v>
       </c>
       <c r="Q89" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -11557,7 +11557,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -11605,7 +11605,7 @@
         <v>15</v>
       </c>
       <c r="Q91" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -11653,7 +11653,7 @@
         <v>15</v>
       </c>
       <c r="Q92" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -11701,7 +11701,7 @@
         <v>15</v>
       </c>
       <c r="Q93" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -11749,7 +11749,7 @@
         <v>15</v>
       </c>
       <c r="Q94" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -11797,7 +11797,7 @@
         <v>15</v>
       </c>
       <c r="Q95" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -11845,7 +11845,7 @@
         <v>15</v>
       </c>
       <c r="Q96" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -11893,7 +11893,7 @@
         <v>30</v>
       </c>
       <c r="Q97" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -11941,7 +11941,7 @@
         <v>30</v>
       </c>
       <c r="Q98" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -11989,7 +11989,7 @@
         <v>15</v>
       </c>
       <c r="Q99" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -12037,7 +12037,7 @@
         <v>15</v>
       </c>
       <c r="Q100" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -12085,7 +12085,7 @@
         <v>15</v>
       </c>
       <c r="Q101" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -12133,7 +12133,7 @@
         <v>15</v>
       </c>
       <c r="Q102" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -12181,7 +12181,7 @@
         <v>15</v>
       </c>
       <c r="Q103" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -12229,7 +12229,7 @@
         <v>15</v>
       </c>
       <c r="Q104" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -12568,7 +12568,7 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12616,7 +12616,7 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12664,7 +12664,7 @@
         <v>5</v>
       </c>
       <c r="Q8" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12712,7 +12712,7 @@
         <v>5</v>
       </c>
       <c r="Q9" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12760,7 +12760,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12808,7 +12808,7 @@
         <v>5</v>
       </c>
       <c r="Q11" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12856,7 +12856,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12904,7 +12904,7 @@
         <v>5</v>
       </c>
       <c r="Q13" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12952,7 +12952,7 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -13000,7 +13000,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -13048,7 +13048,7 @@
         <v>5</v>
       </c>
       <c r="Q16" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13096,7 +13096,7 @@
         <v>5</v>
       </c>
       <c r="Q17" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13144,7 +13144,7 @@
         <v>5</v>
       </c>
       <c r="Q18" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13192,7 +13192,7 @@
         <v>5</v>
       </c>
       <c r="Q19" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13240,7 +13240,7 @@
         <v>5</v>
       </c>
       <c r="Q20" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13288,7 +13288,7 @@
         <v>5</v>
       </c>
       <c r="Q21" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13336,7 +13336,7 @@
         <v>10</v>
       </c>
       <c r="Q22" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13384,7 +13384,7 @@
         <v>10</v>
       </c>
       <c r="Q23" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13432,7 +13432,7 @@
         <v>5</v>
       </c>
       <c r="Q24" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13480,7 +13480,7 @@
         <v>5</v>
       </c>
       <c r="Q25" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13528,7 +13528,7 @@
         <v>5</v>
       </c>
       <c r="Q26" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13576,7 +13576,7 @@
         <v>5</v>
       </c>
       <c r="Q27" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13624,7 +13624,7 @@
         <v>5</v>
       </c>
       <c r="Q28" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13672,7 +13672,7 @@
         <v>5</v>
       </c>
       <c r="Q29" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13720,7 +13720,7 @@
         <v>15</v>
       </c>
       <c r="Q31" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13768,7 +13768,7 @@
         <v>15</v>
       </c>
       <c r="Q32" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13816,7 +13816,7 @@
         <v>7</v>
       </c>
       <c r="Q33" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13864,7 +13864,7 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13912,7 +13912,7 @@
         <v>7</v>
       </c>
       <c r="Q35" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13960,7 +13960,7 @@
         <v>7</v>
       </c>
       <c r="Q36" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -14008,7 +14008,7 @@
         <v>7</v>
       </c>
       <c r="Q37" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -14056,7 +14056,7 @@
         <v>7</v>
       </c>
       <c r="Q38" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -14104,7 +14104,7 @@
         <v>15</v>
       </c>
       <c r="Q39" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -14152,7 +14152,7 @@
         <v>15</v>
       </c>
       <c r="Q40" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -14200,7 +14200,7 @@
         <v>7</v>
       </c>
       <c r="Q41" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -14248,7 +14248,7 @@
         <v>7</v>
       </c>
       <c r="Q42" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -14296,7 +14296,7 @@
         <v>7</v>
       </c>
       <c r="Q43" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -14344,7 +14344,7 @@
         <v>7</v>
       </c>
       <c r="Q44" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -14392,7 +14392,7 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -14440,7 +14440,7 @@
         <v>7</v>
       </c>
       <c r="Q46" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -14488,7 +14488,7 @@
         <v>15</v>
       </c>
       <c r="Q47" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -14536,7 +14536,7 @@
         <v>15</v>
       </c>
       <c r="Q48" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -14584,7 +14584,7 @@
         <v>7</v>
       </c>
       <c r="Q49" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -14632,7 +14632,7 @@
         <v>7</v>
       </c>
       <c r="Q50" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -14680,7 +14680,7 @@
         <v>7</v>
       </c>
       <c r="Q51" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -14728,7 +14728,7 @@
         <v>7</v>
       </c>
       <c r="Q52" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -14776,7 +14776,7 @@
         <v>7</v>
       </c>
       <c r="Q53" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -14824,7 +14824,7 @@
         <v>7</v>
       </c>
       <c r="Q54" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -14889,7 +14889,7 @@
         <v>20</v>
       </c>
       <c r="Q56" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -14937,7 +14937,7 @@
         <v>20</v>
       </c>
       <c r="Q57" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -14985,7 +14985,7 @@
         <v>10</v>
       </c>
       <c r="Q58" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -15033,7 +15033,7 @@
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -15081,7 +15081,7 @@
         <v>10</v>
       </c>
       <c r="Q60" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -15129,7 +15129,7 @@
         <v>10</v>
       </c>
       <c r="Q61" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -15177,7 +15177,7 @@
         <v>10</v>
       </c>
       <c r="Q62" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -15225,7 +15225,7 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -15273,7 +15273,7 @@
         <v>20</v>
       </c>
       <c r="Q64" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -15321,7 +15321,7 @@
         <v>20</v>
       </c>
       <c r="Q65" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -15369,7 +15369,7 @@
         <v>10</v>
       </c>
       <c r="Q66" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -15417,7 +15417,7 @@
         <v>10</v>
       </c>
       <c r="Q67" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -15465,7 +15465,7 @@
         <v>10</v>
       </c>
       <c r="Q68" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -15513,7 +15513,7 @@
         <v>10</v>
       </c>
       <c r="Q69" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -15561,7 +15561,7 @@
         <v>10</v>
       </c>
       <c r="Q70" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -15609,7 +15609,7 @@
         <v>10</v>
       </c>
       <c r="Q71" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -15657,7 +15657,7 @@
         <v>20</v>
       </c>
       <c r="Q72" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -15705,7 +15705,7 @@
         <v>20</v>
       </c>
       <c r="Q73" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -15753,7 +15753,7 @@
         <v>10</v>
       </c>
       <c r="Q74" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -15801,7 +15801,7 @@
         <v>10</v>
       </c>
       <c r="Q75" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -15849,7 +15849,7 @@
         <v>10</v>
       </c>
       <c r="Q76" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -15897,7 +15897,7 @@
         <v>10</v>
       </c>
       <c r="Q77" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -15945,7 +15945,7 @@
         <v>10</v>
       </c>
       <c r="Q78" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -15993,7 +15993,7 @@
         <v>10</v>
       </c>
       <c r="Q79" s="1">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -16056,7 +16056,7 @@
         <v>30</v>
       </c>
       <c r="Q81" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -16104,7 +16104,7 @@
         <v>30</v>
       </c>
       <c r="Q82" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -16152,7 +16152,7 @@
         <v>15</v>
       </c>
       <c r="Q83" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -16200,7 +16200,7 @@
         <v>15</v>
       </c>
       <c r="Q84" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -16248,7 +16248,7 @@
         <v>15</v>
       </c>
       <c r="Q85" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -16296,7 +16296,7 @@
         <v>15</v>
       </c>
       <c r="Q86" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -16344,7 +16344,7 @@
         <v>15</v>
       </c>
       <c r="Q87" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -16392,7 +16392,7 @@
         <v>15</v>
       </c>
       <c r="Q88" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -16440,7 +16440,7 @@
         <v>30</v>
       </c>
       <c r="Q89" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -16488,7 +16488,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -16536,7 +16536,7 @@
         <v>15</v>
       </c>
       <c r="Q91" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -16584,7 +16584,7 @@
         <v>15</v>
       </c>
       <c r="Q92" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -16632,7 +16632,7 @@
         <v>15</v>
       </c>
       <c r="Q93" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -16680,7 +16680,7 @@
         <v>15</v>
       </c>
       <c r="Q94" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -16728,7 +16728,7 @@
         <v>15</v>
       </c>
       <c r="Q95" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -16776,7 +16776,7 @@
         <v>15</v>
       </c>
       <c r="Q96" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -16824,7 +16824,7 @@
         <v>30</v>
       </c>
       <c r="Q97" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -16872,7 +16872,7 @@
         <v>30</v>
       </c>
       <c r="Q98" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -16920,7 +16920,7 @@
         <v>15</v>
       </c>
       <c r="Q99" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -16968,7 +16968,7 @@
         <v>15</v>
       </c>
       <c r="Q100" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -17016,7 +17016,7 @@
         <v>15</v>
       </c>
       <c r="Q101" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -17064,7 +17064,7 @@
         <v>15</v>
       </c>
       <c r="Q102" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -17112,7 +17112,7 @@
         <v>15</v>
       </c>
       <c r="Q103" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -17160,7 +17160,7 @@
         <v>15</v>
       </c>
       <c r="Q104" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -3956,7 +3956,8 @@
         <v>4</v>
       </c>
       <c r="Q31" s="1">
-        <v>14</v>
+        <f t="shared" ref="Q31:Q54" si="0">E31/10*3+10</f>
+        <v>13</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4004,7 +4005,8 @@
         <v>4</v>
       </c>
       <c r="Q32" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4042,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <f t="shared" ref="N33:N38" si="0">E33/10*3+3</f>
+        <f t="shared" ref="N33:N38" si="1">E33/10*3+3</f>
         <v>6</v>
       </c>
       <c r="O33" s="1">
@@ -4052,7 +4054,8 @@
         <v>2</v>
       </c>
       <c r="Q33" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4090,17 +4093,18 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O34" s="1">
+        <v>5</v>
+      </c>
+      <c r="P34" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O34" s="1">
-        <v>5</v>
-      </c>
-      <c r="P34" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4138,17 +4142,18 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O35" s="1">
+        <v>5</v>
+      </c>
+      <c r="P35" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O35" s="1">
-        <v>5</v>
-      </c>
-      <c r="P35" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -4186,17 +4191,18 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O36" s="1">
+        <v>5</v>
+      </c>
+      <c r="P36" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O36" s="1">
-        <v>5</v>
-      </c>
-      <c r="P36" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:17">
@@ -4234,17 +4240,18 @@
         <v>0</v>
       </c>
       <c r="N37" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O37" s="1">
+        <v>5</v>
+      </c>
+      <c r="P37" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O37" s="1">
-        <v>5</v>
-      </c>
-      <c r="P37" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -4282,17 +4289,18 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="O38" s="1">
+        <v>5</v>
+      </c>
+      <c r="P38" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="O38" s="1">
-        <v>5</v>
-      </c>
-      <c r="P38" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -4340,7 +4348,8 @@
         <v>4</v>
       </c>
       <c r="Q39" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -4388,7 +4397,8 @@
         <v>4</v>
       </c>
       <c r="Q40" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -4426,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" ref="N41:N46" si="1">E41/10*3+3</f>
+        <f t="shared" ref="N41:N46" si="2">E41/10*3+3</f>
         <v>6</v>
       </c>
       <c r="O41" s="1">
@@ -4436,7 +4446,8 @@
         <v>2</v>
       </c>
       <c r="Q41" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -4474,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O42" s="1">
@@ -4484,7 +4495,8 @@
         <v>2</v>
       </c>
       <c r="Q42" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -4522,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O43" s="1">
@@ -4532,7 +4544,8 @@
         <v>2</v>
       </c>
       <c r="Q43" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -4570,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O44" s="1">
@@ -4580,7 +4593,8 @@
         <v>2</v>
       </c>
       <c r="Q44" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -4618,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O45" s="1">
@@ -4628,7 +4642,8 @@
         <v>2</v>
       </c>
       <c r="Q45" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -4666,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="O46" s="1">
@@ -4676,7 +4691,8 @@
         <v>2</v>
       </c>
       <c r="Q46" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -4724,7 +4740,8 @@
         <v>4</v>
       </c>
       <c r="Q47" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -4772,7 +4789,8 @@
         <v>4</v>
       </c>
       <c r="Q48" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -4810,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <f t="shared" ref="N49:N54" si="2">E49/10*3+3</f>
+        <f t="shared" ref="N49:N54" si="3">E49/10*3+3</f>
         <v>6</v>
       </c>
       <c r="O49" s="1">
@@ -4820,7 +4838,8 @@
         <v>2</v>
       </c>
       <c r="Q49" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -4858,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O50" s="1">
@@ -4868,7 +4887,8 @@
         <v>2</v>
       </c>
       <c r="Q50" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -4906,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O51" s="1">
@@ -4916,7 +4936,8 @@
         <v>2</v>
       </c>
       <c r="Q51" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -4954,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O52" s="1">
@@ -4964,7 +4985,8 @@
         <v>2</v>
       </c>
       <c r="Q52" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -5002,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O53" s="1">
@@ -5012,7 +5034,8 @@
         <v>2</v>
       </c>
       <c r="Q53" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -5050,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="O54" s="1">
@@ -5060,7 +5083,8 @@
         <v>2</v>
       </c>
       <c r="Q54" s="1">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -5125,7 +5149,8 @@
         <v>6</v>
       </c>
       <c r="Q56" s="1">
-        <v>18</v>
+        <f t="shared" ref="Q56:Q79" si="4">E56/10*3+10</f>
+        <v>16</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -5173,7 +5198,8 @@
         <v>6</v>
       </c>
       <c r="Q57" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -5211,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" ref="N58:N63" si="3">E58/10*3+3</f>
+        <f t="shared" ref="N58:N63" si="5">E58/10*3+3</f>
         <v>9</v>
       </c>
       <c r="O58" s="1">
@@ -5221,7 +5247,8 @@
         <v>3</v>
       </c>
       <c r="Q58" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -5259,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O59" s="1">
@@ -5269,7 +5296,8 @@
         <v>3</v>
       </c>
       <c r="Q59" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -5307,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O60" s="1">
@@ -5317,7 +5345,8 @@
         <v>3</v>
       </c>
       <c r="Q60" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -5355,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O61" s="1">
@@ -5365,7 +5394,8 @@
         <v>3</v>
       </c>
       <c r="Q61" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -5403,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O62" s="1">
@@ -5413,7 +5443,8 @@
         <v>3</v>
       </c>
       <c r="Q62" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -5451,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="O63" s="1">
@@ -5461,7 +5492,8 @@
         <v>3</v>
       </c>
       <c r="Q63" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -5509,7 +5541,8 @@
         <v>6</v>
       </c>
       <c r="Q64" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -5557,7 +5590,8 @@
         <v>6</v>
       </c>
       <c r="Q65" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -5595,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" ref="N66:N71" si="4">E66/10*3+3</f>
+        <f t="shared" ref="N66:N71" si="6">E66/10*3+3</f>
         <v>9</v>
       </c>
       <c r="O66" s="1">
@@ -5605,7 +5639,8 @@
         <v>3</v>
       </c>
       <c r="Q66" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -5643,17 +5678,18 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="O67" s="1">
+        <v>5</v>
+      </c>
+      <c r="P67" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q67" s="1">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O67" s="1">
-        <v>5</v>
-      </c>
-      <c r="P67" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -5691,17 +5727,18 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="O68" s="1">
+        <v>5</v>
+      </c>
+      <c r="P68" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="1">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O68" s="1">
-        <v>5</v>
-      </c>
-      <c r="P68" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -5739,17 +5776,18 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="O69" s="1">
+        <v>5</v>
+      </c>
+      <c r="P69" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q69" s="1">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O69" s="1">
-        <v>5</v>
-      </c>
-      <c r="P69" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q69" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -5787,17 +5825,18 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="O70" s="1">
+        <v>5</v>
+      </c>
+      <c r="P70" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="1">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O70" s="1">
-        <v>5</v>
-      </c>
-      <c r="P70" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q70" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -5835,17 +5874,18 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="O71" s="1">
+        <v>5</v>
+      </c>
+      <c r="P71" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q71" s="1">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O71" s="1">
-        <v>5</v>
-      </c>
-      <c r="P71" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q71" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -5893,7 +5933,8 @@
         <v>6</v>
       </c>
       <c r="Q72" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -5941,7 +5982,8 @@
         <v>6</v>
       </c>
       <c r="Q73" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -5979,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" ref="N74:N79" si="5">E74/10*3+3</f>
+        <f t="shared" ref="N74:N79" si="7">E74/10*3+3</f>
         <v>9</v>
       </c>
       <c r="O74" s="1">
@@ -5989,7 +6031,8 @@
         <v>3</v>
       </c>
       <c r="Q74" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -6027,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="O75" s="1">
@@ -6037,7 +6080,8 @@
         <v>3</v>
       </c>
       <c r="Q75" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -6075,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="O76" s="1">
@@ -6085,7 +6129,8 @@
         <v>3</v>
       </c>
       <c r="Q76" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -6123,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="O77" s="1">
@@ -6133,7 +6178,8 @@
         <v>3</v>
       </c>
       <c r="Q77" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -6171,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="O78" s="1">
@@ -6181,7 +6227,8 @@
         <v>3</v>
       </c>
       <c r="Q78" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -6219,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="O79" s="1">
@@ -6229,7 +6276,8 @@
         <v>3</v>
       </c>
       <c r="Q79" s="1">
-        <v>18</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -6292,7 +6340,8 @@
         <v>8</v>
       </c>
       <c r="Q81" s="1">
-        <v>22</v>
+        <f t="shared" ref="Q81:Q104" si="8">E81/10*3+10</f>
+        <v>19</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -6340,7 +6389,8 @@
         <v>8</v>
       </c>
       <c r="Q82" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -6378,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" ref="N83:N88" si="6">E83/10*3+3</f>
+        <f t="shared" ref="N83:N88" si="9">E83/10*3+3</f>
         <v>12</v>
       </c>
       <c r="O83" s="1">
@@ -6388,7 +6438,8 @@
         <v>4</v>
       </c>
       <c r="Q83" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -6426,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="O84" s="1">
@@ -6436,7 +6487,8 @@
         <v>4</v>
       </c>
       <c r="Q84" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -6474,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="O85" s="1">
@@ -6484,7 +6536,8 @@
         <v>4</v>
       </c>
       <c r="Q85" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -6522,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="O86" s="1">
@@ -6532,7 +6585,8 @@
         <v>4</v>
       </c>
       <c r="Q86" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -6570,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="O87" s="1">
@@ -6580,7 +6634,8 @@
         <v>4</v>
       </c>
       <c r="Q87" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -6618,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="O88" s="1">
@@ -6628,7 +6683,8 @@
         <v>4</v>
       </c>
       <c r="Q88" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -6676,7 +6732,8 @@
         <v>8</v>
       </c>
       <c r="Q89" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -6724,7 +6781,8 @@
         <v>8</v>
       </c>
       <c r="Q90" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -6762,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" ref="N91:N96" si="7">E91/10*3+3</f>
+        <f t="shared" ref="N91:N96" si="10">E91/10*3+3</f>
         <v>12</v>
       </c>
       <c r="O91" s="1">
@@ -6772,7 +6830,8 @@
         <v>4</v>
       </c>
       <c r="Q91" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -6810,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O92" s="1">
@@ -6820,7 +6879,8 @@
         <v>4</v>
       </c>
       <c r="Q92" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -6858,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O93" s="1">
@@ -6868,7 +6928,8 @@
         <v>4</v>
       </c>
       <c r="Q93" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -6906,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O94" s="1">
@@ -6916,7 +6977,8 @@
         <v>4</v>
       </c>
       <c r="Q94" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -6954,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O95" s="1">
@@ -6964,7 +7026,8 @@
         <v>4</v>
       </c>
       <c r="Q95" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -7002,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O96" s="1">
@@ -7012,7 +7075,8 @@
         <v>4</v>
       </c>
       <c r="Q96" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -7060,7 +7124,8 @@
         <v>8</v>
       </c>
       <c r="Q97" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -7108,7 +7173,8 @@
         <v>8</v>
       </c>
       <c r="Q98" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -7146,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <f t="shared" ref="N99:N104" si="8">E99/10*3+3</f>
+        <f t="shared" ref="N99:N104" si="11">E99/10*3+3</f>
         <v>12</v>
       </c>
       <c r="O99" s="1">
@@ -7156,7 +7222,8 @@
         <v>4</v>
       </c>
       <c r="Q99" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -7194,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O100" s="1">
@@ -7204,7 +7271,8 @@
         <v>4</v>
       </c>
       <c r="Q100" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -7242,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O101" s="1">
@@ -7252,7 +7320,8 @@
         <v>4</v>
       </c>
       <c r="Q101" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -7290,7 +7359,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O102" s="1">
@@ -7300,7 +7369,8 @@
         <v>4</v>
       </c>
       <c r="Q102" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -7338,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O103" s="1">
@@ -7348,7 +7418,8 @@
         <v>4</v>
       </c>
       <c r="Q103" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -7386,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O104" s="1">
@@ -7396,7 +7467,8 @@
         <v>4</v>
       </c>
       <c r="Q104" s="1">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>19</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -7637,7 +7709,8 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>26</v>
+        <f t="shared" ref="Q6:Q29" si="0">E6/10*3+10</f>
+        <v>22</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7685,7 +7758,8 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7723,7 +7797,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <f t="shared" ref="N8:N13" si="0">E8/10*3+3</f>
+        <f t="shared" ref="N8:N13" si="1">E8/10*3+3</f>
         <v>15</v>
       </c>
       <c r="O8" s="1">
@@ -7733,7 +7807,8 @@
         <v>5</v>
       </c>
       <c r="Q8" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7771,17 +7846,18 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O9" s="1">
+        <v>5</v>
+      </c>
+      <c r="P9" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="O9" s="1">
-        <v>5</v>
-      </c>
-      <c r="P9" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7819,17 +7895,18 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="P10" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
-      </c>
-      <c r="P10" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7867,17 +7944,18 @@
         <v>0</v>
       </c>
       <c r="N11" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O11" s="1">
+        <v>5</v>
+      </c>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="O11" s="1">
-        <v>5</v>
-      </c>
-      <c r="P11" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7915,17 +7993,18 @@
         <v>0</v>
       </c>
       <c r="N12" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O12" s="1">
+        <v>5</v>
+      </c>
+      <c r="P12" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="O12" s="1">
-        <v>5</v>
-      </c>
-      <c r="P12" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -7963,17 +8042,18 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="O13" s="1">
+        <v>5</v>
+      </c>
+      <c r="P13" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="O13" s="1">
-        <v>5</v>
-      </c>
-      <c r="P13" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8021,7 +8101,8 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8069,7 +8150,8 @@
         <v>10</v>
       </c>
       <c r="Q15" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8107,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" ref="N16:N21" si="1">E16/10*3+3</f>
+        <f t="shared" ref="N16:N21" si="2">E16/10*3+3</f>
         <v>15</v>
       </c>
       <c r="O16" s="1">
@@ -8117,7 +8199,8 @@
         <v>5</v>
       </c>
       <c r="Q16" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8155,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O17" s="1">
@@ -8165,7 +8248,8 @@
         <v>5</v>
       </c>
       <c r="Q17" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8203,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O18" s="1">
@@ -8213,7 +8297,8 @@
         <v>5</v>
       </c>
       <c r="Q18" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8251,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O19" s="1">
@@ -8261,7 +8346,8 @@
         <v>5</v>
       </c>
       <c r="Q19" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8299,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O20" s="1">
@@ -8309,7 +8395,8 @@
         <v>5</v>
       </c>
       <c r="Q20" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8347,7 +8434,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O21" s="1">
@@ -8357,7 +8444,8 @@
         <v>5</v>
       </c>
       <c r="Q21" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8405,7 +8493,8 @@
         <v>10</v>
       </c>
       <c r="Q22" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8453,7 +8542,8 @@
         <v>10</v>
       </c>
       <c r="Q23" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8491,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" ref="N24:N29" si="2">E24/10*3+3</f>
+        <f t="shared" ref="N24:N29" si="3">E24/10*3+3</f>
         <v>15</v>
       </c>
       <c r="O24" s="1">
@@ -8501,7 +8591,8 @@
         <v>5</v>
       </c>
       <c r="Q24" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8539,7 +8630,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="O25" s="1">
@@ -8549,7 +8640,8 @@
         <v>5</v>
       </c>
       <c r="Q25" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8587,7 +8679,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="O26" s="1">
@@ -8597,7 +8689,8 @@
         <v>5</v>
       </c>
       <c r="Q26" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8635,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="O27" s="1">
@@ -8645,7 +8738,8 @@
         <v>5</v>
       </c>
       <c r="Q27" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8683,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="O28" s="1">
@@ -8693,7 +8787,8 @@
         <v>5</v>
       </c>
       <c r="Q28" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8731,7 +8826,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="O29" s="1">
@@ -8741,7 +8836,8 @@
         <v>5</v>
       </c>
       <c r="Q29" s="1">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8789,7 +8885,8 @@
         <v>15</v>
       </c>
       <c r="Q31" s="1">
-        <v>30</v>
+        <f t="shared" ref="Q31:Q54" si="4">E31/10*3+10</f>
+        <v>25</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8837,7 +8934,8 @@
         <v>15</v>
       </c>
       <c r="Q32" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8875,7 +8973,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <f t="shared" ref="N33:N38" si="3">E33/10*3+3</f>
+        <f t="shared" ref="N33:N38" si="5">E33/10*3+3</f>
         <v>18</v>
       </c>
       <c r="O33" s="1">
@@ -8885,7 +8983,8 @@
         <v>7</v>
       </c>
       <c r="Q33" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8923,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="O34" s="1">
@@ -8933,7 +9032,8 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -8971,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="O35" s="1">
@@ -8981,7 +9081,8 @@
         <v>7</v>
       </c>
       <c r="Q35" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -9019,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="O36" s="1">
@@ -9029,7 +9130,8 @@
         <v>7</v>
       </c>
       <c r="Q36" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -9067,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="O37" s="1">
@@ -9077,7 +9179,8 @@
         <v>7</v>
       </c>
       <c r="Q37" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -9115,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="O38" s="1">
@@ -9125,7 +9228,8 @@
         <v>7</v>
       </c>
       <c r="Q38" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -9173,7 +9277,8 @@
         <v>15</v>
       </c>
       <c r="Q39" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -9221,7 +9326,8 @@
         <v>15</v>
       </c>
       <c r="Q40" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -9259,7 +9365,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" ref="N41:N46" si="4">E41/10*3+3</f>
+        <f t="shared" ref="N41:N46" si="6">E41/10*3+3</f>
         <v>18</v>
       </c>
       <c r="O41" s="1">
@@ -9269,7 +9375,8 @@
         <v>7</v>
       </c>
       <c r="Q41" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -9307,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="O42" s="1">
@@ -9317,7 +9424,8 @@
         <v>7</v>
       </c>
       <c r="Q42" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -9355,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="O43" s="1">
@@ -9365,7 +9473,8 @@
         <v>7</v>
       </c>
       <c r="Q43" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -9403,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="O44" s="1">
@@ -9413,7 +9522,8 @@
         <v>7</v>
       </c>
       <c r="Q44" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -9451,7 +9561,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="O45" s="1">
@@ -9461,7 +9571,8 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -9499,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="O46" s="1">
@@ -9509,7 +9620,8 @@
         <v>7</v>
       </c>
       <c r="Q46" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -9557,7 +9669,8 @@
         <v>15</v>
       </c>
       <c r="Q47" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -9605,7 +9718,8 @@
         <v>15</v>
       </c>
       <c r="Q48" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -9643,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <f t="shared" ref="N49:N54" si="5">E49/10*3+3</f>
+        <f t="shared" ref="N49:N54" si="7">E49/10*3+3</f>
         <v>18</v>
       </c>
       <c r="O49" s="1">
@@ -9653,7 +9767,8 @@
         <v>7</v>
       </c>
       <c r="Q49" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -9691,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="O50" s="1">
@@ -9701,7 +9816,8 @@
         <v>7</v>
       </c>
       <c r="Q50" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -9739,7 +9855,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="O51" s="1">
@@ -9749,7 +9865,8 @@
         <v>7</v>
       </c>
       <c r="Q51" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -9787,7 +9904,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="O52" s="1">
@@ -9797,7 +9914,8 @@
         <v>7</v>
       </c>
       <c r="Q52" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -9835,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="O53" s="1">
@@ -9845,7 +9963,8 @@
         <v>7</v>
       </c>
       <c r="Q53" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -9883,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="O54" s="1">
@@ -9893,7 +10012,8 @@
         <v>7</v>
       </c>
       <c r="Q54" s="1">
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>25</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -9958,7 +10078,8 @@
         <v>20</v>
       </c>
       <c r="Q56" s="1">
-        <v>34</v>
+        <f t="shared" ref="Q56:Q79" si="8">E56/10*3+10</f>
+        <v>28</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -10006,7 +10127,8 @@
         <v>20</v>
       </c>
       <c r="Q57" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -10044,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" ref="N58:N63" si="6">E58/10*3+3</f>
+        <f t="shared" ref="N58:N63" si="9">E58/10*3+3</f>
         <v>21</v>
       </c>
       <c r="O58" s="1">
@@ -10054,7 +10176,8 @@
         <v>10</v>
       </c>
       <c r="Q58" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -10092,7 +10215,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="O59" s="1">
@@ -10102,7 +10225,8 @@
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -10140,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="O60" s="1">
@@ -10150,7 +10274,8 @@
         <v>10</v>
       </c>
       <c r="Q60" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -10188,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="O61" s="1">
@@ -10198,7 +10323,8 @@
         <v>10</v>
       </c>
       <c r="Q61" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -10236,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="O62" s="1">
@@ -10246,7 +10372,8 @@
         <v>10</v>
       </c>
       <c r="Q62" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -10284,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="O63" s="1">
@@ -10294,7 +10421,8 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -10342,7 +10470,8 @@
         <v>20</v>
       </c>
       <c r="Q64" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -10390,7 +10519,8 @@
         <v>20</v>
       </c>
       <c r="Q65" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -10428,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" ref="N66:N71" si="7">E66/10*3+3</f>
+        <f t="shared" ref="N66:N71" si="10">E66/10*3+3</f>
         <v>21</v>
       </c>
       <c r="O66" s="1">
@@ -10438,7 +10568,8 @@
         <v>10</v>
       </c>
       <c r="Q66" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -10476,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="O67" s="1">
@@ -10486,7 +10617,8 @@
         <v>10</v>
       </c>
       <c r="Q67" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -10524,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="O68" s="1">
@@ -10534,7 +10666,8 @@
         <v>10</v>
       </c>
       <c r="Q68" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -10572,7 +10705,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="O69" s="1">
@@ -10582,7 +10715,8 @@
         <v>10</v>
       </c>
       <c r="Q69" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -10620,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="O70" s="1">
@@ -10630,7 +10764,8 @@
         <v>10</v>
       </c>
       <c r="Q70" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -10668,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="O71" s="1">
@@ -10678,7 +10813,8 @@
         <v>10</v>
       </c>
       <c r="Q71" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -10726,7 +10862,8 @@
         <v>20</v>
       </c>
       <c r="Q72" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -10774,7 +10911,8 @@
         <v>20</v>
       </c>
       <c r="Q73" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -10812,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" ref="N74:N79" si="8">E74/10*3+3</f>
+        <f t="shared" ref="N74:N79" si="11">E74/10*3+3</f>
         <v>21</v>
       </c>
       <c r="O74" s="1">
@@ -10822,7 +10960,8 @@
         <v>10</v>
       </c>
       <c r="Q74" s="1">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -10860,17 +10999,18 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O75" s="1">
+        <v>5</v>
+      </c>
+      <c r="P75" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q75" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="O75" s="1">
-        <v>5</v>
-      </c>
-      <c r="P75" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -10908,17 +11048,18 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O76" s="1">
+        <v>5</v>
+      </c>
+      <c r="P76" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q76" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="O76" s="1">
-        <v>5</v>
-      </c>
-      <c r="P76" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q76" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -10956,17 +11097,18 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O77" s="1">
+        <v>5</v>
+      </c>
+      <c r="P77" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q77" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="O77" s="1">
-        <v>5</v>
-      </c>
-      <c r="P77" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q77" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -11004,17 +11146,18 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O78" s="1">
+        <v>5</v>
+      </c>
+      <c r="P78" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q78" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="O78" s="1">
-        <v>5</v>
-      </c>
-      <c r="P78" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q78" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -11052,17 +11195,18 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O79" s="1">
+        <v>5</v>
+      </c>
+      <c r="P79" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q79" s="1">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="O79" s="1">
-        <v>5</v>
-      </c>
-      <c r="P79" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q79" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -11125,7 +11269,8 @@
         <v>30</v>
       </c>
       <c r="Q81" s="1">
-        <v>35</v>
+        <f t="shared" ref="Q81:Q104" si="12">E81/10*3+10</f>
+        <v>31</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -11173,7 +11318,8 @@
         <v>30</v>
       </c>
       <c r="Q82" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -11211,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" ref="N83:N88" si="9">E83/10*3+3</f>
+        <f t="shared" ref="N83:N88" si="13">E83/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O83" s="1">
@@ -11221,7 +11367,8 @@
         <v>15</v>
       </c>
       <c r="Q83" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -11259,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="O84" s="1">
@@ -11269,7 +11416,8 @@
         <v>15</v>
       </c>
       <c r="Q84" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -11307,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="O85" s="1">
@@ -11317,7 +11465,8 @@
         <v>15</v>
       </c>
       <c r="Q85" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -11355,7 +11504,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="O86" s="1">
@@ -11365,7 +11514,8 @@
         <v>15</v>
       </c>
       <c r="Q86" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -11403,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="O87" s="1">
@@ -11413,7 +11563,8 @@
         <v>15</v>
       </c>
       <c r="Q87" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -11451,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="O88" s="1">
@@ -11461,7 +11612,8 @@
         <v>15</v>
       </c>
       <c r="Q88" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -11509,7 +11661,8 @@
         <v>30</v>
       </c>
       <c r="Q89" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -11557,7 +11710,8 @@
         <v>30</v>
       </c>
       <c r="Q90" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -11595,7 +11749,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" ref="N91:N96" si="10">E91/10*3+3</f>
+        <f t="shared" ref="N91:N96" si="14">E91/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O91" s="1">
@@ -11605,7 +11759,8 @@
         <v>15</v>
       </c>
       <c r="Q91" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -11643,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="O92" s="1">
@@ -11653,7 +11808,8 @@
         <v>15</v>
       </c>
       <c r="Q92" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -11691,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="O93" s="1">
@@ -11701,7 +11857,8 @@
         <v>15</v>
       </c>
       <c r="Q93" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -11739,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="O94" s="1">
@@ -11749,7 +11906,8 @@
         <v>15</v>
       </c>
       <c r="Q94" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -11787,7 +11945,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="O95" s="1">
@@ -11797,7 +11955,8 @@
         <v>15</v>
       </c>
       <c r="Q95" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -11835,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="O96" s="1">
@@ -11845,7 +12004,8 @@
         <v>15</v>
       </c>
       <c r="Q96" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -11893,7 +12053,8 @@
         <v>30</v>
       </c>
       <c r="Q97" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -11941,7 +12102,8 @@
         <v>30</v>
       </c>
       <c r="Q98" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -11979,7 +12141,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <f t="shared" ref="N99:N104" si="11">E99/10*3+3</f>
+        <f t="shared" ref="N99:N104" si="15">E99/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O99" s="1">
@@ -11989,7 +12151,8 @@
         <v>15</v>
       </c>
       <c r="Q99" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -12027,7 +12190,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="O100" s="1">
@@ -12037,7 +12200,8 @@
         <v>15</v>
       </c>
       <c r="Q100" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -12075,7 +12239,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="O101" s="1">
@@ -12085,7 +12249,8 @@
         <v>15</v>
       </c>
       <c r="Q101" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -12123,7 +12288,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="O102" s="1">
@@ -12133,7 +12298,8 @@
         <v>15</v>
       </c>
       <c r="Q102" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -12171,7 +12337,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="O103" s="1">
@@ -12181,7 +12347,8 @@
         <v>15</v>
       </c>
       <c r="Q103" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -12219,7 +12386,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="O104" s="1">
@@ -12229,7 +12396,8 @@
         <v>15</v>
       </c>
       <c r="Q104" s="1">
-        <v>35</v>
+        <f t="shared" si="12"/>
+        <v>31</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">
@@ -12568,7 +12736,8 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>39</v>
+        <f t="shared" ref="Q6:Q29" si="1">E6/10*3+10</f>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12616,7 +12785,8 @@
         <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12664,7 +12834,8 @@
         <v>5</v>
       </c>
       <c r="Q8" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12712,7 +12883,8 @@
         <v>5</v>
       </c>
       <c r="Q9" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12760,7 +12932,8 @@
         <v>5</v>
       </c>
       <c r="Q10" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12808,7 +12981,8 @@
         <v>5</v>
       </c>
       <c r="Q11" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12856,7 +13030,8 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12904,7 +13079,8 @@
         <v>5</v>
       </c>
       <c r="Q13" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12942,7 +13118,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" ref="N14:N21" si="1">E14/10*3+2</f>
+        <f t="shared" ref="N14:N21" si="2">E14/10*3+2</f>
         <v>26</v>
       </c>
       <c r="O14" s="1">
@@ -12952,7 +13128,8 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -12990,17 +13167,18 @@
         <v>0</v>
       </c>
       <c r="N15" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O15" s="1">
+        <v>5</v>
+      </c>
+      <c r="P15" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O15" s="1">
-        <v>5</v>
-      </c>
-      <c r="P15" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -13038,17 +13216,18 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O16" s="1">
+        <v>5</v>
+      </c>
+      <c r="P16" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O16" s="1">
-        <v>5</v>
-      </c>
-      <c r="P16" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13086,17 +13265,18 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O17" s="1">
+        <v>5</v>
+      </c>
+      <c r="P17" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O17" s="1">
-        <v>5</v>
-      </c>
-      <c r="P17" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13134,17 +13314,18 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O18" s="1">
+        <v>5</v>
+      </c>
+      <c r="P18" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O18" s="1">
-        <v>5</v>
-      </c>
-      <c r="P18" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13182,17 +13363,18 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O19" s="1">
+        <v>5</v>
+      </c>
+      <c r="P19" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O19" s="1">
-        <v>5</v>
-      </c>
-      <c r="P19" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13230,17 +13412,18 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O20" s="1">
+        <v>5</v>
+      </c>
+      <c r="P20" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O20" s="1">
-        <v>5</v>
-      </c>
-      <c r="P20" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13278,17 +13461,18 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O21" s="1">
+        <v>5</v>
+      </c>
+      <c r="P21" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="O21" s="1">
-        <v>5</v>
-      </c>
-      <c r="P21" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13326,7 +13510,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <f t="shared" ref="N22:N29" si="2">E22/10*3+3</f>
+        <f t="shared" ref="N22:N29" si="3">E22/10*3+3</f>
         <v>27</v>
       </c>
       <c r="O22" s="1">
@@ -13336,7 +13520,8 @@
         <v>10</v>
       </c>
       <c r="Q22" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13374,7 +13559,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O23" s="1">
@@ -13384,7 +13569,8 @@
         <v>10</v>
       </c>
       <c r="Q23" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13422,7 +13608,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O24" s="1">
@@ -13432,7 +13618,8 @@
         <v>5</v>
       </c>
       <c r="Q24" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13470,7 +13657,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O25" s="1">
@@ -13480,7 +13667,8 @@
         <v>5</v>
       </c>
       <c r="Q25" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13518,7 +13706,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O26" s="1">
@@ -13528,7 +13716,8 @@
         <v>5</v>
       </c>
       <c r="Q26" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13566,7 +13755,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O27" s="1">
@@ -13576,7 +13765,8 @@
         <v>5</v>
       </c>
       <c r="Q27" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13614,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O28" s="1">
@@ -13624,7 +13814,8 @@
         <v>5</v>
       </c>
       <c r="Q28" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13662,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="O29" s="1">
@@ -13672,7 +13863,8 @@
         <v>5</v>
       </c>
       <c r="Q29" s="1">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13710,7 +13902,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <f t="shared" ref="N31:N38" si="3">E31/10*3+1</f>
+        <f t="shared" ref="N31:N38" si="4">E31/10*3+1</f>
         <v>28</v>
       </c>
       <c r="O31" s="1">
@@ -13720,7 +13912,8 @@
         <v>15</v>
       </c>
       <c r="Q31" s="1">
-        <v>43</v>
+        <f t="shared" ref="Q31:Q54" si="5">E31/10*3+10</f>
+        <v>37</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13758,7 +13951,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O32" s="1">
@@ -13768,7 +13961,8 @@
         <v>15</v>
       </c>
       <c r="Q32" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13806,7 +14000,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O33" s="1">
@@ -13816,7 +14010,8 @@
         <v>7</v>
       </c>
       <c r="Q33" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13854,7 +14049,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O34" s="1">
@@ -13864,7 +14059,8 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13902,7 +14098,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O35" s="1">
@@ -13912,7 +14108,8 @@
         <v>7</v>
       </c>
       <c r="Q35" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13950,7 +14147,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O36" s="1">
@@ -13960,7 +14157,8 @@
         <v>7</v>
       </c>
       <c r="Q36" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
@@ -13998,7 +14196,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O37" s="1">
@@ -14008,7 +14206,8 @@
         <v>7</v>
       </c>
       <c r="Q37" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:17">
@@ -14046,7 +14245,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O38" s="1">
@@ -14056,7 +14255,8 @@
         <v>7</v>
       </c>
       <c r="Q38" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:17">
@@ -14094,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="1">
-        <f t="shared" ref="N39:N46" si="4">E39/10*3+2</f>
+        <f t="shared" ref="N39:N46" si="6">E39/10*3+2</f>
         <v>29</v>
       </c>
       <c r="O39" s="1">
@@ -14104,7 +14304,8 @@
         <v>15</v>
       </c>
       <c r="Q39" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:17">
@@ -14142,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O40" s="1">
@@ -14152,7 +14353,8 @@
         <v>15</v>
       </c>
       <c r="Q40" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:17">
@@ -14190,7 +14392,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O41" s="1">
@@ -14200,7 +14402,8 @@
         <v>7</v>
       </c>
       <c r="Q41" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:17">
@@ -14238,7 +14441,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O42" s="1">
@@ -14248,7 +14451,8 @@
         <v>7</v>
       </c>
       <c r="Q42" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:17">
@@ -14286,7 +14490,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O43" s="1">
@@ -14296,7 +14500,8 @@
         <v>7</v>
       </c>
       <c r="Q43" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:17">
@@ -14334,7 +14539,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O44" s="1">
@@ -14344,7 +14549,8 @@
         <v>7</v>
       </c>
       <c r="Q44" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:17">
@@ -14382,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O45" s="1">
@@ -14392,7 +14598,8 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="3:17">
@@ -14430,7 +14637,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O46" s="1">
@@ -14440,7 +14647,8 @@
         <v>7</v>
       </c>
       <c r="Q46" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:17">
@@ -14478,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="1">
-        <f t="shared" ref="N47:N54" si="5">E47/10*3+3</f>
+        <f t="shared" ref="N47:N54" si="7">E47/10*3+3</f>
         <v>30</v>
       </c>
       <c r="O47" s="1">
@@ -14488,7 +14696,8 @@
         <v>15</v>
       </c>
       <c r="Q47" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:17">
@@ -14526,7 +14735,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O48" s="1">
@@ -14536,7 +14745,8 @@
         <v>15</v>
       </c>
       <c r="Q48" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:17">
@@ -14574,7 +14784,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O49" s="1">
@@ -14584,7 +14794,8 @@
         <v>7</v>
       </c>
       <c r="Q49" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:17">
@@ -14622,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O50" s="1">
@@ -14632,7 +14843,8 @@
         <v>7</v>
       </c>
       <c r="Q50" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:17">
@@ -14670,7 +14882,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O51" s="1">
@@ -14680,7 +14892,8 @@
         <v>7</v>
       </c>
       <c r="Q51" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:17">
@@ -14718,7 +14931,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O52" s="1">
@@ -14728,7 +14941,8 @@
         <v>7</v>
       </c>
       <c r="Q52" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:17">
@@ -14766,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O53" s="1">
@@ -14776,7 +14990,8 @@
         <v>7</v>
       </c>
       <c r="Q53" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:17">
@@ -14814,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="O54" s="1">
@@ -14824,7 +15039,8 @@
         <v>7</v>
       </c>
       <c r="Q54" s="1">
-        <v>43</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:17">
@@ -14879,7 +15095,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="1">
-        <f t="shared" ref="N56:N63" si="6">E56/10*3+1</f>
+        <f t="shared" ref="N56:N63" si="8">E56/10*3+1</f>
         <v>31</v>
       </c>
       <c r="O56" s="1">
@@ -14889,7 +15105,8 @@
         <v>20</v>
       </c>
       <c r="Q56" s="1">
-        <v>47</v>
+        <f t="shared" ref="Q56:Q79" si="9">E56/10*3+10</f>
+        <v>40</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:17">
@@ -14927,7 +15144,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O57" s="1">
@@ -14937,7 +15154,8 @@
         <v>20</v>
       </c>
       <c r="Q57" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:17">
@@ -14975,7 +15193,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O58" s="1">
@@ -14985,7 +15203,8 @@
         <v>10</v>
       </c>
       <c r="Q58" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="3:17">
@@ -15023,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O59" s="1">
@@ -15033,7 +15252,8 @@
         <v>10</v>
       </c>
       <c r="Q59" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:17">
@@ -15071,7 +15291,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O60" s="1">
@@ -15081,7 +15301,8 @@
         <v>10</v>
       </c>
       <c r="Q60" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="3:17">
@@ -15119,7 +15340,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O61" s="1">
@@ -15129,7 +15350,8 @@
         <v>10</v>
       </c>
       <c r="Q61" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:17">
@@ -15167,7 +15389,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O62" s="1">
@@ -15177,7 +15399,8 @@
         <v>10</v>
       </c>
       <c r="Q62" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:17">
@@ -15215,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="O63" s="1">
@@ -15225,7 +15448,8 @@
         <v>10</v>
       </c>
       <c r="Q63" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:17">
@@ -15263,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="1">
-        <f t="shared" ref="N64:N71" si="7">E64/10*3+2</f>
+        <f t="shared" ref="N64:N71" si="10">E64/10*3+2</f>
         <v>32</v>
       </c>
       <c r="O64" s="1">
@@ -15273,7 +15497,8 @@
         <v>20</v>
       </c>
       <c r="Q64" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:17">
@@ -15311,7 +15536,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O65" s="1">
@@ -15321,7 +15546,8 @@
         <v>20</v>
       </c>
       <c r="Q65" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="3:17">
@@ -15359,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O66" s="1">
@@ -15369,7 +15595,8 @@
         <v>10</v>
       </c>
       <c r="Q66" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="3:17">
@@ -15407,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O67" s="1">
@@ -15417,7 +15644,8 @@
         <v>10</v>
       </c>
       <c r="Q67" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="3:17">
@@ -15455,7 +15683,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O68" s="1">
@@ -15465,7 +15693,8 @@
         <v>10</v>
       </c>
       <c r="Q68" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="3:17">
@@ -15503,7 +15732,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O69" s="1">
@@ -15513,7 +15742,8 @@
         <v>10</v>
       </c>
       <c r="Q69" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="3:17">
@@ -15551,7 +15781,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O70" s="1">
@@ -15561,7 +15791,8 @@
         <v>10</v>
       </c>
       <c r="Q70" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="3:17">
@@ -15599,7 +15830,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="O71" s="1">
@@ -15609,7 +15840,8 @@
         <v>10</v>
       </c>
       <c r="Q71" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="3:17">
@@ -15647,7 +15879,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="1">
-        <f t="shared" ref="N72:N79" si="8">E72/10*3+3</f>
+        <f t="shared" ref="N72:N79" si="11">E72/10*3+3</f>
         <v>33</v>
       </c>
       <c r="O72" s="1">
@@ -15657,7 +15889,8 @@
         <v>20</v>
       </c>
       <c r="Q72" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="3:17">
@@ -15695,7 +15928,7 @@
         <v>0</v>
       </c>
       <c r="N73" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O73" s="1">
@@ -15705,7 +15938,8 @@
         <v>20</v>
       </c>
       <c r="Q73" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="3:17">
@@ -15743,7 +15977,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O74" s="1">
@@ -15753,7 +15987,8 @@
         <v>10</v>
       </c>
       <c r="Q74" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="3:17">
@@ -15791,7 +16026,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O75" s="1">
@@ -15801,7 +16036,8 @@
         <v>10</v>
       </c>
       <c r="Q75" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="3:17">
@@ -15839,7 +16075,7 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O76" s="1">
@@ -15849,7 +16085,8 @@
         <v>10</v>
       </c>
       <c r="Q76" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="3:17">
@@ -15887,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O77" s="1">
@@ -15897,7 +16134,8 @@
         <v>10</v>
       </c>
       <c r="Q77" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="3:17">
@@ -15935,7 +16173,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O78" s="1">
@@ -15945,7 +16183,8 @@
         <v>10</v>
       </c>
       <c r="Q78" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="3:17">
@@ -15983,7 +16222,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O79" s="1">
@@ -15993,7 +16232,8 @@
         <v>10</v>
       </c>
       <c r="Q79" s="1">
-        <v>47</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="3:17">
@@ -16046,7 +16286,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="1">
-        <f t="shared" ref="N81:N88" si="9">E81/10*3+1</f>
+        <f t="shared" ref="N81:N88" si="12">E81/10*3+1</f>
         <v>34</v>
       </c>
       <c r="O81" s="1">
@@ -16056,7 +16296,7 @@
         <v>30</v>
       </c>
       <c r="Q81" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="3:17">
@@ -16094,7 +16334,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O82" s="1">
@@ -16104,7 +16344,7 @@
         <v>30</v>
       </c>
       <c r="Q82" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="3:17">
@@ -16142,7 +16382,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O83" s="1">
@@ -16152,7 +16392,7 @@
         <v>15</v>
       </c>
       <c r="Q83" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="3:17">
@@ -16190,7 +16430,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O84" s="1">
@@ -16200,7 +16440,7 @@
         <v>15</v>
       </c>
       <c r="Q84" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="3:17">
@@ -16238,7 +16478,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O85" s="1">
@@ -16248,7 +16488,7 @@
         <v>15</v>
       </c>
       <c r="Q85" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="3:17">
@@ -16286,7 +16526,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O86" s="1">
@@ -16296,7 +16536,7 @@
         <v>15</v>
       </c>
       <c r="Q86" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="3:17">
@@ -16334,7 +16574,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O87" s="1">
@@ -16344,7 +16584,7 @@
         <v>15</v>
       </c>
       <c r="Q87" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="3:17">
@@ -16382,7 +16622,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="O88" s="1">
@@ -16392,7 +16632,7 @@
         <v>15</v>
       </c>
       <c r="Q88" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="3:17">
@@ -16430,7 +16670,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="1">
-        <f t="shared" ref="N89:N96" si="10">E89/10*3+2</f>
+        <f t="shared" ref="N89:N96" si="13">E89/10*3+2</f>
         <v>35</v>
       </c>
       <c r="O89" s="1">
@@ -16440,7 +16680,7 @@
         <v>30</v>
       </c>
       <c r="Q89" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="3:17">
@@ -16478,7 +16718,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O90" s="1">
@@ -16488,7 +16728,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="3:17">
@@ -16526,7 +16766,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O91" s="1">
@@ -16536,7 +16776,7 @@
         <v>15</v>
       </c>
       <c r="Q91" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="3:17">
@@ -16574,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O92" s="1">
@@ -16584,7 +16824,7 @@
         <v>15</v>
       </c>
       <c r="Q92" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="3:17">
@@ -16622,7 +16862,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O93" s="1">
@@ -16632,7 +16872,7 @@
         <v>15</v>
       </c>
       <c r="Q93" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="3:17">
@@ -16670,7 +16910,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O94" s="1">
@@ -16680,7 +16920,7 @@
         <v>15</v>
       </c>
       <c r="Q94" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="3:17">
@@ -16718,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O95" s="1">
@@ -16728,7 +16968,7 @@
         <v>15</v>
       </c>
       <c r="Q95" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="3:17">
@@ -16766,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>35</v>
       </c>
       <c r="O96" s="1">
@@ -16776,7 +17016,7 @@
         <v>15</v>
       </c>
       <c r="Q96" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="3:17">
@@ -16814,7 +17054,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="1">
-        <f t="shared" ref="N97:N104" si="11">E97/10*3+3</f>
+        <f t="shared" ref="N97:N104" si="14">E97/10*3+3</f>
         <v>36</v>
       </c>
       <c r="O97" s="1">
@@ -16824,7 +17064,7 @@
         <v>30</v>
       </c>
       <c r="Q97" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="3:17">
@@ -16862,7 +17102,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O98" s="1">
@@ -16872,7 +17112,7 @@
         <v>30</v>
       </c>
       <c r="Q98" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="3:17">
@@ -16910,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O99" s="1">
@@ -16920,7 +17160,7 @@
         <v>15</v>
       </c>
       <c r="Q99" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="3:17">
@@ -16958,7 +17198,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O100" s="1">
@@ -16968,7 +17208,7 @@
         <v>15</v>
       </c>
       <c r="Q100" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="3:17">
@@ -17006,7 +17246,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O101" s="1">
@@ -17016,7 +17256,7 @@
         <v>15</v>
       </c>
       <c r="Q101" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="3:17">
@@ -17054,7 +17294,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O102" s="1">
@@ -17064,7 +17304,7 @@
         <v>15</v>
       </c>
       <c r="Q102" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="3:17">
@@ -17102,7 +17342,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O103" s="1">
@@ -17112,7 +17352,7 @@
         <v>15</v>
       </c>
       <c r="Q103" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="3:17">
@@ -17150,7 +17390,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="O104" s="1">
@@ -17160,7 +17400,7 @@
         <v>15</v>
       </c>
       <c r="Q104" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105" customFormat="1" customHeight="1" spans="3:17">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -932,7 +937,7 @@
     <t>木龙战刃</t>
   </si>
   <si>
-    <t>16000,15</t>
+    <t>14000,15</t>
   </si>
   <si>
     <t>木龙战甲</t>
@@ -941,7 +946,7 @@
     <t>木龙战链</t>
   </si>
   <si>
-    <t>8000,8</t>
+    <t>7000,8</t>
   </si>
   <si>
     <t>木龙战盔</t>
@@ -1010,7 +1015,7 @@
     <t>土龙战刃</t>
   </si>
   <si>
-    <t>30000,20</t>
+    <t>20000,20</t>
   </si>
   <si>
     <t>土龙战甲</t>
@@ -1019,7 +1024,7 @@
     <t>土龙战链</t>
   </si>
   <si>
-    <t>15000,10</t>
+    <t>10000,10</t>
   </si>
   <si>
     <t>土龙战盔</t>
@@ -8882,7 +8887,7 @@
         <v>5</v>
       </c>
       <c r="P31" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" ref="Q31:Q54" si="4">E31/10*3+10</f>
@@ -8931,7 +8936,7 @@
         <v>5</v>
       </c>
       <c r="P32" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q32" s="1">
         <f t="shared" si="4"/>
@@ -8980,7 +8985,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q33" s="1">
         <f t="shared" si="4"/>
@@ -9029,7 +9034,7 @@
         <v>5</v>
       </c>
       <c r="P34" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q34" s="1">
         <f t="shared" si="4"/>
@@ -9078,7 +9083,7 @@
         <v>5</v>
       </c>
       <c r="P35" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q35" s="1">
         <f t="shared" si="4"/>
@@ -9127,7 +9132,7 @@
         <v>5</v>
       </c>
       <c r="P36" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q36" s="1">
         <f t="shared" si="4"/>
@@ -9176,7 +9181,7 @@
         <v>5</v>
       </c>
       <c r="P37" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q37" s="1">
         <f t="shared" si="4"/>
@@ -9225,7 +9230,7 @@
         <v>5</v>
       </c>
       <c r="P38" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q38" s="1">
         <f t="shared" si="4"/>
@@ -9274,7 +9279,7 @@
         <v>5</v>
       </c>
       <c r="P39" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q39" s="1">
         <f t="shared" si="4"/>
@@ -9323,7 +9328,7 @@
         <v>5</v>
       </c>
       <c r="P40" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q40" s="1">
         <f t="shared" si="4"/>
@@ -9372,7 +9377,7 @@
         <v>5</v>
       </c>
       <c r="P41" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q41" s="1">
         <f t="shared" si="4"/>
@@ -9421,7 +9426,7 @@
         <v>5</v>
       </c>
       <c r="P42" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="1">
         <f t="shared" si="4"/>
@@ -9470,7 +9475,7 @@
         <v>5</v>
       </c>
       <c r="P43" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q43" s="1">
         <f t="shared" si="4"/>
@@ -9519,7 +9524,7 @@
         <v>5</v>
       </c>
       <c r="P44" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q44" s="1">
         <f t="shared" si="4"/>
@@ -9568,7 +9573,7 @@
         <v>5</v>
       </c>
       <c r="P45" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="1">
         <f t="shared" si="4"/>
@@ -9617,7 +9622,7 @@
         <v>5</v>
       </c>
       <c r="P46" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="1">
         <f t="shared" si="4"/>
@@ -9666,7 +9671,7 @@
         <v>5</v>
       </c>
       <c r="P47" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q47" s="1">
         <f t="shared" si="4"/>
@@ -9715,7 +9720,7 @@
         <v>5</v>
       </c>
       <c r="P48" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q48" s="1">
         <f t="shared" si="4"/>
@@ -9764,7 +9769,7 @@
         <v>5</v>
       </c>
       <c r="P49" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q49" s="1">
         <f t="shared" si="4"/>
@@ -9813,7 +9818,7 @@
         <v>5</v>
       </c>
       <c r="P50" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q50" s="1">
         <f t="shared" si="4"/>
@@ -9862,7 +9867,7 @@
         <v>5</v>
       </c>
       <c r="P51" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q51" s="1">
         <f t="shared" si="4"/>
@@ -9911,7 +9916,7 @@
         <v>5</v>
       </c>
       <c r="P52" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="1">
         <f t="shared" si="4"/>
@@ -9960,7 +9965,7 @@
         <v>5</v>
       </c>
       <c r="P53" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q53" s="1">
         <f t="shared" si="4"/>
@@ -10009,7 +10014,7 @@
         <v>5</v>
       </c>
       <c r="P54" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q54" s="1">
         <f t="shared" si="4"/>
@@ -10075,7 +10080,8 @@
         <v>5</v>
       </c>
       <c r="P56" s="1">
-        <v>20</v>
+        <f>(E56/10+1)*2</f>
+        <v>14</v>
       </c>
       <c r="Q56" s="1">
         <f t="shared" ref="Q56:Q79" si="8">E56/10*3+10</f>
@@ -10124,7 +10130,8 @@
         <v>5</v>
       </c>
       <c r="P57" s="1">
-        <v>20</v>
+        <f>(E57/10+1)*2</f>
+        <v>14</v>
       </c>
       <c r="Q57" s="1">
         <f t="shared" si="8"/>
@@ -10173,7 +10180,8 @@
         <v>5</v>
       </c>
       <c r="P58" s="1">
-        <v>10</v>
+        <f t="shared" ref="P58:P63" si="10">E58/10+1</f>
+        <v>7</v>
       </c>
       <c r="Q58" s="1">
         <f t="shared" si="8"/>
@@ -10222,7 +10230,8 @@
         <v>5</v>
       </c>
       <c r="P59" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="Q59" s="1">
         <f t="shared" si="8"/>
@@ -10271,7 +10280,8 @@
         <v>5</v>
       </c>
       <c r="P60" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="Q60" s="1">
         <f t="shared" si="8"/>
@@ -10320,7 +10330,8 @@
         <v>5</v>
       </c>
       <c r="P61" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="Q61" s="1">
         <f t="shared" si="8"/>
@@ -10369,7 +10380,8 @@
         <v>5</v>
       </c>
       <c r="P62" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="Q62" s="1">
         <f t="shared" si="8"/>
@@ -10418,7 +10430,8 @@
         <v>5</v>
       </c>
       <c r="P63" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
       <c r="Q63" s="1">
         <f t="shared" si="8"/>
@@ -10467,7 +10480,8 @@
         <v>5</v>
       </c>
       <c r="P64" s="1">
-        <v>20</v>
+        <f>(E64/10+1)*2</f>
+        <v>14</v>
       </c>
       <c r="Q64" s="1">
         <f t="shared" si="8"/>
@@ -10516,7 +10530,8 @@
         <v>5</v>
       </c>
       <c r="P65" s="1">
-        <v>20</v>
+        <f>(E65/10+1)*2</f>
+        <v>14</v>
       </c>
       <c r="Q65" s="1">
         <f t="shared" si="8"/>
@@ -10558,14 +10573,15 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" ref="N66:N71" si="10">E66/10*3+3</f>
+        <f t="shared" ref="N66:N71" si="11">E66/10*3+3</f>
         <v>21</v>
       </c>
       <c r="O66" s="1">
         <v>5</v>
       </c>
       <c r="P66" s="1">
-        <v>10</v>
+        <f t="shared" ref="P66:P71" si="12">E66/10+1</f>
+        <v>7</v>
       </c>
       <c r="Q66" s="1">
         <f t="shared" si="8"/>
@@ -10607,14 +10623,15 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="O67" s="1">
         <v>5</v>
       </c>
       <c r="P67" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="Q67" s="1">
         <f t="shared" si="8"/>
@@ -10656,14 +10673,15 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="O68" s="1">
         <v>5</v>
       </c>
       <c r="P68" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="Q68" s="1">
         <f t="shared" si="8"/>
@@ -10705,14 +10723,15 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="O69" s="1">
         <v>5</v>
       </c>
       <c r="P69" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="Q69" s="1">
         <f t="shared" si="8"/>
@@ -10754,14 +10773,15 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="O70" s="1">
         <v>5</v>
       </c>
       <c r="P70" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="Q70" s="1">
         <f t="shared" si="8"/>
@@ -10803,14 +10823,15 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="O71" s="1">
         <v>5</v>
       </c>
       <c r="P71" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="Q71" s="1">
         <f t="shared" si="8"/>
@@ -10859,7 +10880,8 @@
         <v>5</v>
       </c>
       <c r="P72" s="1">
-        <v>20</v>
+        <f>(E72/10+1)*2</f>
+        <v>14</v>
       </c>
       <c r="Q72" s="1">
         <f t="shared" si="8"/>
@@ -10908,7 +10930,8 @@
         <v>5</v>
       </c>
       <c r="P73" s="1">
-        <v>20</v>
+        <f>(E73/10+1)*2</f>
+        <v>14</v>
       </c>
       <c r="Q73" s="1">
         <f t="shared" si="8"/>
@@ -10950,14 +10973,15 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" ref="N74:N79" si="11">E74/10*3+3</f>
+        <f t="shared" ref="N74:N79" si="13">E74/10*3+3</f>
         <v>21</v>
       </c>
       <c r="O74" s="1">
         <v>5</v>
       </c>
       <c r="P74" s="1">
-        <v>10</v>
+        <f t="shared" ref="P74:P79" si="14">E74/10+1</f>
+        <v>7</v>
       </c>
       <c r="Q74" s="1">
         <f t="shared" si="8"/>
@@ -10999,14 +11023,15 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="O75" s="1">
         <v>5</v>
       </c>
       <c r="P75" s="1">
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>7</v>
       </c>
       <c r="Q75" s="1">
         <f t="shared" si="8"/>
@@ -11048,14 +11073,15 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="O76" s="1">
         <v>5</v>
       </c>
       <c r="P76" s="1">
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>7</v>
       </c>
       <c r="Q76" s="1">
         <f t="shared" si="8"/>
@@ -11097,14 +11123,15 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="O77" s="1">
         <v>5</v>
       </c>
       <c r="P77" s="1">
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>7</v>
       </c>
       <c r="Q77" s="1">
         <f t="shared" si="8"/>
@@ -11146,14 +11173,15 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="O78" s="1">
         <v>5</v>
       </c>
       <c r="P78" s="1">
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>7</v>
       </c>
       <c r="Q78" s="1">
         <f t="shared" si="8"/>
@@ -11195,14 +11223,15 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="O79" s="1">
         <v>5</v>
       </c>
       <c r="P79" s="1">
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>7</v>
       </c>
       <c r="Q79" s="1">
         <f t="shared" si="8"/>
@@ -11266,10 +11295,11 @@
         <v>5</v>
       </c>
       <c r="P81" s="1">
-        <v>30</v>
+        <f>(E81/10+1)*2</f>
+        <v>16</v>
       </c>
       <c r="Q81" s="1">
-        <f t="shared" ref="Q81:Q104" si="12">E81/10*3+10</f>
+        <f t="shared" ref="Q81:Q104" si="15">E81/10*3+10</f>
         <v>31</v>
       </c>
     </row>
@@ -11315,10 +11345,11 @@
         <v>5</v>
       </c>
       <c r="P82" s="1">
-        <v>30</v>
+        <f>(E82/10+1)*2</f>
+        <v>16</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11357,17 +11388,18 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" ref="N83:N88" si="13">E83/10*3+3</f>
+        <f t="shared" ref="N83:N88" si="16">E83/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O83" s="1">
         <v>5</v>
       </c>
       <c r="P83" s="1">
-        <v>15</v>
+        <f t="shared" ref="P83:P88" si="17">E83/10+1</f>
+        <v>8</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11406,17 +11438,18 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="O84" s="1">
         <v>5</v>
       </c>
       <c r="P84" s="1">
-        <v>15</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11455,17 +11488,18 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="O85" s="1">
         <v>5</v>
       </c>
       <c r="P85" s="1">
-        <v>15</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11504,17 +11538,18 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="O86" s="1">
         <v>5</v>
       </c>
       <c r="P86" s="1">
-        <v>15</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11553,17 +11588,18 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="O87" s="1">
         <v>5</v>
       </c>
       <c r="P87" s="1">
-        <v>15</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11602,17 +11638,18 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="O88" s="1">
         <v>5</v>
       </c>
       <c r="P88" s="1">
-        <v>15</v>
+        <f t="shared" si="17"/>
+        <v>8</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11658,10 +11695,11 @@
         <v>5</v>
       </c>
       <c r="P89" s="1">
-        <v>30</v>
+        <f>(E89/10+1)*2</f>
+        <v>16</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11707,10 +11745,11 @@
         <v>5</v>
       </c>
       <c r="P90" s="1">
-        <v>30</v>
+        <f>(E90/10+1)*2</f>
+        <v>16</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11749,17 +11788,18 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" ref="N91:N96" si="14">E91/10*3+3</f>
+        <f t="shared" ref="N91:N96" si="18">E91/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O91" s="1">
         <v>5</v>
       </c>
       <c r="P91" s="1">
-        <v>15</v>
+        <f t="shared" ref="P91:P96" si="19">E91/10+1</f>
+        <v>8</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11798,17 +11838,18 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="O92" s="1">
         <v>5</v>
       </c>
       <c r="P92" s="1">
-        <v>15</v>
+        <f t="shared" si="19"/>
+        <v>8</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11847,17 +11888,18 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="O93" s="1">
         <v>5</v>
       </c>
       <c r="P93" s="1">
-        <v>15</v>
+        <f t="shared" si="19"/>
+        <v>8</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11896,17 +11938,18 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="O94" s="1">
         <v>5</v>
       </c>
       <c r="P94" s="1">
-        <v>15</v>
+        <f t="shared" si="19"/>
+        <v>8</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11945,17 +11988,18 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="O95" s="1">
         <v>5</v>
       </c>
       <c r="P95" s="1">
-        <v>15</v>
+        <f t="shared" si="19"/>
+        <v>8</v>
       </c>
       <c r="Q95" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -11994,17 +12038,18 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="O96" s="1">
         <v>5</v>
       </c>
       <c r="P96" s="1">
-        <v>15</v>
+        <f t="shared" si="19"/>
+        <v>8</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -12050,10 +12095,11 @@
         <v>5</v>
       </c>
       <c r="P97" s="1">
-        <v>30</v>
+        <f>(E97/10+1)*2</f>
+        <v>16</v>
       </c>
       <c r="Q97" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -12099,10 +12145,11 @@
         <v>5</v>
       </c>
       <c r="P98" s="1">
-        <v>30</v>
+        <f>(E98/10+1)*2</f>
+        <v>16</v>
       </c>
       <c r="Q98" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -12141,17 +12188,18 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <f t="shared" ref="N99:N104" si="15">E99/10*3+3</f>
+        <f t="shared" ref="N99:N104" si="20">E99/10*3+3</f>
         <v>24</v>
       </c>
       <c r="O99" s="1">
         <v>5</v>
       </c>
       <c r="P99" s="1">
-        <v>15</v>
+        <f t="shared" ref="P99:P104" si="21">E99/10+1</f>
+        <v>8</v>
       </c>
       <c r="Q99" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>31</v>
       </c>
     </row>
@@ -12190,17 +12238,18 @@
         <v>0</v>
       </c>
       <c r="N100" s="1">
+        <f t="shared" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="O100" s="1">
+        <v>5</v>
+      </c>
+      <c r="P100" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="Q100" s="1">
         <f t="shared" si="15"/>
-        <v>24</v>
-      </c>
-      <c r="O100" s="1">
-        <v>5</v>
-      </c>
-      <c r="P100" s="1">
-        <v>15</v>
-      </c>
-      <c r="Q100" s="1">
-        <f t="shared" si="12"/>
         <v>31</v>
       </c>
     </row>
@@ -12239,17 +12288,18 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
+        <f t="shared" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="O101" s="1">
+        <v>5</v>
+      </c>
+      <c r="P101" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="Q101" s="1">
         <f t="shared" si="15"/>
-        <v>24</v>
-      </c>
-      <c r="O101" s="1">
-        <v>5</v>
-      </c>
-      <c r="P101" s="1">
-        <v>15</v>
-      </c>
-      <c r="Q101" s="1">
-        <f t="shared" si="12"/>
         <v>31</v>
       </c>
     </row>
@@ -12288,17 +12338,18 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
+        <f t="shared" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="O102" s="1">
+        <v>5</v>
+      </c>
+      <c r="P102" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="Q102" s="1">
         <f t="shared" si="15"/>
-        <v>24</v>
-      </c>
-      <c r="O102" s="1">
-        <v>5</v>
-      </c>
-      <c r="P102" s="1">
-        <v>15</v>
-      </c>
-      <c r="Q102" s="1">
-        <f t="shared" si="12"/>
         <v>31</v>
       </c>
     </row>
@@ -12337,17 +12388,18 @@
         <v>0</v>
       </c>
       <c r="N103" s="1">
+        <f t="shared" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="O103" s="1">
+        <v>5</v>
+      </c>
+      <c r="P103" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="Q103" s="1">
         <f t="shared" si="15"/>
-        <v>24</v>
-      </c>
-      <c r="O103" s="1">
-        <v>5</v>
-      </c>
-      <c r="P103" s="1">
-        <v>15</v>
-      </c>
-      <c r="Q103" s="1">
-        <f t="shared" si="12"/>
         <v>31</v>
       </c>
     </row>
@@ -12386,17 +12438,18 @@
         <v>0</v>
       </c>
       <c r="N104" s="1">
+        <f t="shared" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="O104" s="1">
+        <v>5</v>
+      </c>
+      <c r="P104" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="Q104" s="1">
         <f t="shared" si="15"/>
-        <v>24</v>
-      </c>
-      <c r="O104" s="1">
-        <v>5</v>
-      </c>
-      <c r="P104" s="1">
-        <v>15</v>
-      </c>
-      <c r="Q104" s="1">
-        <f t="shared" si="12"/>
         <v>31</v>
       </c>
     </row>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="430">
   <si>
     <t>_id</t>
   </si>
@@ -1093,24 +1093,21 @@
     <t>冰龙战刃</t>
   </si>
   <si>
-    <t>20,5</t>
+    <t>30000,24</t>
   </si>
   <si>
     <t>冰龙战甲</t>
   </si>
   <si>
-    <t>10,2</t>
-  </si>
-  <si>
     <t>冰龙战链</t>
   </si>
   <si>
+    <t>15000,12</t>
+  </si>
+  <si>
     <t>冰龙战盔</t>
   </si>
   <si>
-    <t>100,10</t>
-  </si>
-  <si>
     <t>冰龙战镯</t>
   </si>
   <si>
@@ -1120,9 +1117,6 @@
     <t>冰龙战带</t>
   </si>
   <si>
-    <t>5,1</t>
-  </si>
-  <si>
     <t>冰龙战靴</t>
   </si>
   <si>
@@ -1177,12 +1171,18 @@
     <t>炎龙战刃</t>
   </si>
   <si>
+    <t>40000,28</t>
+  </si>
+  <si>
     <t>炎龙战甲</t>
   </si>
   <si>
     <t>炎龙战链</t>
   </si>
   <si>
+    <t>20000,14</t>
+  </si>
+  <si>
     <t>炎龙战盔</t>
   </si>
   <si>
@@ -1249,12 +1249,18 @@
     <t>光龙战刃</t>
   </si>
   <si>
+    <t>50000,32</t>
+  </si>
+  <si>
     <t>光龙战甲</t>
   </si>
   <si>
     <t>光龙战链</t>
   </si>
   <si>
+    <t>25000,16</t>
+  </si>
+  <si>
     <t>光龙战盔</t>
   </si>
   <si>
@@ -1321,10 +1327,16 @@
     <t>暗龙战刃</t>
   </si>
   <si>
+    <t>60000,36</t>
+  </si>
+  <si>
     <t>暗龙战甲</t>
   </si>
   <si>
     <t>暗龙战链</t>
+  </si>
+  <si>
+    <t>30000,18</t>
   </si>
   <si>
     <t>暗龙战盔</t>
@@ -12816,7 +12828,7 @@
         <v>27</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -12853,7 +12865,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -12865,7 +12877,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -12914,7 +12926,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -12951,7 +12963,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -12963,7 +12975,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -13000,7 +13012,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -13012,7 +13024,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -13049,7 +13061,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -13061,7 +13073,7 @@
         <v>27</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -13098,7 +13110,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -13110,7 +13122,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -13147,7 +13159,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -13196,7 +13208,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -13208,7 +13220,7 @@
         <v>27</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -13245,7 +13257,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -13257,7 +13269,7 @@
         <v>40</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -13294,7 +13306,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -13306,7 +13318,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -13343,7 +13355,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -13355,7 +13367,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -13392,7 +13404,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -13404,7 +13416,7 @@
         <v>40</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -13441,7 +13453,7 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -13453,7 +13465,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -13490,7 +13502,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -13502,7 +13514,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -13539,7 +13551,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -13588,7 +13600,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -13600,7 +13612,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -13637,7 +13649,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -13649,7 +13661,7 @@
         <v>49</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -13686,7 +13698,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -13698,7 +13710,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -13735,7 +13747,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -13747,7 +13759,7 @@
         <v>31</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -13784,7 +13796,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -13796,7 +13808,7 @@
         <v>49</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -13833,7 +13845,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -13845,7 +13857,7 @@
         <v>27</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -13882,7 +13894,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -13894,7 +13906,7 @@
         <v>31</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -13931,7 +13943,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -13943,7 +13955,7 @@
         <v>24</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -13980,7 +13992,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -13992,7 +14004,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -14029,7 +14041,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -14041,7 +14053,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -14090,7 +14102,7 @@
         <v>31</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -14139,7 +14151,7 @@
         <v>31</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -14188,7 +14200,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -14237,7 +14249,7 @@
         <v>27</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -14286,7 +14298,7 @@
         <v>31</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -14335,7 +14347,7 @@
         <v>40</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -14384,7 +14396,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -14433,7 +14445,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -14482,7 +14494,7 @@
         <v>31</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -14531,7 +14543,7 @@
         <v>31</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -14580,7 +14592,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -14629,7 +14641,7 @@
         <v>27</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -14678,7 +14690,7 @@
         <v>31</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -14727,7 +14739,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -14776,7 +14788,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -14825,7 +14837,7 @@
         <v>49</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -14874,7 +14886,7 @@
         <v>31</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -14923,7 +14935,7 @@
         <v>31</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -14972,7 +14984,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -15021,7 +15033,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -15070,7 +15082,7 @@
         <v>31</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -15136,7 +15148,7 @@
         <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -15173,7 +15185,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -15185,7 +15197,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -15222,7 +15234,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -15234,7 +15246,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -15271,7 +15283,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -15283,7 +15295,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -15320,7 +15332,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -15332,7 +15344,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -15369,7 +15381,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -15381,7 +15393,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -15418,7 +15430,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -15430,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -15467,7 +15479,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -15479,7 +15491,7 @@
         <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -15516,7 +15528,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -15528,7 +15540,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -15565,7 +15577,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -15577,7 +15589,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -15614,7 +15626,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -15626,7 +15638,7 @@
         <v>40</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -15663,7 +15675,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15675,7 +15687,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -15712,7 +15724,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15724,7 +15736,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -15761,7 +15773,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15773,7 +15785,7 @@
         <v>40</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -15810,7 +15822,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15822,7 +15834,7 @@
         <v>27</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -15859,7 +15871,7 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15871,7 +15883,7 @@
         <v>31</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -15908,7 +15920,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -15920,7 +15932,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -15957,7 +15969,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -15969,7 +15981,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -16006,7 +16018,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -16018,7 +16030,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -16055,7 +16067,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -16067,7 +16079,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -16104,7 +16116,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -16116,7 +16128,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -16153,7 +16165,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -16165,7 +16177,7 @@
         <v>49</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -16202,7 +16214,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -16214,7 +16226,7 @@
         <v>27</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -16251,7 +16263,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -16263,7 +16275,7 @@
         <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -16315,7 +16327,7 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -16327,7 +16339,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -16363,7 +16375,7 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -16375,7 +16387,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -16411,7 +16423,7 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -16423,7 +16435,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -16459,7 +16471,7 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -16471,7 +16483,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -16507,7 +16519,7 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -16519,7 +16531,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -16555,7 +16567,7 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -16567,7 +16579,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -16603,7 +16615,7 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -16615,7 +16627,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -16651,7 +16663,7 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16663,7 +16675,7 @@
         <v>31</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -16699,7 +16711,7 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16711,7 +16723,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -16747,7 +16759,7 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16759,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -16795,7 +16807,7 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16807,7 +16819,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -16843,7 +16855,7 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -16855,7 +16867,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -16891,7 +16903,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -16903,7 +16915,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -16939,7 +16951,7 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -16951,7 +16963,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -16987,7 +16999,7 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -16999,7 +17011,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -17035,7 +17047,7 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -17047,7 +17059,7 @@
         <v>31</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -17083,7 +17095,7 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -17095,7 +17107,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -17131,7 +17143,7 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -17143,7 +17155,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -17179,7 +17191,7 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -17191,7 +17203,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -17227,7 +17239,7 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -17239,7 +17251,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -17275,7 +17287,7 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -17287,7 +17299,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -17323,7 +17335,7 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -17335,7 +17347,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -17371,7 +17383,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -17383,7 +17395,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -17419,7 +17431,7 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -17431,7 +17443,7 @@
         <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -17754,7 +17766,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17763,10 +17775,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17801,7 +17813,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17810,10 +17822,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -17885,7 +17897,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17903,7 +17915,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17934,16 +17946,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -17980,10 +17992,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -18053,7 +18065,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -18065,7 +18077,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -18077,7 +18089,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -18099,7 +18111,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -18108,10 +18120,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -18123,7 +18135,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -18145,7 +18157,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -18157,7 +18169,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -18189,7 +18201,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -18201,7 +18213,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -18213,7 +18225,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -18235,7 +18247,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -18244,10 +18256,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -18259,7 +18271,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -18281,7 +18293,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -18293,7 +18305,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -18325,7 +18337,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18334,10 +18346,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18349,7 +18361,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18371,7 +18383,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18383,7 +18395,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18415,7 +18427,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18427,7 +18439,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18477,7 +18489,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18486,10 +18498,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -18501,7 +18513,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18523,7 +18535,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18535,7 +18547,7 @@
         <v>27</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K17" s="2">
         <v>11</v>
@@ -18567,7 +18579,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18579,7 +18591,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="K18" s="2">
         <v>12</v>
@@ -18611,7 +18623,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18620,10 +18632,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18635,7 +18647,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18657,7 +18669,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18669,7 +18681,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18701,7 +18713,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18713,7 +18725,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18745,7 +18757,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18754,10 +18766,10 @@
         <v>36</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18769,7 +18781,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18791,7 +18803,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18803,7 +18815,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18835,7 +18847,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -18847,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -18884,10 +18896,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -18899,7 +18911,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -18915,7 +18927,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -18926,10 +18938,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -18941,7 +18953,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -18966,10 +18978,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -18981,7 +18993,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -19006,10 +19018,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -19021,7 +19033,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -19037,7 +19049,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -19048,10 +19060,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -19063,7 +19075,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -19088,10 +19100,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -19103,7 +19115,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -19128,10 +19140,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -19143,7 +19155,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -19159,7 +19171,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -19170,10 +19182,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -19185,7 +19197,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19210,10 +19222,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -19225,7 +19237,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -19250,10 +19262,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -19265,7 +19277,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -19281,7 +19293,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -19292,10 +19304,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -19307,7 +19319,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -19332,10 +19344,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -19347,7 +19359,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -19372,10 +19384,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -19387,7 +19399,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19403,7 +19415,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19414,10 +19426,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -19429,7 +19441,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19454,10 +19466,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -19469,7 +19481,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19494,10 +19506,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -19509,7 +19521,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19525,7 +19537,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19536,10 +19548,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -19551,7 +19563,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19576,10 +19588,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -19591,7 +19603,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19616,10 +19628,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -19631,7 +19643,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19647,7 +19659,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19658,10 +19670,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -19673,7 +19685,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19698,10 +19710,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -19713,7 +19725,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19738,10 +19750,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -19753,7 +19765,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19769,7 +19781,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19780,10 +19792,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -19795,7 +19807,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19820,10 +19832,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -19835,7 +19847,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="436">
   <si>
     <t>_id</t>
   </si>
@@ -856,7 +856,7 @@
     <t>金龙战刃</t>
   </si>
   <si>
-    <t>8000,12</t>
+    <t>7000,12</t>
   </si>
   <si>
     <t>金龙战甲</t>
@@ -865,13 +865,13 @@
     <t>金龙战链</t>
   </si>
   <si>
-    <t>4000,6</t>
+    <t>3500,6</t>
   </si>
   <si>
     <t>金龙战盔</t>
   </si>
   <si>
-    <t>80000,12</t>
+    <t>70000,12</t>
   </si>
   <si>
     <t>金龙战镯</t>
@@ -937,7 +937,7 @@
     <t>木龙战刃</t>
   </si>
   <si>
-    <t>14000,15</t>
+    <t>10000,15</t>
   </si>
   <si>
     <t>木龙战甲</t>
@@ -946,12 +946,15 @@
     <t>木龙战链</t>
   </si>
   <si>
-    <t>7000,8</t>
+    <t>5000,8</t>
   </si>
   <si>
     <t>木龙战盔</t>
   </si>
   <si>
+    <t>100000,15</t>
+  </si>
+  <si>
     <t>木龙战镯</t>
   </si>
   <si>
@@ -1015,7 +1018,7 @@
     <t>土龙战刃</t>
   </si>
   <si>
-    <t>20000,20</t>
+    <t>15000,20</t>
   </si>
   <si>
     <t>土龙战甲</t>
@@ -1024,12 +1027,15 @@
     <t>土龙战链</t>
   </si>
   <si>
-    <t>10000,10</t>
+    <t>7500,10</t>
   </si>
   <si>
     <t>土龙战盔</t>
   </si>
   <si>
+    <t>150000,20</t>
+  </si>
+  <si>
     <t>土龙战镯</t>
   </si>
   <si>
@@ -1093,7 +1099,7 @@
     <t>冰龙战刃</t>
   </si>
   <si>
-    <t>30000,24</t>
+    <t>20000,24</t>
   </si>
   <si>
     <t>冰龙战甲</t>
@@ -1102,12 +1108,15 @@
     <t>冰龙战链</t>
   </si>
   <si>
-    <t>15000,12</t>
+    <t>10000,12</t>
   </si>
   <si>
     <t>冰龙战盔</t>
   </si>
   <si>
+    <t>200000,24</t>
+  </si>
+  <si>
     <t>冰龙战镯</t>
   </si>
   <si>
@@ -1171,7 +1180,7 @@
     <t>炎龙战刃</t>
   </si>
   <si>
-    <t>40000,28</t>
+    <t>30000,28</t>
   </si>
   <si>
     <t>炎龙战甲</t>
@@ -1180,12 +1189,15 @@
     <t>炎龙战链</t>
   </si>
   <si>
-    <t>20000,14</t>
+    <t>15000,14</t>
   </si>
   <si>
     <t>炎龙战盔</t>
   </si>
   <si>
+    <t>300000,28</t>
+  </si>
+  <si>
     <t>炎龙战镯</t>
   </si>
   <si>
@@ -1249,7 +1261,7 @@
     <t>光龙战刃</t>
   </si>
   <si>
-    <t>50000,32</t>
+    <t>40000,32</t>
   </si>
   <si>
     <t>光龙战甲</t>
@@ -1258,12 +1270,15 @@
     <t>光龙战链</t>
   </si>
   <si>
-    <t>25000,16</t>
+    <t>20000,16</t>
   </si>
   <si>
     <t>光龙战盔</t>
   </si>
   <si>
+    <t>400000,32</t>
+  </si>
+  <si>
     <t>光龙战镯</t>
   </si>
   <si>
@@ -1327,7 +1342,7 @@
     <t>暗龙战刃</t>
   </si>
   <si>
-    <t>60000,36</t>
+    <t>50000,36</t>
   </si>
   <si>
     <t>暗龙战甲</t>
@@ -1336,13 +1351,16 @@
     <t>暗龙战链</t>
   </si>
   <si>
-    <t>30000,18</t>
+    <t>25000,18</t>
   </si>
   <si>
     <t>暗龙战盔</t>
   </si>
   <si>
     <t>暗龙战镯</t>
+  </si>
+  <si>
+    <t>500000,36</t>
   </si>
   <si>
     <t>暗龙战戒</t>
@@ -10223,7 +10241,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -10261,7 +10279,7 @@
         <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -10273,7 +10291,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -10311,7 +10329,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -10361,7 +10379,7 @@
         <v>60</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -10411,7 +10429,7 @@
         <v>60</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -10423,7 +10441,7 @@
         <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -10461,7 +10479,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -10511,7 +10529,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -10561,7 +10579,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -10611,7 +10629,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -10623,7 +10641,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -10661,7 +10679,7 @@
         <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -10673,7 +10691,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -10711,7 +10729,7 @@
         <v>60</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -10761,7 +10779,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -10811,7 +10829,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -10823,7 +10841,7 @@
         <v>31</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -10861,7 +10879,7 @@
         <v>60</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -10911,7 +10929,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -10961,7 +10979,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -11011,7 +11029,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -11023,7 +11041,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -11061,7 +11079,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -11073,7 +11091,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -11111,7 +11129,7 @@
         <v>60</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -11161,7 +11179,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -11211,7 +11229,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -11223,7 +11241,7 @@
         <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -11276,7 +11294,7 @@
         <v>70</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -11288,7 +11306,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -11326,7 +11344,7 @@
         <v>70</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -11338,7 +11356,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -11376,7 +11394,7 @@
         <v>70</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -11388,7 +11406,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -11426,7 +11444,7 @@
         <v>70</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -11438,7 +11456,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -11476,7 +11494,7 @@
         <v>70</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -11488,7 +11506,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -11526,7 +11544,7 @@
         <v>70</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -11538,7 +11556,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -11576,7 +11594,7 @@
         <v>70</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -11588,7 +11606,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -11626,7 +11644,7 @@
         <v>70</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -11638,7 +11656,7 @@
         <v>31</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -11676,7 +11694,7 @@
         <v>70</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -11688,7 +11706,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -11726,7 +11744,7 @@
         <v>70</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -11738,7 +11756,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -11776,7 +11794,7 @@
         <v>70</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -11788,7 +11806,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -11826,7 +11844,7 @@
         <v>70</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -11838,7 +11856,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -11876,7 +11894,7 @@
         <v>70</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -11888,7 +11906,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -11926,7 +11944,7 @@
         <v>70</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -11938,7 +11956,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -11976,7 +11994,7 @@
         <v>70</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -11988,7 +12006,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -12026,7 +12044,7 @@
         <v>70</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -12038,7 +12056,7 @@
         <v>31</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -12076,7 +12094,7 @@
         <v>70</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -12088,7 +12106,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -12126,7 +12144,7 @@
         <v>70</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -12138,7 +12156,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -12176,7 +12194,7 @@
         <v>70</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -12188,7 +12206,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -12226,7 +12244,7 @@
         <v>70</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -12238,7 +12256,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -12276,7 +12294,7 @@
         <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -12288,7 +12306,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -12326,7 +12344,7 @@
         <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -12338,7 +12356,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -12376,7 +12394,7 @@
         <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -12388,7 +12406,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -12426,7 +12444,7 @@
         <v>70</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -12438,7 +12456,7 @@
         <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -12767,7 +12785,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -12779,7 +12797,7 @@
         <v>24</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -12816,7 +12834,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -12828,7 +12846,7 @@
         <v>27</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -12865,7 +12883,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -12877,7 +12895,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -12914,7 +12932,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -12926,7 +12944,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -12963,7 +12981,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -12975,7 +12993,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -13012,7 +13030,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -13024,7 +13042,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -13061,7 +13079,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -13073,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -13110,7 +13128,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -13122,7 +13140,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -13159,7 +13177,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -13171,7 +13189,7 @@
         <v>40</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -13208,7 +13226,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -13220,7 +13238,7 @@
         <v>27</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -13257,7 +13275,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -13269,7 +13287,7 @@
         <v>40</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -13306,7 +13324,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -13318,7 +13336,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -13355,7 +13373,7 @@
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -13367,7 +13385,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -13404,7 +13422,7 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -13416,7 +13434,7 @@
         <v>40</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -13453,7 +13471,7 @@
         <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -13465,7 +13483,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -13502,7 +13520,7 @@
         <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -13514,7 +13532,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -13551,7 +13569,7 @@
         <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -13563,7 +13581,7 @@
         <v>49</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -13600,7 +13618,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -13612,7 +13630,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -13649,7 +13667,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -13661,7 +13679,7 @@
         <v>49</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -13698,7 +13716,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -13710,7 +13728,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -13747,7 +13765,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -13759,7 +13777,7 @@
         <v>31</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -13796,7 +13814,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -13808,7 +13826,7 @@
         <v>49</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -13845,7 +13863,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -13857,7 +13875,7 @@
         <v>27</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -13894,7 +13912,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -13906,7 +13924,7 @@
         <v>31</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -13943,7 +13961,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -13955,7 +13973,7 @@
         <v>24</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -13992,7 +14010,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -14004,7 +14022,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -14041,7 +14059,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -14053,7 +14071,7 @@
         <v>24</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -14090,7 +14108,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -14102,7 +14120,7 @@
         <v>31</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -14139,7 +14157,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -14151,7 +14169,7 @@
         <v>31</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -14188,7 +14206,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G36" s="1">
         <v>7</v>
@@ -14200,7 +14218,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -14237,7 +14255,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G37" s="1">
         <v>9</v>
@@ -14249,7 +14267,7 @@
         <v>27</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -14286,7 +14304,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G38" s="1">
         <v>10</v>
@@ -14298,7 +14316,7 @@
         <v>31</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -14335,7 +14353,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -14347,7 +14365,7 @@
         <v>40</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K39" s="1">
         <v>100</v>
@@ -14384,7 +14402,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -14396,7 +14414,7 @@
         <v>27</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K40" s="1">
         <v>100</v>
@@ -14433,7 +14451,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -14445,7 +14463,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K41" s="1">
         <v>100</v>
@@ -14482,7 +14500,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -14494,7 +14512,7 @@
         <v>31</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K42" s="1">
         <v>100</v>
@@ -14531,7 +14549,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -14543,7 +14561,7 @@
         <v>31</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K43" s="1">
         <v>100</v>
@@ -14580,7 +14598,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -14592,7 +14610,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -14629,7 +14647,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G45" s="1">
         <v>9</v>
@@ -14641,7 +14659,7 @@
         <v>27</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K45" s="1">
         <v>100</v>
@@ -14678,7 +14696,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G46" s="1">
         <v>10</v>
@@ -14690,7 +14708,7 @@
         <v>31</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K46" s="1">
         <v>100</v>
@@ -14727,7 +14745,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G47" s="1">
         <v>1</v>
@@ -14739,7 +14757,7 @@
         <v>49</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K47" s="1">
         <v>100</v>
@@ -14776,7 +14794,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G48" s="1">
         <v>2</v>
@@ -14788,7 +14806,7 @@
         <v>27</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K48" s="1">
         <v>100</v>
@@ -14825,7 +14843,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G49" s="1">
         <v>3</v>
@@ -14837,7 +14855,7 @@
         <v>49</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -14874,7 +14892,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -14886,7 +14904,7 @@
         <v>31</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -14923,7 +14941,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G51" s="1">
         <v>5</v>
@@ -14935,7 +14953,7 @@
         <v>31</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -14972,7 +14990,7 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G52" s="1">
         <v>7</v>
@@ -14984,7 +15002,7 @@
         <v>49</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K52" s="1">
         <v>100</v>
@@ -15021,7 +15039,7 @@
         <v>90</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G53" s="1">
         <v>9</v>
@@ -15033,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -15070,7 +15088,7 @@
         <v>90</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -15082,7 +15100,7 @@
         <v>31</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -15136,7 +15154,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -15148,7 +15166,7 @@
         <v>24</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K56" s="1">
         <v>100</v>
@@ -15185,7 +15203,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -15197,7 +15215,7 @@
         <v>27</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K57" s="1">
         <v>100</v>
@@ -15234,7 +15252,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G58" s="1">
         <v>3</v>
@@ -15246,7 +15264,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -15283,7 +15301,7 @@
         <v>100</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G59" s="1">
         <v>4</v>
@@ -15295,7 +15313,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -15332,7 +15350,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -15344,7 +15362,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -15381,7 +15399,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -15393,7 +15411,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K61" s="1">
         <v>100</v>
@@ -15430,7 +15448,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -15442,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K62" s="1">
         <v>100</v>
@@ -15479,7 +15497,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -15491,7 +15509,7 @@
         <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -15528,7 +15546,7 @@
         <v>100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -15540,7 +15558,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -15577,7 +15595,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -15589,7 +15607,7 @@
         <v>27</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K65" s="1">
         <v>100</v>
@@ -15626,7 +15644,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -15638,7 +15656,7 @@
         <v>40</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -15675,7 +15693,7 @@
         <v>100</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15687,7 +15705,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -15724,7 +15742,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15736,7 +15754,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -15773,7 +15791,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15785,7 +15803,7 @@
         <v>40</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K69" s="1">
         <v>100</v>
@@ -15822,7 +15840,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15834,7 +15852,7 @@
         <v>27</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -15871,7 +15889,7 @@
         <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15883,7 +15901,7 @@
         <v>31</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -15920,7 +15938,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -15932,7 +15950,7 @@
         <v>49</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K72" s="1">
         <v>100</v>
@@ -15969,7 +15987,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -15981,7 +15999,7 @@
         <v>27</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K73" s="1">
         <v>100</v>
@@ -16018,7 +16036,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -16030,7 +16048,7 @@
         <v>49</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K74" s="1">
         <v>100</v>
@@ -16067,7 +16085,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -16079,7 +16097,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -16116,7 +16134,7 @@
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -16128,7 +16146,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -16165,7 +16183,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -16177,7 +16195,7 @@
         <v>49</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K77" s="1">
         <v>100</v>
@@ -16214,7 +16232,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -16226,7 +16244,7 @@
         <v>27</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K78" s="1">
         <v>100</v>
@@ -16263,7 +16281,7 @@
         <v>100</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -16275,7 +16293,7 @@
         <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -16327,7 +16345,7 @@
         <v>110</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -16339,7 +16357,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -16375,7 +16393,7 @@
         <v>110</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -16387,7 +16405,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -16423,7 +16441,7 @@
         <v>110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -16435,7 +16453,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -16471,7 +16489,7 @@
         <v>110</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -16483,7 +16501,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -16519,7 +16537,7 @@
         <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -16531,7 +16549,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -16567,7 +16585,7 @@
         <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -16579,7 +16597,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -16615,7 +16633,7 @@
         <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -16627,7 +16645,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -16663,7 +16681,7 @@
         <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16675,7 +16693,7 @@
         <v>31</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -16711,7 +16729,7 @@
         <v>110</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16723,7 +16741,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -16759,7 +16777,7 @@
         <v>110</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16771,7 +16789,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -16807,7 +16825,7 @@
         <v>110</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16819,7 +16837,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -16855,7 +16873,7 @@
         <v>110</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -16867,7 +16885,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -16903,7 +16921,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -16915,7 +16933,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -16951,7 +16969,7 @@
         <v>110</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -16963,7 +16981,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -16999,7 +17017,7 @@
         <v>110</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -17011,7 +17029,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -17047,7 +17065,7 @@
         <v>110</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -17059,7 +17077,7 @@
         <v>31</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -17095,7 +17113,7 @@
         <v>110</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -17107,7 +17125,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -17143,7 +17161,7 @@
         <v>110</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -17155,7 +17173,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -17191,7 +17209,7 @@
         <v>110</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -17203,7 +17221,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -17239,7 +17257,7 @@
         <v>110</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -17251,7 +17269,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -17287,7 +17305,7 @@
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -17299,7 +17317,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -17335,7 +17353,7 @@
         <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -17347,7 +17365,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -17383,7 +17401,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -17395,7 +17413,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -17431,7 +17449,7 @@
         <v>110</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -17443,7 +17461,7 @@
         <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -17766,7 +17784,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17775,10 +17793,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17813,7 +17831,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17822,10 +17840,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -17897,7 +17915,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17915,7 +17933,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -17946,16 +17964,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -17992,10 +18010,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -18065,7 +18083,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -18077,7 +18095,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -18089,7 +18107,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -18111,7 +18129,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -18120,10 +18138,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -18135,7 +18153,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -18157,7 +18175,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -18169,7 +18187,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -18201,7 +18219,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -18213,7 +18231,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -18225,7 +18243,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -18247,7 +18265,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -18256,10 +18274,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -18271,7 +18289,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -18293,7 +18311,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -18305,7 +18323,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -18337,7 +18355,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18346,10 +18364,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18361,7 +18379,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18383,7 +18401,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18395,7 +18413,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18427,7 +18445,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18439,7 +18457,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18489,7 +18507,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18498,10 +18516,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -18513,7 +18531,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18535,7 +18553,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18547,7 +18565,7 @@
         <v>27</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="K17" s="2">
         <v>11</v>
@@ -18579,7 +18597,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18591,7 +18609,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="K18" s="2">
         <v>12</v>
@@ -18623,7 +18641,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18632,10 +18650,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18647,7 +18665,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18669,7 +18687,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18681,7 +18699,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18713,7 +18731,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18725,7 +18743,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18757,7 +18775,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18766,10 +18784,10 @@
         <v>36</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18781,7 +18799,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18803,7 +18821,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18815,7 +18833,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18847,7 +18865,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -18859,7 +18877,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -18896,10 +18914,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -18911,7 +18929,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -18927,7 +18945,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -18938,10 +18956,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -18953,7 +18971,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -18978,10 +18996,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -18993,7 +19011,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -19018,10 +19036,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -19033,7 +19051,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -19049,7 +19067,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -19060,10 +19078,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -19075,7 +19093,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -19100,10 +19118,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -19115,7 +19133,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -19140,10 +19158,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -19155,7 +19173,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -19171,7 +19189,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -19182,10 +19200,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -19197,7 +19215,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19222,10 +19240,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -19237,7 +19255,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -19262,10 +19280,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -19277,7 +19295,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -19293,7 +19311,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -19304,10 +19322,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -19319,7 +19337,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -19344,10 +19362,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -19359,7 +19377,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -19384,10 +19402,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -19399,7 +19417,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19415,7 +19433,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19426,10 +19444,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -19441,7 +19459,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19466,10 +19484,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -19481,7 +19499,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19506,10 +19524,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -19521,7 +19539,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19537,7 +19555,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19548,10 +19566,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -19563,7 +19581,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19588,10 +19606,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -19603,7 +19621,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19628,10 +19646,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -19643,7 +19661,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19659,7 +19677,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19670,10 +19688,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -19685,7 +19703,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19710,10 +19728,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -19725,7 +19743,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19750,10 +19768,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -19765,7 +19783,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19781,7 +19799,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19792,10 +19810,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -19807,7 +19825,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19832,10 +19850,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -19847,7 +19865,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="435">
   <si>
     <t>_id</t>
   </si>
@@ -1180,7 +1180,7 @@
     <t>炎龙战刃</t>
   </si>
   <si>
-    <t>30000,28</t>
+    <t>25000,28</t>
   </si>
   <si>
     <t>炎龙战甲</t>
@@ -1189,13 +1189,13 @@
     <t>炎龙战链</t>
   </si>
   <si>
-    <t>15000,14</t>
+    <t>12500,14</t>
   </si>
   <si>
     <t>炎龙战盔</t>
   </si>
   <si>
-    <t>300000,28</t>
+    <t>250000,28</t>
   </si>
   <si>
     <t>炎龙战镯</t>
@@ -1261,7 +1261,7 @@
     <t>光龙战刃</t>
   </si>
   <si>
-    <t>40000,32</t>
+    <t>30000,32</t>
   </si>
   <si>
     <t>光龙战甲</t>
@@ -1270,15 +1270,12 @@
     <t>光龙战链</t>
   </si>
   <si>
-    <t>20000,16</t>
+    <t>15000,16</t>
   </si>
   <si>
     <t>光龙战盔</t>
   </si>
   <si>
-    <t>400000,32</t>
-  </si>
-  <si>
     <t>光龙战镯</t>
   </si>
   <si>
@@ -1342,7 +1339,7 @@
     <t>暗龙战刃</t>
   </si>
   <si>
-    <t>50000,36</t>
+    <t>40000,36</t>
   </si>
   <si>
     <t>暗龙战甲</t>
@@ -1351,7 +1348,7 @@
     <t>暗龙战链</t>
   </si>
   <si>
-    <t>25000,18</t>
+    <t>20000,18</t>
   </si>
   <si>
     <t>暗龙战盔</t>
@@ -1360,7 +1357,7 @@
     <t>暗龙战镯</t>
   </si>
   <si>
-    <t>500000,36</t>
+    <t>400000,36</t>
   </si>
   <si>
     <t>暗龙战戒</t>
@@ -15369,7 +15366,7 @@
         <v>31</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K59" s="1">
         <v>100</v>
@@ -15407,7 +15404,7 @@
         <v>51</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -15419,7 +15416,7 @@
         <v>31</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K60" s="1">
         <v>100</v>
@@ -15457,7 +15454,7 @@
         <v>51</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -15507,7 +15504,7 @@
         <v>51</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -15557,7 +15554,7 @@
         <v>51</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -15569,7 +15566,7 @@
         <v>31</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -15607,7 +15604,7 @@
         <v>51</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -15657,7 +15654,7 @@
         <v>51</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -15707,7 +15704,7 @@
         <v>51</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -15757,7 +15754,7 @@
         <v>51</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15769,7 +15766,7 @@
         <v>31</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K67" s="1">
         <v>100</v>
@@ -15807,7 +15804,7 @@
         <v>51</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15819,7 +15816,7 @@
         <v>31</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K68" s="1">
         <v>100</v>
@@ -15857,7 +15854,7 @@
         <v>51</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15907,7 +15904,7 @@
         <v>51</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15957,7 +15954,7 @@
         <v>51</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15969,7 +15966,7 @@
         <v>31</v>
       </c>
       <c r="J71" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K71" s="1">
         <v>100</v>
@@ -16007,7 +16004,7 @@
         <v>51</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -16057,7 +16054,7 @@
         <v>51</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -16107,7 +16104,7 @@
         <v>51</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -16157,7 +16154,7 @@
         <v>51</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -16169,7 +16166,7 @@
         <v>31</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -16207,7 +16204,7 @@
         <v>51</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -16219,7 +16216,7 @@
         <v>31</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K76" s="1">
         <v>100</v>
@@ -16257,7 +16254,7 @@
         <v>51</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -16307,7 +16304,7 @@
         <v>51</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -16357,7 +16354,7 @@
         <v>51</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -16369,7 +16366,7 @@
         <v>31</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -16422,7 +16419,7 @@
         <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -16434,7 +16431,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -16472,7 +16469,7 @@
         <v>56</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -16484,7 +16481,7 @@
         <v>27</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -16522,7 +16519,7 @@
         <v>56</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -16534,7 +16531,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K83" s="1">
         <v>100</v>
@@ -16572,7 +16569,7 @@
         <v>56</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -16584,7 +16581,7 @@
         <v>31</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -16622,7 +16619,7 @@
         <v>56</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -16634,7 +16631,7 @@
         <v>31</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -16672,7 +16669,7 @@
         <v>56</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -16684,7 +16681,7 @@
         <v>24</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K86" s="1">
         <v>100</v>
@@ -16722,7 +16719,7 @@
         <v>56</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -16734,7 +16731,7 @@
         <v>27</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K87" s="1">
         <v>100</v>
@@ -16772,7 +16769,7 @@
         <v>56</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16784,7 +16781,7 @@
         <v>31</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="K88" s="1">
         <v>100</v>
@@ -16822,7 +16819,7 @@
         <v>56</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16834,7 +16831,7 @@
         <v>40</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K89" s="1">
         <v>100</v>
@@ -16872,7 +16869,7 @@
         <v>56</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16884,7 +16881,7 @@
         <v>27</v>
       </c>
       <c r="J90" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K90" s="1">
         <v>100</v>
@@ -16922,7 +16919,7 @@
         <v>56</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16934,7 +16931,7 @@
         <v>40</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K91" s="1">
         <v>100</v>
@@ -16972,7 +16969,7 @@
         <v>56</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -16984,7 +16981,7 @@
         <v>31</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K92" s="1">
         <v>100</v>
@@ -17022,7 +17019,7 @@
         <v>56</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -17034,7 +17031,7 @@
         <v>31</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K93" s="1">
         <v>100</v>
@@ -17072,7 +17069,7 @@
         <v>56</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -17084,7 +17081,7 @@
         <v>40</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K94" s="1">
         <v>100</v>
@@ -17122,7 +17119,7 @@
         <v>56</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -17134,7 +17131,7 @@
         <v>27</v>
       </c>
       <c r="J95" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K95" s="1">
         <v>100</v>
@@ -17172,7 +17169,7 @@
         <v>56</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -17184,7 +17181,7 @@
         <v>31</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="K96" s="1">
         <v>100</v>
@@ -17222,7 +17219,7 @@
         <v>56</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -17234,7 +17231,7 @@
         <v>49</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K97" s="1">
         <v>100</v>
@@ -17272,7 +17269,7 @@
         <v>56</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -17284,7 +17281,7 @@
         <v>27</v>
       </c>
       <c r="J98" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K98" s="1">
         <v>100</v>
@@ -17322,7 +17319,7 @@
         <v>56</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -17334,7 +17331,7 @@
         <v>49</v>
       </c>
       <c r="J99" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K99" s="1">
         <v>100</v>
@@ -17372,7 +17369,7 @@
         <v>56</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -17384,7 +17381,7 @@
         <v>31</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K100" s="1">
         <v>100</v>
@@ -17422,7 +17419,7 @@
         <v>56</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -17434,7 +17431,7 @@
         <v>31</v>
       </c>
       <c r="J101" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K101" s="1">
         <v>100</v>
@@ -17472,7 +17469,7 @@
         <v>56</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -17484,7 +17481,7 @@
         <v>49</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K102" s="1">
         <v>100</v>
@@ -17522,7 +17519,7 @@
         <v>56</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -17534,7 +17531,7 @@
         <v>27</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K103" s="1">
         <v>100</v>
@@ -17572,7 +17569,7 @@
         <v>56</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -17584,7 +17581,7 @@
         <v>31</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -17909,19 +17906,19 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="17" t="s">
+      <c r="J6" s="17" t="s">
         <v>355</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>356</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17956,19 +17953,19 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="J7" s="17" t="s">
         <v>358</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>359</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -18040,7 +18037,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18058,7 +18055,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18089,16 +18086,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -18135,10 +18132,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -18208,7 +18205,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -18220,7 +18217,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -18232,7 +18229,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -18254,7 +18251,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -18263,10 +18260,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>369</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>370</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -18278,7 +18275,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -18300,7 +18297,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -18312,7 +18309,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -18344,7 +18341,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -18356,7 +18353,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -18368,7 +18365,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -18390,19 +18387,19 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J10" s="17" t="s">
         <v>376</v>
-      </c>
-      <c r="G10" s="1">
-        <v>3</v>
-      </c>
-      <c r="H10" s="1">
-        <v>3</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>377</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -18414,7 +18411,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -18436,7 +18433,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -18448,7 +18445,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -18480,19 +18477,19 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>380</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>381</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18504,7 +18501,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18526,7 +18523,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18538,7 +18535,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18570,7 +18567,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18582,7 +18579,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18632,7 +18629,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
@@ -18641,10 +18638,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K16" s="2">
         <v>10</v>
@@ -18656,7 +18653,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -18678,7 +18675,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
@@ -18690,7 +18687,7 @@
         <v>27</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K17" s="2">
         <v>11</v>
@@ -18722,7 +18719,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G18" s="1">
         <v>7</v>
@@ -18734,7 +18731,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K18" s="2">
         <v>12</v>
@@ -18766,19 +18763,19 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J19" s="17" t="s">
         <v>392</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="K19" s="2">
         <v>13</v>
@@ -18790,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -18812,7 +18809,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G20" s="1">
         <v>5</v>
@@ -18824,7 +18821,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
@@ -18856,7 +18853,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
@@ -18868,7 +18865,7 @@
         <v>27</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K21" s="2">
         <v>15</v>
@@ -18900,7 +18897,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G22" s="1">
         <v>7</v>
@@ -18909,10 +18906,10 @@
         <v>36</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K22" s="2">
         <v>16</v>
@@ -18924,7 +18921,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -18946,7 +18943,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -18958,7 +18955,7 @@
         <v>31</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K23" s="2">
         <v>17</v>
@@ -18990,7 +18987,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G24" s="1">
         <v>10</v>
@@ -19002,7 +18999,7 @@
         <v>27</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K24" s="2">
         <v>18</v>
@@ -19039,10 +19036,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C26" s="1">
         <v>201019</v>
@@ -19054,7 +19051,7 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -19070,7 +19067,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="O26" s="1">
         <v>0</v>
@@ -19081,10 +19078,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C27" s="1">
         <v>201020</v>
@@ -19096,7 +19093,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G27" s="1">
         <v>3</v>
@@ -19121,10 +19118,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C28" s="1">
         <v>201021</v>
@@ -19136,7 +19133,7 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
@@ -19161,10 +19158,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C31" s="2">
         <v>211019</v>
@@ -19176,7 +19173,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -19192,7 +19189,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -19203,10 +19200,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C32" s="2">
         <v>211020</v>
@@ -19218,7 +19215,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -19243,10 +19240,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C33" s="2">
         <v>211021</v>
@@ -19258,7 +19255,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -19283,10 +19280,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C34" s="2">
         <v>211022</v>
@@ -19298,7 +19295,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -19314,7 +19311,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -19325,10 +19322,10 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C35" s="2">
         <v>211023</v>
@@ -19340,7 +19337,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19365,10 +19362,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2">
         <v>211024</v>
@@ -19380,7 +19377,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -19405,10 +19402,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2">
         <v>211025</v>
@@ -19420,7 +19417,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -19436,7 +19433,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -19447,10 +19444,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2">
         <v>211026</v>
@@ -19462,7 +19459,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -19487,10 +19484,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2">
         <v>211027</v>
@@ -19502,7 +19499,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G39" s="1">
         <v>9</v>
@@ -19527,10 +19524,10 @@
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2">
         <v>211031</v>
@@ -19542,7 +19539,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G42" s="1">
         <v>3</v>
@@ -19558,7 +19555,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19569,10 +19566,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2">
         <v>211032</v>
@@ -19584,7 +19581,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G43" s="1">
         <v>7</v>
@@ -19609,10 +19606,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2">
         <v>211033</v>
@@ -19624,7 +19621,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G44" s="1">
         <v>9</v>
@@ -19649,10 +19646,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2">
         <v>211034</v>
@@ -19664,7 +19661,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G45" s="2">
         <v>2</v>
@@ -19680,7 +19677,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19691,10 +19688,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2">
         <v>211035</v>
@@ -19706,7 +19703,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -19731,10 +19728,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C47" s="2">
         <v>211036</v>
@@ -19746,7 +19743,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -19771,10 +19768,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2">
         <v>211037</v>
@@ -19786,7 +19783,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -19802,7 +19799,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="O48" s="1">
         <v>0</v>
@@ -19813,10 +19810,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C49" s="2">
         <v>211038</v>
@@ -19828,7 +19825,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G49" s="1">
         <v>5</v>
@@ -19853,10 +19850,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2">
         <v>211039</v>
@@ -19868,7 +19865,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G50" s="1">
         <v>7</v>
@@ -19893,10 +19890,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A51" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2">
         <v>211040</v>
@@ -19908,7 +19905,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -19924,7 +19921,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
@@ -19935,10 +19932,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A52" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2">
         <v>211041</v>
@@ -19950,7 +19947,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G52" s="1">
         <v>5</v>
@@ -19975,10 +19972,10 @@
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C53" s="2">
         <v>211042</v>
@@ -19990,7 +19987,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G53" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="440">
   <si>
     <t>_id</t>
   </si>
@@ -1567,28 +1567,43 @@
     <t>暴击铁履</t>
   </si>
   <si>
+    <t>致命之剑</t>
+  </si>
+  <si>
+    <t>36000,18</t>
+  </si>
+  <si>
+    <t>攻击概率降低50%，概率2倍，5倍，10倍，100倍</t>
+  </si>
+  <si>
+    <t>致命之镯</t>
+  </si>
+  <si>
+    <t>360000,18</t>
+  </si>
+  <si>
+    <t>致命之戒</t>
+  </si>
+  <si>
     <t>天命之剑</t>
   </si>
   <si>
-    <t>攻击概率降低50%，概率2倍，5倍，10倍，100倍</t>
+    <t>50000,20</t>
+  </si>
+  <si>
+    <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
   </si>
   <si>
     <t>天命之链</t>
   </si>
   <si>
+    <t>500000,20</t>
+  </si>
+  <si>
     <t>天命之戒</t>
   </si>
   <si>
-    <t>致命之剑</t>
-  </si>
-  <si>
-    <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
-  </si>
-  <si>
-    <t>致命之镯</t>
-  </si>
-  <si>
-    <t>致命之戒</t>
+    <t>50000,29</t>
   </si>
   <si>
     <t>背刺之匕</t>
@@ -18004,7 +18019,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -18601,26 +18616,54 @@
     <row r="15" customFormat="1" customHeight="1" spans="1:16">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="C15" s="1">
+        <v>201010</v>
+      </c>
+      <c r="D15" s="2">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
+        <v>40</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="K15" s="2">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2">
+        <v>7</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1">
-        <v>201010</v>
+        <v>201011</v>
       </c>
       <c r="D16" s="2">
         <v>10</v>
@@ -18629,22 +18672,22 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G16" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="1">
-        <v>4</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>368</v>
+        <v>3</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>386</v>
       </c>
       <c r="K16" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L16" s="2">
         <v>7</v>
@@ -18652,9 +18695,7 @@
       <c r="M16" s="2">
         <v>1</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>387</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="1">
         <v>0</v>
       </c>
@@ -18666,7 +18707,7 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="1">
-        <v>201011</v>
+        <v>201012</v>
       </c>
       <c r="D17" s="2">
         <v>10</v>
@@ -18675,22 +18716,22 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G17" s="1">
-        <v>3</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>386</v>
+        <v>31</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>390</v>
       </c>
       <c r="K17" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L17" s="2">
         <v>7</v>
@@ -18706,35 +18747,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="1" customHeight="1" spans="1:16">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="1">
-        <v>201012</v>
+        <v>201013</v>
       </c>
       <c r="D18" s="2">
         <v>10</v>
       </c>
       <c r="E18" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="G18" s="1">
-        <v>7</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>36</v>
+        <v>391</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>31</v>
+        <v>368</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K18" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L18" s="2">
         <v>7</v>
@@ -18742,7 +18783,9 @@
       <c r="M18" s="2">
         <v>1</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" s="2" t="s">
+        <v>393</v>
+      </c>
       <c r="O18" s="1">
         <v>0</v>
       </c>
@@ -18754,7 +18797,7 @@
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1">
-        <v>201013</v>
+        <v>201014</v>
       </c>
       <c r="D19" s="2">
         <v>10</v>
@@ -18763,22 +18806,22 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1</v>
+        <v>394</v>
+      </c>
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>368</v>
+        <v>31</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K19" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2">
         <v>7</v>
@@ -18786,9 +18829,7 @@
       <c r="M19" s="2">
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="s">
-        <v>393</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="1">
         <v>0</v>
       </c>
@@ -18800,7 +18841,7 @@
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="1">
-        <v>201014</v>
+        <v>201015</v>
       </c>
       <c r="D20" s="2">
         <v>10</v>
@@ -18809,22 +18850,22 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G20" s="1">
-        <v>5</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>34</v>
+        <v>9</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="K20" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L20" s="2">
         <v>7</v>
@@ -18844,31 +18885,31 @@
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="1">
-        <v>201015</v>
+        <v>201016</v>
       </c>
       <c r="D21" s="2">
         <v>10</v>
       </c>
       <c r="E21" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G21" s="1">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>27</v>
+        <v>368</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K21" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L21" s="2">
         <v>7</v>
@@ -18876,7 +18917,9 @@
       <c r="M21" s="2">
         <v>1</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" s="2" t="s">
+        <v>399</v>
+      </c>
       <c r="O21" s="1">
         <v>0</v>
       </c>
@@ -18888,7 +18931,7 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="1">
-        <v>201016</v>
+        <v>201017</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -18897,22 +18940,22 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="G22" s="1">
-        <v>7</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>36</v>
+        <v>400</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>368</v>
+        <v>31</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K22" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" s="2">
         <v>7</v>
@@ -18920,9 +18963,7 @@
       <c r="M22" s="2">
         <v>1</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>399</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="1">
         <v>0</v>
       </c>
@@ -18934,7 +18975,7 @@
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="1">
-        <v>201017</v>
+        <v>201018</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -18943,22 +18984,22 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G23" s="2">
-        <v>2</v>
-      </c>
-      <c r="H23" s="2">
-        <v>2</v>
+        <v>402</v>
+      </c>
+      <c r="G23" s="1">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1">
+        <v>10</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K23" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="2">
         <v>7</v>
@@ -18976,33 +19017,32 @@
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
       <c r="C24" s="1">
-        <v>201018</v>
+        <v>201019</v>
       </c>
       <c r="D24" s="2">
         <v>10</v>
       </c>
       <c r="E24" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G24" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>27</v>
+        <v>368</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="K24" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L24" s="2">
         <v>7</v>
@@ -19010,7 +19050,9 @@
       <c r="M24" s="2">
         <v>1</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" s="2" t="s">
+        <v>405</v>
+      </c>
       <c r="O24" s="1">
         <v>0</v>
       </c>
@@ -19020,55 +19062,83 @@
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
+      <c r="C25" s="1">
+        <v>201020</v>
+      </c>
+      <c r="D25" s="2">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2">
+        <v>70</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="K25" s="2">
+        <v>20</v>
+      </c>
+      <c r="L25" s="2">
+        <v>7</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1</v>
+      </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A26" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>359</v>
-      </c>
+      <c r="A26" s="2"/>
       <c r="C26" s="1">
-        <v>201019</v>
+        <v>201021</v>
       </c>
       <c r="D26" s="2">
         <v>10</v>
       </c>
       <c r="E26" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>404</v>
+      </c>
       <c r="K26" s="2">
-        <v>2</v>
-      </c>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2" t="s">
-        <v>404</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L26" s="2">
+        <v>7</v>
+      </c>
+      <c r="M26" s="2">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="1">
         <v>0</v>
       </c>
@@ -19077,38 +19147,44 @@
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A27" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>359</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="1">
-        <v>201020</v>
+        <v>201022</v>
       </c>
       <c r="D27" s="2">
         <v>10</v>
       </c>
       <c r="E27" s="2">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="1">
-        <v>3</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>410</v>
+      </c>
       <c r="K27" s="2">
-        <v>2</v>
-      </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="L27" s="2">
+        <v>7</v>
+      </c>
+      <c r="M27" s="2">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>411</v>
+      </c>
       <c r="O27" s="1">
         <v>0</v>
       </c>
@@ -19117,42 +19193,132 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A28" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>359</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="1">
-        <v>201021</v>
+        <v>201023</v>
       </c>
       <c r="D28" s="2">
         <v>10</v>
       </c>
       <c r="E28" s="2">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="G28" s="1">
+        <v>3</v>
+      </c>
+      <c r="H28" s="1">
+        <v>3</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="K28" s="2">
+        <v>23</v>
+      </c>
+      <c r="L28" s="2">
         <v>7</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2">
-        <v>2</v>
-      </c>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+      <c r="M28" s="2">
+        <v>1</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="1">
         <v>0</v>
       </c>
       <c r="P28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="1">
+        <v>201024</v>
+      </c>
+      <c r="D29" s="2">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2">
+        <v>80</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="G29" s="1">
+        <v>7</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="K29" s="2">
+        <v>24</v>
+      </c>
+      <c r="L29" s="2">
+        <v>7</v>
+      </c>
+      <c r="M29" s="2">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A30" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="2">
+        <v>211022</v>
+      </c>
+      <c r="D30" s="2">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2">
+        <v>9</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
         <v>0</v>
       </c>
     </row>
@@ -19164,7 +19330,7 @@
         <v>359</v>
       </c>
       <c r="C31" s="2">
-        <v>211019</v>
+        <v>211023</v>
       </c>
       <c r="D31" s="2">
         <v>10</v>
@@ -19173,24 +19339,22 @@
         <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H31" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="2" t="s">
-        <v>408</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="1">
         <v>0</v>
       </c>
@@ -19206,7 +19370,7 @@
         <v>359</v>
       </c>
       <c r="C32" s="2">
-        <v>211020</v>
+        <v>211024</v>
       </c>
       <c r="D32" s="2">
         <v>10</v>
@@ -19215,18 +19379,18 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="G32" s="1">
-        <v>5</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>10</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -19246,7 +19410,7 @@
         <v>359</v>
       </c>
       <c r="C33" s="2">
-        <v>211021</v>
+        <v>211025</v>
       </c>
       <c r="D33" s="2">
         <v>10</v>
@@ -19255,22 +19419,24 @@
         <v>10</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G33" s="1">
-        <v>7</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>36</v>
+        <v>420</v>
+      </c>
+      <c r="G33" s="2">
+        <v>2</v>
+      </c>
+      <c r="H33" s="2">
+        <v>2</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
+      <c r="N33" s="2" t="s">
+        <v>421</v>
+      </c>
       <c r="O33" s="1">
         <v>0</v>
       </c>
@@ -19286,7 +19452,7 @@
         <v>359</v>
       </c>
       <c r="C34" s="2">
-        <v>211022</v>
+        <v>211026</v>
       </c>
       <c r="D34" s="2">
         <v>10</v>
@@ -19295,24 +19461,22 @@
         <v>10</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="2" t="s">
-        <v>412</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="1">
         <v>0</v>
       </c>
@@ -19328,7 +19492,7 @@
         <v>359</v>
       </c>
       <c r="C35" s="2">
-        <v>211023</v>
+        <v>211027</v>
       </c>
       <c r="D35" s="2">
         <v>10</v>
@@ -19337,7 +19501,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19348,7 +19512,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -19360,89 +19524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A36" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C36" s="2">
-        <v>211024</v>
-      </c>
-      <c r="D36" s="2">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2">
-        <v>10</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="G36" s="1">
-        <v>10</v>
-      </c>
-      <c r="H36" s="1">
-        <v>10</v>
-      </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2">
-        <v>9</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A37" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C37" s="2">
-        <v>211025</v>
-      </c>
-      <c r="D37" s="2">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2">
-        <v>10</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="G37" s="2">
-        <v>2</v>
-      </c>
-      <c r="H37" s="2">
-        <v>2</v>
-      </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2">
-        <v>6</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:16">
+    <row r="38" customFormat="1" customHeight="1" spans="1:16">
       <c r="A38" s="2" t="s">
         <v>359</v>
       </c>
@@ -19450,7 +19532,7 @@
         <v>359</v>
       </c>
       <c r="C38" s="2">
-        <v>211026</v>
+        <v>211031</v>
       </c>
       <c r="D38" s="2">
         <v>10</v>
@@ -19459,22 +19541,24 @@
         <v>10</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="G38" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" s="1">
-        <v>4</v>
-      </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2">
-        <v>6</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8">
+        <v>13</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8" t="s">
+        <v>425</v>
+      </c>
       <c r="O38" s="1">
         <v>0</v>
       </c>
@@ -19490,7 +19574,7 @@
         <v>359</v>
       </c>
       <c r="C39" s="2">
-        <v>211027</v>
+        <v>211032</v>
       </c>
       <c r="D39" s="2">
         <v>10</v>
@@ -19499,18 +19583,18 @@
         <v>10</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="G39" s="1">
-        <v>9</v>
-      </c>
-      <c r="H39" s="1">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="2">
-        <v>6</v>
+      <c r="K39" s="8">
+        <v>13</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -19522,7 +19606,89 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:16">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A40" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C40" s="2">
+        <v>211033</v>
+      </c>
+      <c r="D40" s="2">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2">
+        <v>10</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G40" s="1">
+        <v>9</v>
+      </c>
+      <c r="H40" s="1">
+        <v>9</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="8">
+        <v>13</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A41" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C41" s="2">
+        <v>211034</v>
+      </c>
+      <c r="D41" s="2">
+        <v>10</v>
+      </c>
+      <c r="E41" s="2">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2</v>
+      </c>
+      <c r="H41" s="2">
+        <v>2</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2">
+        <v>14</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
         <v>359</v>
       </c>
@@ -19530,7 +19696,7 @@
         <v>359</v>
       </c>
       <c r="C42" s="2">
-        <v>211031</v>
+        <v>211035</v>
       </c>
       <c r="D42" s="2">
         <v>10</v>
@@ -19539,24 +19705,22 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="G42" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" s="1">
-        <v>3</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8">
-        <v>13</v>
-      </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8" t="s">
-        <v>420</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2">
+        <v>14</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
       <c r="O42" s="1">
         <v>0</v>
       </c>
@@ -19572,7 +19736,7 @@
         <v>359</v>
       </c>
       <c r="C43" s="2">
-        <v>211032</v>
+        <v>211036</v>
       </c>
       <c r="D43" s="2">
         <v>10</v>
@@ -19581,18 +19745,18 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="G43" s="1">
-        <v>7</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>36</v>
+        <v>10</v>
+      </c>
+      <c r="H43" s="1">
+        <v>10</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="8">
-        <v>13</v>
+      <c r="K43" s="2">
+        <v>14</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -19612,7 +19776,7 @@
         <v>359</v>
       </c>
       <c r="C44" s="2">
-        <v>211033</v>
+        <v>211037</v>
       </c>
       <c r="D44" s="2">
         <v>10</v>
@@ -19621,22 +19785,24 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="G44" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="8">
-        <v>13</v>
+      <c r="K44" s="2">
+        <v>10</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
+      <c r="N44" s="2" t="s">
+        <v>433</v>
+      </c>
       <c r="O44" s="1">
         <v>0</v>
       </c>
@@ -19652,7 +19818,7 @@
         <v>359</v>
       </c>
       <c r="C45" s="2">
-        <v>211034</v>
+        <v>211038</v>
       </c>
       <c r="D45" s="2">
         <v>10</v>
@@ -19661,24 +19827,22 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="G45" s="2">
-        <v>2</v>
-      </c>
-      <c r="H45" s="2">
-        <v>2</v>
+        <v>434</v>
+      </c>
+      <c r="G45" s="1">
+        <v>5</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
-      <c r="N45" s="2" t="s">
-        <v>424</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="1">
         <v>0</v>
       </c>
@@ -19694,7 +19858,7 @@
         <v>359</v>
       </c>
       <c r="C46" s="2">
-        <v>211035</v>
+        <v>211039</v>
       </c>
       <c r="D46" s="2">
         <v>10</v>
@@ -19703,18 +19867,18 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="G46" s="1">
-        <v>4</v>
-      </c>
-      <c r="H46" s="1">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -19734,7 +19898,7 @@
         <v>359</v>
       </c>
       <c r="C47" s="2">
-        <v>211036</v>
+        <v>211040</v>
       </c>
       <c r="D47" s="2">
         <v>10</v>
@@ -19743,22 +19907,24 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="G47" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H47" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
+      <c r="N47" s="2" t="s">
+        <v>437</v>
+      </c>
       <c r="O47" s="1">
         <v>0</v>
       </c>
@@ -19774,7 +19940,7 @@
         <v>359</v>
       </c>
       <c r="C48" s="2">
-        <v>211037</v>
+        <v>211041</v>
       </c>
       <c r="D48" s="2">
         <v>10</v>
@@ -19783,24 +19949,22 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
-      <c r="N48" s="2" t="s">
-        <v>428</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="1">
         <v>0</v>
       </c>
@@ -19816,7 +19980,7 @@
         <v>359</v>
       </c>
       <c r="C49" s="2">
-        <v>211038</v>
+        <v>211042</v>
       </c>
       <c r="D49" s="2">
         <v>10</v>
@@ -19825,18 +19989,18 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="G49" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -19848,175 +20012,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A50" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C50" s="2">
-        <v>211039</v>
-      </c>
-      <c r="D50" s="2">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2">
-        <v>10</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G50" s="1">
-        <v>7</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2">
-        <v>10</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A51" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C51" s="2">
-        <v>211040</v>
-      </c>
-      <c r="D51" s="2">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2">
-        <v>10</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="G51" s="1">
-        <v>3</v>
-      </c>
-      <c r="H51" s="1">
-        <v>3</v>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2">
-        <v>3</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A52" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C52" s="2">
-        <v>211041</v>
-      </c>
-      <c r="D52" s="2">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2">
-        <v>10</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="G52" s="1">
-        <v>5</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2">
-        <v>3</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A53" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C53" s="2">
-        <v>211042</v>
-      </c>
-      <c r="D53" s="2">
-        <v>10</v>
-      </c>
-      <c r="E53" s="2">
-        <v>10</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G53" s="1">
-        <v>7</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2">
-        <v>3</v>
-      </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="15:16">
-      <c r="O83"/>
-      <c r="P83"/>
-    </row>
-    <row r="84" customHeight="1" spans="15:16">
-      <c r="O84"/>
-      <c r="P84"/>
+    <row r="79" customHeight="1" spans="15:16">
+      <c r="O79"/>
+      <c r="P79"/>
+    </row>
+    <row r="80" customHeight="1" spans="15:16">
+      <c r="O80"/>
+      <c r="P80"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="445">
   <si>
     <t>_id</t>
   </si>
@@ -1603,31 +1603,46 @@
     <t>天命之戒</t>
   </si>
   <si>
-    <t>50000,29</t>
-  </si>
-  <si>
-    <t>背刺之匕</t>
+    <t>福运护面</t>
+  </si>
+  <si>
+    <t>60000,22</t>
   </si>
   <si>
     <t>首次攻击敌人，降低敌人10%最大生命</t>
   </si>
   <si>
-    <t>背刺之带</t>
-  </si>
-  <si>
-    <t>背刺之靴</t>
-  </si>
-  <si>
-    <t>坚韧之甲</t>
+    <t>福运护手</t>
+  </si>
+  <si>
+    <t>6000,22</t>
+  </si>
+  <si>
+    <t>福运护袍</t>
+  </si>
+  <si>
+    <t>寻宝扳指</t>
+  </si>
+  <si>
+    <t>70000,24</t>
   </si>
   <si>
     <t>最高承伤10%</t>
   </si>
   <si>
-    <t>坚韧之盔</t>
-  </si>
-  <si>
-    <t>坚韧之带</t>
+    <t>寻宝项链</t>
+  </si>
+  <si>
+    <t>7000,24</t>
+  </si>
+  <si>
+    <t>寻宝玉带</t>
+  </si>
+  <si>
+    <t>背刺</t>
+  </si>
+  <si>
+    <t>斩杀</t>
   </si>
   <si>
     <t>幸运项链</t>
@@ -18019,7 +18034,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -19261,7 +19276,7 @@
         <v>27</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="K29" s="2">
         <v>24</v>
@@ -19281,37 +19296,41 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A30" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C30" s="2">
-        <v>211022</v>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="1">
+        <v>201025</v>
       </c>
       <c r="D30" s="2">
         <v>10</v>
       </c>
       <c r="E30" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30" s="1">
+        <v>4</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1</v>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
       <c r="K30" s="2">
-        <v>9</v>
-      </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="L30" s="2">
+        <v>7</v>
+      </c>
+      <c r="M30" s="2">
+        <v>1</v>
+      </c>
       <c r="N30" s="2" t="s">
         <v>417</v>
       </c>
@@ -19323,37 +19342,41 @@
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A31" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C31" s="2">
-        <v>211023</v>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="1">
+        <v>201026</v>
       </c>
       <c r="D31" s="2">
         <v>10</v>
       </c>
       <c r="E31" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>418</v>
       </c>
       <c r="G31" s="1">
-        <v>9</v>
-      </c>
-      <c r="H31" s="1">
-        <v>9</v>
-      </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>419</v>
+      </c>
       <c r="K31" s="2">
-        <v>9</v>
-      </c>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="L31" s="2">
+        <v>7</v>
+      </c>
+      <c r="M31" s="2">
+        <v>1</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="1">
         <v>0</v>
@@ -19363,37 +19386,41 @@
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A32" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C32" s="2">
-        <v>211024</v>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="1">
+        <v>201027</v>
       </c>
       <c r="D32" s="2">
         <v>10</v>
       </c>
       <c r="E32" s="2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="G32" s="1">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
       <c r="K32" s="2">
-        <v>9</v>
-      </c>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="L32" s="2">
+        <v>7</v>
+      </c>
+      <c r="M32" s="2">
+        <v>1</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" s="1">
         <v>0</v>
@@ -19403,39 +19430,43 @@
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A33" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C33" s="2">
-        <v>211025</v>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="1">
+        <v>201028</v>
       </c>
       <c r="D33" s="2">
         <v>10</v>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G33" s="2">
-        <v>2</v>
-      </c>
-      <c r="H33" s="2">
-        <v>2</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="G33" s="1">
+        <v>7</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>422</v>
+      </c>
       <c r="K33" s="2">
-        <v>6</v>
-      </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="L33" s="2">
+        <v>7</v>
+      </c>
+      <c r="M33" s="2">
+        <v>1</v>
+      </c>
       <c r="N33" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -19445,37 +19476,41 @@
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A34" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C34" s="2">
-        <v>211026</v>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="1">
+        <v>201029</v>
       </c>
       <c r="D34" s="2">
         <v>10</v>
       </c>
       <c r="E34" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G34" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" s="1">
-        <v>4</v>
-      </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>425</v>
+      </c>
       <c r="K34" s="2">
-        <v>6</v>
-      </c>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="L34" s="2">
+        <v>7</v>
+      </c>
+      <c r="M34" s="2">
+        <v>1</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="1">
         <v>0</v>
@@ -19485,23 +19520,19 @@
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A35" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C35" s="2">
-        <v>211027</v>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="1">
+        <v>201030</v>
       </c>
       <c r="D35" s="2">
         <v>10</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19509,13 +19540,21 @@
       <c r="H35" s="1">
         <v>9</v>
       </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
+      <c r="I35" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>425</v>
+      </c>
       <c r="K35" s="2">
-        <v>6</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="L35" s="2">
+        <v>7</v>
+      </c>
+      <c r="M35" s="2">
+        <v>1</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="1">
         <v>0</v>
@@ -19524,171 +19563,167 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36" customHeight="1" spans="1:16">
+      <c r="A36" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C36" s="1">
+        <v>201031</v>
+      </c>
+      <c r="D36" s="2">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1">
+        <v>110</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:16">
+      <c r="A37" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C37" s="1">
+        <v>201032</v>
+      </c>
+      <c r="D37" s="2">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1">
+        <v>110</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
     <row r="38" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C38" s="2">
-        <v>211031</v>
+      <c r="C38" s="1">
+        <v>201033</v>
       </c>
       <c r="D38" s="2">
         <v>10</v>
       </c>
-      <c r="E38" s="2">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="G38" s="1">
-        <v>3</v>
-      </c>
-      <c r="H38" s="1">
-        <v>3</v>
-      </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8">
-        <v>13</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A39" s="2" t="s">
+      <c r="E38" s="1">
+        <v>110</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A39" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C39" s="2">
-        <v>211032</v>
+      <c r="C39" s="1">
+        <v>201034</v>
       </c>
       <c r="D39" s="2">
         <v>10</v>
       </c>
-      <c r="E39" s="2">
-        <v>10</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="G39" s="1">
-        <v>7</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="8">
-        <v>13</v>
-      </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A40" s="2" t="s">
+      <c r="E39" s="1">
+        <v>120</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A40" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C40" s="2">
-        <v>211033</v>
+      <c r="C40" s="1">
+        <v>201035</v>
       </c>
       <c r="D40" s="2">
         <v>10</v>
       </c>
-      <c r="E40" s="2">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="G40" s="1">
-        <v>9</v>
-      </c>
-      <c r="H40" s="1">
-        <v>9</v>
-      </c>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="8">
-        <v>13</v>
-      </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A41" s="2" t="s">
+      <c r="E40" s="1">
+        <v>120</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A41" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C41" s="2">
-        <v>211034</v>
+      <c r="C41" s="1">
+        <v>201036</v>
       </c>
       <c r="D41" s="2">
         <v>10</v>
       </c>
-      <c r="E41" s="2">
-        <v>10</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="E41" s="1">
+        <v>120</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G41" s="2">
-        <v>2</v>
-      </c>
-      <c r="H41" s="2">
-        <v>2</v>
-      </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2">
-        <v>14</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
         <v>359</v>
       </c>
@@ -19696,7 +19731,7 @@
         <v>359</v>
       </c>
       <c r="C42" s="2">
-        <v>211035</v>
+        <v>211031</v>
       </c>
       <c r="D42" s="2">
         <v>10</v>
@@ -19705,22 +19740,24 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="G42" s="1">
+        <v>3</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3</v>
+      </c>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8">
+        <v>13</v>
+      </c>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="G42" s="1">
-        <v>4</v>
-      </c>
-      <c r="H42" s="1">
-        <v>4</v>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2">
-        <v>14</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
       <c r="O42" s="1">
         <v>0</v>
       </c>
@@ -19736,7 +19773,7 @@
         <v>359</v>
       </c>
       <c r="C43" s="2">
-        <v>211036</v>
+        <v>211032</v>
       </c>
       <c r="D43" s="2">
         <v>10</v>
@@ -19748,15 +19785,15 @@
         <v>431</v>
       </c>
       <c r="G43" s="1">
-        <v>10</v>
-      </c>
-      <c r="H43" s="1">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2">
-        <v>14</v>
+      <c r="K43" s="8">
+        <v>13</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -19776,7 +19813,7 @@
         <v>359</v>
       </c>
       <c r="C44" s="2">
-        <v>211037</v>
+        <v>211033</v>
       </c>
       <c r="D44" s="2">
         <v>10</v>
@@ -19788,21 +19825,19 @@
         <v>432</v>
       </c>
       <c r="G44" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H44" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2">
-        <v>10</v>
+      <c r="K44" s="8">
+        <v>13</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
-      <c r="N44" s="2" t="s">
-        <v>433</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="1">
         <v>0</v>
       </c>
@@ -19818,7 +19853,7 @@
         <v>359</v>
       </c>
       <c r="C45" s="2">
-        <v>211038</v>
+        <v>211034</v>
       </c>
       <c r="D45" s="2">
         <v>10</v>
@@ -19827,22 +19862,24 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G45" s="1">
-        <v>5</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>34</v>
+        <v>433</v>
+      </c>
+      <c r="G45" s="2">
+        <v>2</v>
+      </c>
+      <c r="H45" s="2">
+        <v>2</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
+      <c r="N45" s="2" t="s">
+        <v>434</v>
+      </c>
       <c r="O45" s="1">
         <v>0</v>
       </c>
@@ -19858,7 +19895,7 @@
         <v>359</v>
       </c>
       <c r="C46" s="2">
-        <v>211039</v>
+        <v>211035</v>
       </c>
       <c r="D46" s="2">
         <v>10</v>
@@ -19870,15 +19907,15 @@
         <v>435</v>
       </c>
       <c r="G46" s="1">
-        <v>7</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>36</v>
+        <v>4</v>
+      </c>
+      <c r="H46" s="1">
+        <v>4</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -19898,7 +19935,7 @@
         <v>359</v>
       </c>
       <c r="C47" s="2">
-        <v>211040</v>
+        <v>211036</v>
       </c>
       <c r="D47" s="2">
         <v>10</v>
@@ -19910,21 +19947,19 @@
         <v>436</v>
       </c>
       <c r="G47" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H47" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
-      <c r="N47" s="2" t="s">
-        <v>437</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="1">
         <v>0</v>
       </c>
@@ -19940,7 +19975,7 @@
         <v>359</v>
       </c>
       <c r="C48" s="2">
-        <v>211041</v>
+        <v>211037</v>
       </c>
       <c r="D48" s="2">
         <v>10</v>
@@ -19949,22 +19984,24 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G48" s="1">
-        <v>5</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
+      <c r="N48" s="2" t="s">
+        <v>438</v>
+      </c>
       <c r="O48" s="1">
         <v>0</v>
       </c>
@@ -19980,7 +20017,7 @@
         <v>359</v>
       </c>
       <c r="C49" s="2">
-        <v>211042</v>
+        <v>211038</v>
       </c>
       <c r="D49" s="2">
         <v>10</v>
@@ -19992,15 +20029,15 @@
         <v>439</v>
       </c>
       <c r="G49" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -20012,13 +20049,175 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="15:16">
-      <c r="O79"/>
-      <c r="P79"/>
-    </row>
-    <row r="80" customHeight="1" spans="15:16">
-      <c r="O80"/>
-      <c r="P80"/>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A50" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C50" s="2">
+        <v>211039</v>
+      </c>
+      <c r="D50" s="2">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2">
+        <v>10</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G50" s="1">
+        <v>7</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2">
+        <v>10</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A51" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C51" s="2">
+        <v>211040</v>
+      </c>
+      <c r="D51" s="2">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2">
+        <v>10</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+      <c r="H51" s="1">
+        <v>3</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2">
+        <v>3</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="O51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A52" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C52" s="2">
+        <v>211041</v>
+      </c>
+      <c r="D52" s="2">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2">
+        <v>10</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G52" s="1">
+        <v>5</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2">
+        <v>3</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A53" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C53" s="2">
+        <v>211042</v>
+      </c>
+      <c r="D53" s="2">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2">
+        <v>10</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="G53" s="1">
+        <v>7</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2">
+        <v>3</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="15:16">
+      <c r="O83"/>
+      <c r="P83"/>
+    </row>
+    <row r="84" customHeight="1" spans="15:16">
+      <c r="O84"/>
+      <c r="P84"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="445">
   <si>
     <t>_id</t>
   </si>
@@ -1639,34 +1639,34 @@
     <t>寻宝玉带</t>
   </si>
   <si>
-    <t>背刺</t>
-  </si>
-  <si>
-    <t>斩杀</t>
-  </si>
-  <si>
-    <t>幸运项链</t>
-  </si>
-  <si>
-    <t>幸运+3</t>
-  </si>
-  <si>
-    <t>幸运戒指</t>
-  </si>
-  <si>
-    <t>幸运腰带</t>
-  </si>
-  <si>
-    <t>诅咒魔甲</t>
-  </si>
-  <si>
-    <t>诅咒+3</t>
-  </si>
-  <si>
-    <t>诅咒魔面</t>
-  </si>
-  <si>
-    <t>诅咒魔靴</t>
+    <t>背刺之刺</t>
+  </si>
+  <si>
+    <t>80000,26</t>
+  </si>
+  <si>
+    <t>背刺面罩</t>
+  </si>
+  <si>
+    <t>8000,26</t>
+  </si>
+  <si>
+    <t>背刺之镯</t>
+  </si>
+  <si>
+    <t>斩杀板甲</t>
+  </si>
+  <si>
+    <t>90000,28</t>
+  </si>
+  <si>
+    <t>斩杀扳指</t>
+  </si>
+  <si>
+    <t>9000,28</t>
+  </si>
+  <si>
+    <t>斩杀铁履</t>
   </si>
   <si>
     <t>毒蛇之刺</t>
@@ -18034,7 +18034,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -19564,12 +19564,6 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:16">
-      <c r="A36" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C36" s="1">
         <v>201031</v>
       </c>
@@ -19582,14 +19576,36 @@
       <c r="F36" s="1" t="s">
         <v>427</v>
       </c>
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="K36" s="2">
+        <v>31</v>
+      </c>
+      <c r="L36" s="2">
+        <v>7</v>
+      </c>
+      <c r="M36" s="2">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customHeight="1" spans="1:16">
-      <c r="A37" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C37" s="1">
         <v>201032</v>
       </c>
@@ -19600,16 +19616,40 @@
         <v>110</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
+      </c>
+      <c r="G37" s="1">
+        <v>4</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="K37" s="2">
+        <v>32</v>
+      </c>
+      <c r="L37" s="2">
+        <v>7</v>
+      </c>
+      <c r="M37" s="2">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A38" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
       <c r="C38" s="1">
         <v>201033</v>
       </c>
@@ -19620,26 +19660,40 @@
         <v>110</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
+        <v>431</v>
+      </c>
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="K38" s="2">
+        <v>33</v>
+      </c>
+      <c r="L38" s="2">
+        <v>7</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A39" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
       <c r="C39" s="1">
         <v>201034</v>
       </c>
@@ -19650,26 +19704,40 @@
         <v>120</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
+        <v>432</v>
+      </c>
+      <c r="G39" s="2">
+        <v>2</v>
+      </c>
+      <c r="H39" s="2">
+        <v>2</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="K39" s="2">
+        <v>34</v>
+      </c>
+      <c r="L39" s="2">
+        <v>7</v>
+      </c>
+      <c r="M39" s="2">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A40" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
       <c r="C40" s="1">
         <v>201035</v>
       </c>
@@ -19680,26 +19748,40 @@
         <v>120</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
+        <v>434</v>
+      </c>
+      <c r="G40" s="1">
+        <v>7</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="K40" s="2">
+        <v>35</v>
+      </c>
+      <c r="L40" s="2">
+        <v>7</v>
+      </c>
+      <c r="M40" s="2">
+        <v>1</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A41" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="1">
         <v>201036</v>
       </c>
@@ -19710,20 +19792,38 @@
         <v>120</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:16">
+        <v>436</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1">
+        <v>10</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="K41" s="2">
+        <v>36</v>
+      </c>
+      <c r="L41" s="2">
+        <v>7</v>
+      </c>
+      <c r="M41" s="2">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
         <v>359</v>
       </c>
@@ -19731,7 +19831,7 @@
         <v>359</v>
       </c>
       <c r="C42" s="2">
-        <v>211031</v>
+        <v>211037</v>
       </c>
       <c r="D42" s="2">
         <v>10</v>
@@ -19740,23 +19840,23 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="G42" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="1">
-        <v>3</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8">
-        <v>13</v>
-      </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8" t="s">
-        <v>430</v>
+        <v>1</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2">
+        <v>10</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2" t="s">
+        <v>438</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19773,7 +19873,7 @@
         <v>359</v>
       </c>
       <c r="C43" s="2">
-        <v>211032</v>
+        <v>211038</v>
       </c>
       <c r="D43" s="2">
         <v>10</v>
@@ -19782,18 +19882,18 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="G43" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="8">
-        <v>13</v>
+      <c r="K43" s="2">
+        <v>10</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -19813,7 +19913,7 @@
         <v>359</v>
       </c>
       <c r="C44" s="2">
-        <v>211033</v>
+        <v>211039</v>
       </c>
       <c r="D44" s="2">
         <v>10</v>
@@ -19822,18 +19922,18 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="G44" s="1">
-        <v>9</v>
-      </c>
-      <c r="H44" s="1">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="8">
-        <v>13</v>
+      <c r="K44" s="2">
+        <v>10</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -19853,7 +19953,7 @@
         <v>359</v>
       </c>
       <c r="C45" s="2">
-        <v>211034</v>
+        <v>211040</v>
       </c>
       <c r="D45" s="2">
         <v>10</v>
@@ -19862,23 +19962,23 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="G45" s="2">
-        <v>2</v>
-      </c>
-      <c r="H45" s="2">
-        <v>2</v>
+        <v>441</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3</v>
+      </c>
+      <c r="H45" s="1">
+        <v>3</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19895,7 +19995,7 @@
         <v>359</v>
       </c>
       <c r="C46" s="2">
-        <v>211035</v>
+        <v>211041</v>
       </c>
       <c r="D46" s="2">
         <v>10</v>
@@ -19904,18 +20004,18 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="G46" s="1">
-        <v>4</v>
-      </c>
-      <c r="H46" s="1">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -19935,7 +20035,7 @@
         <v>359</v>
       </c>
       <c r="C47" s="2">
-        <v>211036</v>
+        <v>211042</v>
       </c>
       <c r="D47" s="2">
         <v>10</v>
@@ -19944,18 +20044,18 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="G47" s="1">
-        <v>10</v>
-      </c>
-      <c r="H47" s="1">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -19967,257 +20067,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A48" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C48" s="2">
-        <v>211037</v>
-      </c>
-      <c r="D48" s="2">
-        <v>10</v>
-      </c>
-      <c r="E48" s="2">
-        <v>10</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="G48" s="1">
-        <v>1</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1</v>
-      </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2">
-        <v>10</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="O48" s="1">
-        <v>0</v>
-      </c>
-      <c r="P48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A49" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C49" s="2">
-        <v>211038</v>
-      </c>
-      <c r="D49" s="2">
-        <v>10</v>
-      </c>
-      <c r="E49" s="2">
-        <v>10</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="G49" s="1">
-        <v>5</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2">
-        <v>10</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A50" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C50" s="2">
-        <v>211039</v>
-      </c>
-      <c r="D50" s="2">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2">
-        <v>10</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="G50" s="1">
-        <v>7</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2">
-        <v>10</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A51" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C51" s="2">
-        <v>211040</v>
-      </c>
-      <c r="D51" s="2">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2">
-        <v>10</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="G51" s="1">
-        <v>3</v>
-      </c>
-      <c r="H51" s="1">
-        <v>3</v>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2">
-        <v>3</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A52" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C52" s="2">
-        <v>211041</v>
-      </c>
-      <c r="D52" s="2">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2">
-        <v>10</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="G52" s="1">
-        <v>5</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2">
-        <v>3</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A53" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C53" s="2">
-        <v>211042</v>
-      </c>
-      <c r="D53" s="2">
-        <v>10</v>
-      </c>
-      <c r="E53" s="2">
-        <v>10</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="G53" s="1">
-        <v>7</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2">
-        <v>3</v>
-      </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="15:16">
-      <c r="O83"/>
-      <c r="P83"/>
-    </row>
-    <row r="84" customHeight="1" spans="15:16">
-      <c r="O84"/>
-      <c r="P84"/>
+    <row r="77" customHeight="1" spans="15:16">
+      <c r="O77"/>
+      <c r="P77"/>
+    </row>
+    <row r="78" customHeight="1" spans="15:16">
+      <c r="O78"/>
+      <c r="P78"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -356,7 +356,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="446">
   <si>
     <t>_id</t>
   </si>
@@ -1276,6 +1276,9 @@
     <t>光龙战盔</t>
   </si>
   <si>
+    <t>300000,32</t>
+  </si>
+  <si>
     <t>光龙战镯</t>
   </si>
   <si>
@@ -1354,10 +1357,10 @@
     <t>暗龙战盔</t>
   </si>
   <si>
+    <t>400000,36</t>
+  </si>
+  <si>
     <t>暗龙战镯</t>
-  </si>
-  <si>
-    <t>400000,36</t>
   </si>
   <si>
     <t>暗龙战戒</t>
@@ -6391,7 +6394,8 @@
         <v>112</v>
       </c>
       <c r="K81" s="9">
-        <v>100</v>
+        <f>(E81-1)/5*300+300</f>
+        <v>1200</v>
       </c>
       <c r="L81" s="9">
         <v>1</v>
@@ -6440,7 +6444,8 @@
         <v>112</v>
       </c>
       <c r="K82" s="9">
-        <v>100</v>
+        <f>(E82-1)/5*300+300</f>
+        <v>1200</v>
       </c>
       <c r="L82" s="9">
         <v>1</v>
@@ -6489,7 +6494,8 @@
         <v>115</v>
       </c>
       <c r="K83" s="9">
-        <v>100</v>
+        <f t="shared" ref="K83:K88" si="9">(E83-1)/5*100+100</f>
+        <v>400</v>
       </c>
       <c r="L83" s="9">
         <v>1</v>
@@ -6498,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="9">
-        <f t="shared" ref="N83:N88" si="9">(E83-1)/5*3+3</f>
+        <f t="shared" ref="N83:N88" si="10">(E83-1)/5*3+3</f>
         <v>12</v>
       </c>
       <c r="O83" s="9">
@@ -6538,7 +6544,8 @@
         <v>117</v>
       </c>
       <c r="K84" s="9">
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>400</v>
       </c>
       <c r="L84" s="9">
         <v>1</v>
@@ -6547,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O84" s="9">
@@ -6587,7 +6594,8 @@
         <v>117</v>
       </c>
       <c r="K85" s="9">
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>400</v>
       </c>
       <c r="L85" s="9">
         <v>1</v>
@@ -6596,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O85" s="9">
@@ -6636,7 +6644,8 @@
         <v>115</v>
       </c>
       <c r="K86" s="9">
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>400</v>
       </c>
       <c r="L86" s="9">
         <v>1</v>
@@ -6645,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O86" s="9">
@@ -6685,7 +6694,8 @@
         <v>115</v>
       </c>
       <c r="K87" s="9">
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>400</v>
       </c>
       <c r="L87" s="9">
         <v>1</v>
@@ -6694,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O87" s="9">
@@ -6734,7 +6744,8 @@
         <v>117</v>
       </c>
       <c r="K88" s="9">
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>400</v>
       </c>
       <c r="L88" s="9">
         <v>1</v>
@@ -6743,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O88" s="9">
@@ -6783,7 +6794,8 @@
         <v>112</v>
       </c>
       <c r="K89" s="9">
-        <v>100</v>
+        <f>(E89-1)/5*300+300</f>
+        <v>1200</v>
       </c>
       <c r="L89" s="9">
         <v>2</v>
@@ -6832,7 +6844,8 @@
         <v>112</v>
       </c>
       <c r="K90" s="9">
-        <v>100</v>
+        <f>(E90-1)/5*300+300</f>
+        <v>1200</v>
       </c>
       <c r="L90" s="9">
         <v>2</v>
@@ -6881,7 +6894,8 @@
         <v>115</v>
       </c>
       <c r="K91" s="9">
-        <v>100</v>
+        <f t="shared" ref="K91:K96" si="11">(E91-1)/5*100+100</f>
+        <v>400</v>
       </c>
       <c r="L91" s="9">
         <v>2</v>
@@ -6890,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="9">
-        <f t="shared" ref="N91:N96" si="10">(E91-1)/5*3+3</f>
+        <f t="shared" ref="N91:N96" si="12">(E91-1)/5*3+3</f>
         <v>12</v>
       </c>
       <c r="O91" s="9">
@@ -6930,7 +6944,8 @@
         <v>117</v>
       </c>
       <c r="K92" s="9">
-        <v>100</v>
+        <f t="shared" si="11"/>
+        <v>400</v>
       </c>
       <c r="L92" s="9">
         <v>2</v>
@@ -6939,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="O92" s="9">
@@ -6979,7 +6994,8 @@
         <v>117</v>
       </c>
       <c r="K93" s="9">
-        <v>100</v>
+        <f t="shared" si="11"/>
+        <v>400</v>
       </c>
       <c r="L93" s="9">
         <v>2</v>
@@ -6988,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="O93" s="9">
@@ -7028,7 +7044,8 @@
         <v>115</v>
       </c>
       <c r="K94" s="9">
-        <v>100</v>
+        <f t="shared" si="11"/>
+        <v>400</v>
       </c>
       <c r="L94" s="9">
         <v>2</v>
@@ -7037,7 +7054,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="O94" s="9">
@@ -7077,7 +7094,8 @@
         <v>115</v>
       </c>
       <c r="K95" s="9">
-        <v>100</v>
+        <f t="shared" si="11"/>
+        <v>400</v>
       </c>
       <c r="L95" s="9">
         <v>2</v>
@@ -7086,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="O95" s="9">
@@ -7126,7 +7144,8 @@
         <v>117</v>
       </c>
       <c r="K96" s="9">
-        <v>100</v>
+        <f t="shared" si="11"/>
+        <v>400</v>
       </c>
       <c r="L96" s="9">
         <v>2</v>
@@ -7135,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="O96" s="9">
@@ -7175,7 +7194,8 @@
         <v>112</v>
       </c>
       <c r="K97" s="9">
-        <v>100</v>
+        <f>(E97-1)/5*300+300</f>
+        <v>1200</v>
       </c>
       <c r="L97" s="9">
         <v>3</v>
@@ -7224,7 +7244,8 @@
         <v>112</v>
       </c>
       <c r="K98" s="9">
-        <v>100</v>
+        <f>(E98-1)/5*300+300</f>
+        <v>1200</v>
       </c>
       <c r="L98" s="9">
         <v>3</v>
@@ -7273,7 +7294,8 @@
         <v>115</v>
       </c>
       <c r="K99" s="9">
-        <v>100</v>
+        <f t="shared" ref="K99:K104" si="13">(E99-1)/5*100+100</f>
+        <v>400</v>
       </c>
       <c r="L99" s="9">
         <v>3</v>
@@ -7282,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="9">
-        <f t="shared" ref="N99:N104" si="11">(E99-1)/5*3+3</f>
+        <f t="shared" ref="N99:N104" si="14">(E99-1)/5*3+3</f>
         <v>12</v>
       </c>
       <c r="O99" s="9">
@@ -7322,7 +7344,8 @@
         <v>117</v>
       </c>
       <c r="K100" s="9">
-        <v>100</v>
+        <f t="shared" si="13"/>
+        <v>400</v>
       </c>
       <c r="L100" s="9">
         <v>3</v>
@@ -7331,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="O100" s="9">
@@ -7371,7 +7394,8 @@
         <v>117</v>
       </c>
       <c r="K101" s="9">
-        <v>100</v>
+        <f t="shared" si="13"/>
+        <v>400</v>
       </c>
       <c r="L101" s="9">
         <v>3</v>
@@ -7380,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="O101" s="9">
@@ -7420,7 +7444,8 @@
         <v>115</v>
       </c>
       <c r="K102" s="9">
-        <v>100</v>
+        <f t="shared" si="13"/>
+        <v>400</v>
       </c>
       <c r="L102" s="9">
         <v>3</v>
@@ -7429,7 +7454,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="O102" s="9">
@@ -7469,7 +7494,8 @@
         <v>115</v>
       </c>
       <c r="K103" s="9">
-        <v>100</v>
+        <f t="shared" si="13"/>
+        <v>400</v>
       </c>
       <c r="L103" s="9">
         <v>3</v>
@@ -7478,7 +7504,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="O103" s="9">
@@ -7518,7 +7544,8 @@
         <v>117</v>
       </c>
       <c r="K104" s="9">
-        <v>100</v>
+        <f t="shared" si="13"/>
+        <v>400</v>
       </c>
       <c r="L104" s="9">
         <v>3</v>
@@ -7527,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="O104" s="9">
@@ -7757,7 +7784,8 @@
         <v>139</v>
       </c>
       <c r="K6" s="9">
-        <v>100</v>
+        <f>(E6-1)/5*300+300</f>
+        <v>1500</v>
       </c>
       <c r="L6" s="9">
         <v>1</v>
@@ -7806,7 +7834,8 @@
         <v>139</v>
       </c>
       <c r="K7" s="9">
-        <v>100</v>
+        <f>(E7-1)/5*300+300</f>
+        <v>1500</v>
       </c>
       <c r="L7" s="9">
         <v>1</v>
@@ -7855,7 +7884,8 @@
         <v>142</v>
       </c>
       <c r="K8" s="9">
-        <v>100</v>
+        <f t="shared" ref="K8:K13" si="1">(E8-1)/5*100+100</f>
+        <v>500</v>
       </c>
       <c r="L8" s="9">
         <v>1</v>
@@ -7864,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="9">
-        <f t="shared" ref="N8:N13" si="1">(E8-1)/5*3+3</f>
+        <f t="shared" ref="N8:N13" si="2">(E8-1)/5*3+3</f>
         <v>15</v>
       </c>
       <c r="O8" s="9">
@@ -7904,7 +7934,8 @@
         <v>144</v>
       </c>
       <c r="K9" s="9">
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="L9" s="9">
         <v>1</v>
@@ -7913,7 +7944,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O9" s="9">
@@ -7953,7 +7984,8 @@
         <v>144</v>
       </c>
       <c r="K10" s="9">
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="L10" s="9">
         <v>1</v>
@@ -7962,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O10" s="9">
@@ -8002,7 +8034,8 @@
         <v>142</v>
       </c>
       <c r="K11" s="9">
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="L11" s="9">
         <v>1</v>
@@ -8011,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O11" s="9">
@@ -8051,7 +8084,8 @@
         <v>142</v>
       </c>
       <c r="K12" s="9">
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="L12" s="9">
         <v>1</v>
@@ -8060,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O12" s="9">
@@ -8100,7 +8134,8 @@
         <v>144</v>
       </c>
       <c r="K13" s="9">
-        <v>100</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="L13" s="9">
         <v>1</v>
@@ -8109,7 +8144,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="O13" s="9">
@@ -8149,7 +8184,8 @@
         <v>139</v>
       </c>
       <c r="K14" s="9">
-        <v>100</v>
+        <f>(E14-1)/5*300+300</f>
+        <v>1500</v>
       </c>
       <c r="L14" s="9">
         <v>2</v>
@@ -8198,7 +8234,8 @@
         <v>139</v>
       </c>
       <c r="K15" s="9">
-        <v>100</v>
+        <f>(E15-1)/5*300+300</f>
+        <v>1500</v>
       </c>
       <c r="L15" s="9">
         <v>2</v>
@@ -8247,7 +8284,8 @@
         <v>142</v>
       </c>
       <c r="K16" s="9">
-        <v>100</v>
+        <f t="shared" ref="K16:K21" si="3">(E16-1)/5*100+100</f>
+        <v>500</v>
       </c>
       <c r="L16" s="9">
         <v>2</v>
@@ -8256,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="9">
-        <f t="shared" ref="N16:N21" si="2">(E16-1)/5*3+3</f>
+        <f t="shared" ref="N16:N21" si="4">(E16-1)/5*3+3</f>
         <v>15</v>
       </c>
       <c r="O16" s="9">
@@ -8296,7 +8334,8 @@
         <v>144</v>
       </c>
       <c r="K17" s="9">
-        <v>100</v>
+        <f t="shared" si="3"/>
+        <v>500</v>
       </c>
       <c r="L17" s="9">
         <v>2</v>
@@ -8305,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="O17" s="9">
@@ -8345,7 +8384,8 @@
         <v>144</v>
       </c>
       <c r="K18" s="9">
-        <v>100</v>
+        <f t="shared" si="3"/>
+        <v>500</v>
       </c>
       <c r="L18" s="9">
         <v>2</v>
@@ -8354,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="O18" s="9">
@@ -8394,7 +8434,8 @@
         <v>142</v>
       </c>
       <c r="K19" s="9">
-        <v>100</v>
+        <f t="shared" si="3"/>
+        <v>500</v>
       </c>
       <c r="L19" s="9">
         <v>2</v>
@@ -8403,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="O19" s="9">
@@ -8443,7 +8484,8 @@
         <v>142</v>
       </c>
       <c r="K20" s="9">
-        <v>100</v>
+        <f t="shared" si="3"/>
+        <v>500</v>
       </c>
       <c r="L20" s="9">
         <v>2</v>
@@ -8452,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="O20" s="9">
@@ -8492,7 +8534,8 @@
         <v>144</v>
       </c>
       <c r="K21" s="9">
-        <v>100</v>
+        <f t="shared" si="3"/>
+        <v>500</v>
       </c>
       <c r="L21" s="9">
         <v>2</v>
@@ -8501,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="O21" s="9">
@@ -8541,7 +8584,8 @@
         <v>139</v>
       </c>
       <c r="K22" s="9">
-        <v>100</v>
+        <f>(E22-1)/5*300+300</f>
+        <v>1500</v>
       </c>
       <c r="L22" s="9">
         <v>3</v>
@@ -8590,7 +8634,8 @@
         <v>139</v>
       </c>
       <c r="K23" s="9">
-        <v>100</v>
+        <f>(E23-1)/5*300+300</f>
+        <v>1500</v>
       </c>
       <c r="L23" s="9">
         <v>3</v>
@@ -8639,7 +8684,8 @@
         <v>142</v>
       </c>
       <c r="K24" s="9">
-        <v>100</v>
+        <f t="shared" ref="K24:K29" si="5">(E24-1)/5*100+100</f>
+        <v>500</v>
       </c>
       <c r="L24" s="9">
         <v>3</v>
@@ -8648,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" ref="N24:N29" si="3">(E24-1)/5*3+3</f>
+        <f t="shared" ref="N24:N29" si="6">(E24-1)/5*3+3</f>
         <v>15</v>
       </c>
       <c r="O24" s="9">
@@ -8688,7 +8734,8 @@
         <v>144</v>
       </c>
       <c r="K25" s="9">
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>500</v>
       </c>
       <c r="L25" s="9">
         <v>3</v>
@@ -8697,7 +8744,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O25" s="9">
@@ -8737,7 +8784,8 @@
         <v>144</v>
       </c>
       <c r="K26" s="9">
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>500</v>
       </c>
       <c r="L26" s="9">
         <v>3</v>
@@ -8746,7 +8794,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O26" s="9">
@@ -8786,7 +8834,8 @@
         <v>142</v>
       </c>
       <c r="K27" s="9">
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>500</v>
       </c>
       <c r="L27" s="9">
         <v>3</v>
@@ -8795,7 +8844,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O27" s="9">
@@ -8835,7 +8884,8 @@
         <v>142</v>
       </c>
       <c r="K28" s="9">
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>500</v>
       </c>
       <c r="L28" s="9">
         <v>3</v>
@@ -8844,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O28" s="9">
@@ -8884,7 +8934,8 @@
         <v>144</v>
       </c>
       <c r="K29" s="9">
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>500</v>
       </c>
       <c r="L29" s="9">
         <v>3</v>
@@ -8893,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="O29" s="9">
@@ -8933,7 +8984,8 @@
         <v>166</v>
       </c>
       <c r="K31" s="9">
-        <v>100</v>
+        <f>(E31-1)/5*300+300</f>
+        <v>1800</v>
       </c>
       <c r="L31" s="9">
         <v>1</v>
@@ -8952,7 +9004,7 @@
         <v>12</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" ref="Q31:Q54" si="4">(E31-1)/5*3+10</f>
+        <f t="shared" ref="Q31:Q54" si="7">(E31-1)/5*3+10</f>
         <v>25</v>
       </c>
     </row>
@@ -8982,7 +9034,8 @@
         <v>166</v>
       </c>
       <c r="K32" s="9">
-        <v>100</v>
+        <f>(E32-1)/5*300+300</f>
+        <v>1800</v>
       </c>
       <c r="L32" s="9">
         <v>1</v>
@@ -9001,7 +9054,7 @@
         <v>12</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9031,7 +9084,8 @@
         <v>169</v>
       </c>
       <c r="K33" s="9">
-        <v>100</v>
+        <f t="shared" ref="K33:K38" si="8">(E33-1)/5*100+100</f>
+        <v>600</v>
       </c>
       <c r="L33" s="9">
         <v>1</v>
@@ -9040,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" ref="N33:N38" si="5">(E33-1)/5*3+3</f>
+        <f t="shared" ref="N33:N38" si="9">(E33-1)/5*3+3</f>
         <v>18</v>
       </c>
       <c r="O33" s="9">
@@ -9050,7 +9104,7 @@
         <v>6</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9080,7 +9134,8 @@
         <v>171</v>
       </c>
       <c r="K34" s="9">
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>600</v>
       </c>
       <c r="L34" s="9">
         <v>1</v>
@@ -9089,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="O34" s="9">
@@ -9099,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9129,7 +9184,8 @@
         <v>171</v>
       </c>
       <c r="K35" s="9">
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>600</v>
       </c>
       <c r="L35" s="9">
         <v>1</v>
@@ -9138,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="O35" s="9">
@@ -9148,7 +9204,7 @@
         <v>6</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9178,7 +9234,8 @@
         <v>169</v>
       </c>
       <c r="K36" s="9">
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>600</v>
       </c>
       <c r="L36" s="9">
         <v>1</v>
@@ -9187,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="O36" s="9">
@@ -9197,7 +9254,7 @@
         <v>6</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9227,7 +9284,8 @@
         <v>169</v>
       </c>
       <c r="K37" s="9">
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>600</v>
       </c>
       <c r="L37" s="9">
         <v>1</v>
@@ -9236,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="O37" s="9">
@@ -9246,7 +9304,7 @@
         <v>6</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9276,7 +9334,8 @@
         <v>171</v>
       </c>
       <c r="K38" s="9">
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>600</v>
       </c>
       <c r="L38" s="9">
         <v>1</v>
@@ -9285,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="O38" s="9">
@@ -9295,7 +9354,7 @@
         <v>6</v>
       </c>
       <c r="Q38" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9325,7 +9384,8 @@
         <v>166</v>
       </c>
       <c r="K39" s="9">
-        <v>100</v>
+        <f>(E39-1)/5*300+300</f>
+        <v>1800</v>
       </c>
       <c r="L39" s="9">
         <v>2</v>
@@ -9344,7 +9404,7 @@
         <v>12</v>
       </c>
       <c r="Q39" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9374,7 +9434,8 @@
         <v>166</v>
       </c>
       <c r="K40" s="9">
-        <v>100</v>
+        <f>(E40-1)/5*300+300</f>
+        <v>1800</v>
       </c>
       <c r="L40" s="9">
         <v>2</v>
@@ -9393,7 +9454,7 @@
         <v>12</v>
       </c>
       <c r="Q40" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9423,7 +9484,8 @@
         <v>169</v>
       </c>
       <c r="K41" s="9">
-        <v>100</v>
+        <f t="shared" ref="K41:K46" si="10">(E41-1)/5*100+100</f>
+        <v>600</v>
       </c>
       <c r="L41" s="9">
         <v>2</v>
@@ -9432,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="9">
-        <f t="shared" ref="N41:N46" si="6">(E41-1)/5*3+3</f>
+        <f t="shared" ref="N41:N46" si="11">(E41-1)/5*3+3</f>
         <v>18</v>
       </c>
       <c r="O41" s="9">
@@ -9442,7 +9504,7 @@
         <v>6</v>
       </c>
       <c r="Q41" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9472,7 +9534,8 @@
         <v>171</v>
       </c>
       <c r="K42" s="9">
-        <v>100</v>
+        <f t="shared" si="10"/>
+        <v>600</v>
       </c>
       <c r="L42" s="9">
         <v>2</v>
@@ -9481,7 +9544,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="O42" s="9">
@@ -9491,7 +9554,7 @@
         <v>6</v>
       </c>
       <c r="Q42" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9521,7 +9584,8 @@
         <v>171</v>
       </c>
       <c r="K43" s="9">
-        <v>100</v>
+        <f t="shared" si="10"/>
+        <v>600</v>
       </c>
       <c r="L43" s="9">
         <v>2</v>
@@ -9530,7 +9594,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="O43" s="9">
@@ -9540,7 +9604,7 @@
         <v>6</v>
       </c>
       <c r="Q43" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9570,7 +9634,8 @@
         <v>169</v>
       </c>
       <c r="K44" s="9">
-        <v>100</v>
+        <f t="shared" si="10"/>
+        <v>600</v>
       </c>
       <c r="L44" s="9">
         <v>2</v>
@@ -9579,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="O44" s="9">
@@ -9589,7 +9654,7 @@
         <v>6</v>
       </c>
       <c r="Q44" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9619,7 +9684,8 @@
         <v>169</v>
       </c>
       <c r="K45" s="9">
-        <v>100</v>
+        <f t="shared" si="10"/>
+        <v>600</v>
       </c>
       <c r="L45" s="9">
         <v>2</v>
@@ -9628,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="O45" s="9">
@@ -9638,7 +9704,7 @@
         <v>6</v>
       </c>
       <c r="Q45" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9668,7 +9734,8 @@
         <v>171</v>
       </c>
       <c r="K46" s="9">
-        <v>100</v>
+        <f t="shared" si="10"/>
+        <v>600</v>
       </c>
       <c r="L46" s="9">
         <v>2</v>
@@ -9677,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="O46" s="9">
@@ -9687,7 +9754,7 @@
         <v>6</v>
       </c>
       <c r="Q46" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9717,7 +9784,8 @@
         <v>166</v>
       </c>
       <c r="K47" s="9">
-        <v>100</v>
+        <f>(E47-1)/5*300+300</f>
+        <v>1800</v>
       </c>
       <c r="L47" s="9">
         <v>3</v>
@@ -9736,7 +9804,7 @@
         <v>12</v>
       </c>
       <c r="Q47" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9766,7 +9834,8 @@
         <v>166</v>
       </c>
       <c r="K48" s="9">
-        <v>100</v>
+        <f>(E48-1)/5*300+300</f>
+        <v>1800</v>
       </c>
       <c r="L48" s="9">
         <v>3</v>
@@ -9785,7 +9854,7 @@
         <v>12</v>
       </c>
       <c r="Q48" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9815,7 +9884,8 @@
         <v>169</v>
       </c>
       <c r="K49" s="9">
-        <v>100</v>
+        <f t="shared" ref="K49:K54" si="12">(E49-1)/5*100+100</f>
+        <v>600</v>
       </c>
       <c r="L49" s="9">
         <v>3</v>
@@ -9824,7 +9894,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="9">
-        <f t="shared" ref="N49:N54" si="7">(E49-1)/5*3+3</f>
+        <f t="shared" ref="N49:N54" si="13">(E49-1)/5*3+3</f>
         <v>18</v>
       </c>
       <c r="O49" s="9">
@@ -9834,7 +9904,7 @@
         <v>6</v>
       </c>
       <c r="Q49" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9864,7 +9934,8 @@
         <v>171</v>
       </c>
       <c r="K50" s="9">
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>600</v>
       </c>
       <c r="L50" s="9">
         <v>3</v>
@@ -9873,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="O50" s="9">
@@ -9883,7 +9954,7 @@
         <v>6</v>
       </c>
       <c r="Q50" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9913,7 +9984,8 @@
         <v>171</v>
       </c>
       <c r="K51" s="9">
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>600</v>
       </c>
       <c r="L51" s="9">
         <v>3</v>
@@ -9922,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="O51" s="9">
@@ -9932,7 +10004,7 @@
         <v>6</v>
       </c>
       <c r="Q51" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -9962,7 +10034,8 @@
         <v>169</v>
       </c>
       <c r="K52" s="9">
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>600</v>
       </c>
       <c r="L52" s="9">
         <v>3</v>
@@ -9971,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="O52" s="9">
@@ -9981,7 +10054,7 @@
         <v>6</v>
       </c>
       <c r="Q52" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -10011,7 +10084,8 @@
         <v>169</v>
       </c>
       <c r="K53" s="9">
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>600</v>
       </c>
       <c r="L53" s="9">
         <v>3</v>
@@ -10020,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="O53" s="9">
@@ -10030,7 +10104,7 @@
         <v>6</v>
       </c>
       <c r="Q53" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -10060,7 +10134,8 @@
         <v>171</v>
       </c>
       <c r="K54" s="9">
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>600</v>
       </c>
       <c r="L54" s="9">
         <v>3</v>
@@ -10069,7 +10144,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="O54" s="9">
@@ -10079,7 +10154,7 @@
         <v>6</v>
       </c>
       <c r="Q54" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
     </row>
@@ -10126,7 +10201,8 @@
         <v>193</v>
       </c>
       <c r="K56" s="9">
-        <v>100</v>
+        <f>(E56-1)/5*300+300</f>
+        <v>2100</v>
       </c>
       <c r="L56" s="9">
         <v>1</v>
@@ -10142,11 +10218,11 @@
         <v>5</v>
       </c>
       <c r="P56" s="9">
-        <f t="shared" ref="P56:P58" si="8">((E56-1)/5+1)*2</f>
+        <f t="shared" ref="P56:P58" si="14">((E56-1)/5+1)*2</f>
         <v>14</v>
       </c>
       <c r="Q56" s="9">
-        <f t="shared" ref="Q56:Q79" si="9">(E56-1)/5*3+10</f>
+        <f t="shared" ref="Q56:Q79" si="15">(E56-1)/5*3+10</f>
         <v>28</v>
       </c>
     </row>
@@ -10176,7 +10252,8 @@
         <v>193</v>
       </c>
       <c r="K57" s="9">
-        <v>100</v>
+        <f>(E57-1)/5*300+300</f>
+        <v>2100</v>
       </c>
       <c r="L57" s="9">
         <v>1</v>
@@ -10192,11 +10269,11 @@
         <v>5</v>
       </c>
       <c r="P57" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="Q57" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10226,7 +10303,8 @@
         <v>196</v>
       </c>
       <c r="K58" s="9">
-        <v>100</v>
+        <f t="shared" ref="K58:K63" si="16">(E58-1)/5*100+100</f>
+        <v>700</v>
       </c>
       <c r="L58" s="9">
         <v>1</v>
@@ -10235,18 +10313,18 @@
         <v>0</v>
       </c>
       <c r="N58" s="9">
-        <f t="shared" ref="N58:N63" si="10">(E58-1)/5*3+3</f>
+        <f t="shared" ref="N58:N63" si="17">(E58-1)/5*3+3</f>
         <v>21</v>
       </c>
       <c r="O58" s="9">
         <v>5</v>
       </c>
       <c r="P58" s="9">
-        <f t="shared" ref="P58:P63" si="11">((E58-1)/5+1)*1</f>
+        <f t="shared" ref="P58:P63" si="18">((E58-1)/5+1)*1</f>
         <v>7</v>
       </c>
       <c r="Q58" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10276,7 +10354,8 @@
         <v>198</v>
       </c>
       <c r="K59" s="9">
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>700</v>
       </c>
       <c r="L59" s="9">
         <v>1</v>
@@ -10285,18 +10364,18 @@
         <v>0</v>
       </c>
       <c r="N59" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="O59" s="9">
         <v>5</v>
       </c>
       <c r="P59" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="Q59" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10326,7 +10405,8 @@
         <v>198</v>
       </c>
       <c r="K60" s="9">
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>700</v>
       </c>
       <c r="L60" s="9">
         <v>1</v>
@@ -10335,18 +10415,18 @@
         <v>0</v>
       </c>
       <c r="N60" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="O60" s="9">
         <v>5</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="Q60" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10376,7 +10456,8 @@
         <v>196</v>
       </c>
       <c r="K61" s="9">
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>700</v>
       </c>
       <c r="L61" s="9">
         <v>1</v>
@@ -10385,18 +10466,18 @@
         <v>0</v>
       </c>
       <c r="N61" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="O61" s="9">
         <v>5</v>
       </c>
       <c r="P61" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="Q61" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10426,7 +10507,8 @@
         <v>196</v>
       </c>
       <c r="K62" s="9">
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>700</v>
       </c>
       <c r="L62" s="9">
         <v>1</v>
@@ -10435,18 +10517,18 @@
         <v>0</v>
       </c>
       <c r="N62" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="O62" s="9">
         <v>5</v>
       </c>
       <c r="P62" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="Q62" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10476,7 +10558,8 @@
         <v>198</v>
       </c>
       <c r="K63" s="9">
-        <v>100</v>
+        <f t="shared" si="16"/>
+        <v>700</v>
       </c>
       <c r="L63" s="9">
         <v>1</v>
@@ -10485,18 +10568,18 @@
         <v>0</v>
       </c>
       <c r="N63" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>21</v>
       </c>
       <c r="O63" s="9">
         <v>5</v>
       </c>
       <c r="P63" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="Q63" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10526,7 +10609,8 @@
         <v>193</v>
       </c>
       <c r="K64" s="9">
-        <v>100</v>
+        <f>(E64-1)/5*300+300</f>
+        <v>2100</v>
       </c>
       <c r="L64" s="9">
         <v>2</v>
@@ -10546,7 +10630,7 @@
         <v>14</v>
       </c>
       <c r="Q64" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10576,7 +10660,8 @@
         <v>193</v>
       </c>
       <c r="K65" s="9">
-        <v>100</v>
+        <f>(E65-1)/5*300+300</f>
+        <v>2100</v>
       </c>
       <c r="L65" s="9">
         <v>2</v>
@@ -10596,7 +10681,7 @@
         <v>14</v>
       </c>
       <c r="Q65" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10626,7 +10711,8 @@
         <v>196</v>
       </c>
       <c r="K66" s="9">
-        <v>100</v>
+        <f t="shared" ref="K66:K71" si="19">(E66-1)/5*100+100</f>
+        <v>700</v>
       </c>
       <c r="L66" s="9">
         <v>2</v>
@@ -10635,18 +10721,18 @@
         <v>0</v>
       </c>
       <c r="N66" s="9">
-        <f t="shared" ref="N66:N71" si="12">(E66-1)/5*3+3</f>
+        <f t="shared" ref="N66:N71" si="20">(E66-1)/5*3+3</f>
         <v>21</v>
       </c>
       <c r="O66" s="9">
         <v>5</v>
       </c>
       <c r="P66" s="9">
-        <f t="shared" ref="P66:P71" si="13">((E66-1)/5+1)*1</f>
+        <f t="shared" ref="P66:P71" si="21">((E66-1)/5+1)*1</f>
         <v>7</v>
       </c>
       <c r="Q66" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10676,7 +10762,8 @@
         <v>198</v>
       </c>
       <c r="K67" s="9">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>700</v>
       </c>
       <c r="L67" s="9">
         <v>2</v>
@@ -10685,18 +10772,18 @@
         <v>0</v>
       </c>
       <c r="N67" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="O67" s="9">
         <v>5</v>
       </c>
       <c r="P67" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="Q67" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10726,7 +10813,8 @@
         <v>198</v>
       </c>
       <c r="K68" s="9">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>700</v>
       </c>
       <c r="L68" s="9">
         <v>2</v>
@@ -10735,18 +10823,18 @@
         <v>0</v>
       </c>
       <c r="N68" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="O68" s="9">
         <v>5</v>
       </c>
       <c r="P68" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="Q68" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10776,7 +10864,8 @@
         <v>196</v>
       </c>
       <c r="K69" s="9">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>700</v>
       </c>
       <c r="L69" s="9">
         <v>2</v>
@@ -10785,18 +10874,18 @@
         <v>0</v>
       </c>
       <c r="N69" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="O69" s="9">
         <v>5</v>
       </c>
       <c r="P69" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="Q69" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10826,7 +10915,8 @@
         <v>196</v>
       </c>
       <c r="K70" s="9">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>700</v>
       </c>
       <c r="L70" s="9">
         <v>2</v>
@@ -10835,18 +10925,18 @@
         <v>0</v>
       </c>
       <c r="N70" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="O70" s="9">
         <v>5</v>
       </c>
       <c r="P70" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="Q70" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10876,7 +10966,8 @@
         <v>198</v>
       </c>
       <c r="K71" s="9">
-        <v>100</v>
+        <f t="shared" si="19"/>
+        <v>700</v>
       </c>
       <c r="L71" s="9">
         <v>2</v>
@@ -10885,18 +10976,18 @@
         <v>0</v>
       </c>
       <c r="N71" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>21</v>
       </c>
       <c r="O71" s="9">
         <v>5</v>
       </c>
       <c r="P71" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
       <c r="Q71" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10926,7 +11017,8 @@
         <v>193</v>
       </c>
       <c r="K72" s="9">
-        <v>100</v>
+        <f>(E72-1)/5*300+300</f>
+        <v>2100</v>
       </c>
       <c r="L72" s="9">
         <v>3</v>
@@ -10946,7 +11038,7 @@
         <v>14</v>
       </c>
       <c r="Q72" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -10976,7 +11068,8 @@
         <v>193</v>
       </c>
       <c r="K73" s="9">
-        <v>100</v>
+        <f>(E73-1)/5*300+300</f>
+        <v>2100</v>
       </c>
       <c r="L73" s="9">
         <v>3</v>
@@ -10996,7 +11089,7 @@
         <v>14</v>
       </c>
       <c r="Q73" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -11026,7 +11119,8 @@
         <v>196</v>
       </c>
       <c r="K74" s="9">
-        <v>100</v>
+        <f t="shared" ref="K74:K79" si="22">(E74-1)/5*100+100</f>
+        <v>700</v>
       </c>
       <c r="L74" s="9">
         <v>3</v>
@@ -11035,18 +11129,18 @@
         <v>0</v>
       </c>
       <c r="N74" s="9">
-        <f t="shared" ref="N74:N79" si="14">(E74-1)/5*3+3</f>
+        <f t="shared" ref="N74:N79" si="23">(E74-1)/5*3+3</f>
         <v>21</v>
       </c>
       <c r="O74" s="9">
         <v>5</v>
       </c>
       <c r="P74" s="9">
-        <f t="shared" ref="P74:P79" si="15">((E74-1)/5+1)*1</f>
+        <f t="shared" ref="P74:P79" si="24">((E74-1)/5+1)*1</f>
         <v>7</v>
       </c>
       <c r="Q74" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
     </row>
@@ -11076,7 +11170,8 @@
         <v>198</v>
       </c>
       <c r="K75" s="9">
-        <v>100</v>
+        <f t="shared" si="22"/>
+        <v>700</v>
       </c>
       <c r="L75" s="9">
         <v>3</v>
@@ -11085,18 +11180,18 @@
         <v>0</v>
       </c>
       <c r="N75" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="O75" s="9">
         <v>5</v>
       </c>
       <c r="P75" s="9">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="Q75" s="9">
         <f t="shared" si="15"/>
-        <v>7</v>
-      </c>
-      <c r="Q75" s="9">
-        <f t="shared" si="9"/>
         <v>28</v>
       </c>
     </row>
@@ -11126,7 +11221,8 @@
         <v>198</v>
       </c>
       <c r="K76" s="9">
-        <v>100</v>
+        <f t="shared" si="22"/>
+        <v>700</v>
       </c>
       <c r="L76" s="9">
         <v>3</v>
@@ -11135,18 +11231,18 @@
         <v>0</v>
       </c>
       <c r="N76" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="O76" s="9">
         <v>5</v>
       </c>
       <c r="P76" s="9">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="Q76" s="9">
         <f t="shared" si="15"/>
-        <v>7</v>
-      </c>
-      <c r="Q76" s="9">
-        <f t="shared" si="9"/>
         <v>28</v>
       </c>
     </row>
@@ -11176,7 +11272,8 @@
         <v>196</v>
       </c>
       <c r="K77" s="9">
-        <v>100</v>
+        <f t="shared" si="22"/>
+        <v>700</v>
       </c>
       <c r="L77" s="9">
         <v>3</v>
@@ -11185,18 +11282,18 @@
         <v>0</v>
       </c>
       <c r="N77" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="O77" s="9">
         <v>5</v>
       </c>
       <c r="P77" s="9">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="Q77" s="9">
         <f t="shared" si="15"/>
-        <v>7</v>
-      </c>
-      <c r="Q77" s="9">
-        <f t="shared" si="9"/>
         <v>28</v>
       </c>
     </row>
@@ -11226,7 +11323,8 @@
         <v>196</v>
       </c>
       <c r="K78" s="9">
-        <v>100</v>
+        <f t="shared" si="22"/>
+        <v>700</v>
       </c>
       <c r="L78" s="9">
         <v>3</v>
@@ -11235,18 +11333,18 @@
         <v>0</v>
       </c>
       <c r="N78" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="O78" s="9">
         <v>5</v>
       </c>
       <c r="P78" s="9">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="Q78" s="9">
         <f t="shared" si="15"/>
-        <v>7</v>
-      </c>
-      <c r="Q78" s="9">
-        <f t="shared" si="9"/>
         <v>28</v>
       </c>
     </row>
@@ -11276,7 +11374,8 @@
         <v>198</v>
       </c>
       <c r="K79" s="9">
-        <v>100</v>
+        <f t="shared" si="22"/>
+        <v>700</v>
       </c>
       <c r="L79" s="9">
         <v>3</v>
@@ -11285,18 +11384,18 @@
         <v>0</v>
       </c>
       <c r="N79" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="23"/>
         <v>21</v>
       </c>
       <c r="O79" s="9">
         <v>5</v>
       </c>
       <c r="P79" s="9">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="Q79" s="9">
         <f t="shared" si="15"/>
-        <v>7</v>
-      </c>
-      <c r="Q79" s="9">
-        <f t="shared" si="9"/>
         <v>28</v>
       </c>
     </row>
@@ -11341,7 +11440,8 @@
         <v>220</v>
       </c>
       <c r="K81" s="9">
-        <v>100</v>
+        <f>(E81-1)/5*300+300</f>
+        <v>2400</v>
       </c>
       <c r="L81" s="9">
         <v>1</v>
@@ -11361,7 +11461,7 @@
         <v>16</v>
       </c>
       <c r="Q81" s="9">
-        <f t="shared" ref="Q81:Q104" si="16">(E81-1)/5*3+10</f>
+        <f t="shared" ref="Q81:Q104" si="25">(E81-1)/5*3+10</f>
         <v>31</v>
       </c>
     </row>
@@ -11391,7 +11491,8 @@
         <v>220</v>
       </c>
       <c r="K82" s="9">
-        <v>100</v>
+        <f>(E82-1)/5*300+300</f>
+        <v>2400</v>
       </c>
       <c r="L82" s="9">
         <v>1</v>
@@ -11411,7 +11512,7 @@
         <v>16</v>
       </c>
       <c r="Q82" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11441,7 +11542,8 @@
         <v>223</v>
       </c>
       <c r="K83" s="9">
-        <v>100</v>
+        <f t="shared" ref="K83:K88" si="26">(E83-1)/5*100+100</f>
+        <v>800</v>
       </c>
       <c r="L83" s="9">
         <v>1</v>
@@ -11450,18 +11552,18 @@
         <v>0</v>
       </c>
       <c r="N83" s="9">
-        <f t="shared" ref="N83:N88" si="17">(E83-1)/5*3+3</f>
+        <f t="shared" ref="N83:N88" si="27">(E83-1)/5*3+3</f>
         <v>24</v>
       </c>
       <c r="O83" s="9">
         <v>5</v>
       </c>
       <c r="P83" s="9">
-        <f t="shared" ref="P83:P88" si="18">((E83-1)/5+1)*1</f>
+        <f t="shared" ref="P83:P88" si="28">((E83-1)/5+1)*1</f>
         <v>8</v>
       </c>
       <c r="Q83" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11491,7 +11593,8 @@
         <v>225</v>
       </c>
       <c r="K84" s="9">
-        <v>100</v>
+        <f t="shared" si="26"/>
+        <v>800</v>
       </c>
       <c r="L84" s="9">
         <v>1</v>
@@ -11500,18 +11603,18 @@
         <v>0</v>
       </c>
       <c r="N84" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>24</v>
       </c>
       <c r="O84" s="9">
         <v>5</v>
       </c>
       <c r="P84" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="Q84" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11541,7 +11644,8 @@
         <v>225</v>
       </c>
       <c r="K85" s="9">
-        <v>100</v>
+        <f t="shared" si="26"/>
+        <v>800</v>
       </c>
       <c r="L85" s="9">
         <v>1</v>
@@ -11550,18 +11654,18 @@
         <v>0</v>
       </c>
       <c r="N85" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>24</v>
       </c>
       <c r="O85" s="9">
         <v>5</v>
       </c>
       <c r="P85" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="Q85" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11591,7 +11695,8 @@
         <v>223</v>
       </c>
       <c r="K86" s="9">
-        <v>100</v>
+        <f t="shared" si="26"/>
+        <v>800</v>
       </c>
       <c r="L86" s="9">
         <v>1</v>
@@ -11600,18 +11705,18 @@
         <v>0</v>
       </c>
       <c r="N86" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>24</v>
       </c>
       <c r="O86" s="9">
         <v>5</v>
       </c>
       <c r="P86" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="Q86" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11641,7 +11746,8 @@
         <v>223</v>
       </c>
       <c r="K87" s="9">
-        <v>100</v>
+        <f t="shared" si="26"/>
+        <v>800</v>
       </c>
       <c r="L87" s="9">
         <v>1</v>
@@ -11650,18 +11756,18 @@
         <v>0</v>
       </c>
       <c r="N87" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>24</v>
       </c>
       <c r="O87" s="9">
         <v>5</v>
       </c>
       <c r="P87" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="Q87" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11691,7 +11797,8 @@
         <v>225</v>
       </c>
       <c r="K88" s="9">
-        <v>100</v>
+        <f t="shared" si="26"/>
+        <v>800</v>
       </c>
       <c r="L88" s="9">
         <v>1</v>
@@ -11700,18 +11807,18 @@
         <v>0</v>
       </c>
       <c r="N88" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="27"/>
         <v>24</v>
       </c>
       <c r="O88" s="9">
         <v>5</v>
       </c>
       <c r="P88" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="Q88" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11741,7 +11848,8 @@
         <v>220</v>
       </c>
       <c r="K89" s="9">
-        <v>100</v>
+        <f>(E89-1)/5*300+300</f>
+        <v>2400</v>
       </c>
       <c r="L89" s="9">
         <v>2</v>
@@ -11761,7 +11869,7 @@
         <v>16</v>
       </c>
       <c r="Q89" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11791,7 +11899,8 @@
         <v>220</v>
       </c>
       <c r="K90" s="9">
-        <v>100</v>
+        <f>(E90-1)/5*300+300</f>
+        <v>2400</v>
       </c>
       <c r="L90" s="9">
         <v>2</v>
@@ -11811,7 +11920,7 @@
         <v>16</v>
       </c>
       <c r="Q90" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11841,7 +11950,8 @@
         <v>223</v>
       </c>
       <c r="K91" s="9">
-        <v>100</v>
+        <f t="shared" ref="K91:K96" si="29">(E91-1)/5*100+100</f>
+        <v>800</v>
       </c>
       <c r="L91" s="9">
         <v>2</v>
@@ -11850,18 +11960,18 @@
         <v>0</v>
       </c>
       <c r="N91" s="9">
-        <f t="shared" ref="N91:N96" si="19">(E91-1)/5*3+3</f>
+        <f t="shared" ref="N91:N96" si="30">(E91-1)/5*3+3</f>
         <v>24</v>
       </c>
       <c r="O91" s="9">
         <v>5</v>
       </c>
       <c r="P91" s="9">
-        <f t="shared" ref="P91:P96" si="20">((E91-1)/5+1)*1</f>
+        <f t="shared" ref="P91:P96" si="31">((E91-1)/5+1)*1</f>
         <v>8</v>
       </c>
       <c r="Q91" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11891,7 +12001,8 @@
         <v>225</v>
       </c>
       <c r="K92" s="9">
-        <v>100</v>
+        <f t="shared" si="29"/>
+        <v>800</v>
       </c>
       <c r="L92" s="9">
         <v>2</v>
@@ -11900,18 +12011,18 @@
         <v>0</v>
       </c>
       <c r="N92" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>24</v>
       </c>
       <c r="O92" s="9">
         <v>5</v>
       </c>
       <c r="P92" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="Q92" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11941,7 +12052,8 @@
         <v>225</v>
       </c>
       <c r="K93" s="9">
-        <v>100</v>
+        <f t="shared" si="29"/>
+        <v>800</v>
       </c>
       <c r="L93" s="9">
         <v>2</v>
@@ -11950,18 +12062,18 @@
         <v>0</v>
       </c>
       <c r="N93" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>24</v>
       </c>
       <c r="O93" s="9">
         <v>5</v>
       </c>
       <c r="P93" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="Q93" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -11991,7 +12103,8 @@
         <v>223</v>
       </c>
       <c r="K94" s="9">
-        <v>100</v>
+        <f t="shared" si="29"/>
+        <v>800</v>
       </c>
       <c r="L94" s="9">
         <v>2</v>
@@ -12000,18 +12113,18 @@
         <v>0</v>
       </c>
       <c r="N94" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>24</v>
       </c>
       <c r="O94" s="9">
         <v>5</v>
       </c>
       <c r="P94" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="Q94" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12041,7 +12154,8 @@
         <v>223</v>
       </c>
       <c r="K95" s="9">
-        <v>100</v>
+        <f t="shared" si="29"/>
+        <v>800</v>
       </c>
       <c r="L95" s="9">
         <v>2</v>
@@ -12050,18 +12164,18 @@
         <v>0</v>
       </c>
       <c r="N95" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>24</v>
       </c>
       <c r="O95" s="9">
         <v>5</v>
       </c>
       <c r="P95" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="Q95" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12091,7 +12205,8 @@
         <v>225</v>
       </c>
       <c r="K96" s="9">
-        <v>100</v>
+        <f t="shared" si="29"/>
+        <v>800</v>
       </c>
       <c r="L96" s="9">
         <v>2</v>
@@ -12100,18 +12215,18 @@
         <v>0</v>
       </c>
       <c r="N96" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="30"/>
         <v>24</v>
       </c>
       <c r="O96" s="9">
         <v>5</v>
       </c>
       <c r="P96" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="31"/>
         <v>8</v>
       </c>
       <c r="Q96" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12141,7 +12256,8 @@
         <v>220</v>
       </c>
       <c r="K97" s="9">
-        <v>100</v>
+        <f>(E97-1)/5*300+300</f>
+        <v>2400</v>
       </c>
       <c r="L97" s="9">
         <v>3</v>
@@ -12161,7 +12277,7 @@
         <v>16</v>
       </c>
       <c r="Q97" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12191,7 +12307,8 @@
         <v>220</v>
       </c>
       <c r="K98" s="9">
-        <v>100</v>
+        <f>(E98-1)/5*300+300</f>
+        <v>2400</v>
       </c>
       <c r="L98" s="9">
         <v>3</v>
@@ -12211,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="Q98" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12241,7 +12358,8 @@
         <v>223</v>
       </c>
       <c r="K99" s="9">
-        <v>100</v>
+        <f t="shared" ref="K99:K104" si="32">(E99-1)/5*100+100</f>
+        <v>800</v>
       </c>
       <c r="L99" s="9">
         <v>3</v>
@@ -12250,18 +12368,18 @@
         <v>0</v>
       </c>
       <c r="N99" s="9">
-        <f t="shared" ref="N99:N104" si="21">(E99-1)/5*3+3</f>
+        <f t="shared" ref="N99:N104" si="33">(E99-1)/5*3+3</f>
         <v>24</v>
       </c>
       <c r="O99" s="9">
         <v>5</v>
       </c>
       <c r="P99" s="9">
-        <f t="shared" ref="P99:P104" si="22">((E99-1)/5+1)*1</f>
+        <f t="shared" ref="P99:P104" si="34">((E99-1)/5+1)*1</f>
         <v>8</v>
       </c>
       <c r="Q99" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12291,7 +12409,8 @@
         <v>225</v>
       </c>
       <c r="K100" s="9">
-        <v>100</v>
+        <f t="shared" si="32"/>
+        <v>800</v>
       </c>
       <c r="L100" s="9">
         <v>3</v>
@@ -12300,18 +12419,18 @@
         <v>0</v>
       </c>
       <c r="N100" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>24</v>
       </c>
       <c r="O100" s="9">
         <v>5</v>
       </c>
       <c r="P100" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>8</v>
       </c>
       <c r="Q100" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12341,7 +12460,8 @@
         <v>225</v>
       </c>
       <c r="K101" s="9">
-        <v>100</v>
+        <f t="shared" si="32"/>
+        <v>800</v>
       </c>
       <c r="L101" s="9">
         <v>3</v>
@@ -12350,18 +12470,18 @@
         <v>0</v>
       </c>
       <c r="N101" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>24</v>
       </c>
       <c r="O101" s="9">
         <v>5</v>
       </c>
       <c r="P101" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>8</v>
       </c>
       <c r="Q101" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12391,7 +12511,8 @@
         <v>223</v>
       </c>
       <c r="K102" s="9">
-        <v>100</v>
+        <f t="shared" si="32"/>
+        <v>800</v>
       </c>
       <c r="L102" s="9">
         <v>3</v>
@@ -12400,18 +12521,18 @@
         <v>0</v>
       </c>
       <c r="N102" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>24</v>
       </c>
       <c r="O102" s="9">
         <v>5</v>
       </c>
       <c r="P102" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>8</v>
       </c>
       <c r="Q102" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12441,7 +12562,8 @@
         <v>223</v>
       </c>
       <c r="K103" s="9">
-        <v>100</v>
+        <f t="shared" si="32"/>
+        <v>800</v>
       </c>
       <c r="L103" s="9">
         <v>3</v>
@@ -12450,18 +12572,18 @@
         <v>0</v>
       </c>
       <c r="N103" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>24</v>
       </c>
       <c r="O103" s="9">
         <v>5</v>
       </c>
       <c r="P103" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>8</v>
       </c>
       <c r="Q103" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12491,7 +12613,8 @@
         <v>225</v>
       </c>
       <c r="K104" s="9">
-        <v>100</v>
+        <f t="shared" si="32"/>
+        <v>800</v>
       </c>
       <c r="L104" s="9">
         <v>3</v>
@@ -12500,18 +12623,18 @@
         <v>0</v>
       </c>
       <c r="N104" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>24</v>
       </c>
       <c r="O104" s="9">
         <v>5</v>
       </c>
       <c r="P104" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>8</v>
       </c>
       <c r="Q104" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
     </row>
@@ -12831,8 +12954,9 @@
       <c r="J6" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K6" s="1">
-        <v>100</v>
+      <c r="K6" s="9">
+        <f>(E6-1)/5*300+300</f>
+        <v>2700</v>
       </c>
       <c r="L6" s="1">
         <v>1</v>
@@ -12881,8 +13005,9 @@
       <c r="J7" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K7" s="1">
-        <v>100</v>
+      <c r="K7" s="9">
+        <f>(E7-1)/5*300+300</f>
+        <v>2700</v>
       </c>
       <c r="L7" s="1">
         <v>1</v>
@@ -12931,8 +13056,9 @@
       <c r="J8" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K8" s="1">
-        <v>100</v>
+      <c r="K8" s="9">
+        <f t="shared" ref="K8:K13" si="1">(E8-1)/5*100+100</f>
+        <v>900</v>
       </c>
       <c r="L8" s="1">
         <v>1</v>
@@ -12941,14 +13067,14 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <f t="shared" ref="N8:N13" si="1">(E8-1)/5*3+3</f>
+        <f t="shared" ref="N8:N13" si="2">(E8-1)/5*3+3</f>
         <v>27</v>
       </c>
       <c r="O8" s="1">
         <v>5</v>
       </c>
       <c r="P8" s="9">
-        <f t="shared" ref="P8:P13" si="2">((E8-1)/5+1)*1</f>
+        <f t="shared" ref="P8:P13" si="3">((E8-1)/5+1)*1</f>
         <v>9</v>
       </c>
       <c r="Q8" s="1">
@@ -12981,8 +13107,9 @@
       <c r="J9" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K9" s="1">
-        <v>100</v>
+      <c r="K9" s="9">
+        <f t="shared" si="1"/>
+        <v>900</v>
       </c>
       <c r="L9" s="1">
         <v>1</v>
@@ -12991,14 +13118,14 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="O9" s="1">
         <v>5</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="Q9" s="1">
@@ -13031,8 +13158,9 @@
       <c r="J10" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K10" s="1">
-        <v>100</v>
+      <c r="K10" s="9">
+        <f t="shared" si="1"/>
+        <v>900</v>
       </c>
       <c r="L10" s="1">
         <v>1</v>
@@ -13041,14 +13169,14 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="O10" s="1">
         <v>5</v>
       </c>
       <c r="P10" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="Q10" s="1">
@@ -13081,8 +13209,9 @@
       <c r="J11" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K11" s="1">
-        <v>100</v>
+      <c r="K11" s="9">
+        <f t="shared" si="1"/>
+        <v>900</v>
       </c>
       <c r="L11" s="1">
         <v>1</v>
@@ -13091,14 +13220,14 @@
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
       </c>
       <c r="P11" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="Q11" s="1">
@@ -13131,8 +13260,9 @@
       <c r="J12" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K12" s="1">
-        <v>100</v>
+      <c r="K12" s="9">
+        <f t="shared" si="1"/>
+        <v>900</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
@@ -13141,14 +13271,14 @@
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="O12" s="1">
         <v>5</v>
       </c>
       <c r="P12" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="Q12" s="1">
@@ -13181,8 +13311,9 @@
       <c r="J13" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K13" s="1">
-        <v>100</v>
+      <c r="K13" s="9">
+        <f t="shared" si="1"/>
+        <v>900</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
@@ -13191,14 +13322,14 @@
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="O13" s="1">
         <v>5</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="Q13" s="1">
@@ -13231,8 +13362,9 @@
       <c r="J14" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K14" s="1">
-        <v>100</v>
+      <c r="K14" s="9">
+        <f>(E14-1)/5*300+300</f>
+        <v>2700</v>
       </c>
       <c r="L14" s="1">
         <v>2</v>
@@ -13281,8 +13413,9 @@
       <c r="J15" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K15" s="1">
-        <v>100</v>
+      <c r="K15" s="9">
+        <f>(E15-1)/5*300+300</f>
+        <v>2700</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
@@ -13331,8 +13464,9 @@
       <c r="J16" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K16" s="1">
-        <v>100</v>
+      <c r="K16" s="9">
+        <f t="shared" ref="K16:K21" si="4">(E16-1)/5*100+100</f>
+        <v>900</v>
       </c>
       <c r="L16" s="1">
         <v>2</v>
@@ -13341,14 +13475,14 @@
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" ref="N16:N21" si="3">(E16-1)/5*3+3</f>
+        <f t="shared" ref="N16:N21" si="5">(E16-1)/5*3+3</f>
         <v>27</v>
       </c>
       <c r="O16" s="1">
         <v>5</v>
       </c>
       <c r="P16" s="9">
-        <f t="shared" ref="P16:P21" si="4">((E16-1)/5+1)*1</f>
+        <f t="shared" ref="P16:P21" si="6">((E16-1)/5+1)*1</f>
         <v>9</v>
       </c>
       <c r="Q16" s="1">
@@ -13381,8 +13515,9 @@
       <c r="J17" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K17" s="1">
-        <v>100</v>
+      <c r="K17" s="9">
+        <f t="shared" si="4"/>
+        <v>900</v>
       </c>
       <c r="L17" s="1">
         <v>2</v>
@@ -13391,14 +13526,14 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O17" s="1">
         <v>5</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q17" s="1">
@@ -13431,8 +13566,9 @@
       <c r="J18" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K18" s="1">
-        <v>100</v>
+      <c r="K18" s="9">
+        <f t="shared" si="4"/>
+        <v>900</v>
       </c>
       <c r="L18" s="1">
         <v>2</v>
@@ -13441,14 +13577,14 @@
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O18" s="1">
         <v>5</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q18" s="1">
@@ -13481,8 +13617,9 @@
       <c r="J19" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K19" s="1">
-        <v>100</v>
+      <c r="K19" s="9">
+        <f t="shared" si="4"/>
+        <v>900</v>
       </c>
       <c r="L19" s="1">
         <v>2</v>
@@ -13491,14 +13628,14 @@
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O19" s="1">
         <v>5</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q19" s="1">
@@ -13531,8 +13668,9 @@
       <c r="J20" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K20" s="1">
-        <v>100</v>
+      <c r="K20" s="9">
+        <f t="shared" si="4"/>
+        <v>900</v>
       </c>
       <c r="L20" s="1">
         <v>2</v>
@@ -13541,14 +13679,14 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O20" s="1">
         <v>5</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q20" s="1">
@@ -13581,8 +13719,9 @@
       <c r="J21" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K21" s="1">
-        <v>100</v>
+      <c r="K21" s="9">
+        <f t="shared" si="4"/>
+        <v>900</v>
       </c>
       <c r="L21" s="1">
         <v>2</v>
@@ -13591,14 +13730,14 @@
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O21" s="1">
         <v>5</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Q21" s="1">
@@ -13631,8 +13770,9 @@
       <c r="J22" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K22" s="1">
-        <v>100</v>
+      <c r="K22" s="9">
+        <f>(E22-1)/5*300+300</f>
+        <v>2700</v>
       </c>
       <c r="L22" s="1">
         <v>3</v>
@@ -13681,8 +13821,9 @@
       <c r="J23" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K23" s="1">
-        <v>100</v>
+      <c r="K23" s="9">
+        <f>(E23-1)/5*300+300</f>
+        <v>2700</v>
       </c>
       <c r="L23" s="1">
         <v>3</v>
@@ -13731,8 +13872,9 @@
       <c r="J24" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K24" s="1">
-        <v>100</v>
+      <c r="K24" s="9">
+        <f t="shared" ref="K24:K29" si="7">(E24-1)/5*100+100</f>
+        <v>900</v>
       </c>
       <c r="L24" s="1">
         <v>3</v>
@@ -13741,14 +13883,14 @@
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" ref="N24:N29" si="5">(E24-1)/5*3+3</f>
+        <f t="shared" ref="N24:N29" si="8">(E24-1)/5*3+3</f>
         <v>27</v>
       </c>
       <c r="O24" s="1">
         <v>5</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" ref="P24:P29" si="6">((E24-1)/5+1)*1</f>
+        <f t="shared" ref="P24:P29" si="9">((E24-1)/5+1)*1</f>
         <v>9</v>
       </c>
       <c r="Q24" s="1">
@@ -13781,8 +13923,9 @@
       <c r="J25" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K25" s="1">
-        <v>100</v>
+      <c r="K25" s="9">
+        <f t="shared" si="7"/>
+        <v>900</v>
       </c>
       <c r="L25" s="1">
         <v>3</v>
@@ -13791,14 +13934,14 @@
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="O25" s="1">
         <v>5</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Q25" s="1">
@@ -13831,8 +13974,9 @@
       <c r="J26" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K26" s="1">
-        <v>100</v>
+      <c r="K26" s="9">
+        <f t="shared" si="7"/>
+        <v>900</v>
       </c>
       <c r="L26" s="1">
         <v>3</v>
@@ -13841,14 +13985,14 @@
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="O26" s="1">
         <v>5</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Q26" s="1">
@@ -13881,8 +14025,9 @@
       <c r="J27" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K27" s="1">
-        <v>100</v>
+      <c r="K27" s="9">
+        <f t="shared" si="7"/>
+        <v>900</v>
       </c>
       <c r="L27" s="1">
         <v>3</v>
@@ -13891,14 +14036,14 @@
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="O27" s="1">
         <v>5</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Q27" s="1">
@@ -13931,8 +14076,9 @@
       <c r="J28" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="K28" s="1">
-        <v>100</v>
+      <c r="K28" s="9">
+        <f t="shared" si="7"/>
+        <v>900</v>
       </c>
       <c r="L28" s="1">
         <v>3</v>
@@ -13941,14 +14087,14 @@
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="O28" s="1">
         <v>5</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Q28" s="1">
@@ -13981,8 +14127,9 @@
       <c r="J29" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="K29" s="1">
-        <v>100</v>
+      <c r="K29" s="9">
+        <f t="shared" si="7"/>
+        <v>900</v>
       </c>
       <c r="L29" s="1">
         <v>3</v>
@@ -13991,14 +14138,14 @@
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="O29" s="1">
         <v>5</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Q29" s="1">
@@ -14031,8 +14178,9 @@
       <c r="J31" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="K31" s="1">
-        <v>100</v>
+      <c r="K31" s="9">
+        <f>(E31-1)/5*300+300</f>
+        <v>3000</v>
       </c>
       <c r="L31" s="1">
         <v>1</v>
@@ -14052,7 +14200,7 @@
         <v>20</v>
       </c>
       <c r="Q31" s="1">
-        <f t="shared" ref="Q31:Q54" si="7">(E31-1)/5*3+10</f>
+        <f t="shared" ref="Q31:Q54" si="10">(E31-1)/5*3+10</f>
         <v>37</v>
       </c>
     </row>
@@ -14081,8 +14229,9 @@
       <c r="J32" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="K32" s="1">
-        <v>100</v>
+      <c r="K32" s="9">
+        <f>(E32-1)/5*300+300</f>
+        <v>3000</v>
       </c>
       <c r="L32" s="1">
         <v>1</v>
@@ -14102,7 +14251,7 @@
         <v>20</v>
       </c>
       <c r="Q32" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14131,8 +14280,9 @@
       <c r="J33" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K33" s="1">
-        <v>100</v>
+      <c r="K33" s="9">
+        <f t="shared" ref="K33:K38" si="11">(E33-1)/5*100+100</f>
+        <v>1000</v>
       </c>
       <c r="L33" s="1">
         <v>1</v>
@@ -14141,18 +14291,18 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <f t="shared" ref="N33:N38" si="8">(E33-1)/5*3+3</f>
+        <f t="shared" ref="N33:N38" si="12">(E33-1)/5*3+3</f>
         <v>30</v>
       </c>
       <c r="O33" s="1">
         <v>5</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" ref="P33:P38" si="9">((E33-1)/5+1)*1</f>
+        <f t="shared" ref="P33:P38" si="13">((E33-1)/5+1)*1</f>
         <v>10</v>
       </c>
       <c r="Q33" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14181,8 +14331,9 @@
       <c r="J34" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K34" s="1">
-        <v>100</v>
+      <c r="K34" s="9">
+        <f t="shared" si="11"/>
+        <v>1000</v>
       </c>
       <c r="L34" s="1">
         <v>1</v>
@@ -14191,18 +14342,18 @@
         <v>0</v>
       </c>
       <c r="N34" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="O34" s="1">
         <v>5</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="Q34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14231,8 +14382,9 @@
       <c r="J35" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K35" s="1">
-        <v>100</v>
+      <c r="K35" s="9">
+        <f t="shared" si="11"/>
+        <v>1000</v>
       </c>
       <c r="L35" s="1">
         <v>1</v>
@@ -14241,18 +14393,18 @@
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="O35" s="1">
         <v>5</v>
       </c>
       <c r="P35" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="Q35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14281,8 +14433,9 @@
       <c r="J36" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K36" s="1">
-        <v>100</v>
+      <c r="K36" s="9">
+        <f t="shared" si="11"/>
+        <v>1000</v>
       </c>
       <c r="L36" s="1">
         <v>1</v>
@@ -14291,18 +14444,18 @@
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="O36" s="1">
         <v>5</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="Q36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14331,8 +14484,9 @@
       <c r="J37" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K37" s="1">
-        <v>100</v>
+      <c r="K37" s="9">
+        <f t="shared" si="11"/>
+        <v>1000</v>
       </c>
       <c r="L37" s="1">
         <v>1</v>
@@ -14341,18 +14495,18 @@
         <v>0</v>
       </c>
       <c r="N37" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="O37" s="1">
         <v>5</v>
       </c>
       <c r="P37" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="Q37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14381,8 +14535,9 @@
       <c r="J38" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K38" s="1">
-        <v>100</v>
+      <c r="K38" s="9">
+        <f t="shared" si="11"/>
+        <v>1000</v>
       </c>
       <c r="L38" s="1">
         <v>1</v>
@@ -14391,18 +14546,18 @@
         <v>0</v>
       </c>
       <c r="N38" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="O38" s="1">
         <v>5</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14431,8 +14586,9 @@
       <c r="J39" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="K39" s="1">
-        <v>100</v>
+      <c r="K39" s="9">
+        <f>(E39-1)/5*300+300</f>
+        <v>3000</v>
       </c>
       <c r="L39" s="1">
         <v>2</v>
@@ -14452,7 +14608,7 @@
         <v>20</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14481,8 +14637,9 @@
       <c r="J40" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="K40" s="1">
-        <v>100</v>
+      <c r="K40" s="9">
+        <f>(E40-1)/5*300+300</f>
+        <v>3000</v>
       </c>
       <c r="L40" s="1">
         <v>2</v>
@@ -14502,7 +14659,7 @@
         <v>20</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14531,8 +14688,9 @@
       <c r="J41" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K41" s="1">
-        <v>100</v>
+      <c r="K41" s="9">
+        <f t="shared" ref="K41:K46" si="14">(E41-1)/5*100+100</f>
+        <v>1000</v>
       </c>
       <c r="L41" s="1">
         <v>2</v>
@@ -14541,18 +14699,18 @@
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" ref="N41:N46" si="10">(E41-1)/5*3+3</f>
+        <f t="shared" ref="N41:N46" si="15">(E41-1)/5*3+3</f>
         <v>30</v>
       </c>
       <c r="O41" s="1">
         <v>5</v>
       </c>
       <c r="P41" s="9">
-        <f t="shared" ref="P41:P46" si="11">((E41-1)/5+1)*1</f>
+        <f t="shared" ref="P41:P46" si="16">((E41-1)/5+1)*1</f>
         <v>10</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14581,8 +14739,9 @@
       <c r="J42" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K42" s="1">
-        <v>100</v>
+      <c r="K42" s="9">
+        <f t="shared" si="14"/>
+        <v>1000</v>
       </c>
       <c r="L42" s="1">
         <v>2</v>
@@ -14591,18 +14750,18 @@
         <v>0</v>
       </c>
       <c r="N42" s="1">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="O42" s="1">
+        <v>5</v>
+      </c>
+      <c r="P42" s="9">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="Q42" s="1">
         <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="O42" s="1">
-        <v>5</v>
-      </c>
-      <c r="P42" s="9">
-        <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="Q42" s="1">
-        <f t="shared" si="7"/>
         <v>37</v>
       </c>
     </row>
@@ -14631,8 +14790,9 @@
       <c r="J43" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K43" s="1">
-        <v>100</v>
+      <c r="K43" s="9">
+        <f t="shared" si="14"/>
+        <v>1000</v>
       </c>
       <c r="L43" s="1">
         <v>2</v>
@@ -14641,18 +14801,18 @@
         <v>0</v>
       </c>
       <c r="N43" s="1">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="O43" s="1">
+        <v>5</v>
+      </c>
+      <c r="P43" s="9">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="Q43" s="1">
         <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="O43" s="1">
-        <v>5</v>
-      </c>
-      <c r="P43" s="9">
-        <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="Q43" s="1">
-        <f t="shared" si="7"/>
         <v>37</v>
       </c>
     </row>
@@ -14681,8 +14841,9 @@
       <c r="J44" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K44" s="1">
-        <v>100</v>
+      <c r="K44" s="9">
+        <f t="shared" si="14"/>
+        <v>1000</v>
       </c>
       <c r="L44" s="1">
         <v>2</v>
@@ -14691,18 +14852,18 @@
         <v>0</v>
       </c>
       <c r="N44" s="1">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="O44" s="1">
+        <v>5</v>
+      </c>
+      <c r="P44" s="9">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="Q44" s="1">
         <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="O44" s="1">
-        <v>5</v>
-      </c>
-      <c r="P44" s="9">
-        <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="Q44" s="1">
-        <f t="shared" si="7"/>
         <v>37</v>
       </c>
     </row>
@@ -14731,8 +14892,9 @@
       <c r="J45" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K45" s="1">
-        <v>100</v>
+      <c r="K45" s="9">
+        <f t="shared" si="14"/>
+        <v>1000</v>
       </c>
       <c r="L45" s="1">
         <v>2</v>
@@ -14741,18 +14903,18 @@
         <v>0</v>
       </c>
       <c r="N45" s="1">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="O45" s="1">
+        <v>5</v>
+      </c>
+      <c r="P45" s="9">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="Q45" s="1">
         <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="O45" s="1">
-        <v>5</v>
-      </c>
-      <c r="P45" s="9">
-        <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="Q45" s="1">
-        <f t="shared" si="7"/>
         <v>37</v>
       </c>
     </row>
@@ -14781,8 +14943,9 @@
       <c r="J46" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K46" s="1">
-        <v>100</v>
+      <c r="K46" s="9">
+        <f t="shared" si="14"/>
+        <v>1000</v>
       </c>
       <c r="L46" s="1">
         <v>2</v>
@@ -14791,18 +14954,18 @@
         <v>0</v>
       </c>
       <c r="N46" s="1">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="O46" s="1">
+        <v>5</v>
+      </c>
+      <c r="P46" s="9">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="Q46" s="1">
         <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="O46" s="1">
-        <v>5</v>
-      </c>
-      <c r="P46" s="9">
-        <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="Q46" s="1">
-        <f t="shared" si="7"/>
         <v>37</v>
       </c>
     </row>
@@ -14831,8 +14994,9 @@
       <c r="J47" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="K47" s="1">
-        <v>100</v>
+      <c r="K47" s="9">
+        <f>(E47-1)/5*300+300</f>
+        <v>3000</v>
       </c>
       <c r="L47" s="1">
         <v>3</v>
@@ -14852,7 +15016,7 @@
         <v>20</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14881,8 +15045,9 @@
       <c r="J48" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="K48" s="1">
-        <v>100</v>
+      <c r="K48" s="9">
+        <f>(E48-1)/5*300+300</f>
+        <v>3000</v>
       </c>
       <c r="L48" s="1">
         <v>3</v>
@@ -14902,7 +15067,7 @@
         <v>20</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14931,8 +15096,9 @@
       <c r="J49" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K49" s="1">
-        <v>100</v>
+      <c r="K49" s="9">
+        <f t="shared" ref="K49:K54" si="17">(E49-1)/5*100+100</f>
+        <v>1000</v>
       </c>
       <c r="L49" s="1">
         <v>3</v>
@@ -14941,18 +15107,18 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <f t="shared" ref="N49:N54" si="12">(E49-1)/5*3+3</f>
+        <f t="shared" ref="N49:N54" si="18">(E49-1)/5*3+3</f>
         <v>30</v>
       </c>
       <c r="O49" s="1">
         <v>5</v>
       </c>
       <c r="P49" s="9">
-        <f t="shared" ref="P49:P54" si="13">((E49-1)/5+1)*1</f>
+        <f t="shared" ref="P49:P54" si="19">((E49-1)/5+1)*1</f>
         <v>10</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -14981,8 +15147,9 @@
       <c r="J50" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K50" s="1">
-        <v>100</v>
+      <c r="K50" s="9">
+        <f t="shared" si="17"/>
+        <v>1000</v>
       </c>
       <c r="L50" s="1">
         <v>3</v>
@@ -14991,18 +15158,18 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="O50" s="1">
         <v>5</v>
       </c>
       <c r="P50" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -15031,8 +15198,9 @@
       <c r="J51" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K51" s="1">
-        <v>100</v>
+      <c r="K51" s="9">
+        <f t="shared" si="17"/>
+        <v>1000</v>
       </c>
       <c r="L51" s="1">
         <v>3</v>
@@ -15041,18 +15209,18 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="O51" s="1">
         <v>5</v>
       </c>
       <c r="P51" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -15081,8 +15249,9 @@
       <c r="J52" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K52" s="1">
-        <v>100</v>
+      <c r="K52" s="9">
+        <f t="shared" si="17"/>
+        <v>1000</v>
       </c>
       <c r="L52" s="1">
         <v>3</v>
@@ -15091,18 +15260,18 @@
         <v>0</v>
       </c>
       <c r="N52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="O52" s="1">
         <v>5</v>
       </c>
       <c r="P52" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -15131,8 +15300,9 @@
       <c r="J53" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="K53" s="1">
-        <v>100</v>
+      <c r="K53" s="9">
+        <f t="shared" si="17"/>
+        <v>1000</v>
       </c>
       <c r="L53" s="1">
         <v>3</v>
@@ -15141,18 +15311,18 @@
         <v>0</v>
       </c>
       <c r="N53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="O53" s="1">
         <v>5</v>
       </c>
       <c r="P53" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -15181,8 +15351,9 @@
       <c r="J54" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="1">
-        <v>100</v>
+      <c r="K54" s="9">
+        <f t="shared" si="17"/>
+        <v>1000</v>
       </c>
       <c r="L54" s="1">
         <v>3</v>
@@ -15191,18 +15362,18 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>30</v>
       </c>
       <c r="O54" s="1">
         <v>5</v>
       </c>
       <c r="P54" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
     </row>
@@ -15248,8 +15419,9 @@
       <c r="J56" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K56" s="1">
-        <v>100</v>
+      <c r="K56" s="9">
+        <f>(E56-1)/5*300+300</f>
+        <v>3300</v>
       </c>
       <c r="L56" s="1">
         <v>1</v>
@@ -15269,7 +15441,7 @@
         <v>22</v>
       </c>
       <c r="Q56" s="1">
-        <f t="shared" ref="Q56:Q79" si="14">(E56-1)/5*3+10</f>
+        <f t="shared" ref="Q56:Q79" si="20">(E56-1)/5*3+10</f>
         <v>40</v>
       </c>
     </row>
@@ -15298,8 +15470,9 @@
       <c r="J57" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K57" s="1">
-        <v>100</v>
+      <c r="K57" s="9">
+        <f>(E57-1)/5*300+300</f>
+        <v>3300</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
@@ -15319,7 +15492,7 @@
         <v>22</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15348,8 +15521,9 @@
       <c r="J58" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K58" s="1">
-        <v>100</v>
+      <c r="K58" s="9">
+        <f t="shared" ref="K58:K63" si="21">(E58-1)/5*100+100</f>
+        <v>1100</v>
       </c>
       <c r="L58" s="1">
         <v>1</v>
@@ -15358,18 +15532,18 @@
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" ref="N58:N63" si="15">(E58-1)/5*3+3</f>
+        <f t="shared" ref="N58:N63" si="22">(E58-1)/5*3+3</f>
         <v>33</v>
       </c>
       <c r="O58" s="1">
         <v>5</v>
       </c>
       <c r="P58" s="9">
-        <f t="shared" ref="P58:P63" si="16">((E58-1)/5+1)*1</f>
+        <f t="shared" ref="P58:P63" si="23">((E58-1)/5+1)*1</f>
         <v>11</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15396,10 +15570,11 @@
         <v>31</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K59" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K59" s="9">
+        <f t="shared" si="21"/>
+        <v>1100</v>
       </c>
       <c r="L59" s="1">
         <v>1</v>
@@ -15408,18 +15583,18 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>33</v>
       </c>
       <c r="O59" s="1">
         <v>5</v>
       </c>
       <c r="P59" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Q59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15434,7 +15609,7 @@
         <v>51</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G60" s="1">
         <v>5</v>
@@ -15446,10 +15621,11 @@
         <v>31</v>
       </c>
       <c r="J60" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K60" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K60" s="9">
+        <f t="shared" si="21"/>
+        <v>1100</v>
       </c>
       <c r="L60" s="1">
         <v>1</v>
@@ -15458,18 +15634,18 @@
         <v>0</v>
       </c>
       <c r="N60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>33</v>
       </c>
       <c r="O60" s="1">
         <v>5</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Q60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15484,7 +15660,7 @@
         <v>51</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G61" s="1">
         <v>7</v>
@@ -15498,8 +15674,9 @@
       <c r="J61" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K61" s="1">
-        <v>100</v>
+      <c r="K61" s="9">
+        <f t="shared" si="21"/>
+        <v>1100</v>
       </c>
       <c r="L61" s="1">
         <v>1</v>
@@ -15508,18 +15685,18 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>33</v>
       </c>
       <c r="O61" s="1">
         <v>5</v>
       </c>
       <c r="P61" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Q61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15534,7 +15711,7 @@
         <v>51</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G62" s="1">
         <v>9</v>
@@ -15548,8 +15725,9 @@
       <c r="J62" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K62" s="1">
-        <v>100</v>
+      <c r="K62" s="9">
+        <f t="shared" si="21"/>
+        <v>1100</v>
       </c>
       <c r="L62" s="1">
         <v>1</v>
@@ -15558,18 +15736,18 @@
         <v>0</v>
       </c>
       <c r="N62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>33</v>
       </c>
       <c r="O62" s="1">
         <v>5</v>
       </c>
       <c r="P62" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15584,7 +15762,7 @@
         <v>51</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G63" s="1">
         <v>10</v>
@@ -15596,10 +15774,11 @@
         <v>31</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K63" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K63" s="9">
+        <f t="shared" si="21"/>
+        <v>1100</v>
       </c>
       <c r="L63" s="1">
         <v>1</v>
@@ -15608,18 +15787,18 @@
         <v>0</v>
       </c>
       <c r="N63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>33</v>
       </c>
       <c r="O63" s="1">
         <v>5</v>
       </c>
       <c r="P63" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15634,7 +15813,7 @@
         <v>51</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -15648,8 +15827,9 @@
       <c r="J64" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K64" s="1">
-        <v>100</v>
+      <c r="K64" s="9">
+        <f>(E64-1)/5*300+300</f>
+        <v>3300</v>
       </c>
       <c r="L64" s="1">
         <v>2</v>
@@ -15669,7 +15849,7 @@
         <v>22</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15684,7 +15864,7 @@
         <v>51</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G65" s="1">
         <v>2</v>
@@ -15698,8 +15878,9 @@
       <c r="J65" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K65" s="1">
-        <v>100</v>
+      <c r="K65" s="9">
+        <f>(E65-1)/5*300+300</f>
+        <v>3300</v>
       </c>
       <c r="L65" s="1">
         <v>2</v>
@@ -15719,7 +15900,7 @@
         <v>22</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15734,7 +15915,7 @@
         <v>51</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G66" s="1">
         <v>3</v>
@@ -15748,8 +15929,9 @@
       <c r="J66" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K66" s="1">
-        <v>100</v>
+      <c r="K66" s="9">
+        <f t="shared" ref="K66:K71" si="24">(E66-1)/5*100+100</f>
+        <v>1100</v>
       </c>
       <c r="L66" s="1">
         <v>2</v>
@@ -15758,18 +15940,18 @@
         <v>0</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" ref="N66:N71" si="17">(E66-1)/5*3+3</f>
+        <f t="shared" ref="N66:N71" si="25">(E66-1)/5*3+3</f>
         <v>33</v>
       </c>
       <c r="O66" s="1">
         <v>5</v>
       </c>
       <c r="P66" s="9">
-        <f t="shared" ref="P66:P71" si="18">((E66-1)/5+1)*1</f>
+        <f t="shared" ref="P66:P71" si="26">((E66-1)/5+1)*1</f>
         <v>11</v>
       </c>
       <c r="Q66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15784,7 +15966,7 @@
         <v>51</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G67" s="1">
         <v>4</v>
@@ -15796,10 +15978,11 @@
         <v>31</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K67" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K67" s="9">
+        <f t="shared" si="24"/>
+        <v>1100</v>
       </c>
       <c r="L67" s="1">
         <v>2</v>
@@ -15808,18 +15991,18 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>33</v>
       </c>
       <c r="O67" s="1">
         <v>5</v>
       </c>
       <c r="P67" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15834,7 +16017,7 @@
         <v>51</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G68" s="1">
         <v>5</v>
@@ -15846,10 +16029,11 @@
         <v>31</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K68" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K68" s="9">
+        <f t="shared" si="24"/>
+        <v>1100</v>
       </c>
       <c r="L68" s="1">
         <v>2</v>
@@ -15858,18 +16042,18 @@
         <v>0</v>
       </c>
       <c r="N68" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>33</v>
       </c>
       <c r="O68" s="1">
         <v>5</v>
       </c>
       <c r="P68" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15884,7 +16068,7 @@
         <v>51</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G69" s="1">
         <v>7</v>
@@ -15898,8 +16082,9 @@
       <c r="J69" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K69" s="1">
-        <v>100</v>
+      <c r="K69" s="9">
+        <f t="shared" si="24"/>
+        <v>1100</v>
       </c>
       <c r="L69" s="1">
         <v>2</v>
@@ -15908,18 +16093,18 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>33</v>
       </c>
       <c r="O69" s="1">
         <v>5</v>
       </c>
       <c r="P69" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15934,7 +16119,7 @@
         <v>51</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G70" s="1">
         <v>9</v>
@@ -15948,8 +16133,9 @@
       <c r="J70" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K70" s="1">
-        <v>100</v>
+      <c r="K70" s="9">
+        <f t="shared" si="24"/>
+        <v>1100</v>
       </c>
       <c r="L70" s="1">
         <v>2</v>
@@ -15958,18 +16144,18 @@
         <v>0</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>33</v>
       </c>
       <c r="O70" s="1">
         <v>5</v>
       </c>
       <c r="P70" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="Q70" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -15984,7 +16170,7 @@
         <v>51</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G71" s="1">
         <v>10</v>
@@ -15996,10 +16182,11 @@
         <v>31</v>
       </c>
       <c r="J71" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K71" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K71" s="9">
+        <f t="shared" si="24"/>
+        <v>1100</v>
       </c>
       <c r="L71" s="1">
         <v>2</v>
@@ -16008,18 +16195,18 @@
         <v>0</v>
       </c>
       <c r="N71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>33</v>
       </c>
       <c r="O71" s="1">
         <v>5</v>
       </c>
       <c r="P71" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="Q71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -16034,7 +16221,7 @@
         <v>51</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -16048,8 +16235,9 @@
       <c r="J72" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K72" s="1">
-        <v>100</v>
+      <c r="K72" s="9">
+        <f>(E72-1)/5*300+300</f>
+        <v>3300</v>
       </c>
       <c r="L72" s="1">
         <v>3</v>
@@ -16069,7 +16257,7 @@
         <v>22</v>
       </c>
       <c r="Q72" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -16084,7 +16272,7 @@
         <v>51</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G73" s="1">
         <v>2</v>
@@ -16098,8 +16286,9 @@
       <c r="J73" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K73" s="1">
-        <v>100</v>
+      <c r="K73" s="9">
+        <f>(E73-1)/5*300+300</f>
+        <v>3300</v>
       </c>
       <c r="L73" s="1">
         <v>3</v>
@@ -16119,7 +16308,7 @@
         <v>22</v>
       </c>
       <c r="Q73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -16134,7 +16323,7 @@
         <v>51</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G74" s="1">
         <v>3</v>
@@ -16148,8 +16337,9 @@
       <c r="J74" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K74" s="1">
-        <v>100</v>
+      <c r="K74" s="9">
+        <f t="shared" ref="K74:K79" si="27">(E74-1)/5*100+100</f>
+        <v>1100</v>
       </c>
       <c r="L74" s="1">
         <v>3</v>
@@ -16158,18 +16348,18 @@
         <v>0</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" ref="N74:N79" si="19">(E74-1)/5*3+3</f>
+        <f t="shared" ref="N74:N79" si="28">(E74-1)/5*3+3</f>
         <v>33</v>
       </c>
       <c r="O74" s="1">
         <v>5</v>
       </c>
       <c r="P74" s="9">
-        <f t="shared" ref="P74:P79" si="20">((E74-1)/5+1)*1</f>
+        <f t="shared" ref="P74:P79" si="29">((E74-1)/5+1)*1</f>
         <v>11</v>
       </c>
       <c r="Q74" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>40</v>
       </c>
     </row>
@@ -16184,7 +16374,7 @@
         <v>51</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G75" s="1">
         <v>4</v>
@@ -16196,10 +16386,11 @@
         <v>31</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K75" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K75" s="9">
+        <f t="shared" si="27"/>
+        <v>1100</v>
       </c>
       <c r="L75" s="1">
         <v>3</v>
@@ -16208,18 +16399,18 @@
         <v>0</v>
       </c>
       <c r="N75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>33</v>
       </c>
       <c r="O75" s="1">
         <v>5</v>
       </c>
       <c r="P75" s="9">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="Q75" s="1">
         <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="Q75" s="1">
-        <f t="shared" si="14"/>
         <v>40</v>
       </c>
     </row>
@@ -16234,7 +16425,7 @@
         <v>51</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G76" s="1">
         <v>5</v>
@@ -16246,10 +16437,11 @@
         <v>31</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K76" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K76" s="9">
+        <f t="shared" si="27"/>
+        <v>1100</v>
       </c>
       <c r="L76" s="1">
         <v>3</v>
@@ -16258,18 +16450,18 @@
         <v>0</v>
       </c>
       <c r="N76" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>33</v>
       </c>
       <c r="O76" s="1">
         <v>5</v>
       </c>
       <c r="P76" s="9">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="Q76" s="1">
         <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="Q76" s="1">
-        <f t="shared" si="14"/>
         <v>40</v>
       </c>
     </row>
@@ -16284,7 +16476,7 @@
         <v>51</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G77" s="1">
         <v>7</v>
@@ -16298,8 +16490,9 @@
       <c r="J77" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K77" s="1">
-        <v>100</v>
+      <c r="K77" s="9">
+        <f t="shared" si="27"/>
+        <v>1100</v>
       </c>
       <c r="L77" s="1">
         <v>3</v>
@@ -16308,18 +16501,18 @@
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>33</v>
       </c>
       <c r="O77" s="1">
         <v>5</v>
       </c>
       <c r="P77" s="9">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="Q77" s="1">
         <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="Q77" s="1">
-        <f t="shared" si="14"/>
         <v>40</v>
       </c>
     </row>
@@ -16334,7 +16527,7 @@
         <v>51</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G78" s="1">
         <v>9</v>
@@ -16348,8 +16541,9 @@
       <c r="J78" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="K78" s="1">
-        <v>100</v>
+      <c r="K78" s="9">
+        <f t="shared" si="27"/>
+        <v>1100</v>
       </c>
       <c r="L78" s="1">
         <v>3</v>
@@ -16358,18 +16552,18 @@
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>33</v>
       </c>
       <c r="O78" s="1">
         <v>5</v>
       </c>
       <c r="P78" s="9">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="Q78" s="1">
         <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="Q78" s="1">
-        <f t="shared" si="14"/>
         <v>40</v>
       </c>
     </row>
@@ -16384,7 +16578,7 @@
         <v>51</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G79" s="1">
         <v>10</v>
@@ -16396,10 +16590,11 @@
         <v>31</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="K79" s="1">
-        <v>100</v>
+        <v>306</v>
+      </c>
+      <c r="K79" s="9">
+        <f t="shared" si="27"/>
+        <v>1100</v>
       </c>
       <c r="L79" s="1">
         <v>3</v>
@@ -16408,18 +16603,18 @@
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>33</v>
       </c>
       <c r="O79" s="1">
         <v>5</v>
       </c>
       <c r="P79" s="9">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="Q79" s="1">
         <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="Q79" s="1">
-        <f t="shared" si="14"/>
         <v>40</v>
       </c>
     </row>
@@ -16449,7 +16644,7 @@
         <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G81" s="1">
         <v>1</v>
@@ -16461,10 +16656,11 @@
         <v>24</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K81" s="1">
-        <v>100</v>
+        <v>328</v>
+      </c>
+      <c r="K81" s="9">
+        <f>(E81-1)/5*300+300</f>
+        <v>3600</v>
       </c>
       <c r="L81" s="1">
         <v>1</v>
@@ -16484,7 +16680,7 @@
         <v>24</v>
       </c>
       <c r="Q81" s="1">
-        <f t="shared" ref="Q81:Q104" si="21">(E81-1)/5*3+10</f>
+        <f t="shared" ref="Q81:Q104" si="30">(E81-1)/5*3+10</f>
         <v>43</v>
       </c>
     </row>
@@ -16499,7 +16695,7 @@
         <v>56</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -16511,10 +16707,11 @@
         <v>27</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K82" s="1">
-        <v>100</v>
+        <v>328</v>
+      </c>
+      <c r="K82" s="9">
+        <f>(E82-1)/5*300+300</f>
+        <v>3600</v>
       </c>
       <c r="L82" s="1">
         <v>1</v>
@@ -16534,7 +16731,7 @@
         <v>24</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16549,7 +16746,7 @@
         <v>56</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G83" s="1">
         <v>3</v>
@@ -16561,10 +16758,11 @@
         <v>24</v>
       </c>
       <c r="J83" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K83" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K83" s="9">
+        <f t="shared" ref="K83:K88" si="31">(E83-1)/5*100+100</f>
+        <v>1200</v>
       </c>
       <c r="L83" s="1">
         <v>1</v>
@@ -16573,18 +16771,18 @@
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" ref="N83:N88" si="22">(E83-1)/5*3+3</f>
+        <f t="shared" ref="N83:N88" si="32">(E83-1)/5*3+3</f>
         <v>36</v>
       </c>
       <c r="O83" s="1">
         <v>5</v>
       </c>
       <c r="P83" s="9">
-        <f t="shared" ref="P83:P88" si="23">((E83-1)/5+1)*1</f>
+        <f t="shared" ref="P83:P88" si="33">((E83-1)/5+1)*1</f>
         <v>12</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16599,7 +16797,7 @@
         <v>56</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G84" s="1">
         <v>4</v>
@@ -16611,10 +16809,11 @@
         <v>31</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K84" s="1">
-        <v>100</v>
+        <v>333</v>
+      </c>
+      <c r="K84" s="9">
+        <f t="shared" si="31"/>
+        <v>1200</v>
       </c>
       <c r="L84" s="1">
         <v>1</v>
@@ -16623,18 +16822,18 @@
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>36</v>
       </c>
       <c r="O84" s="1">
         <v>5</v>
       </c>
       <c r="P84" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>12</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16649,7 +16848,7 @@
         <v>56</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G85" s="1">
         <v>5</v>
@@ -16663,8 +16862,9 @@
       <c r="J85" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="K85" s="1">
-        <v>100</v>
+      <c r="K85" s="9">
+        <f t="shared" si="31"/>
+        <v>1200</v>
       </c>
       <c r="L85" s="1">
         <v>1</v>
@@ -16673,18 +16873,18 @@
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>36</v>
       </c>
       <c r="O85" s="1">
         <v>5</v>
       </c>
       <c r="P85" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>12</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16699,7 +16899,7 @@
         <v>56</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G86" s="1">
         <v>7</v>
@@ -16711,10 +16911,11 @@
         <v>24</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K86" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K86" s="9">
+        <f t="shared" si="31"/>
+        <v>1200</v>
       </c>
       <c r="L86" s="1">
         <v>1</v>
@@ -16723,18 +16924,18 @@
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>36</v>
       </c>
       <c r="O86" s="1">
         <v>5</v>
       </c>
       <c r="P86" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>12</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16749,7 +16950,7 @@
         <v>56</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G87" s="1">
         <v>9</v>
@@ -16761,10 +16962,11 @@
         <v>27</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K87" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K87" s="9">
+        <f t="shared" si="31"/>
+        <v>1200</v>
       </c>
       <c r="L87" s="1">
         <v>1</v>
@@ -16773,18 +16975,18 @@
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>36</v>
       </c>
       <c r="O87" s="1">
         <v>5</v>
       </c>
       <c r="P87" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>12</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16799,7 +17001,7 @@
         <v>56</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G88" s="1">
         <v>10</v>
@@ -16811,10 +17013,11 @@
         <v>31</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K88" s="1">
-        <v>100</v>
+        <v>333</v>
+      </c>
+      <c r="K88" s="9">
+        <f t="shared" si="31"/>
+        <v>1200</v>
       </c>
       <c r="L88" s="1">
         <v>1</v>
@@ -16823,18 +17026,18 @@
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>36</v>
       </c>
       <c r="O88" s="1">
         <v>5</v>
       </c>
       <c r="P88" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>12</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16849,7 +17052,7 @@
         <v>56</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -16861,10 +17064,11 @@
         <v>40</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K89" s="1">
-        <v>100</v>
+        <v>328</v>
+      </c>
+      <c r="K89" s="9">
+        <f>(E89-1)/5*300+300</f>
+        <v>3600</v>
       </c>
       <c r="L89" s="1">
         <v>2</v>
@@ -16884,7 +17088,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16899,7 +17103,7 @@
         <v>56</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G90" s="1">
         <v>2</v>
@@ -16911,10 +17115,11 @@
         <v>27</v>
       </c>
       <c r="J90" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K90" s="1">
-        <v>100</v>
+        <v>328</v>
+      </c>
+      <c r="K90" s="9">
+        <f>(E90-1)/5*300+300</f>
+        <v>3600</v>
       </c>
       <c r="L90" s="1">
         <v>2</v>
@@ -16934,7 +17139,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16949,7 +17154,7 @@
         <v>56</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G91" s="1">
         <v>3</v>
@@ -16961,10 +17166,11 @@
         <v>40</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K91" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K91" s="9">
+        <f t="shared" ref="K91:K96" si="34">(E91-1)/5*100+100</f>
+        <v>1200</v>
       </c>
       <c r="L91" s="1">
         <v>2</v>
@@ -16973,18 +17179,18 @@
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" ref="N91:N96" si="24">(E91-1)/5*3+3</f>
+        <f t="shared" ref="N91:N96" si="35">(E91-1)/5*3+3</f>
         <v>36</v>
       </c>
       <c r="O91" s="1">
         <v>5</v>
       </c>
       <c r="P91" s="9">
-        <f t="shared" ref="P91:P96" si="25">((E91-1)/5+1)*1</f>
+        <f t="shared" ref="P91:P96" si="36">((E91-1)/5+1)*1</f>
         <v>12</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -16999,7 +17205,7 @@
         <v>56</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -17011,10 +17217,11 @@
         <v>31</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K92" s="1">
-        <v>100</v>
+        <v>333</v>
+      </c>
+      <c r="K92" s="9">
+        <f t="shared" si="34"/>
+        <v>1200</v>
       </c>
       <c r="L92" s="1">
         <v>2</v>
@@ -17023,18 +17230,18 @@
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>36</v>
       </c>
       <c r="O92" s="1">
         <v>5</v>
       </c>
       <c r="P92" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17049,7 +17256,7 @@
         <v>56</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G93" s="1">
         <v>5</v>
@@ -17063,8 +17270,9 @@
       <c r="J93" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="K93" s="1">
-        <v>100</v>
+      <c r="K93" s="9">
+        <f t="shared" si="34"/>
+        <v>1200</v>
       </c>
       <c r="L93" s="1">
         <v>2</v>
@@ -17073,18 +17281,18 @@
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>36</v>
       </c>
       <c r="O93" s="1">
         <v>5</v>
       </c>
       <c r="P93" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17099,7 +17307,7 @@
         <v>56</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G94" s="1">
         <v>7</v>
@@ -17111,10 +17319,11 @@
         <v>40</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K94" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K94" s="9">
+        <f t="shared" si="34"/>
+        <v>1200</v>
       </c>
       <c r="L94" s="1">
         <v>2</v>
@@ -17123,18 +17332,18 @@
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>36</v>
       </c>
       <c r="O94" s="1">
         <v>5</v>
       </c>
       <c r="P94" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17149,7 +17358,7 @@
         <v>56</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G95" s="1">
         <v>9</v>
@@ -17161,10 +17370,11 @@
         <v>27</v>
       </c>
       <c r="J95" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K95" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K95" s="9">
+        <f t="shared" si="34"/>
+        <v>1200</v>
       </c>
       <c r="L95" s="1">
         <v>2</v>
@@ -17173,18 +17383,18 @@
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>36</v>
       </c>
       <c r="O95" s="1">
         <v>5</v>
       </c>
       <c r="P95" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="Q95" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17199,7 +17409,7 @@
         <v>56</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G96" s="1">
         <v>10</v>
@@ -17211,10 +17421,11 @@
         <v>31</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K96" s="1">
-        <v>100</v>
+        <v>333</v>
+      </c>
+      <c r="K96" s="9">
+        <f t="shared" si="34"/>
+        <v>1200</v>
       </c>
       <c r="L96" s="1">
         <v>2</v>
@@ -17223,18 +17434,18 @@
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="35"/>
         <v>36</v>
       </c>
       <c r="O96" s="1">
         <v>5</v>
       </c>
       <c r="P96" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17249,7 +17460,7 @@
         <v>56</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G97" s="1">
         <v>1</v>
@@ -17261,10 +17472,11 @@
         <v>49</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K97" s="1">
-        <v>100</v>
+        <v>328</v>
+      </c>
+      <c r="K97" s="9">
+        <f>(E97-1)/5*300+300</f>
+        <v>3600</v>
       </c>
       <c r="L97" s="1">
         <v>3</v>
@@ -17284,7 +17496,7 @@
         <v>24</v>
       </c>
       <c r="Q97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17299,7 +17511,7 @@
         <v>56</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G98" s="1">
         <v>2</v>
@@ -17311,10 +17523,11 @@
         <v>27</v>
       </c>
       <c r="J98" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K98" s="1">
-        <v>100</v>
+        <v>328</v>
+      </c>
+      <c r="K98" s="9">
+        <f>(E98-1)/5*300+300</f>
+        <v>3600</v>
       </c>
       <c r="L98" s="1">
         <v>3</v>
@@ -17334,7 +17547,7 @@
         <v>24</v>
       </c>
       <c r="Q98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17349,7 +17562,7 @@
         <v>56</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G99" s="1">
         <v>3</v>
@@ -17361,10 +17574,11 @@
         <v>49</v>
       </c>
       <c r="J99" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K99" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K99" s="9">
+        <f t="shared" ref="K99:K104" si="37">(E99-1)/5*100+100</f>
+        <v>1200</v>
       </c>
       <c r="L99" s="1">
         <v>3</v>
@@ -17373,18 +17587,18 @@
         <v>0</v>
       </c>
       <c r="N99" s="1">
-        <f t="shared" ref="N99:N104" si="26">(E99-1)/5*3+3</f>
+        <f t="shared" ref="N99:N104" si="38">(E99-1)/5*3+3</f>
         <v>36</v>
       </c>
       <c r="O99" s="1">
         <v>5</v>
       </c>
       <c r="P99" s="9">
-        <f t="shared" ref="P99:P104" si="27">((E99-1)/5+1)*1</f>
+        <f t="shared" ref="P99:P104" si="39">((E99-1)/5+1)*1</f>
         <v>12</v>
       </c>
       <c r="Q99" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17399,7 +17613,7 @@
         <v>56</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G100" s="1">
         <v>4</v>
@@ -17411,10 +17625,11 @@
         <v>31</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K100" s="1">
-        <v>100</v>
+        <v>333</v>
+      </c>
+      <c r="K100" s="9">
+        <f t="shared" si="37"/>
+        <v>1200</v>
       </c>
       <c r="L100" s="1">
         <v>3</v>
@@ -17423,18 +17638,18 @@
         <v>0</v>
       </c>
       <c r="N100" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>36</v>
       </c>
       <c r="O100" s="1">
         <v>5</v>
       </c>
       <c r="P100" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>12</v>
       </c>
       <c r="Q100" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17449,7 +17664,7 @@
         <v>56</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
@@ -17463,8 +17678,9 @@
       <c r="J101" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="K101" s="1">
-        <v>100</v>
+      <c r="K101" s="9">
+        <f t="shared" si="37"/>
+        <v>1200</v>
       </c>
       <c r="L101" s="1">
         <v>3</v>
@@ -17473,18 +17689,18 @@
         <v>0</v>
       </c>
       <c r="N101" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>36</v>
       </c>
       <c r="O101" s="1">
         <v>5</v>
       </c>
       <c r="P101" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>12</v>
       </c>
       <c r="Q101" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17499,7 +17715,7 @@
         <v>56</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G102" s="1">
         <v>7</v>
@@ -17511,10 +17727,11 @@
         <v>49</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K102" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K102" s="9">
+        <f t="shared" si="37"/>
+        <v>1200</v>
       </c>
       <c r="L102" s="1">
         <v>3</v>
@@ -17523,18 +17740,18 @@
         <v>0</v>
       </c>
       <c r="N102" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>36</v>
       </c>
       <c r="O102" s="1">
         <v>5</v>
       </c>
       <c r="P102" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>12</v>
       </c>
       <c r="Q102" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17549,7 +17766,7 @@
         <v>56</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G103" s="1">
         <v>9</v>
@@ -17561,10 +17778,11 @@
         <v>27</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="K103" s="1">
-        <v>100</v>
+        <v>331</v>
+      </c>
+      <c r="K103" s="9">
+        <f t="shared" si="37"/>
+        <v>1200</v>
       </c>
       <c r="L103" s="1">
         <v>3</v>
@@ -17573,18 +17791,18 @@
         <v>0</v>
       </c>
       <c r="N103" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>36</v>
       </c>
       <c r="O103" s="1">
         <v>5</v>
       </c>
       <c r="P103" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>12</v>
       </c>
       <c r="Q103" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17599,7 +17817,7 @@
         <v>56</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G104" s="1">
         <v>10</v>
@@ -17611,10 +17829,11 @@
         <v>31</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K104" s="1">
-        <v>100</v>
+        <v>333</v>
+      </c>
+      <c r="K104" s="9">
+        <f t="shared" si="37"/>
+        <v>1200</v>
       </c>
       <c r="L104" s="1">
         <v>3</v>
@@ -17623,18 +17842,18 @@
         <v>0</v>
       </c>
       <c r="N104" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>36</v>
       </c>
       <c r="O104" s="1">
         <v>5</v>
       </c>
       <c r="P104" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>12</v>
       </c>
       <c r="Q104" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="30"/>
         <v>43</v>
       </c>
     </row>
@@ -17936,7 +18155,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -17945,10 +18164,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -17983,7 +18202,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -17992,10 +18211,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -18067,7 +18286,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18085,7 +18304,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18116,16 +18335,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -18162,10 +18381,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -18235,7 +18454,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -18247,7 +18466,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -18259,7 +18478,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -18281,7 +18500,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -18290,10 +18509,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -18305,7 +18524,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -18327,7 +18546,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -18339,7 +18558,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -18371,7 +18590,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -18383,7 +18602,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -18395,7 +18614,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -18417,7 +18636,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -18426,10 +18645,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -18441,7 +18660,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -18463,7 +18682,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -18475,7 +18694,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -18507,7 +18726,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18516,10 +18735,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18531,7 +18750,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18553,7 +18772,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18565,7 +18784,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18597,7 +18816,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18609,7 +18828,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18641,7 +18860,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G15" s="1">
         <v>4</v>
@@ -18650,10 +18869,10 @@
         <v>4</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K15" s="2">
         <v>10</v>
@@ -18665,7 +18884,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -18687,7 +18906,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -18699,7 +18918,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K16" s="2">
         <v>11</v>
@@ -18731,7 +18950,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G17" s="1">
         <v>7</v>
@@ -18743,7 +18962,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K17" s="2">
         <v>12</v>
@@ -18775,7 +18994,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18784,10 +19003,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K18" s="2">
         <v>13</v>
@@ -18799,7 +19018,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -18821,7 +19040,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G19" s="1">
         <v>5</v>
@@ -18833,7 +19052,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K19" s="2">
         <v>14</v>
@@ -18865,7 +19084,7 @@
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -18877,7 +19096,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K20" s="2">
         <v>15</v>
@@ -18909,7 +19128,7 @@
         <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G21" s="1">
         <v>7</v>
@@ -18918,10 +19137,10 @@
         <v>36</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K21" s="2">
         <v>16</v>
@@ -18933,7 +19152,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -18955,7 +19174,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -18967,7 +19186,7 @@
         <v>31</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K22" s="2">
         <v>17</v>
@@ -18999,7 +19218,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G23" s="1">
         <v>10</v>
@@ -19011,7 +19230,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K23" s="2">
         <v>18</v>
@@ -19042,7 +19261,7 @@
         <v>70</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -19051,10 +19270,10 @@
         <v>1</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K24" s="2">
         <v>19</v>
@@ -19066,7 +19285,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -19087,7 +19306,7 @@
         <v>70</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G25" s="1">
         <v>5</v>
@@ -19099,7 +19318,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K25" s="2">
         <v>20</v>
@@ -19130,7 +19349,7 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G26" s="1">
         <v>7</v>
@@ -19142,7 +19361,7 @@
         <v>27</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K26" s="2">
         <v>21</v>
@@ -19174,7 +19393,7 @@
         <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -19183,10 +19402,10 @@
         <v>1</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K27" s="2">
         <v>22</v>
@@ -19198,7 +19417,7 @@
         <v>1</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -19220,7 +19439,7 @@
         <v>80</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G28" s="1">
         <v>3</v>
@@ -19232,7 +19451,7 @@
         <v>31</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K28" s="2">
         <v>23</v>
@@ -19264,7 +19483,7 @@
         <v>80</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G29" s="1">
         <v>7</v>
@@ -19276,7 +19495,7 @@
         <v>27</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K29" s="2">
         <v>24</v>
@@ -19308,7 +19527,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -19320,7 +19539,7 @@
         <v>31</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K30" s="2">
         <v>25</v>
@@ -19332,7 +19551,7 @@
         <v>1</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -19354,7 +19573,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G31" s="1">
         <v>5</v>
@@ -19363,10 +19582,10 @@
         <v>34</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K31" s="2">
         <v>26</v>
@@ -19398,7 +19617,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G32" s="2">
         <v>2</v>
@@ -19410,7 +19629,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K32" s="2">
         <v>27</v>
@@ -19442,7 +19661,7 @@
         <v>100</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -19454,7 +19673,7 @@
         <v>31</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K33" s="2">
         <v>28</v>
@@ -19466,7 +19685,7 @@
         <v>1</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -19488,7 +19707,7 @@
         <v>100</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G34" s="1">
         <v>3</v>
@@ -19497,10 +19716,10 @@
         <v>3</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K34" s="2">
         <v>29</v>
@@ -19532,7 +19751,7 @@
         <v>100</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19544,7 +19763,7 @@
         <v>27</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K35" s="2">
         <v>30</v>
@@ -19574,7 +19793,7 @@
         <v>110</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -19586,7 +19805,7 @@
         <v>31</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K36" s="2">
         <v>31</v>
@@ -19616,7 +19835,7 @@
         <v>110</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G37" s="1">
         <v>4</v>
@@ -19625,10 +19844,10 @@
         <v>4</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K37" s="2">
         <v>32</v>
@@ -19660,7 +19879,7 @@
         <v>110</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G38" s="1">
         <v>5</v>
@@ -19672,7 +19891,7 @@
         <v>27</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K38" s="2">
         <v>33</v>
@@ -19704,7 +19923,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G39" s="2">
         <v>2</v>
@@ -19716,7 +19935,7 @@
         <v>31</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K39" s="2">
         <v>34</v>
@@ -19748,7 +19967,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G40" s="1">
         <v>7</v>
@@ -19757,10 +19976,10 @@
         <v>36</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K40" s="2">
         <v>35</v>
@@ -19792,7 +20011,7 @@
         <v>120</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G41" s="1">
         <v>10</v>
@@ -19804,7 +20023,7 @@
         <v>27</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K41" s="2">
         <v>36</v>
@@ -19825,10 +20044,10 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2">
         <v>211037</v>
@@ -19840,7 +20059,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -19856,7 +20075,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -19867,10 +20086,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2">
         <v>211038</v>
@@ -19882,7 +20101,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -19907,10 +20126,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2">
         <v>211039</v>
@@ -19922,7 +20141,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -19947,10 +20166,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2">
         <v>211040</v>
@@ -19962,7 +20181,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G45" s="1">
         <v>3</v>
@@ -19978,7 +20197,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -19989,10 +20208,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2">
         <v>211041</v>
@@ -20004,7 +20223,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G46" s="1">
         <v>5</v>
@@ -20029,10 +20248,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2">
         <v>211042</v>
@@ -20044,7 +20263,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G47" s="1">
         <v>7</v>
